--- a/tableur/prix-salon-prive-2026.xlsx
+++ b/tableur/prix-salon-prive-2026.xlsx
@@ -647,7 +647,11 @@
           <t>AOC Cru Bourgeois Haut-Médoc — Château Balac</t>
         </is>
       </c>
-      <c r="C8" s="12" t="n"/>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>Rouge</t>
+        </is>
+      </c>
       <c r="D8" s="12" t="n"/>
       <c r="E8" s="12" t="n"/>
       <c r="F8" s="13" t="n"/>
@@ -808,7 +812,11 @@
           <t>AOP Champagne — Trois Crus Brut</t>
         </is>
       </c>
-      <c r="C15" s="12" t="n"/>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>Blanc effervescent</t>
+        </is>
+      </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
           <t>—</t>
@@ -835,7 +843,11 @@
           <t>AOP Champagne — Terroir Blanc</t>
         </is>
       </c>
-      <c r="C16" s="12" t="n"/>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>Blanc effervescent</t>
+        </is>
+      </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
           <t>—</t>
@@ -862,7 +874,11 @@
           <t>AOP Champagne — Terroir Meunier</t>
         </is>
       </c>
-      <c r="C17" s="12" t="n"/>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>Blanc effervescent</t>
+        </is>
+      </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
           <t>—</t>
@@ -889,7 +905,11 @@
           <t>AOC Champagne — Brut Nature</t>
         </is>
       </c>
-      <c r="C18" s="12" t="n"/>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>Blanc effervescent</t>
+        </is>
+      </c>
       <c r="D18" s="12" t="n"/>
       <c r="E18" s="12" t="n"/>
       <c r="F18" s="13" t="n"/>
@@ -908,7 +928,11 @@
           <t>AOC Champagne — Millésime Expression</t>
         </is>
       </c>
-      <c r="C19" s="12" t="n"/>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>Blanc effervescent</t>
+        </is>
+      </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
           <t>2018</t>
@@ -1199,7 +1223,11 @@
           <t>AOC Muscadet Sèvre et Maine — L'envol</t>
         </is>
       </c>
-      <c r="C32" s="12" t="n"/>
+      <c r="C32" s="12" t="inlineStr">
+        <is>
+          <t>Blanc</t>
+        </is>
+      </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
           <t>2023</t>
@@ -1519,7 +1547,11 @@
           <t>AOC Bourgogne Passe-Tout-Grain</t>
         </is>
       </c>
-      <c r="C44" s="12" t="n"/>
+      <c r="C44" s="12" t="inlineStr">
+        <is>
+          <t>Rouge</t>
+        </is>
+      </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
           <t>2025</t>
@@ -1542,7 +1574,11 @@
           <t>Les Bulles du Puits</t>
         </is>
       </c>
-      <c r="C45" s="12" t="n"/>
+      <c r="C45" s="12" t="inlineStr">
+        <is>
+          <t>Rosé effervescent</t>
+        </is>
+      </c>
       <c r="D45" s="12" t="n"/>
       <c r="E45" s="12" t="n"/>
       <c r="F45" s="13" t="n"/>
@@ -2164,7 +2200,11 @@
           <t>IGP Méditerranée — Premières Fleurs</t>
         </is>
       </c>
-      <c r="C69" s="12" t="n"/>
+      <c r="C69" s="12" t="inlineStr">
+        <is>
+          <t>Blanc</t>
+        </is>
+      </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
           <t>2025</t>
@@ -2187,7 +2227,11 @@
           <t>AOC Muscat BDV — Or des Dentelles</t>
         </is>
       </c>
-      <c r="C70" s="12" t="n"/>
+      <c r="C70" s="12" t="inlineStr">
+        <is>
+          <t>Blanc moelleux</t>
+        </is>
+      </c>
       <c r="D70" s="12" t="inlineStr">
         <is>
           <t>2023</t>
@@ -2210,7 +2254,11 @@
           <t>AOC Muscat BDV — Or des Dentelles</t>
         </is>
       </c>
-      <c r="C71" s="12" t="n"/>
+      <c r="C71" s="12" t="inlineStr">
+        <is>
+          <t>Blanc moelleux</t>
+        </is>
+      </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
           <t>2022</t>
@@ -2992,7 +3040,11 @@
           <t>La Grange Jaumain – Grolleau Noir</t>
         </is>
       </c>
-      <c r="C101" s="12" t="n"/>
+      <c r="C101" s="12" t="inlineStr">
+        <is>
+          <t>Rouge</t>
+        </is>
+      </c>
       <c r="D101" s="12" t="inlineStr">
         <is>
           <t>2024</t>
@@ -3325,7 +3377,11 @@
           <t>AOC Bugey — Mas de Lusanne Mondeuse</t>
         </is>
       </c>
-      <c r="C116" s="12" t="n"/>
+      <c r="C116" s="12" t="inlineStr">
+        <is>
+          <t>Rouge</t>
+        </is>
+      </c>
       <c r="D116" s="12" t="inlineStr">
         <is>
           <t>2023</t>
@@ -3348,7 +3404,11 @@
           <t>AOC Bugey — Mas de Lusanne Pinot Noir</t>
         </is>
       </c>
-      <c r="C117" s="12" t="n"/>
+      <c r="C117" s="12" t="inlineStr">
+        <is>
+          <t>Rouge</t>
+        </is>
+      </c>
       <c r="D117" s="12" t="inlineStr">
         <is>
           <t>2023</t>
@@ -3425,7 +3485,11 @@
           <t>AOC Bugey — Mas de Lusanne Gamay</t>
         </is>
       </c>
-      <c r="C120" s="12" t="n"/>
+      <c r="C120" s="12" t="inlineStr">
+        <is>
+          <t>Rouge</t>
+        </is>
+      </c>
       <c r="D120" s="12" t="n"/>
       <c r="E120" s="12" t="n"/>
       <c r="F120" s="13" t="n"/>
@@ -3444,7 +3508,11 @@
           <t>AOC Bugey — Mas de Lusanne Chardonnay</t>
         </is>
       </c>
-      <c r="C121" s="12" t="n"/>
+      <c r="C121" s="12" t="inlineStr">
+        <is>
+          <t>Blanc</t>
+        </is>
+      </c>
       <c r="D121" s="12" t="inlineStr">
         <is>
           <t>2020</t>
@@ -3663,7 +3731,11 @@
           <t>AOC Saint-Chinian — Juliette</t>
         </is>
       </c>
-      <c r="C130" s="12" t="n"/>
+      <c r="C130" s="12" t="inlineStr">
+        <is>
+          <t>Blanc</t>
+        </is>
+      </c>
       <c r="D130" s="12" t="inlineStr">
         <is>
           <t>2025</t>
@@ -4504,7 +4576,11 @@
           <t>AOC Pouilly-Fumé — Vignes de Tréleau</t>
         </is>
       </c>
-      <c r="C165" s="12" t="n"/>
+      <c r="C165" s="12" t="inlineStr">
+        <is>
+          <t>Blanc</t>
+        </is>
+      </c>
       <c r="D165" s="12" t="inlineStr">
         <is>
           <t>2023</t>
@@ -6126,7 +6202,11 @@
           <t>AOC Fronsac — Château Lafargue</t>
         </is>
       </c>
-      <c r="C231" s="12" t="n"/>
+      <c r="C231" s="12" t="inlineStr">
+        <is>
+          <t>Rouge</t>
+        </is>
+      </c>
       <c r="D231" s="12" t="inlineStr">
         <is>
           <t>2020</t>
@@ -6353,7 +6433,11 @@
           <t>IGP Val de Loire — L'Eberluant – Chardonnay</t>
         </is>
       </c>
-      <c r="C240" s="12" t="n"/>
+      <c r="C240" s="12" t="inlineStr">
+        <is>
+          <t>Blanc pétillant</t>
+        </is>
+      </c>
       <c r="D240" s="12" t="inlineStr">
         <is>
           <t>2025</t>

--- a/tableur/prix-salon-prive-2026.xlsx
+++ b/tableur/prix-salon-prive-2026.xlsx
@@ -511,7 +511,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I255"/>
+  <dimension ref="A1:I265"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -644,7 +644,7 @@
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>AOC Cru Bourgeois Haut-Médoc — Château Balac</t>
+          <t>AOC Haut-Médoc Cru Bourgeois Supérieur — Château Balac Rouge</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -652,7 +652,11 @@
           <t>Rouge</t>
         </is>
       </c>
-      <c r="D8" s="12" t="n"/>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="E8" s="12" t="n"/>
       <c r="F8" s="13" t="n"/>
       <c r="G8" s="13" t="n"/>
@@ -667,7 +671,7 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>Vin de France — Balac Sans Sulfites (100 % Merlot)</t>
+          <t>VDF — Balac sans sulfites</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
@@ -698,7 +702,7 @@
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>Vin de France — Inopine (100 % Merlot)</t>
+          <t>VDF — L’inopine de Balac</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
@@ -729,7 +733,7 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>Vin de France — Syrah de Balac</t>
+          <t>VDF — Syrah de Balac</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
@@ -809,7 +813,7 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>AOP Champagne — Trois Crus Brut</t>
+          <t>AOC Champagne — Trois Crus Brut</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
@@ -840,7 +844,7 @@
       </c>
       <c r="B16" s="12" t="inlineStr">
         <is>
-          <t>AOP Champagne — Terroir Blanc</t>
+          <t>AOC Champagne — Le Terroir Blanc Blanc de Blancs Brut</t>
         </is>
       </c>
       <c r="C16" s="12" t="inlineStr">
@@ -871,7 +875,7 @@
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>AOP Champagne — Terroir Meunier</t>
+          <t>AOC Champagne — Le Terroir Meunier Blanc de Meuniers Extra-Brut</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
@@ -910,7 +914,11 @@
           <t>Blanc effervescent</t>
         </is>
       </c>
-      <c r="D18" s="12" t="n"/>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="E18" s="12" t="n"/>
       <c r="F18" s="13" t="n"/>
       <c r="G18" s="13" t="n"/>
@@ -993,7 +1001,7 @@
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>AOP Corbières — Terre Rouge</t>
+          <t>AOC Corbières — Terre Rouge</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
@@ -1024,7 +1032,7 @@
       </c>
       <c r="B24" s="12" t="inlineStr">
         <is>
-          <t>AOP Corbières — 4 Saisons</t>
+          <t>AOC Corbières — 4 saisons</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
@@ -1055,7 +1063,7 @@
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>AOP Corbières — La Potion</t>
+          <t>AOC Corbières — La Potion</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
@@ -1086,7 +1094,7 @@
       </c>
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>AOP Corbières — Clos de Cassis – élevé en fûts de chêne</t>
+          <t>AOC Corbières — Clos de Cassis</t>
         </is>
       </c>
       <c r="C26" s="12" t="inlineStr">
@@ -1117,7 +1125,7 @@
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>IGP Pays d'Oc — Blanc Albas</t>
+          <t>IGP Pays d’Oc — Albas</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
@@ -1189,7 +1197,7 @@
       </c>
       <c r="B31" s="12" t="inlineStr">
         <is>
-          <t>AOP Muscadet Sèvre et Maine sur lie — Cuvée des deux Colombes</t>
+          <t>AOC Muscadet Sèvre et Maine sur lie — Cuvée des deux Colombes</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
@@ -1220,7 +1228,7 @@
       </c>
       <c r="B32" s="12" t="inlineStr">
         <is>
-          <t>AOC Muscadet Sèvre et Maine — L'envol</t>
+          <t>AOC Muscadet Sèvre et Maine sur lie — L’envol</t>
         </is>
       </c>
       <c r="C32" s="12" t="inlineStr">
@@ -1247,7 +1255,7 @@
       </c>
       <c r="B33" s="12" t="inlineStr">
         <is>
-          <t>AOP Muscadet Sèvre et Maine — CRU Mouzillon – Tillières</t>
+          <t>AOC Muscadet Sèvre et Maine — Cru Mouzillon-Tillières</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
@@ -1278,7 +1286,7 @@
       </c>
       <c r="B34" s="12" t="inlineStr">
         <is>
-          <t>IGP Chardonnay — Le Prestige de Beaulieu</t>
+          <t>IGP Chardonnay — Le prestige de Beaulieu</t>
         </is>
       </c>
       <c r="C34" s="12" t="inlineStr">
@@ -1340,7 +1348,7 @@
       </c>
       <c r="B36" s="12" t="inlineStr">
         <is>
-          <t>IGP — Rouge au lèvres</t>
+          <t>IGP Val de Loire — Rouge au lèvres</t>
         </is>
       </c>
       <c r="C36" s="12" t="inlineStr">
@@ -1350,7 +1358,7 @@
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E36" s="12" t="inlineStr">
@@ -1451,7 +1459,7 @@
       </c>
       <c r="B41" s="12" t="inlineStr">
         <is>
-          <t>AOP Mâcon — Mâcon Chardonnay</t>
+          <t>AOC Mâcon Chardonnay</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
@@ -1482,7 +1490,7 @@
       </c>
       <c r="B42" s="12" t="inlineStr">
         <is>
-          <t>AOP Mâcon Mancey — Mâcon Mancey</t>
+          <t>AOC Mâcon Mancey Blanc</t>
         </is>
       </c>
       <c r="C42" s="12" t="inlineStr">
@@ -1513,7 +1521,7 @@
       </c>
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t>AOP Mâcon Mancey — Mâcon Mancey</t>
+          <t>AOC Mâcon Rouge</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
@@ -1544,7 +1552,7 @@
       </c>
       <c r="B44" s="12" t="inlineStr">
         <is>
-          <t>AOC Bourgogne Passe-Tout-Grain</t>
+          <t>AOC Bourgogne Passe-Tout-Grain Rouge</t>
         </is>
       </c>
       <c r="C44" s="12" t="inlineStr">
@@ -1571,7 +1579,7 @@
       </c>
       <c r="B45" s="12" t="inlineStr">
         <is>
-          <t>Les Bulles du Puits</t>
+          <t>Les Bulles du Puits Rosé</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
@@ -1579,7 +1587,11 @@
           <t>Rosé effervescent</t>
         </is>
       </c>
-      <c r="D45" s="12" t="n"/>
+      <c r="D45" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="E45" s="12" t="n"/>
       <c r="F45" s="13" t="n"/>
       <c r="G45" s="13" t="n"/>
@@ -1643,7 +1655,7 @@
       </c>
       <c r="B49" s="12" t="inlineStr">
         <is>
-          <t>IGP Côtes-de-Gascogne — N°1 Littorine</t>
+          <t>IGP Côtes de Gascogne — N°1 Littorine Blanc</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
@@ -1674,7 +1686,7 @@
       </c>
       <c r="B50" s="12" t="inlineStr">
         <is>
-          <t>IGP Côtes-de-Gascogne — N°6 Fossiles</t>
+          <t>IGP Côtes de Gascogne — N°6 Fossiles Blanc</t>
         </is>
       </c>
       <c r="C50" s="12" t="inlineStr">
@@ -1705,7 +1717,7 @@
       </c>
       <c r="B51" s="12" t="inlineStr">
         <is>
-          <t>IGP Côtes-de-Gascogne — N°3 Gulf Stream</t>
+          <t>IGP Côtes de Gascogne — N°3 Gulf Stream Rosé</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
@@ -1736,7 +1748,7 @@
       </c>
       <c r="B52" s="12" t="inlineStr">
         <is>
-          <t>IGP Côtes-de-Gascogne — N°4 Triton</t>
+          <t>IGP Côtes de Gascogne — N°4 Triton Rouge</t>
         </is>
       </c>
       <c r="C52" s="12" t="inlineStr">
@@ -1767,12 +1779,12 @@
       </c>
       <c r="B53" s="12" t="inlineStr">
         <is>
-          <t>IGP Côtes-de-Gascogne — N°8 Grand Pavois</t>
+          <t>IGP Côtes de Gascogne — N°8 Grand Pavois Rouge</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>Doux</t>
+          <t>Rouge</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr">
@@ -1798,12 +1810,12 @@
       </c>
       <c r="B54" s="12" t="inlineStr">
         <is>
-          <t>IGP Côtes-de-Gascogne — N°7 Venus</t>
+          <t>IGP Côtes de Gascogne — N°7 Vénus Blanc Moelleux</t>
         </is>
       </c>
       <c r="C54" s="12" t="inlineStr">
         <is>
-          <t>Doux</t>
+          <t>Blanc moelleux</t>
         </is>
       </c>
       <c r="D54" s="12" t="inlineStr">
@@ -1829,7 +1841,7 @@
       </c>
       <c r="B55" s="12" t="inlineStr">
         <is>
-          <t>IGP Côtes de Gascogne — N°10</t>
+          <t>IGP Côtes de Gascogne — N°10 Pétillant</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
@@ -1837,7 +1849,11 @@
           <t>Pétillant</t>
         </is>
       </c>
-      <c r="D55" s="12" t="n"/>
+      <c r="D55" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="E55" s="12" t="n"/>
       <c r="F55" s="13" t="n"/>
       <c r="G55" s="13" t="n"/>
@@ -1901,7 +1917,7 @@
       </c>
       <c r="B59" s="12" t="inlineStr">
         <is>
-          <t>Vin de France — Chardonnay-Viognier</t>
+          <t>VDF — Chardonnay-Viognier Blanc</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
@@ -1928,7 +1944,7 @@
       </c>
       <c r="B60" s="12" t="inlineStr">
         <is>
-          <t>Vin de France-Syrah — La Pousterle</t>
+          <t>VDF — Syrah Rouge</t>
         </is>
       </c>
       <c r="C60" s="12" t="inlineStr">
@@ -1959,7 +1975,7 @@
       </c>
       <c r="B61" s="12" t="inlineStr">
         <is>
-          <t>Luberon — Terroir d'Ansouis</t>
+          <t>AOC Luberon — Terroir d’Ansouis Blanc</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
@@ -2016,7 +2032,7 @@
       </c>
       <c r="B63" s="12" t="inlineStr">
         <is>
-          <t>AOP Côtes du Rhône — Le Prieuré</t>
+          <t>AOC Côtes du Rhône — Le Prieuré Rouge</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
@@ -2047,7 +2063,7 @@
       </c>
       <c r="B64" s="12" t="inlineStr">
         <is>
-          <t>AOP Châteauneuf-du-Pape — Vieilles Vignes</t>
+          <t>AOC Châteauneuf-du-Pape — Vieilles Vignes Rouge</t>
         </is>
       </c>
       <c r="C64" s="12" t="inlineStr">
@@ -2078,7 +2094,7 @@
       </c>
       <c r="B65" s="12" t="inlineStr">
         <is>
-          <t>AOP Châteauneuf-du-Pape — Vieilles Vignes</t>
+          <t>AOC Châteauneuf-du-Pape — Vieilles Vignes Rouge</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
@@ -2109,7 +2125,7 @@
       </c>
       <c r="B66" s="12" t="inlineStr">
         <is>
-          <t>AOC Châteauneuf-du-Pape — Le Couchant</t>
+          <t>AOC Châteauneuf-du-Pape — Le Couchant Rouge</t>
         </is>
       </c>
       <c r="C66" s="12" t="inlineStr">
@@ -2166,7 +2182,7 @@
       </c>
       <c r="B68" s="12" t="inlineStr">
         <is>
-          <t>IGP Méditerranée — Première Fleur</t>
+          <t>IGP Méditerranée — Premières Fleurs Blanc</t>
         </is>
       </c>
       <c r="C68" s="12" t="inlineStr">
@@ -2197,12 +2213,12 @@
       </c>
       <c r="B69" s="12" t="inlineStr">
         <is>
-          <t>IGP Méditerranée — Premières Fleurs</t>
+          <t>IGP Méditerranée — Premières Fleurs Rouge</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>Blanc</t>
+          <t>Rouge</t>
         </is>
       </c>
       <c r="D69" s="12" t="inlineStr">
@@ -2224,7 +2240,7 @@
       </c>
       <c r="B70" s="12" t="inlineStr">
         <is>
-          <t>AOC Muscat BDV — Or des Dentelles</t>
+          <t>AOC Muscat BDV — Or des Dentelles Blanc Moelleux</t>
         </is>
       </c>
       <c r="C70" s="12" t="inlineStr">
@@ -2251,7 +2267,7 @@
       </c>
       <c r="B71" s="12" t="inlineStr">
         <is>
-          <t>AOC Muscat BDV — Or des Dentelles</t>
+          <t>AOC Muscat BDV — Or des Dentelles Blanc Moelleux</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
@@ -2278,7 +2294,7 @@
       </c>
       <c r="B72" s="12" t="inlineStr">
         <is>
-          <t>Côtes du Rhône</t>
+          <t>AOC Côtes du Rhône — Côtes du Rhône Rouge</t>
         </is>
       </c>
       <c r="C72" s="12" t="inlineStr">
@@ -2350,7 +2366,7 @@
       </c>
       <c r="B76" s="12" t="inlineStr">
         <is>
-          <t>AOP Côtes de Bourg — Les Demoiselles de Falfas</t>
+          <t>AOC Côtes de Bourg — Les Demoiselles de Falfas</t>
         </is>
       </c>
       <c r="C76" s="12" t="inlineStr">
@@ -2381,7 +2397,7 @@
       </c>
       <c r="B77" s="12" t="inlineStr">
         <is>
-          <t>AOP Côtes de Bourg — Château Falfas</t>
+          <t>AOC Côtes de Bourg — Château Falfas</t>
         </is>
       </c>
       <c r="C77" s="12" t="inlineStr">
@@ -2412,7 +2428,7 @@
       </c>
       <c r="B78" s="12" t="inlineStr">
         <is>
-          <t>AOP Côtes de Bourg — Château Falfas</t>
+          <t>AOC Côtes de Bourg — Château Falfas</t>
         </is>
       </c>
       <c r="C78" s="12" t="inlineStr">
@@ -2443,7 +2459,7 @@
       </c>
       <c r="B79" s="12" t="inlineStr">
         <is>
-          <t>AOP Côtes de Bourg — Château Falfas</t>
+          <t>AOC Côtes de Bourg — Château Falfas</t>
         </is>
       </c>
       <c r="C79" s="12" t="inlineStr">
@@ -2474,7 +2490,7 @@
       </c>
       <c r="B80" s="12" t="inlineStr">
         <is>
-          <t>AOP Côtes de Bourg — Château Falfas Le Chevalier (Vieilles Vignes)</t>
+          <t>AOC Côtes de Bourg — Château Falfas Chevalier</t>
         </is>
       </c>
       <c r="C80" s="12" t="inlineStr">
@@ -2505,7 +2521,7 @@
       </c>
       <c r="B81" s="12" t="inlineStr">
         <is>
-          <t>AOP Côtes de Bourg — Château Falfas Le Chevalier (Vieilles Vignes)</t>
+          <t>AOC Côtes de Bourg — Château Falfas Chevalier</t>
         </is>
       </c>
       <c r="C81" s="12" t="inlineStr">
@@ -2536,7 +2552,7 @@
       </c>
       <c r="B82" s="12" t="inlineStr">
         <is>
-          <t>AOP Côtes de Bourg — Château Falfas</t>
+          <t>AOC Côtes de Bourg — Château Falfas</t>
         </is>
       </c>
       <c r="C82" s="12" t="inlineStr">
@@ -2616,7 +2632,7 @@
       </c>
       <c r="B86" s="12" t="inlineStr">
         <is>
-          <t>AOP Crémant d’Alsace — Brut Nature</t>
+          <t>AOC Crémant d’Alsace</t>
         </is>
       </c>
       <c r="C86" s="12" t="inlineStr">
@@ -2647,12 +2663,12 @@
       </c>
       <c r="B87" s="12" t="inlineStr">
         <is>
-          <t>AOP Alsace — Molse Blanc (Assemblage)</t>
+          <t>AOC Alsace — Molse Blanc</t>
         </is>
       </c>
       <c r="C87" s="12" t="inlineStr">
         <is>
-          <t>Blanc sec</t>
+          <t>Blanc</t>
         </is>
       </c>
       <c r="D87" s="12" t="inlineStr">
@@ -2678,12 +2694,12 @@
       </c>
       <c r="B88" s="12" t="inlineStr">
         <is>
-          <t>AOP Alsace — Leimen (Sylvaner)</t>
+          <t>AOC Alsace — Molse Rouge</t>
         </is>
       </c>
       <c r="C88" s="12" t="inlineStr">
         <is>
-          <t>Blanc sec</t>
+          <t>Rouge</t>
         </is>
       </c>
       <c r="D88" s="12" t="inlineStr">
@@ -2709,7 +2725,7 @@
       </c>
       <c r="B89" s="12" t="inlineStr">
         <is>
-          <t>AOP Alsace — Holderhurst (Riesling)</t>
+          <t>AOC Alsace — Leimen Sylvaner</t>
         </is>
       </c>
       <c r="C89" s="12" t="inlineStr">
@@ -2719,7 +2735,7 @@
       </c>
       <c r="D89" s="12" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E89" s="12" t="inlineStr">
@@ -2740,7 +2756,7 @@
       </c>
       <c r="B90" s="12" t="inlineStr">
         <is>
-          <t>AOP Alsace — Hahnenberg (Riesling)</t>
+          <t>AOC Alsace — Riesling Holderhurst</t>
         </is>
       </c>
       <c r="C90" s="12" t="inlineStr">
@@ -2750,7 +2766,7 @@
       </c>
       <c r="D90" s="12" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="E90" s="12" t="inlineStr">
@@ -2771,7 +2787,7 @@
       </c>
       <c r="B91" s="12" t="inlineStr">
         <is>
-          <t>AOP Alsace Grand Cru — Bruderthal (Gewurztraminer)</t>
+          <t>AOC Alsace — Riesling Hahnenberg</t>
         </is>
       </c>
       <c r="C91" s="12" t="inlineStr">
@@ -2781,7 +2797,7 @@
       </c>
       <c r="D91" s="12" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E91" s="12" t="inlineStr">
@@ -2802,7 +2818,7 @@
       </c>
       <c r="B92" s="12" t="inlineStr">
         <is>
-          <t>AOP Alsace Grand Cru — Bruderthal (Riesling)</t>
+          <t>Gewurztraminer Grand Cru Bruderthal</t>
         </is>
       </c>
       <c r="C92" s="12" t="inlineStr">
@@ -2825,126 +2841,126 @@
       <c r="H92" s="13" t="n"/>
       <c r="I92" s="13" t="n"/>
     </row>
-    <row r="94" ht="22" customHeight="1">
-      <c r="A94" s="5" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="11" t="inlineStr">
+        <is>
+          <t>S09 V08</t>
+        </is>
+      </c>
+      <c r="B93" s="12" t="inlineStr">
+        <is>
+          <t>Riesling Grand Cru Bruderthal</t>
+        </is>
+      </c>
+      <c r="C93" s="12" t="inlineStr">
+        <is>
+          <t>Blanc sec</t>
+        </is>
+      </c>
+      <c r="D93" s="12" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E93" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
+      <c r="F93" s="13" t="n"/>
+      <c r="G93" s="13" t="n"/>
+      <c r="H93" s="13" t="n"/>
+      <c r="I93" s="13" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="11" t="inlineStr">
+        <is>
+          <t>S09 V09</t>
+        </is>
+      </c>
+      <c r="B94" s="12" t="inlineStr">
+        <is>
+          <t>AOC Alsace — Seiler Rouge</t>
+        </is>
+      </c>
+      <c r="C94" s="12" t="inlineStr">
+        <is>
+          <t>Rouge</t>
+        </is>
+      </c>
+      <c r="D94" s="12" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="E94" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
+      <c r="F94" s="13" t="n"/>
+      <c r="G94" s="13" t="n"/>
+      <c r="H94" s="13" t="n"/>
+      <c r="I94" s="13" t="n"/>
+    </row>
+    <row r="96" ht="22" customHeight="1">
+      <c r="A96" s="5" t="inlineStr">
         <is>
           <t>S10</t>
         </is>
       </c>
-      <c r="B94" s="6" t="inlineStr">
+      <c r="B96" s="6" t="inlineStr">
         <is>
           <t>Stand 10 — François Reverdy (Loire)</t>
         </is>
       </c>
-      <c r="C94" s="7" t="n"/>
-      <c r="D94" s="7" t="n"/>
-      <c r="E94" s="7" t="n"/>
-      <c r="F94" s="7" t="n"/>
-      <c r="G94" s="7" t="n"/>
-      <c r="H94" s="7" t="n"/>
-      <c r="I94" s="7" t="n"/>
-    </row>
-    <row r="95" ht="26" customHeight="1">
-      <c r="B95" s="8" t="inlineStr">
+      <c r="C96" s="7" t="n"/>
+      <c r="D96" s="7" t="n"/>
+      <c r="E96" s="7" t="n"/>
+      <c r="F96" s="7" t="n"/>
+      <c r="G96" s="7" t="n"/>
+      <c r="H96" s="7" t="n"/>
+      <c r="I96" s="7" t="n"/>
+    </row>
+    <row r="97" ht="26" customHeight="1">
+      <c r="B97" s="8" t="inlineStr">
         <is>
           <t>François Reverdy — paliers du tarif</t>
         </is>
       </c>
-      <c r="C95" s="9" t="n"/>
-      <c r="D95" s="9" t="n"/>
-      <c r="E95" s="9" t="n"/>
-      <c r="F95" s="8" t="inlineStr">
+      <c r="C97" s="9" t="n"/>
+      <c r="D97" s="9" t="n"/>
+      <c r="E97" s="9" t="n"/>
+      <c r="F97" s="8" t="inlineStr">
         <is>
           <t>Prix unique</t>
         </is>
       </c>
-      <c r="G95" s="10" t="inlineStr">
+      <c r="G97" s="10" t="inlineStr">
         <is>
           <t>Jusqu'à 36 bts</t>
         </is>
       </c>
-      <c r="H95" s="10" t="inlineStr">
+      <c r="H97" s="10" t="inlineStr">
         <is>
           <t>À partir de 48 bts</t>
         </is>
       </c>
-      <c r="I95" s="10" t="inlineStr">
+      <c r="I97" s="10" t="inlineStr">
         <is>
           <t>À partir de 120 bts</t>
         </is>
       </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="11" t="inlineStr">
-        <is>
-          <t>S10 V01</t>
-        </is>
-      </c>
-      <c r="B96" s="12" t="inlineStr">
-        <is>
-          <t>AOP Anjou — François Reverdy – Schistes Vert</t>
-        </is>
-      </c>
-      <c r="C96" s="12" t="inlineStr">
-        <is>
-          <t>Blanc</t>
-        </is>
-      </c>
-      <c r="D96" s="12" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E96" s="12" t="inlineStr">
-        <is>
-          <t>75 cl</t>
-        </is>
-      </c>
-      <c r="F96" s="13" t="n"/>
-      <c r="G96" s="13" t="n"/>
-      <c r="H96" s="13" t="n"/>
-      <c r="I96" s="13" t="n"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="11" t="inlineStr">
-        <is>
-          <t>S10 V02</t>
-        </is>
-      </c>
-      <c r="B97" s="12" t="inlineStr">
-        <is>
-          <t>IGP Val de Loire — La Grange Jaumain – Chenin Blanc</t>
-        </is>
-      </c>
-      <c r="C97" s="12" t="inlineStr">
-        <is>
-          <t>Blanc</t>
-        </is>
-      </c>
-      <c r="D97" s="12" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E97" s="12" t="inlineStr">
-        <is>
-          <t>75 cl</t>
-        </is>
-      </c>
-      <c r="F97" s="13" t="n"/>
-      <c r="G97" s="13" t="n"/>
-      <c r="H97" s="13" t="n"/>
-      <c r="I97" s="13" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="11" t="inlineStr">
         <is>
-          <t>S10 V03</t>
+          <t>S10 V01</t>
         </is>
       </c>
       <c r="B98" s="12" t="inlineStr">
         <is>
-          <t>AOP Saumur — François Reverdy – Tuffeau</t>
+          <t>AOP Anjou Blanc</t>
         </is>
       </c>
       <c r="C98" s="12" t="inlineStr">
@@ -2954,7 +2970,7 @@
       </c>
       <c r="D98" s="12" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="E98" s="12" t="inlineStr">
@@ -2970,12 +2986,12 @@
     <row r="99">
       <c r="A99" s="11" t="inlineStr">
         <is>
-          <t>S10 V04</t>
+          <t>S10 V02</t>
         </is>
       </c>
       <c r="B99" s="12" t="inlineStr">
         <is>
-          <t>AOP Quincy — François Reverdy – Graves Argileuses</t>
+          <t>IGP Val de Loire — La Grange Jaumain Blanc</t>
         </is>
       </c>
       <c r="C99" s="12" t="inlineStr">
@@ -2985,7 +3001,7 @@
       </c>
       <c r="D99" s="12" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E99" s="12" t="inlineStr">
@@ -3001,12 +3017,12 @@
     <row r="100">
       <c r="A100" s="11" t="inlineStr">
         <is>
-          <t>S10 V05</t>
+          <t>S10 V03</t>
         </is>
       </c>
       <c r="B100" s="12" t="inlineStr">
         <is>
-          <t>AOP Sancerre — François Reverdy – Les Villaudes</t>
+          <t>AOP Saumur Blanc</t>
         </is>
       </c>
       <c r="C100" s="12" t="inlineStr">
@@ -3016,7 +3032,7 @@
       </c>
       <c r="D100" s="12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E100" s="12" t="inlineStr">
@@ -3032,25 +3048,29 @@
     <row r="101">
       <c r="A101" s="11" t="inlineStr">
         <is>
-          <t>S10 V06</t>
+          <t>S10 V04</t>
         </is>
       </c>
       <c r="B101" s="12" t="inlineStr">
         <is>
-          <t>La Grange Jaumain – Grolleau Noir</t>
+          <t>AOP Quincy</t>
         </is>
       </c>
       <c r="C101" s="12" t="inlineStr">
         <is>
-          <t>Rouge</t>
+          <t>Blanc</t>
         </is>
       </c>
       <c r="D101" s="12" t="inlineStr">
         <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="E101" s="12" t="n"/>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E101" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
       <c r="F101" s="13" t="n"/>
       <c r="G101" s="13" t="n"/>
       <c r="H101" s="13" t="n"/>
@@ -3059,22 +3079,22 @@
     <row r="102">
       <c r="A102" s="11" t="inlineStr">
         <is>
-          <t>S10 V07</t>
+          <t>S10 V05</t>
         </is>
       </c>
       <c r="B102" s="12" t="inlineStr">
         <is>
-          <t>AOP Chinon — François Reverdy – Franc / Graves</t>
+          <t>AOP Sancerre Blanc — Les Villaudes</t>
         </is>
       </c>
       <c r="C102" s="12" t="inlineStr">
         <is>
-          <t>Rouge</t>
+          <t>Blanc</t>
         </is>
       </c>
       <c r="D102" s="12" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E102" s="12" t="inlineStr">
@@ -3090,12 +3110,12 @@
     <row r="103">
       <c r="A103" s="11" t="inlineStr">
         <is>
-          <t>S10 V08</t>
+          <t>S10 V06</t>
         </is>
       </c>
       <c r="B103" s="12" t="inlineStr">
         <is>
-          <t>AOP Chinon — Cravant</t>
+          <t>La Grange Jaumain Rouge – Grolleau Noir</t>
         </is>
       </c>
       <c r="C103" s="12" t="inlineStr">
@@ -3114,304 +3134,320 @@
       <c r="H103" s="13" t="n"/>
       <c r="I103" s="13" t="n"/>
     </row>
-    <row r="105" ht="22" customHeight="1">
-      <c r="A105" s="5" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="11" t="inlineStr">
+        <is>
+          <t>S10 V07</t>
+        </is>
+      </c>
+      <c r="B104" s="12" t="inlineStr">
+        <is>
+          <t>AOP Chinon — Franc Rouge</t>
+        </is>
+      </c>
+      <c r="C104" s="12" t="inlineStr">
+        <is>
+          <t>Rouge</t>
+        </is>
+      </c>
+      <c r="D104" s="12" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="E104" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
+      <c r="F104" s="13" t="n"/>
+      <c r="G104" s="13" t="n"/>
+      <c r="H104" s="13" t="n"/>
+      <c r="I104" s="13" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="11" t="inlineStr">
+        <is>
+          <t>S10 V08</t>
+        </is>
+      </c>
+      <c r="B105" s="12" t="inlineStr">
+        <is>
+          <t>AOP Chinon — Cravant Rouge</t>
+        </is>
+      </c>
+      <c r="C105" s="12" t="inlineStr">
+        <is>
+          <t>Rouge</t>
+        </is>
+      </c>
+      <c r="D105" s="12" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="E105" s="12" t="n"/>
+      <c r="F105" s="13" t="n"/>
+      <c r="G105" s="13" t="n"/>
+      <c r="H105" s="13" t="n"/>
+      <c r="I105" s="13" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="11" t="inlineStr">
+        <is>
+          <t>S10 V09</t>
+        </is>
+      </c>
+      <c r="B106" s="12" t="inlineStr">
+        <is>
+          <t>IGP Val de Loire — La Grange Jaumain Les Soudannes Rouge</t>
+        </is>
+      </c>
+      <c r="C106" s="12" t="inlineStr">
+        <is>
+          <t>Rouge</t>
+        </is>
+      </c>
+      <c r="D106" s="12" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E106" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
+      <c r="F106" s="13" t="n"/>
+      <c r="G106" s="13" t="n"/>
+      <c r="H106" s="13" t="n"/>
+      <c r="I106" s="13" t="n"/>
+    </row>
+    <row r="108" ht="22" customHeight="1">
+      <c r="A108" s="5" t="inlineStr">
         <is>
           <t>S11</t>
         </is>
       </c>
-      <c r="B105" s="6" t="inlineStr">
+      <c r="B108" s="6" t="inlineStr">
         <is>
           <t>Stand 11 — Champagne Dekeyne (Champagne)</t>
         </is>
       </c>
-      <c r="C105" s="7" t="n"/>
-      <c r="D105" s="7" t="n"/>
-      <c r="E105" s="7" t="n"/>
-      <c r="F105" s="7" t="n"/>
-      <c r="G105" s="7" t="n"/>
-      <c r="H105" s="7" t="n"/>
-      <c r="I105" s="7" t="n"/>
-    </row>
-    <row r="106" ht="26" customHeight="1">
-      <c r="B106" s="8" t="inlineStr">
+      <c r="C108" s="7" t="n"/>
+      <c r="D108" s="7" t="n"/>
+      <c r="E108" s="7" t="n"/>
+      <c r="F108" s="7" t="n"/>
+      <c r="G108" s="7" t="n"/>
+      <c r="H108" s="7" t="n"/>
+      <c r="I108" s="7" t="n"/>
+    </row>
+    <row r="109" ht="26" customHeight="1">
+      <c r="B109" s="8" t="inlineStr">
         <is>
           <t>Champagne Dekeyne — paliers du tarif</t>
         </is>
       </c>
-      <c r="C106" s="9" t="n"/>
-      <c r="D106" s="9" t="n"/>
-      <c r="E106" s="9" t="n"/>
-      <c r="F106" s="8" t="inlineStr">
+      <c r="C109" s="9" t="n"/>
+      <c r="D109" s="9" t="n"/>
+      <c r="E109" s="9" t="n"/>
+      <c r="F109" s="8" t="inlineStr">
         <is>
           <t>Prix unique</t>
         </is>
       </c>
-      <c r="G106" s="10" t="inlineStr">
+      <c r="G109" s="10" t="inlineStr">
         <is>
           <t>À partir de 48 bts</t>
         </is>
       </c>
-      <c r="H106" s="10" t="n"/>
-      <c r="I106" s="10" t="n"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="11" t="inlineStr">
-        <is>
-          <t>S11 V01</t>
-        </is>
-      </c>
-      <c r="B107" s="12" t="inlineStr">
-        <is>
-          <t>AOP Champagne — Voglonniers</t>
-        </is>
-      </c>
-      <c r="C107" s="12" t="inlineStr">
-        <is>
-          <t>Blanc extra brut</t>
-        </is>
-      </c>
-      <c r="D107" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E107" s="12" t="inlineStr">
-        <is>
-          <t>75 cl</t>
-        </is>
-      </c>
-      <c r="F107" s="13" t="n"/>
-      <c r="G107" s="13" t="n"/>
-      <c r="H107" s="14" t="n"/>
-      <c r="I107" s="14" t="n"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="11" t="inlineStr">
-        <is>
-          <t>S11 V02</t>
-        </is>
-      </c>
-      <c r="B108" s="12" t="inlineStr">
-        <is>
-          <t>AOP Champagne — Nature</t>
-        </is>
-      </c>
-      <c r="C108" s="12" t="inlineStr">
-        <is>
-          <t>Blanc extra brut</t>
-        </is>
-      </c>
-      <c r="D108" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E108" s="12" t="inlineStr">
-        <is>
-          <t>75 cl</t>
-        </is>
-      </c>
-      <c r="F108" s="13" t="n"/>
-      <c r="G108" s="13" t="n"/>
-      <c r="H108" s="14" t="n"/>
-      <c r="I108" s="14" t="n"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="11" t="inlineStr">
-        <is>
-          <t>S11 V03</t>
-        </is>
-      </c>
-      <c r="B109" s="12" t="inlineStr">
-        <is>
-          <t>AOP Champagne — Chardonnay Vignes de 1962</t>
-        </is>
-      </c>
-      <c r="C109" s="12" t="inlineStr">
-        <is>
-          <t>Blanc extra brut</t>
-        </is>
-      </c>
-      <c r="D109" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E109" s="12" t="inlineStr">
-        <is>
-          <t>75 cl</t>
-        </is>
-      </c>
-      <c r="F109" s="13" t="n"/>
-      <c r="G109" s="13" t="n"/>
-      <c r="H109" s="14" t="n"/>
-      <c r="I109" s="14" t="n"/>
+      <c r="H109" s="10" t="n"/>
+      <c r="I109" s="10" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="11" t="inlineStr">
         <is>
-          <t>S11 V04</t>
+          <t>S11 V01</t>
         </is>
       </c>
       <c r="B110" s="12" t="inlineStr">
         <is>
-          <t>AOC Champagne — Supernova Extra-Brut Zéro Dosage</t>
+          <t>AOC Champagne — Voglonniers Brut</t>
         </is>
       </c>
       <c r="C110" s="12" t="inlineStr">
         <is>
-          <t>Extra-brut, zéro dosage</t>
-        </is>
-      </c>
-      <c r="D110" s="12" t="n"/>
-      <c r="E110" s="12" t="n"/>
+          <t>Blanc extra brut</t>
+        </is>
+      </c>
+      <c r="D110" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E110" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
       <c r="F110" s="13" t="n"/>
       <c r="G110" s="13" t="n"/>
       <c r="H110" s="14" t="n"/>
       <c r="I110" s="14" t="n"/>
     </row>
-    <row r="112" ht="22" customHeight="1">
-      <c r="A112" s="5" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="11" t="inlineStr">
+        <is>
+          <t>S11 V02</t>
+        </is>
+      </c>
+      <c r="B111" s="12" t="inlineStr">
+        <is>
+          <t>AOC Champagne — Nature Brut</t>
+        </is>
+      </c>
+      <c r="C111" s="12" t="inlineStr">
+        <is>
+          <t>Blanc extra brut</t>
+        </is>
+      </c>
+      <c r="D111" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E111" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
+      <c r="F111" s="13" t="n"/>
+      <c r="G111" s="13" t="n"/>
+      <c r="H111" s="14" t="n"/>
+      <c r="I111" s="14" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="11" t="inlineStr">
+        <is>
+          <t>S11 V03</t>
+        </is>
+      </c>
+      <c r="B112" s="12" t="inlineStr">
+        <is>
+          <t>AOC Champagne — Chardonnay Extra-Brut</t>
+        </is>
+      </c>
+      <c r="C112" s="12" t="inlineStr">
+        <is>
+          <t>Blanc extra brut</t>
+        </is>
+      </c>
+      <c r="D112" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E112" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
+      <c r="F112" s="13" t="n"/>
+      <c r="G112" s="13" t="n"/>
+      <c r="H112" s="14" t="n"/>
+      <c r="I112" s="14" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="11" t="inlineStr">
+        <is>
+          <t>S11 V04</t>
+        </is>
+      </c>
+      <c r="B113" s="12" t="inlineStr">
+        <is>
+          <t>AOC Champagne — Supernova Extra-Brut Zéro Dosage</t>
+        </is>
+      </c>
+      <c r="C113" s="12" t="n"/>
+      <c r="D113" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E113" s="12" t="n"/>
+      <c r="F113" s="13" t="n"/>
+      <c r="G113" s="13" t="n"/>
+      <c r="H113" s="14" t="n"/>
+      <c r="I113" s="14" t="n"/>
+    </row>
+    <row r="115" ht="22" customHeight="1">
+      <c r="A115" s="5" t="inlineStr">
         <is>
           <t>S12</t>
         </is>
       </c>
-      <c r="B112" s="6" t="inlineStr">
+      <c r="B115" s="6" t="inlineStr">
         <is>
           <t>Stand 12 — Domaine Trichon (Rhône)</t>
         </is>
       </c>
-      <c r="C112" s="7" t="n"/>
-      <c r="D112" s="7" t="n"/>
-      <c r="E112" s="7" t="n"/>
-      <c r="F112" s="7" t="n"/>
-      <c r="G112" s="7" t="n"/>
-      <c r="H112" s="7" t="n"/>
-      <c r="I112" s="7" t="n"/>
-    </row>
-    <row r="113" ht="26" customHeight="1">
-      <c r="B113" s="8" t="inlineStr">
+      <c r="C115" s="7" t="n"/>
+      <c r="D115" s="7" t="n"/>
+      <c r="E115" s="7" t="n"/>
+      <c r="F115" s="7" t="n"/>
+      <c r="G115" s="7" t="n"/>
+      <c r="H115" s="7" t="n"/>
+      <c r="I115" s="7" t="n"/>
+    </row>
+    <row r="116" ht="26" customHeight="1">
+      <c r="B116" s="8" t="inlineStr">
         <is>
           <t>Domaine Trichon — paliers du tarif</t>
         </is>
       </c>
-      <c r="C113" s="9" t="n"/>
-      <c r="D113" s="9" t="n"/>
-      <c r="E113" s="9" t="n"/>
-      <c r="F113" s="8" t="inlineStr">
+      <c r="C116" s="9" t="n"/>
+      <c r="D116" s="9" t="n"/>
+      <c r="E116" s="9" t="n"/>
+      <c r="F116" s="8" t="inlineStr">
         <is>
           <t>Prix unique</t>
         </is>
       </c>
-      <c r="G113" s="10" t="inlineStr">
+      <c r="G116" s="10" t="inlineStr">
         <is>
           <t>À partir de 120 cols</t>
         </is>
       </c>
-      <c r="H113" s="10" t="inlineStr">
+      <c r="H116" s="10" t="inlineStr">
         <is>
           <t>À partir de 300 cols</t>
         </is>
       </c>
-      <c r="I113" s="10" t="inlineStr">
+      <c r="I116" s="10" t="inlineStr">
         <is>
           <t>À partir de 600 cols</t>
         </is>
       </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="11" t="inlineStr">
-        <is>
-          <t>S12 V01</t>
-        </is>
-      </c>
-      <c r="B114" s="12" t="inlineStr">
-        <is>
-          <t>AOC Bugey — Mas de Lusanne Brut Blanc</t>
-        </is>
-      </c>
-      <c r="C114" s="12" t="inlineStr">
-        <is>
-          <t>Blanc brut</t>
-        </is>
-      </c>
-      <c r="D114" s="12" t="n"/>
-      <c r="E114" s="12" t="n"/>
-      <c r="F114" s="13" t="n"/>
-      <c r="G114" s="13" t="n"/>
-      <c r="H114" s="13" t="n"/>
-      <c r="I114" s="13" t="n"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="11" t="inlineStr">
-        <is>
-          <t>S12 V02</t>
-        </is>
-      </c>
-      <c r="B115" s="12" t="inlineStr">
-        <is>
-          <t>AOC Bugey — Mas de Lusanne Extra-Brut Blanc</t>
-        </is>
-      </c>
-      <c r="C115" s="12" t="inlineStr">
-        <is>
-          <t>Blanc extra-brut</t>
-        </is>
-      </c>
-      <c r="D115" s="12" t="n"/>
-      <c r="E115" s="12" t="n"/>
-      <c r="F115" s="13" t="n"/>
-      <c r="G115" s="13" t="n"/>
-      <c r="H115" s="13" t="n"/>
-      <c r="I115" s="13" t="n"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="11" t="inlineStr">
-        <is>
-          <t>S12 V03</t>
-        </is>
-      </c>
-      <c r="B116" s="12" t="inlineStr">
-        <is>
-          <t>AOC Bugey — Mas de Lusanne Mondeuse</t>
-        </is>
-      </c>
-      <c r="C116" s="12" t="inlineStr">
-        <is>
-          <t>Rouge</t>
-        </is>
-      </c>
-      <c r="D116" s="12" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E116" s="12" t="n"/>
-      <c r="F116" s="13" t="n"/>
-      <c r="G116" s="13" t="n"/>
-      <c r="H116" s="13" t="n"/>
-      <c r="I116" s="13" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="11" t="inlineStr">
         <is>
-          <t>S12 V04</t>
+          <t>S12 V01</t>
         </is>
       </c>
       <c r="B117" s="12" t="inlineStr">
         <is>
-          <t>AOC Bugey — Mas de Lusanne Pinot Noir</t>
+          <t>AOC Bugey — Mas de Lusanne Brut Blanc</t>
         </is>
       </c>
       <c r="C117" s="12" t="inlineStr">
         <is>
-          <t>Rouge</t>
+          <t>Blanc effervescent</t>
         </is>
       </c>
       <c r="D117" s="12" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E117" s="12" t="n"/>
@@ -3423,29 +3459,25 @@
     <row r="118">
       <c r="A118" s="11" t="inlineStr">
         <is>
-          <t>S12 V05</t>
+          <t>S12 V02</t>
         </is>
       </c>
       <c r="B118" s="12" t="inlineStr">
         <is>
-          <t>AOP Côtes du Rhône — Côtes du Rhône</t>
+          <t>AOC Bugey — Mas de Lusanne Extra-Brut Blanc</t>
         </is>
       </c>
       <c r="C118" s="12" t="inlineStr">
         <is>
-          <t>Rouge</t>
+          <t>Blanc effervescent</t>
         </is>
       </c>
       <c r="D118" s="12" t="inlineStr">
         <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="E118" s="12" t="inlineStr">
-        <is>
-          <t>75 cl</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E118" s="12" t="n"/>
       <c r="F118" s="13" t="n"/>
       <c r="G118" s="13" t="n"/>
       <c r="H118" s="13" t="n"/>
@@ -3454,20 +3486,24 @@
     <row r="119">
       <c r="A119" s="11" t="inlineStr">
         <is>
-          <t>S12 V06</t>
+          <t>S12 V03</t>
         </is>
       </c>
       <c r="B119" s="12" t="inlineStr">
         <is>
-          <t>Mas de Lusanne Pétillant de Jus de Raisin 0 %</t>
+          <t>AOC Bugey — Mas de Lusanne Mondeuse Rouge</t>
         </is>
       </c>
       <c r="C119" s="12" t="inlineStr">
         <is>
-          <t>Pétillant de jus de raisin, 0 %</t>
-        </is>
-      </c>
-      <c r="D119" s="12" t="n"/>
+          <t>Rouge</t>
+        </is>
+      </c>
+      <c r="D119" s="12" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
       <c r="E119" s="12" t="n"/>
       <c r="F119" s="13" t="n"/>
       <c r="G119" s="13" t="n"/>
@@ -3477,12 +3513,12 @@
     <row r="120">
       <c r="A120" s="11" t="inlineStr">
         <is>
-          <t>S12 V07</t>
+          <t>S12 V04</t>
         </is>
       </c>
       <c r="B120" s="12" t="inlineStr">
         <is>
-          <t>AOC Bugey — Mas de Lusanne Gamay</t>
+          <t>AOC Bugey — Mas de Lusanne Pinot Noir Rouge</t>
         </is>
       </c>
       <c r="C120" s="12" t="inlineStr">
@@ -3490,7 +3526,11 @@
           <t>Rouge</t>
         </is>
       </c>
-      <c r="D120" s="12" t="n"/>
+      <c r="D120" s="12" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
       <c r="E120" s="12" t="n"/>
       <c r="F120" s="13" t="n"/>
       <c r="G120" s="13" t="n"/>
@@ -3500,25 +3540,29 @@
     <row r="121">
       <c r="A121" s="11" t="inlineStr">
         <is>
-          <t>S12 V08</t>
+          <t>S12 V05</t>
         </is>
       </c>
       <c r="B121" s="12" t="inlineStr">
         <is>
-          <t>AOC Bugey — Mas de Lusanne Chardonnay</t>
+          <t>AOC Côtes du Rhône — Mas de Lusanne Rouge</t>
         </is>
       </c>
       <c r="C121" s="12" t="inlineStr">
         <is>
-          <t>Blanc</t>
+          <t>Rouge</t>
         </is>
       </c>
       <c r="D121" s="12" t="inlineStr">
         <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="E121" s="12" t="n"/>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="E121" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
       <c r="F121" s="13" t="n"/>
       <c r="G121" s="13" t="n"/>
       <c r="H121" s="13" t="n"/>
@@ -3527,29 +3571,25 @@
     <row r="122">
       <c r="A122" s="11" t="inlineStr">
         <is>
-          <t>S12 V09</t>
+          <t>S12 V06</t>
         </is>
       </c>
       <c r="B122" s="12" t="inlineStr">
         <is>
-          <t>AOP Vacqueyras — Vacqueyras</t>
+          <t>AOC Bugey — Mas de Lusanne Gamay Rouge</t>
         </is>
       </c>
       <c r="C122" s="12" t="inlineStr">
         <is>
-          <t>Blanc</t>
+          <t>Rouge</t>
         </is>
       </c>
       <c r="D122" s="12" t="inlineStr">
         <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E122" s="12" t="inlineStr">
-        <is>
-          <t>75 cl</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E122" s="12" t="n"/>
       <c r="F122" s="13" t="n"/>
       <c r="G122" s="13" t="n"/>
       <c r="H122" s="13" t="n"/>
@@ -3558,190 +3598,182 @@
     <row r="123">
       <c r="A123" s="11" t="inlineStr">
         <is>
-          <t>S12 V10</t>
+          <t>S12 V07</t>
         </is>
       </c>
       <c r="B123" s="12" t="inlineStr">
         <is>
-          <t>AOP Vacqueyras — Vacqueyras</t>
+          <t>AOC Bugey — Mas de Lusanne Chardonnay Blanc</t>
         </is>
       </c>
       <c r="C123" s="12" t="inlineStr">
         <is>
-          <t>Rouge</t>
+          <t>Blanc</t>
         </is>
       </c>
       <c r="D123" s="12" t="inlineStr">
         <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E123" s="12" t="inlineStr">
-        <is>
-          <t>75 cl</t>
-        </is>
-      </c>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="E123" s="12" t="n"/>
       <c r="F123" s="13" t="n"/>
       <c r="G123" s="13" t="n"/>
       <c r="H123" s="13" t="n"/>
       <c r="I123" s="13" t="n"/>
     </row>
-    <row r="125" ht="22" customHeight="1">
-      <c r="A125" s="5" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="11" t="inlineStr">
+        <is>
+          <t>S12 V08</t>
+        </is>
+      </c>
+      <c r="B124" s="12" t="inlineStr">
+        <is>
+          <t>AOC Vacqueyras — Mas de Lusanne Vacqueyras Blanc</t>
+        </is>
+      </c>
+      <c r="C124" s="12" t="inlineStr">
+        <is>
+          <t>Blanc</t>
+        </is>
+      </c>
+      <c r="D124" s="12" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E124" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
+      <c r="F124" s="13" t="n"/>
+      <c r="G124" s="13" t="n"/>
+      <c r="H124" s="13" t="n"/>
+      <c r="I124" s="13" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="11" t="inlineStr">
+        <is>
+          <t>S12 V09</t>
+        </is>
+      </c>
+      <c r="B125" s="12" t="inlineStr">
+        <is>
+          <t>AOC Vacqueyras — Mas de Lusanne Vacqueyras Rouge</t>
+        </is>
+      </c>
+      <c r="C125" s="12" t="inlineStr">
+        <is>
+          <t>Rouge</t>
+        </is>
+      </c>
+      <c r="D125" s="12" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E125" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
+      <c r="F125" s="13" t="n"/>
+      <c r="G125" s="13" t="n"/>
+      <c r="H125" s="13" t="n"/>
+      <c r="I125" s="13" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="11" t="inlineStr">
+        <is>
+          <t>S12 V10</t>
+        </is>
+      </c>
+      <c r="B126" s="12" t="inlineStr">
+        <is>
+          <t>Mas de Lusanne Pétillant de Jus de Raisin 0 %</t>
+        </is>
+      </c>
+      <c r="C126" s="12" t="n"/>
+      <c r="D126" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E126" s="12" t="n"/>
+      <c r="F126" s="13" t="n"/>
+      <c r="G126" s="13" t="n"/>
+      <c r="H126" s="13" t="n"/>
+      <c r="I126" s="13" t="n"/>
+    </row>
+    <row r="128" ht="22" customHeight="1">
+      <c r="A128" s="5" t="inlineStr">
         <is>
           <t>S13</t>
         </is>
       </c>
-      <c r="B125" s="6" t="inlineStr">
+      <c r="B128" s="6" t="inlineStr">
         <is>
           <t>Stand 13 — Château de Gragnos (Languedoc)</t>
         </is>
       </c>
-      <c r="C125" s="7" t="n"/>
-      <c r="D125" s="7" t="n"/>
-      <c r="E125" s="7" t="n"/>
-      <c r="F125" s="7" t="n"/>
-      <c r="G125" s="7" t="n"/>
-      <c r="H125" s="7" t="n"/>
-      <c r="I125" s="7" t="n"/>
-    </row>
-    <row r="126" ht="26" customHeight="1">
-      <c r="B126" s="8" t="inlineStr">
+      <c r="C128" s="7" t="n"/>
+      <c r="D128" s="7" t="n"/>
+      <c r="E128" s="7" t="n"/>
+      <c r="F128" s="7" t="n"/>
+      <c r="G128" s="7" t="n"/>
+      <c r="H128" s="7" t="n"/>
+      <c r="I128" s="7" t="n"/>
+    </row>
+    <row r="129" ht="26" customHeight="1">
+      <c r="B129" s="8" t="inlineStr">
         <is>
           <t>Château de Gragnos — paliers du tarif</t>
         </is>
       </c>
-      <c r="C126" s="9" t="n"/>
-      <c r="D126" s="9" t="n"/>
-      <c r="E126" s="9" t="n"/>
-      <c r="F126" s="8" t="inlineStr">
+      <c r="C129" s="9" t="n"/>
+      <c r="D129" s="9" t="n"/>
+      <c r="E129" s="9" t="n"/>
+      <c r="F129" s="8" t="inlineStr">
         <is>
           <t>Prix unique</t>
         </is>
       </c>
-      <c r="G126" s="10" t="inlineStr">
+      <c r="G129" s="10" t="inlineStr">
         <is>
           <t>Tarif</t>
         </is>
       </c>
-      <c r="H126" s="10" t="n"/>
-      <c r="I126" s="10" t="n"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="11" t="inlineStr">
-        <is>
-          <t>S13 V01</t>
-        </is>
-      </c>
-      <c r="B127" s="12" t="inlineStr">
-        <is>
-          <t>Vin de France — Léon</t>
-        </is>
-      </c>
-      <c r="C127" s="12" t="inlineStr">
-        <is>
-          <t>Rouge</t>
-        </is>
-      </c>
-      <c r="D127" s="12" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="E127" s="12" t="inlineStr">
-        <is>
-          <t>75 cl</t>
-        </is>
-      </c>
-      <c r="F127" s="13" t="n"/>
-      <c r="G127" s="13" t="n"/>
-      <c r="H127" s="14" t="n"/>
-      <c r="I127" s="14" t="n"/>
-    </row>
-    <row r="128">
-      <c r="A128" s="11" t="inlineStr">
-        <is>
-          <t>S13 V02</t>
-        </is>
-      </c>
-      <c r="B128" s="12" t="inlineStr">
-        <is>
-          <t>AOP Saint Chinian — Lou Daro</t>
-        </is>
-      </c>
-      <c r="C128" s="12" t="inlineStr">
-        <is>
-          <t>Rouge</t>
-        </is>
-      </c>
-      <c r="D128" s="12" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E128" s="12" t="inlineStr">
-        <is>
-          <t>75 cl</t>
-        </is>
-      </c>
-      <c r="F128" s="13" t="n"/>
-      <c r="G128" s="13" t="n"/>
-      <c r="H128" s="14" t="n"/>
-      <c r="I128" s="14" t="n"/>
-    </row>
-    <row r="129">
-      <c r="A129" s="11" t="inlineStr">
-        <is>
-          <t>S13 V03</t>
-        </is>
-      </c>
-      <c r="B129" s="12" t="inlineStr">
-        <is>
-          <t>AOP Saint Chinian — Henri</t>
-        </is>
-      </c>
-      <c r="C129" s="12" t="inlineStr">
-        <is>
-          <t>Rouge</t>
-        </is>
-      </c>
-      <c r="D129" s="12" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="E129" s="12" t="inlineStr">
-        <is>
-          <t>75 cl</t>
-        </is>
-      </c>
-      <c r="F129" s="13" t="n"/>
-      <c r="G129" s="13" t="n"/>
-      <c r="H129" s="14" t="n"/>
-      <c r="I129" s="14" t="n"/>
+      <c r="H129" s="10" t="n"/>
+      <c r="I129" s="10" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="11" t="inlineStr">
         <is>
-          <t>S13 V04</t>
+          <t>S13 V01</t>
         </is>
       </c>
       <c r="B130" s="12" t="inlineStr">
         <is>
-          <t>AOC Saint-Chinian — Juliette</t>
+          <t>VDF — Léon Rouge</t>
         </is>
       </c>
       <c r="C130" s="12" t="inlineStr">
         <is>
-          <t>Blanc</t>
+          <t>Rouge</t>
         </is>
       </c>
       <c r="D130" s="12" t="inlineStr">
         <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E130" s="12" t="n"/>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="E130" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
       <c r="F130" s="13" t="n"/>
       <c r="G130" s="13" t="n"/>
       <c r="H130" s="14" t="n"/>
@@ -3750,22 +3782,22 @@
     <row r="131">
       <c r="A131" s="11" t="inlineStr">
         <is>
-          <t>S13 V05</t>
+          <t>S13 V02</t>
         </is>
       </c>
       <c r="B131" s="12" t="inlineStr">
         <is>
-          <t>AOP Saint Chinian — Grain de Blanc</t>
+          <t>AOC Saint-Chinian — Lou Daro Rouge</t>
         </is>
       </c>
       <c r="C131" s="12" t="inlineStr">
         <is>
-          <t>Blanc</t>
+          <t>Rouge</t>
         </is>
       </c>
       <c r="D131" s="12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="E131" s="12" t="inlineStr">
@@ -3778,170 +3810,166 @@
       <c r="H131" s="14" t="n"/>
       <c r="I131" s="14" t="n"/>
     </row>
-    <row r="133" ht="22" customHeight="1">
-      <c r="A133" s="5" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="11" t="inlineStr">
+        <is>
+          <t>S13 V03</t>
+        </is>
+      </c>
+      <c r="B132" s="12" t="inlineStr">
+        <is>
+          <t>AOC Saint-Chinian — Henri Rouge</t>
+        </is>
+      </c>
+      <c r="C132" s="12" t="inlineStr">
+        <is>
+          <t>Rouge</t>
+        </is>
+      </c>
+      <c r="D132" s="12" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="E132" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
+      <c r="F132" s="13" t="n"/>
+      <c r="G132" s="13" t="n"/>
+      <c r="H132" s="14" t="n"/>
+      <c r="I132" s="14" t="n"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="11" t="inlineStr">
+        <is>
+          <t>S13 V04</t>
+        </is>
+      </c>
+      <c r="B133" s="12" t="inlineStr">
+        <is>
+          <t>AOC Saint-Chinian — Juliette Blanc</t>
+        </is>
+      </c>
+      <c r="C133" s="12" t="inlineStr">
+        <is>
+          <t>Blanc</t>
+        </is>
+      </c>
+      <c r="D133" s="12" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E133" s="12" t="n"/>
+      <c r="F133" s="13" t="n"/>
+      <c r="G133" s="13" t="n"/>
+      <c r="H133" s="14" t="n"/>
+      <c r="I133" s="14" t="n"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="11" t="inlineStr">
+        <is>
+          <t>S13 V05</t>
+        </is>
+      </c>
+      <c r="B134" s="12" t="inlineStr">
+        <is>
+          <t>IGP Pays d’Hérault Monts de la Grage — Grain de Blanc</t>
+        </is>
+      </c>
+      <c r="C134" s="12" t="inlineStr">
+        <is>
+          <t>Blanc</t>
+        </is>
+      </c>
+      <c r="D134" s="12" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E134" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
+      <c r="F134" s="13" t="n"/>
+      <c r="G134" s="13" t="n"/>
+      <c r="H134" s="14" t="n"/>
+      <c r="I134" s="14" t="n"/>
+    </row>
+    <row r="136" ht="22" customHeight="1">
+      <c r="A136" s="5" t="inlineStr">
         <is>
           <t>S14</t>
         </is>
       </c>
-      <c r="B133" s="6" t="inlineStr">
+      <c r="B136" s="6" t="inlineStr">
         <is>
           <t>Stand 14 — Domaine des Noëls (Loire)</t>
         </is>
       </c>
-      <c r="C133" s="7" t="n"/>
-      <c r="D133" s="7" t="n"/>
-      <c r="E133" s="7" t="n"/>
-      <c r="F133" s="7" t="n"/>
-      <c r="G133" s="7" t="n"/>
-      <c r="H133" s="7" t="n"/>
-      <c r="I133" s="7" t="n"/>
-    </row>
-    <row r="134" ht="26" customHeight="1">
-      <c r="B134" s="8" t="inlineStr">
+      <c r="C136" s="7" t="n"/>
+      <c r="D136" s="7" t="n"/>
+      <c r="E136" s="7" t="n"/>
+      <c r="F136" s="7" t="n"/>
+      <c r="G136" s="7" t="n"/>
+      <c r="H136" s="7" t="n"/>
+      <c r="I136" s="7" t="n"/>
+    </row>
+    <row r="137" ht="26" customHeight="1">
+      <c r="B137" s="8" t="inlineStr">
         <is>
           <t>Domaine des Noëls — paliers du tarif</t>
         </is>
       </c>
-      <c r="C134" s="9" t="n"/>
-      <c r="D134" s="9" t="n"/>
-      <c r="E134" s="9" t="n"/>
-      <c r="F134" s="8" t="inlineStr">
+      <c r="C137" s="9" t="n"/>
+      <c r="D137" s="9" t="n"/>
+      <c r="E137" s="9" t="n"/>
+      <c r="F137" s="8" t="inlineStr">
         <is>
           <t>Prix unique</t>
         </is>
       </c>
-      <c r="G134" s="10" t="inlineStr">
+      <c r="G137" s="10" t="inlineStr">
         <is>
           <t>À partir de 120 bts</t>
         </is>
       </c>
-      <c r="H134" s="10" t="inlineStr">
+      <c r="H137" s="10" t="inlineStr">
         <is>
           <t>À partir de 240 bts</t>
         </is>
       </c>
-      <c r="I134" s="10" t="inlineStr">
+      <c r="I137" s="10" t="inlineStr">
         <is>
           <t>À partir de 360 bts</t>
         </is>
       </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="11" t="inlineStr">
-        <is>
-          <t>S14 V01</t>
-        </is>
-      </c>
-      <c r="B135" s="12" t="inlineStr">
-        <is>
-          <t>AOC Anjou</t>
-        </is>
-      </c>
-      <c r="C135" s="12" t="inlineStr">
-        <is>
-          <t>Blanc</t>
-        </is>
-      </c>
-      <c r="D135" s="12" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="E135" s="12" t="n"/>
-      <c r="F135" s="13" t="n"/>
-      <c r="G135" s="13" t="n"/>
-      <c r="H135" s="13" t="n"/>
-      <c r="I135" s="13" t="n"/>
-    </row>
-    <row r="136">
-      <c r="A136" s="11" t="inlineStr">
-        <is>
-          <t>S14 V02</t>
-        </is>
-      </c>
-      <c r="B136" s="12" t="inlineStr">
-        <is>
-          <t>AOP Anjou — Promenade des Noëls</t>
-        </is>
-      </c>
-      <c r="C136" s="12" t="inlineStr">
-        <is>
-          <t>Blanc sec</t>
-        </is>
-      </c>
-      <c r="D136" s="12" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="E136" s="12" t="inlineStr">
-        <is>
-          <t>75 cl</t>
-        </is>
-      </c>
-      <c r="F136" s="13" t="n"/>
-      <c r="G136" s="13" t="n"/>
-      <c r="H136" s="13" t="n"/>
-      <c r="I136" s="13" t="n"/>
-    </row>
-    <row r="137">
-      <c r="A137" s="11" t="inlineStr">
-        <is>
-          <t>S14 V03</t>
-        </is>
-      </c>
-      <c r="B137" s="12" t="inlineStr">
-        <is>
-          <t>IGP Val de Loire — Sauvignon</t>
-        </is>
-      </c>
-      <c r="C137" s="12" t="inlineStr">
-        <is>
-          <t>Blanc sec</t>
-        </is>
-      </c>
-      <c r="D137" s="12" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E137" s="12" t="inlineStr">
-        <is>
-          <t>75 cl</t>
-        </is>
-      </c>
-      <c r="F137" s="13" t="n"/>
-      <c r="G137" s="13" t="n"/>
-      <c r="H137" s="13" t="n"/>
-      <c r="I137" s="13" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="11" t="inlineStr">
         <is>
-          <t>S14 V04</t>
+          <t>S14 V01</t>
         </is>
       </c>
       <c r="B138" s="12" t="inlineStr">
         <is>
-          <t>AOP Coteaux du Layon — Coteaux du Layon</t>
+          <t>AOC Anjou Blanc</t>
         </is>
       </c>
       <c r="C138" s="12" t="inlineStr">
         <is>
-          <t>Blanc moelleux</t>
+          <t>Blanc</t>
         </is>
       </c>
       <c r="D138" s="12" t="inlineStr">
         <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E138" s="12" t="inlineStr">
-        <is>
-          <t>75 cl</t>
-        </is>
-      </c>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="E138" s="12" t="n"/>
       <c r="F138" s="13" t="n"/>
       <c r="G138" s="13" t="n"/>
       <c r="H138" s="13" t="n"/>
@@ -3950,22 +3978,22 @@
     <row r="139">
       <c r="A139" s="11" t="inlineStr">
         <is>
-          <t>S14 V05</t>
+          <t>S14 V02</t>
         </is>
       </c>
       <c r="B139" s="12" t="inlineStr">
         <is>
-          <t>AOP Coteaux du Layon Faye — Coteaux du Layon Faye</t>
+          <t>AOC Anjou Blanc — Promenade de Noëls</t>
         </is>
       </c>
       <c r="C139" s="12" t="inlineStr">
         <is>
-          <t>Blanc moelleux</t>
+          <t>Blanc</t>
         </is>
       </c>
       <c r="D139" s="12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E139" s="12" t="inlineStr">
@@ -3981,22 +4009,22 @@
     <row r="140">
       <c r="A140" s="11" t="inlineStr">
         <is>
-          <t>S14 V06</t>
+          <t>S14 V03</t>
         </is>
       </c>
       <c r="B140" s="12" t="inlineStr">
         <is>
-          <t>AOP Crémant de Loire — Crémant de Loire</t>
+          <t>AOC Sauvignon</t>
         </is>
       </c>
       <c r="C140" s="12" t="inlineStr">
         <is>
-          <t>Blanc brut</t>
+          <t>Blanc sec</t>
         </is>
       </c>
       <c r="D140" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E140" s="12" t="inlineStr">
@@ -4012,17 +4040,17 @@
     <row r="141">
       <c r="A141" s="11" t="inlineStr">
         <is>
-          <t>S14 V07</t>
+          <t>S14 V04</t>
         </is>
       </c>
       <c r="B141" s="12" t="inlineStr">
         <is>
-          <t>AOP Rosé de Loire — Rosé de Loire</t>
+          <t>AOC Coteaux du Layon</t>
         </is>
       </c>
       <c r="C141" s="12" t="inlineStr">
         <is>
-          <t>Rosé sec léger</t>
+          <t>Blanc moelleux</t>
         </is>
       </c>
       <c r="D141" s="12" t="inlineStr">
@@ -4040,159 +4068,167 @@
       <c r="H141" s="13" t="n"/>
       <c r="I141" s="13" t="n"/>
     </row>
-    <row r="143" ht="22" customHeight="1">
-      <c r="A143" s="5" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="11" t="inlineStr">
+        <is>
+          <t>S14 V05</t>
+        </is>
+      </c>
+      <c r="B142" s="12" t="inlineStr">
+        <is>
+          <t>AOC Coteaux du Layon Faye</t>
+        </is>
+      </c>
+      <c r="C142" s="12" t="inlineStr">
+        <is>
+          <t>Blanc moelleux</t>
+        </is>
+      </c>
+      <c r="D142" s="12" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E142" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
+      <c r="F142" s="13" t="n"/>
+      <c r="G142" s="13" t="n"/>
+      <c r="H142" s="13" t="n"/>
+      <c r="I142" s="13" t="n"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="11" t="inlineStr">
+        <is>
+          <t>S14 V06</t>
+        </is>
+      </c>
+      <c r="B143" s="12" t="inlineStr">
+        <is>
+          <t>AOC Crémant de Loire</t>
+        </is>
+      </c>
+      <c r="C143" s="12" t="inlineStr">
+        <is>
+          <t>Blanc brut</t>
+        </is>
+      </c>
+      <c r="D143" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E143" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
+      <c r="F143" s="13" t="n"/>
+      <c r="G143" s="13" t="n"/>
+      <c r="H143" s="13" t="n"/>
+      <c r="I143" s="13" t="n"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="11" t="inlineStr">
+        <is>
+          <t>S14 V07</t>
+        </is>
+      </c>
+      <c r="B144" s="12" t="inlineStr">
+        <is>
+          <t>AOC Rosé de Loire</t>
+        </is>
+      </c>
+      <c r="C144" s="12" t="inlineStr">
+        <is>
+          <t>Rosé sec léger</t>
+        </is>
+      </c>
+      <c r="D144" s="12" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E144" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
+      <c r="F144" s="13" t="n"/>
+      <c r="G144" s="13" t="n"/>
+      <c r="H144" s="13" t="n"/>
+      <c r="I144" s="13" t="n"/>
+    </row>
+    <row r="146" ht="22" customHeight="1">
+      <c r="A146" s="5" t="inlineStr">
         <is>
           <t>S15</t>
         </is>
       </c>
-      <c r="B143" s="6" t="inlineStr">
+      <c r="B146" s="6" t="inlineStr">
         <is>
           <t>Stand 15 — Champagne Vazart-Coquart (Champagne)</t>
         </is>
       </c>
-      <c r="C143" s="7" t="n"/>
-      <c r="D143" s="7" t="n"/>
-      <c r="E143" s="7" t="n"/>
-      <c r="F143" s="7" t="n"/>
-      <c r="G143" s="7" t="n"/>
-      <c r="H143" s="7" t="n"/>
-      <c r="I143" s="7" t="n"/>
-    </row>
-    <row r="144" ht="26" customHeight="1">
-      <c r="B144" s="8" t="inlineStr">
+      <c r="C146" s="7" t="n"/>
+      <c r="D146" s="7" t="n"/>
+      <c r="E146" s="7" t="n"/>
+      <c r="F146" s="7" t="n"/>
+      <c r="G146" s="7" t="n"/>
+      <c r="H146" s="7" t="n"/>
+      <c r="I146" s="7" t="n"/>
+    </row>
+    <row r="147" ht="26" customHeight="1">
+      <c r="B147" s="8" t="inlineStr">
         <is>
           <t>Vazart-Coquart &amp; Fils — paliers du tarif</t>
         </is>
       </c>
-      <c r="C144" s="9" t="n"/>
-      <c r="D144" s="9" t="n"/>
-      <c r="E144" s="9" t="n"/>
-      <c r="F144" s="8" t="inlineStr">
+      <c r="C147" s="9" t="n"/>
+      <c r="D147" s="9" t="n"/>
+      <c r="E147" s="9" t="n"/>
+      <c r="F147" s="8" t="inlineStr">
         <is>
           <t>Prix unique</t>
         </is>
       </c>
-      <c r="G144" s="10" t="inlineStr">
+      <c r="G147" s="10" t="inlineStr">
         <is>
           <t>À partir de 48 bts</t>
         </is>
       </c>
-      <c r="H144" s="10" t="inlineStr">
+      <c r="H147" s="10" t="inlineStr">
         <is>
           <t>À partir de 78 bts</t>
         </is>
       </c>
-      <c r="I144" s="10" t="inlineStr">
+      <c r="I147" s="10" t="inlineStr">
         <is>
           <t>À partir de 96 bts</t>
         </is>
       </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="11" t="inlineStr">
-        <is>
-          <t>S15 V01</t>
-        </is>
-      </c>
-      <c r="B145" s="12" t="inlineStr">
-        <is>
-          <t>AOP Champagne Grand Cru — Cuvée Camille</t>
-        </is>
-      </c>
-      <c r="C145" s="12" t="inlineStr">
-        <is>
-          <t>Blanc brut</t>
-        </is>
-      </c>
-      <c r="D145" s="12" t="inlineStr">
-        <is>
-          <t>Base 2023</t>
-        </is>
-      </c>
-      <c r="E145" s="12" t="inlineStr">
-        <is>
-          <t>75 cl</t>
-        </is>
-      </c>
-      <c r="F145" s="13" t="n"/>
-      <c r="G145" s="13" t="n"/>
-      <c r="H145" s="13" t="n"/>
-      <c r="I145" s="13" t="n"/>
-    </row>
-    <row r="146">
-      <c r="A146" s="11" t="inlineStr">
-        <is>
-          <t>S15 V02</t>
-        </is>
-      </c>
-      <c r="B146" s="12" t="inlineStr">
-        <is>
-          <t>AOP Champagne Grand Cru — Brut Réserve</t>
-        </is>
-      </c>
-      <c r="C146" s="12" t="inlineStr">
-        <is>
-          <t>Blanc de Blancs</t>
-        </is>
-      </c>
-      <c r="D146" s="12" t="inlineStr">
-        <is>
-          <t>Base 2022</t>
-        </is>
-      </c>
-      <c r="E146" s="12" t="inlineStr">
-        <is>
-          <t>75 cl</t>
-        </is>
-      </c>
-      <c r="F146" s="13" t="n"/>
-      <c r="G146" s="13" t="n"/>
-      <c r="H146" s="13" t="n"/>
-      <c r="I146" s="13" t="n"/>
-    </row>
-    <row r="147">
-      <c r="A147" s="11" t="inlineStr">
-        <is>
-          <t>S15 V03</t>
-        </is>
-      </c>
-      <c r="B147" s="12" t="inlineStr">
-        <is>
-          <t>Grand Cru Chouilly — Rosé Brut</t>
-        </is>
-      </c>
-      <c r="C147" s="12" t="inlineStr">
-        <is>
-          <t>Rosé brut</t>
-        </is>
-      </c>
-      <c r="D147" s="12" t="n"/>
-      <c r="E147" s="12" t="n"/>
-      <c r="F147" s="13" t="n"/>
-      <c r="G147" s="13" t="n"/>
-      <c r="H147" s="13" t="n"/>
-      <c r="I147" s="13" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="11" t="inlineStr">
         <is>
-          <t>S15 V04</t>
+          <t>S15 V01</t>
         </is>
       </c>
       <c r="B148" s="12" t="inlineStr">
         <is>
-          <t>AOP Champagne Grand Cru — Special Club</t>
+          <t>Grand Cru Chouilly — Cuvée Camille Extra-Brut Blanc de Blancs</t>
         </is>
       </c>
       <c r="C148" s="12" t="inlineStr">
         <is>
-          <t>Blanc de Blancs</t>
+          <t>Blanc brut</t>
         </is>
       </c>
       <c r="D148" s="12" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E148" s="12" t="inlineStr">
@@ -4208,12 +4244,12 @@
     <row r="149">
       <c r="A149" s="11" t="inlineStr">
         <is>
-          <t>S15 V05</t>
+          <t>S15 V02</t>
         </is>
       </c>
       <c r="B149" s="12" t="inlineStr">
         <is>
-          <t>AOP Champagne Grand Cru — Extra Brut</t>
+          <t>Grand Cru Chouilly — Brut Réserve Blanc de Blancs</t>
         </is>
       </c>
       <c r="C149" s="12" t="inlineStr">
@@ -4223,7 +4259,7 @@
       </c>
       <c r="D149" s="12" t="inlineStr">
         <is>
-          <t>Base 2020</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E149" s="12" t="inlineStr">
@@ -4239,297 +4275,309 @@
     <row r="150">
       <c r="A150" s="11" t="inlineStr">
         <is>
-          <t>S15 V06</t>
+          <t>S15 V03</t>
         </is>
       </c>
       <c r="B150" s="12" t="inlineStr">
         <is>
-          <t>Grand Cru Chouilly — 82/17 Blanc de Blancs Zéro Dosage</t>
+          <t>Grand Cru Chouilly — Rosé Brut</t>
         </is>
       </c>
       <c r="C150" s="12" t="inlineStr">
         <is>
-          <t>Blanc de Blancs, zéro dosage</t>
-        </is>
-      </c>
-      <c r="D150" s="12" t="n"/>
+          <t>Rosé effervescent</t>
+        </is>
+      </c>
+      <c r="D150" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="E150" s="12" t="n"/>
       <c r="F150" s="13" t="n"/>
       <c r="G150" s="13" t="n"/>
       <c r="H150" s="13" t="n"/>
       <c r="I150" s="13" t="n"/>
     </row>
-    <row r="152" ht="22" customHeight="1">
-      <c r="A152" s="5" t="inlineStr">
+    <row r="151">
+      <c r="A151" s="11" t="inlineStr">
+        <is>
+          <t>S15 V04</t>
+        </is>
+      </c>
+      <c r="B151" s="12" t="inlineStr">
+        <is>
+          <t>Grand Cru Chouilly — Spécial Club Blanc de Blancs Extra-Brut</t>
+        </is>
+      </c>
+      <c r="C151" s="12" t="inlineStr">
+        <is>
+          <t>Blanc de Blancs</t>
+        </is>
+      </c>
+      <c r="D151" s="12" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="E151" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
+      <c r="F151" s="13" t="n"/>
+      <c r="G151" s="13" t="n"/>
+      <c r="H151" s="13" t="n"/>
+      <c r="I151" s="13" t="n"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="11" t="inlineStr">
+        <is>
+          <t>S15 V05</t>
+        </is>
+      </c>
+      <c r="B152" s="12" t="inlineStr">
+        <is>
+          <t>Grand Cru Chouilly — Extra Brut</t>
+        </is>
+      </c>
+      <c r="C152" s="12" t="inlineStr">
+        <is>
+          <t>Blanc de Blancs</t>
+        </is>
+      </c>
+      <c r="D152" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E152" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
+      <c r="F152" s="13" t="n"/>
+      <c r="G152" s="13" t="n"/>
+      <c r="H152" s="13" t="n"/>
+      <c r="I152" s="13" t="n"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="11" t="inlineStr">
+        <is>
+          <t>S15 V06</t>
+        </is>
+      </c>
+      <c r="B153" s="12" t="inlineStr">
+        <is>
+          <t>Grand Cru Chouilly — 82/18 Blanc de Blancs Zéro Dosage</t>
+        </is>
+      </c>
+      <c r="C153" s="12" t="n"/>
+      <c r="D153" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E153" s="12" t="n"/>
+      <c r="F153" s="13" t="n"/>
+      <c r="G153" s="13" t="n"/>
+      <c r="H153" s="13" t="n"/>
+      <c r="I153" s="13" t="n"/>
+    </row>
+    <row r="155" ht="22" customHeight="1">
+      <c r="A155" s="5" t="inlineStr">
         <is>
           <t>S16</t>
         </is>
       </c>
-      <c r="B152" s="6" t="inlineStr">
+      <c r="B155" s="6" t="inlineStr">
         <is>
           <t>Stand 16 — Château Pré La Lande (Bordeaux)</t>
         </is>
       </c>
-      <c r="C152" s="7" t="n"/>
-      <c r="D152" s="7" t="n"/>
-      <c r="E152" s="7" t="n"/>
-      <c r="F152" s="7" t="n"/>
-      <c r="G152" s="7" t="n"/>
-      <c r="H152" s="7" t="n"/>
-      <c r="I152" s="7" t="n"/>
-    </row>
-    <row r="153" ht="26" customHeight="1">
-      <c r="B153" s="8" t="inlineStr">
+      <c r="C155" s="7" t="n"/>
+      <c r="D155" s="7" t="n"/>
+      <c r="E155" s="7" t="n"/>
+      <c r="F155" s="7" t="n"/>
+      <c r="G155" s="7" t="n"/>
+      <c r="H155" s="7" t="n"/>
+      <c r="I155" s="7" t="n"/>
+    </row>
+    <row r="156" ht="26" customHeight="1">
+      <c r="B156" s="8" t="inlineStr">
         <is>
           <t>Château Pré la Lande — paliers du tarif</t>
         </is>
       </c>
-      <c r="C153" s="9" t="n"/>
-      <c r="D153" s="9" t="n"/>
-      <c r="E153" s="9" t="n"/>
-      <c r="F153" s="8" t="inlineStr">
+      <c r="C156" s="9" t="n"/>
+      <c r="D156" s="9" t="n"/>
+      <c r="E156" s="9" t="n"/>
+      <c r="F156" s="8" t="inlineStr">
         <is>
           <t>Prix unique</t>
         </is>
       </c>
-      <c r="G153" s="10" t="inlineStr">
+      <c r="G156" s="10" t="inlineStr">
         <is>
           <t>Tarif</t>
         </is>
       </c>
-      <c r="H153" s="10" t="n"/>
-      <c r="I153" s="10" t="n"/>
-    </row>
-    <row r="154">
-      <c r="A154" s="11" t="inlineStr">
+      <c r="H156" s="10" t="n"/>
+      <c r="I156" s="10" t="n"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="11" t="inlineStr">
         <is>
           <t>S16 V01</t>
         </is>
       </c>
-      <c r="B154" s="12" t="inlineStr">
-        <is>
-          <t>AOP Sainte-Foy Côtes de Bordeaux — Cuvée Diane / Le Vin Cœur</t>
-        </is>
-      </c>
-      <c r="C154" s="12" t="inlineStr">
-        <is>
-          <t>Rouge</t>
-        </is>
-      </c>
-      <c r="D154" s="12" t="inlineStr">
+      <c r="B157" s="12" t="inlineStr">
+        <is>
+          <t>AOC Sainte-Foy Côtes de Bordeaux — Cuvée Diane Rouge</t>
+        </is>
+      </c>
+      <c r="C157" s="12" t="inlineStr">
+        <is>
+          <t>Rouge</t>
+        </is>
+      </c>
+      <c r="D157" s="12" t="inlineStr">
         <is>
           <t>2016</t>
         </is>
       </c>
-      <c r="E154" s="12" t="inlineStr">
-        <is>
-          <t>75 cl</t>
-        </is>
-      </c>
-      <c r="F154" s="13" t="n"/>
-      <c r="G154" s="13" t="n"/>
-      <c r="H154" s="14" t="n"/>
-      <c r="I154" s="14" t="n"/>
-    </row>
-    <row r="155">
-      <c r="A155" s="11" t="inlineStr">
+      <c r="E157" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
+      <c r="F157" s="13" t="n"/>
+      <c r="G157" s="13" t="n"/>
+      <c r="H157" s="14" t="n"/>
+      <c r="I157" s="14" t="n"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="11" t="inlineStr">
         <is>
           <t>S16 V02</t>
         </is>
       </c>
-      <c r="B155" s="12" t="inlineStr">
-        <is>
-          <t>AOP Sainte-Foy Côtes de Bordeaux — Cuvée TerraCotta / L'An Fort des Haltères</t>
-        </is>
-      </c>
-      <c r="C155" s="12" t="inlineStr">
-        <is>
-          <t>Rouge</t>
-        </is>
-      </c>
-      <c r="D155" s="12" t="inlineStr">
+      <c r="B158" s="12" t="inlineStr">
+        <is>
+          <t>AOC Sainte-Foy Côtes de Bordeaux — Cuvée TerraCotta</t>
+        </is>
+      </c>
+      <c r="C158" s="12" t="inlineStr">
+        <is>
+          <t>Rouge</t>
+        </is>
+      </c>
+      <c r="D158" s="12" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="E155" s="12" t="inlineStr">
-        <is>
-          <t>75 cl</t>
-        </is>
-      </c>
-      <c r="F155" s="13" t="n"/>
-      <c r="G155" s="13" t="n"/>
-      <c r="H155" s="14" t="n"/>
-      <c r="I155" s="14" t="n"/>
-    </row>
-    <row r="156">
-      <c r="A156" s="11" t="inlineStr">
+      <c r="E158" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
+      <c r="F158" s="13" t="n"/>
+      <c r="G158" s="13" t="n"/>
+      <c r="H158" s="14" t="n"/>
+      <c r="I158" s="14" t="n"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="11" t="inlineStr">
         <is>
           <t>S16 V03</t>
         </is>
       </c>
-      <c r="B156" s="12" t="inlineStr">
-        <is>
-          <t>AOP Sainte-Foy Côtes de Bordeaux — Cuvée des Fontenelles / Y'a Rien qui Presse</t>
-        </is>
-      </c>
-      <c r="C156" s="12" t="inlineStr">
-        <is>
-          <t>Rouge</t>
-        </is>
-      </c>
-      <c r="D156" s="12" t="inlineStr">
+      <c r="B159" s="12" t="inlineStr">
+        <is>
+          <t>AOC Sainte-Foy Côtes de Bordeaux — Cuvée des Fontenelles</t>
+        </is>
+      </c>
+      <c r="C159" s="12" t="inlineStr">
+        <is>
+          <t>Rouge</t>
+        </is>
+      </c>
+      <c r="D159" s="12" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E156" s="12" t="inlineStr">
-        <is>
-          <t>75 cl</t>
-        </is>
-      </c>
-      <c r="F156" s="13" t="n"/>
-      <c r="G156" s="13" t="n"/>
-      <c r="H156" s="14" t="n"/>
-      <c r="I156" s="14" t="n"/>
-    </row>
-    <row r="158" ht="22" customHeight="1">
-      <c r="A158" s="5" t="inlineStr">
+      <c r="E159" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
+      <c r="F159" s="13" t="n"/>
+      <c r="G159" s="13" t="n"/>
+      <c r="H159" s="14" t="n"/>
+      <c r="I159" s="14" t="n"/>
+    </row>
+    <row r="161" ht="22" customHeight="1">
+      <c r="A161" s="5" t="inlineStr">
         <is>
           <t>S17</t>
         </is>
       </c>
-      <c r="B158" s="6" t="inlineStr">
+      <c r="B161" s="6" t="inlineStr">
         <is>
           <t>Stand 17 — Vignobles Jean de Villebois (Loire)</t>
         </is>
       </c>
-      <c r="C158" s="7" t="n"/>
-      <c r="D158" s="7" t="n"/>
-      <c r="E158" s="7" t="n"/>
-      <c r="F158" s="7" t="n"/>
-      <c r="G158" s="7" t="n"/>
-      <c r="H158" s="7" t="n"/>
-      <c r="I158" s="7" t="n"/>
-    </row>
-    <row r="159" ht="26" customHeight="1">
-      <c r="B159" s="8" t="inlineStr">
+      <c r="C161" s="7" t="n"/>
+      <c r="D161" s="7" t="n"/>
+      <c r="E161" s="7" t="n"/>
+      <c r="F161" s="7" t="n"/>
+      <c r="G161" s="7" t="n"/>
+      <c r="H161" s="7" t="n"/>
+      <c r="I161" s="7" t="n"/>
+    </row>
+    <row r="162" ht="26" customHeight="1">
+      <c r="B162" s="8" t="inlineStr">
         <is>
           <t>Domaine Jean de Villebois — paliers du tarif</t>
         </is>
       </c>
-      <c r="C159" s="9" t="n"/>
-      <c r="D159" s="9" t="n"/>
-      <c r="E159" s="9" t="n"/>
-      <c r="F159" s="8" t="inlineStr">
+      <c r="C162" s="9" t="n"/>
+      <c r="D162" s="9" t="n"/>
+      <c r="E162" s="9" t="n"/>
+      <c r="F162" s="8" t="inlineStr">
         <is>
           <t>Prix unique</t>
         </is>
       </c>
-      <c r="G159" s="10" t="inlineStr">
+      <c r="G162" s="10" t="inlineStr">
         <is>
           <t>Tarif</t>
         </is>
       </c>
-      <c r="H159" s="10" t="n"/>
-      <c r="I159" s="10" t="n"/>
-    </row>
-    <row r="160">
-      <c r="A160" s="11" t="inlineStr">
-        <is>
-          <t>S17 V01</t>
-        </is>
-      </c>
-      <c r="B160" s="12" t="inlineStr">
-        <is>
-          <t>AOC Menetou-Salon</t>
-        </is>
-      </c>
-      <c r="C160" s="12" t="inlineStr">
-        <is>
-          <t>Rouge</t>
-        </is>
-      </c>
-      <c r="D160" s="12" t="n"/>
-      <c r="E160" s="12" t="n"/>
-      <c r="F160" s="13" t="n"/>
-      <c r="G160" s="13" t="n"/>
-      <c r="H160" s="14" t="n"/>
-      <c r="I160" s="14" t="n"/>
-    </row>
-    <row r="161">
-      <c r="A161" s="11" t="inlineStr">
-        <is>
-          <t>S17 V02</t>
-        </is>
-      </c>
-      <c r="B161" s="12" t="inlineStr">
-        <is>
-          <t>AOP Menetou-Salon</t>
-        </is>
-      </c>
-      <c r="C161" s="12" t="inlineStr">
-        <is>
-          <t>Blanc</t>
-        </is>
-      </c>
-      <c r="D161" s="12" t="inlineStr">
-        <is>
-          <t>2024/2025</t>
-        </is>
-      </c>
-      <c r="E161" s="12" t="n"/>
-      <c r="F161" s="13" t="n"/>
-      <c r="G161" s="13" t="n"/>
-      <c r="H161" s="14" t="n"/>
-      <c r="I161" s="14" t="n"/>
-    </row>
-    <row r="162">
-      <c r="A162" s="11" t="inlineStr">
-        <is>
-          <t>S17 V03</t>
-        </is>
-      </c>
-      <c r="B162" s="12" t="inlineStr">
-        <is>
-          <t>AOP Quincy</t>
-        </is>
-      </c>
-      <c r="C162" s="12" t="inlineStr">
-        <is>
-          <t>Blanc</t>
-        </is>
-      </c>
-      <c r="D162" s="12" t="inlineStr">
-        <is>
-          <t>2023/2024</t>
-        </is>
-      </c>
-      <c r="E162" s="12" t="n"/>
-      <c r="F162" s="13" t="n"/>
-      <c r="G162" s="13" t="n"/>
-      <c r="H162" s="14" t="n"/>
-      <c r="I162" s="14" t="n"/>
+      <c r="H162" s="10" t="n"/>
+      <c r="I162" s="10" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="11" t="inlineStr">
         <is>
-          <t>S17 V04</t>
+          <t>S17 V01</t>
         </is>
       </c>
       <c r="B163" s="12" t="inlineStr">
         <is>
-          <t>AOC Sancerre — Les Beltins</t>
+          <t>AOC Menetou-Salon Rouge</t>
         </is>
       </c>
       <c r="C163" s="12" t="inlineStr">
         <is>
-          <t>Blanc</t>
+          <t>Rouge</t>
         </is>
       </c>
       <c r="D163" s="12" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E163" s="12" t="n"/>
@@ -4541,12 +4589,12 @@
     <row r="164">
       <c r="A164" s="11" t="inlineStr">
         <is>
-          <t>S17 V05</t>
+          <t>S17 V02</t>
         </is>
       </c>
       <c r="B164" s="12" t="inlineStr">
         <is>
-          <t>AOP Sancerre — Chêne à la Rouline</t>
+          <t>AOC Menetou-Salon Blanc</t>
         </is>
       </c>
       <c r="C164" s="12" t="inlineStr">
@@ -4556,7 +4604,7 @@
       </c>
       <c r="D164" s="12" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E164" s="12" t="n"/>
@@ -4568,12 +4616,12 @@
     <row r="165">
       <c r="A165" s="11" t="inlineStr">
         <is>
-          <t>S17 V06</t>
+          <t>S17 V03</t>
         </is>
       </c>
       <c r="B165" s="12" t="inlineStr">
         <is>
-          <t>AOC Pouilly-Fumé — Vignes de Tréleau</t>
+          <t>AOC Quincy</t>
         </is>
       </c>
       <c r="C165" s="12" t="inlineStr">
@@ -4583,7 +4631,7 @@
       </c>
       <c r="D165" s="12" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E165" s="12" t="n"/>
@@ -4595,22 +4643,22 @@
     <row r="166">
       <c r="A166" s="11" t="inlineStr">
         <is>
-          <t>S17 V07</t>
+          <t>S17 V04</t>
         </is>
       </c>
       <c r="B166" s="12" t="inlineStr">
         <is>
-          <t>AOP Sancerre — La Louisonne</t>
+          <t>AOC Sancerre — Les Beltins Blanc</t>
         </is>
       </c>
       <c r="C166" s="12" t="inlineStr">
         <is>
-          <t>Rouge</t>
+          <t>Blanc</t>
         </is>
       </c>
       <c r="D166" s="12" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="E166" s="12" t="n"/>
@@ -4622,12 +4670,12 @@
     <row r="167">
       <c r="A167" s="11" t="inlineStr">
         <is>
-          <t>S17 V08</t>
+          <t>S17 V05</t>
         </is>
       </c>
       <c r="B167" s="12" t="inlineStr">
         <is>
-          <t>AOP Pouilly-Fumé</t>
+          <t>AOC Sancerre — Chêne à la rouline Blanc</t>
         </is>
       </c>
       <c r="C167" s="12" t="inlineStr">
@@ -4637,7 +4685,7 @@
       </c>
       <c r="D167" s="12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="E167" s="12" t="n"/>
@@ -4649,12 +4697,12 @@
     <row r="168">
       <c r="A168" s="11" t="inlineStr">
         <is>
-          <t>S17 V09</t>
+          <t>S17 V06</t>
         </is>
       </c>
       <c r="B168" s="12" t="inlineStr">
         <is>
-          <t>AOP Touraine Chenonceaux</t>
+          <t>AOC Pouilly-Fumé — Vignes de Tréleau Blanc</t>
         </is>
       </c>
       <c r="C168" s="12" t="inlineStr">
@@ -4664,7 +4712,7 @@
       </c>
       <c r="D168" s="12" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="E168" s="12" t="n"/>
@@ -4676,22 +4724,22 @@
     <row r="169">
       <c r="A169" s="11" t="inlineStr">
         <is>
-          <t>S17 V10</t>
+          <t>S17 V07</t>
         </is>
       </c>
       <c r="B169" s="12" t="inlineStr">
         <is>
-          <t>IGP Val de Loire Sauvignon</t>
+          <t>AOC Sancerre — La Louisonne Rouge</t>
         </is>
       </c>
       <c r="C169" s="12" t="inlineStr">
         <is>
-          <t>Blanc</t>
+          <t>Rouge</t>
         </is>
       </c>
       <c r="D169" s="12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="E169" s="12" t="n"/>
@@ -4703,22 +4751,22 @@
     <row r="170">
       <c r="A170" s="11" t="inlineStr">
         <is>
-          <t>S17 V11</t>
+          <t>S17 V08</t>
         </is>
       </c>
       <c r="B170" s="12" t="inlineStr">
         <is>
-          <t>Vin de France Pinot Noir</t>
+          <t>AOC Pouilly-Fumé</t>
         </is>
       </c>
       <c r="C170" s="12" t="inlineStr">
         <is>
-          <t>Rosé</t>
+          <t>Blanc</t>
         </is>
       </c>
       <c r="D170" s="12" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E170" s="12" t="n"/>
@@ -4730,22 +4778,22 @@
     <row r="171">
       <c r="A171" s="11" t="inlineStr">
         <is>
-          <t>S17 V12</t>
+          <t>S17 V09</t>
         </is>
       </c>
       <c r="B171" s="12" t="inlineStr">
         <is>
-          <t>Vin de France Pinot Noir</t>
+          <t>AOC Touraine Chenonceaux</t>
         </is>
       </c>
       <c r="C171" s="12" t="inlineStr">
         <is>
-          <t>Rouge</t>
+          <t>Blanc</t>
         </is>
       </c>
       <c r="D171" s="12" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E171" s="12" t="n"/>
@@ -4754,155 +4802,147 @@
       <c r="H171" s="14" t="n"/>
       <c r="I171" s="14" t="n"/>
     </row>
-    <row r="173" ht="22" customHeight="1">
-      <c r="A173" s="5" t="inlineStr">
+    <row r="172">
+      <c r="A172" s="11" t="inlineStr">
+        <is>
+          <t>S17 V10</t>
+        </is>
+      </c>
+      <c r="B172" s="12" t="inlineStr">
+        <is>
+          <t>AOC Sauvignon Blanc</t>
+        </is>
+      </c>
+      <c r="C172" s="12" t="inlineStr">
+        <is>
+          <t>Blanc</t>
+        </is>
+      </c>
+      <c r="D172" s="12" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E172" s="12" t="n"/>
+      <c r="F172" s="13" t="n"/>
+      <c r="G172" s="13" t="n"/>
+      <c r="H172" s="14" t="n"/>
+      <c r="I172" s="14" t="n"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="11" t="inlineStr">
+        <is>
+          <t>S17 V11</t>
+        </is>
+      </c>
+      <c r="B173" s="12" t="inlineStr">
+        <is>
+          <t>AOC Pinot Noir Rosé</t>
+        </is>
+      </c>
+      <c r="C173" s="12" t="inlineStr">
+        <is>
+          <t>Rosé</t>
+        </is>
+      </c>
+      <c r="D173" s="12" t="inlineStr">
+        <is>
+          <t>2024/25</t>
+        </is>
+      </c>
+      <c r="E173" s="12" t="n"/>
+      <c r="F173" s="13" t="n"/>
+      <c r="G173" s="13" t="n"/>
+      <c r="H173" s="14" t="n"/>
+      <c r="I173" s="14" t="n"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="11" t="inlineStr">
+        <is>
+          <t>S17 V12</t>
+        </is>
+      </c>
+      <c r="B174" s="12" t="inlineStr">
+        <is>
+          <t>AOC Pinot Noir</t>
+        </is>
+      </c>
+      <c r="C174" s="12" t="inlineStr">
+        <is>
+          <t>Rouge</t>
+        </is>
+      </c>
+      <c r="D174" s="12" t="inlineStr">
+        <is>
+          <t>2024/25</t>
+        </is>
+      </c>
+      <c r="E174" s="12" t="n"/>
+      <c r="F174" s="13" t="n"/>
+      <c r="G174" s="13" t="n"/>
+      <c r="H174" s="14" t="n"/>
+      <c r="I174" s="14" t="n"/>
+    </row>
+    <row r="176" ht="22" customHeight="1">
+      <c r="A176" s="5" t="inlineStr">
         <is>
           <t>S18</t>
         </is>
       </c>
-      <c r="B173" s="6" t="inlineStr">
+      <c r="B176" s="6" t="inlineStr">
         <is>
           <t>Stand 18 — Domaine Sébastien Magnien (Bourgogne)</t>
         </is>
       </c>
-      <c r="C173" s="7" t="n"/>
-      <c r="D173" s="7" t="n"/>
-      <c r="E173" s="7" t="n"/>
-      <c r="F173" s="7" t="n"/>
-      <c r="G173" s="7" t="n"/>
-      <c r="H173" s="7" t="n"/>
-      <c r="I173" s="7" t="n"/>
-    </row>
-    <row r="174" ht="26" customHeight="1">
-      <c r="B174" s="8" t="inlineStr">
+      <c r="C176" s="7" t="n"/>
+      <c r="D176" s="7" t="n"/>
+      <c r="E176" s="7" t="n"/>
+      <c r="F176" s="7" t="n"/>
+      <c r="G176" s="7" t="n"/>
+      <c r="H176" s="7" t="n"/>
+      <c r="I176" s="7" t="n"/>
+    </row>
+    <row r="177" ht="26" customHeight="1">
+      <c r="B177" s="8" t="inlineStr">
         <is>
           <t>Domaine Sébastien Magnien — paliers du tarif</t>
         </is>
       </c>
-      <c r="C174" s="9" t="n"/>
-      <c r="D174" s="9" t="n"/>
-      <c r="E174" s="9" t="n"/>
-      <c r="F174" s="8" t="inlineStr">
+      <c r="C177" s="9" t="n"/>
+      <c r="D177" s="9" t="n"/>
+      <c r="E177" s="9" t="n"/>
+      <c r="F177" s="8" t="inlineStr">
         <is>
           <t>Prix unique</t>
         </is>
       </c>
-      <c r="G174" s="10" t="inlineStr">
+      <c r="G177" s="10" t="inlineStr">
         <is>
           <t>Tarif</t>
         </is>
       </c>
-      <c r="H174" s="10" t="n"/>
-      <c r="I174" s="10" t="n"/>
-    </row>
-    <row r="175">
-      <c r="A175" s="11" t="inlineStr">
-        <is>
-          <t>S18 V01</t>
-        </is>
-      </c>
-      <c r="B175" s="12" t="inlineStr">
-        <is>
-          <t>AOP Hautes-Côtes de Beaune — Hautes-Côtes</t>
-        </is>
-      </c>
-      <c r="C175" s="12" t="inlineStr">
-        <is>
-          <t>Blanc</t>
-        </is>
-      </c>
-      <c r="D175" s="12" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="E175" s="12" t="inlineStr">
-        <is>
-          <t>75 cl</t>
-        </is>
-      </c>
-      <c r="F175" s="13" t="n"/>
-      <c r="G175" s="13" t="n"/>
-      <c r="H175" s="14" t="n"/>
-      <c r="I175" s="14" t="n"/>
-    </row>
-    <row r="176">
-      <c r="A176" s="11" t="inlineStr">
-        <is>
-          <t>S18 V02</t>
-        </is>
-      </c>
-      <c r="B176" s="12" t="inlineStr">
-        <is>
-          <t>AOC Meursault</t>
-        </is>
-      </c>
-      <c r="C176" s="12" t="inlineStr">
-        <is>
-          <t>Blanc</t>
-        </is>
-      </c>
-      <c r="D176" s="12" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="E176" s="12" t="n"/>
-      <c r="F176" s="13" t="n"/>
-      <c r="G176" s="13" t="n"/>
-      <c r="H176" s="14" t="n"/>
-      <c r="I176" s="14" t="n"/>
-    </row>
-    <row r="177">
-      <c r="A177" s="11" t="inlineStr">
-        <is>
-          <t>S18 V03</t>
-        </is>
-      </c>
-      <c r="B177" s="12" t="inlineStr">
-        <is>
-          <t>AOP Hautes-Côtes de Beaune — Clos de la Perrière</t>
-        </is>
-      </c>
-      <c r="C177" s="12" t="inlineStr">
-        <is>
-          <t>Rouge</t>
-        </is>
-      </c>
-      <c r="D177" s="12" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E177" s="12" t="inlineStr">
-        <is>
-          <t>75 cl</t>
-        </is>
-      </c>
-      <c r="F177" s="13" t="n"/>
-      <c r="G177" s="13" t="n"/>
-      <c r="H177" s="14" t="n"/>
-      <c r="I177" s="14" t="n"/>
+      <c r="H177" s="10" t="n"/>
+      <c r="I177" s="10" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="11" t="inlineStr">
         <is>
-          <t>S18 V04</t>
+          <t>S18 V01</t>
         </is>
       </c>
       <c r="B178" s="12" t="inlineStr">
         <is>
-          <t>AOP Beaune — Les Bons Feuvres</t>
+          <t>AOC Hautes-Côtes de Beaune</t>
         </is>
       </c>
       <c r="C178" s="12" t="inlineStr">
         <is>
-          <t>Rouge</t>
+          <t>Blanc</t>
         </is>
       </c>
       <c r="D178" s="12" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E178" s="12" t="inlineStr">
@@ -4918,17 +4958,17 @@
     <row r="179">
       <c r="A179" s="11" t="inlineStr">
         <is>
-          <t>S18 V05</t>
+          <t>S18 V02</t>
         </is>
       </c>
       <c r="B179" s="12" t="inlineStr">
         <is>
-          <t>AOP Beaune 1er Cru — Les Aigrots</t>
+          <t>AOC Meursault</t>
         </is>
       </c>
       <c r="C179" s="12" t="inlineStr">
         <is>
-          <t>Rouge</t>
+          <t>Blanc</t>
         </is>
       </c>
       <c r="D179" s="12" t="inlineStr">
@@ -4936,11 +4976,7 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="E179" s="12" t="inlineStr">
-        <is>
-          <t>75 cl</t>
-        </is>
-      </c>
+      <c r="E179" s="12" t="n"/>
       <c r="F179" s="13" t="n"/>
       <c r="G179" s="13" t="n"/>
       <c r="H179" s="14" t="n"/>
@@ -4949,92 +4985,132 @@
     <row r="180">
       <c r="A180" s="11" t="inlineStr">
         <is>
-          <t>S18 V06</t>
+          <t>S18 V03</t>
         </is>
       </c>
       <c r="B180" s="12" t="inlineStr">
         <is>
-          <t>AOP Pommard — Les Perrières</t>
+          <t>Beaune 1er Cru — Les Aigrots</t>
         </is>
       </c>
       <c r="C180" s="12" t="inlineStr">
         <is>
-          <t>Rouge</t>
+          <t>Blanc</t>
         </is>
       </c>
       <c r="D180" s="12" t="inlineStr">
         <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="E180" s="12" t="inlineStr">
-        <is>
-          <t>75 cl</t>
-        </is>
-      </c>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E180" s="12" t="n"/>
       <c r="F180" s="13" t="n"/>
       <c r="G180" s="13" t="n"/>
       <c r="H180" s="14" t="n"/>
       <c r="I180" s="14" t="n"/>
     </row>
-    <row r="182" ht="22" customHeight="1">
-      <c r="A182" s="5" t="inlineStr">
-        <is>
-          <t>S19</t>
-        </is>
-      </c>
-      <c r="B182" s="6" t="inlineStr">
-        <is>
-          <t>Stand 19 — Bastide de Blacailloux (Provence)</t>
-        </is>
-      </c>
-      <c r="C182" s="7" t="n"/>
-      <c r="D182" s="7" t="n"/>
-      <c r="E182" s="7" t="n"/>
-      <c r="F182" s="7" t="n"/>
-      <c r="G182" s="7" t="n"/>
-      <c r="H182" s="7" t="n"/>
-      <c r="I182" s="7" t="n"/>
-    </row>
-    <row r="183" ht="26" customHeight="1">
-      <c r="B183" s="8" t="inlineStr">
-        <is>
-          <t>Bastide de Blacailloux — paliers du tarif</t>
-        </is>
-      </c>
-      <c r="C183" s="9" t="n"/>
-      <c r="D183" s="9" t="n"/>
-      <c r="E183" s="9" t="n"/>
-      <c r="F183" s="8" t="inlineStr">
-        <is>
-          <t>Prix unique</t>
-        </is>
-      </c>
-      <c r="G183" s="10" t="inlineStr">
-        <is>
-          <t>À partir de 60 bts</t>
-        </is>
-      </c>
-      <c r="H183" s="10" t="inlineStr">
-        <is>
-          <t>À partir de 120 bts</t>
-        </is>
-      </c>
-      <c r="I183" s="10" t="inlineStr">
-        <is>
-          <t>À partir de 180 bts</t>
-        </is>
-      </c>
+    <row r="181">
+      <c r="A181" s="11" t="inlineStr">
+        <is>
+          <t>S18 V04</t>
+        </is>
+      </c>
+      <c r="B181" s="12" t="inlineStr">
+        <is>
+          <t>AOC Hautes-Côtes de Beaune — Clos de la Perrière</t>
+        </is>
+      </c>
+      <c r="C181" s="12" t="inlineStr">
+        <is>
+          <t>Rouge</t>
+        </is>
+      </c>
+      <c r="D181" s="12" t="inlineStr">
+        <is>
+          <t>2023/24</t>
+        </is>
+      </c>
+      <c r="E181" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
+      <c r="F181" s="13" t="n"/>
+      <c r="G181" s="13" t="n"/>
+      <c r="H181" s="14" t="n"/>
+      <c r="I181" s="14" t="n"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="11" t="inlineStr">
+        <is>
+          <t>S18 V05</t>
+        </is>
+      </c>
+      <c r="B182" s="12" t="inlineStr">
+        <is>
+          <t>AOC Beaune — Les Bons Feuvres</t>
+        </is>
+      </c>
+      <c r="C182" s="12" t="inlineStr">
+        <is>
+          <t>Rouge</t>
+        </is>
+      </c>
+      <c r="D182" s="12" t="inlineStr">
+        <is>
+          <t>2023/24</t>
+        </is>
+      </c>
+      <c r="E182" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
+      <c r="F182" s="13" t="n"/>
+      <c r="G182" s="13" t="n"/>
+      <c r="H182" s="14" t="n"/>
+      <c r="I182" s="14" t="n"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="11" t="inlineStr">
+        <is>
+          <t>S18 V06</t>
+        </is>
+      </c>
+      <c r="B183" s="12" t="inlineStr">
+        <is>
+          <t>Beaune 1er Cru — Les Aigrots</t>
+        </is>
+      </c>
+      <c r="C183" s="12" t="inlineStr">
+        <is>
+          <t>Rouge</t>
+        </is>
+      </c>
+      <c r="D183" s="12" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="E183" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
+      <c r="F183" s="13" t="n"/>
+      <c r="G183" s="13" t="n"/>
+      <c r="H183" s="14" t="n"/>
+      <c r="I183" s="14" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="11" t="inlineStr">
         <is>
-          <t>S19 V01</t>
+          <t>S18 V07</t>
         </is>
       </c>
       <c r="B184" s="12" t="inlineStr">
         <is>
-          <t>IGP Var Sainte Baume — SAINT PROBACE</t>
+          <t>AOC Pommard — Les Perrières</t>
         </is>
       </c>
       <c r="C184" s="12" t="inlineStr">
@@ -5044,130 +5120,94 @@
       </c>
       <c r="D184" s="12" t="inlineStr">
         <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E184" s="12" t="n"/>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="E184" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
       <c r="F184" s="13" t="n"/>
       <c r="G184" s="13" t="n"/>
-      <c r="H184" s="13" t="n"/>
-      <c r="I184" s="13" t="n"/>
-    </row>
-    <row r="185">
-      <c r="A185" s="11" t="inlineStr">
-        <is>
-          <t>S19 V02</t>
-        </is>
-      </c>
-      <c r="B185" s="12" t="inlineStr">
-        <is>
-          <t>AOP Coteaux Varois en Provence — JOIO</t>
-        </is>
-      </c>
-      <c r="C185" s="12" t="inlineStr">
-        <is>
-          <t>Rosé</t>
-        </is>
-      </c>
-      <c r="D185" s="12" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E185" s="12" t="inlineStr">
-        <is>
-          <t>75 cl</t>
-        </is>
-      </c>
-      <c r="F185" s="13" t="n"/>
-      <c r="G185" s="13" t="n"/>
-      <c r="H185" s="13" t="n"/>
-      <c r="I185" s="13" t="n"/>
-    </row>
-    <row r="186">
-      <c r="A186" s="11" t="inlineStr">
-        <is>
-          <t>S19 V03</t>
-        </is>
-      </c>
-      <c r="B186" s="12" t="inlineStr">
-        <is>
-          <t>AOP Coteaux Varois en Provence — JOIO</t>
-        </is>
-      </c>
-      <c r="C186" s="12" t="inlineStr">
-        <is>
-          <t>Blanc</t>
-        </is>
-      </c>
-      <c r="D186" s="12" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E186" s="12" t="inlineStr">
-        <is>
-          <t>75 cl</t>
-        </is>
-      </c>
-      <c r="F186" s="13" t="n"/>
-      <c r="G186" s="13" t="n"/>
-      <c r="H186" s="13" t="n"/>
-      <c r="I186" s="13" t="n"/>
-    </row>
-    <row r="187">
-      <c r="A187" s="11" t="inlineStr">
-        <is>
-          <t>S19 V04</t>
-        </is>
-      </c>
-      <c r="B187" s="12" t="inlineStr">
-        <is>
-          <t>AOP Coteaux Varois en Provence — JOIO</t>
-        </is>
-      </c>
-      <c r="C187" s="12" t="inlineStr">
-        <is>
-          <t>Rouge</t>
-        </is>
-      </c>
-      <c r="D187" s="12" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="E187" s="12" t="inlineStr">
-        <is>
-          <t>75 cl</t>
-        </is>
-      </c>
-      <c r="F187" s="13" t="n"/>
-      <c r="G187" s="13" t="n"/>
-      <c r="H187" s="13" t="n"/>
-      <c r="I187" s="13" t="n"/>
+      <c r="H184" s="14" t="n"/>
+      <c r="I184" s="14" t="n"/>
+    </row>
+    <row r="186" ht="22" customHeight="1">
+      <c r="A186" s="5" t="inlineStr">
+        <is>
+          <t>S19</t>
+        </is>
+      </c>
+      <c r="B186" s="6" t="inlineStr">
+        <is>
+          <t>Stand 19 — Bastide de Blacailloux (Provence)</t>
+        </is>
+      </c>
+      <c r="C186" s="7" t="n"/>
+      <c r="D186" s="7" t="n"/>
+      <c r="E186" s="7" t="n"/>
+      <c r="F186" s="7" t="n"/>
+      <c r="G186" s="7" t="n"/>
+      <c r="H186" s="7" t="n"/>
+      <c r="I186" s="7" t="n"/>
+    </row>
+    <row r="187" ht="26" customHeight="1">
+      <c r="B187" s="8" t="inlineStr">
+        <is>
+          <t>Bastide de Blacailloux — paliers du tarif</t>
+        </is>
+      </c>
+      <c r="C187" s="9" t="n"/>
+      <c r="D187" s="9" t="n"/>
+      <c r="E187" s="9" t="n"/>
+      <c r="F187" s="8" t="inlineStr">
+        <is>
+          <t>Prix unique</t>
+        </is>
+      </c>
+      <c r="G187" s="10" t="inlineStr">
+        <is>
+          <t>À partir de 60 bts</t>
+        </is>
+      </c>
+      <c r="H187" s="10" t="inlineStr">
+        <is>
+          <t>À partir de 120 bts</t>
+        </is>
+      </c>
+      <c r="I187" s="10" t="inlineStr">
+        <is>
+          <t>À partir de 180 bts</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="11" t="inlineStr">
         <is>
-          <t>S19 V05</t>
+          <t>S19 V01</t>
         </is>
       </c>
       <c r="B188" s="12" t="inlineStr">
         <is>
-          <t>AOC Coteaux Varois en Provence — Miraia</t>
+          <t>IGP Var Sainte Baume — St Probace Rosé</t>
         </is>
       </c>
       <c r="C188" s="12" t="inlineStr">
         <is>
-          <t>Blanc</t>
+          <t>Rosé</t>
         </is>
       </c>
       <c r="D188" s="12" t="inlineStr">
         <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="E188" s="12" t="n"/>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E188" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
       <c r="F188" s="13" t="n"/>
       <c r="G188" s="13" t="n"/>
       <c r="H188" s="13" t="n"/>
@@ -5176,25 +5216,29 @@
     <row r="189">
       <c r="A189" s="11" t="inlineStr">
         <is>
-          <t>S19 V06</t>
+          <t>S19 V02</t>
         </is>
       </c>
       <c r="B189" s="12" t="inlineStr">
         <is>
-          <t>AOC Coteaux Varois en Provence — Miraia</t>
+          <t>IGP Var Sainte Baume — St Probace Blanc</t>
         </is>
       </c>
       <c r="C189" s="12" t="inlineStr">
         <is>
-          <t>Rouge</t>
+          <t>Blanc</t>
         </is>
       </c>
       <c r="D189" s="12" t="inlineStr">
         <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="E189" s="12" t="n"/>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E189" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
       <c r="F189" s="13" t="n"/>
       <c r="G189" s="13" t="n"/>
       <c r="H189" s="13" t="n"/>
@@ -5203,12 +5247,12 @@
     <row r="190">
       <c r="A190" s="11" t="inlineStr">
         <is>
-          <t>S19 V07</t>
+          <t>S19 V03</t>
         </is>
       </c>
       <c r="B190" s="12" t="inlineStr">
         <is>
-          <t>AOC Coteaux Varois en Provence — Aquino</t>
+          <t>IGP Var Sainte Baume — St Probace Rouge</t>
         </is>
       </c>
       <c r="C190" s="12" t="inlineStr">
@@ -5218,7 +5262,7 @@
       </c>
       <c r="D190" s="12" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E190" s="12" t="n"/>
@@ -5230,88 +5274,132 @@
     <row r="191">
       <c r="A191" s="11" t="inlineStr">
         <is>
-          <t>S19 V08</t>
+          <t>S19 V04</t>
         </is>
       </c>
       <c r="B191" s="12" t="inlineStr">
         <is>
-          <t>AOC Coteaux Varois en Provence — Aquino</t>
+          <t>AOC Coteaux Varois en Provence — Joio Rosé</t>
         </is>
       </c>
       <c r="C191" s="12" t="inlineStr">
         <is>
-          <t>Blanc</t>
+          <t>Rosé</t>
         </is>
       </c>
       <c r="D191" s="12" t="inlineStr">
         <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="E191" s="12" t="n"/>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E191" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
       <c r="F191" s="13" t="n"/>
       <c r="G191" s="13" t="n"/>
       <c r="H191" s="13" t="n"/>
       <c r="I191" s="13" t="n"/>
     </row>
-    <row r="193" ht="22" customHeight="1">
-      <c r="A193" s="5" t="inlineStr">
-        <is>
-          <t>S20</t>
-        </is>
-      </c>
-      <c r="B193" s="6" t="inlineStr">
-        <is>
-          <t>Stand 20 — Domaine Stratéus (Sud-Ouest)</t>
-        </is>
-      </c>
-      <c r="C193" s="7" t="n"/>
-      <c r="D193" s="7" t="n"/>
-      <c r="E193" s="7" t="n"/>
-      <c r="F193" s="7" t="n"/>
-      <c r="G193" s="7" t="n"/>
-      <c r="H193" s="7" t="n"/>
-      <c r="I193" s="7" t="n"/>
-    </row>
-    <row r="194" ht="26" customHeight="1">
-      <c r="B194" s="8" t="inlineStr">
-        <is>
-          <t>Domaine Stratéus — paliers du tarif</t>
-        </is>
-      </c>
-      <c r="C194" s="9" t="n"/>
-      <c r="D194" s="9" t="n"/>
-      <c r="E194" s="9" t="n"/>
-      <c r="F194" s="8" t="inlineStr">
-        <is>
-          <t>Prix unique</t>
-        </is>
-      </c>
-      <c r="G194" s="10" t="inlineStr">
-        <is>
-          <t>À partir de 36 bts</t>
-        </is>
-      </c>
-      <c r="H194" s="10" t="inlineStr">
-        <is>
-          <t>À partir de 60 bts</t>
-        </is>
-      </c>
-      <c r="I194" s="10" t="inlineStr">
-        <is>
-          <t>À partir de 120 bts</t>
-        </is>
-      </c>
+    <row r="192">
+      <c r="A192" s="11" t="inlineStr">
+        <is>
+          <t>S19 V05</t>
+        </is>
+      </c>
+      <c r="B192" s="12" t="inlineStr">
+        <is>
+          <t>AOC Coteaux Varois en Provence — Joio Blanc</t>
+        </is>
+      </c>
+      <c r="C192" s="12" t="inlineStr">
+        <is>
+          <t>Blanc</t>
+        </is>
+      </c>
+      <c r="D192" s="12" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E192" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
+      <c r="F192" s="13" t="n"/>
+      <c r="G192" s="13" t="n"/>
+      <c r="H192" s="13" t="n"/>
+      <c r="I192" s="13" t="n"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="11" t="inlineStr">
+        <is>
+          <t>S19 V06</t>
+        </is>
+      </c>
+      <c r="B193" s="12" t="inlineStr">
+        <is>
+          <t>AOC Coteaux Varois en Provence — Joio Rouge</t>
+        </is>
+      </c>
+      <c r="C193" s="12" t="inlineStr">
+        <is>
+          <t>Rouge</t>
+        </is>
+      </c>
+      <c r="D193" s="12" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="E193" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
+      <c r="F193" s="13" t="n"/>
+      <c r="G193" s="13" t="n"/>
+      <c r="H193" s="13" t="n"/>
+      <c r="I193" s="13" t="n"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="11" t="inlineStr">
+        <is>
+          <t>S19 V07</t>
+        </is>
+      </c>
+      <c r="B194" s="12" t="inlineStr">
+        <is>
+          <t>AOC Coteaux Varois en Provence — Miraia Blanc</t>
+        </is>
+      </c>
+      <c r="C194" s="12" t="inlineStr">
+        <is>
+          <t>Blanc</t>
+        </is>
+      </c>
+      <c r="D194" s="12" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="E194" s="12" t="n"/>
+      <c r="F194" s="13" t="n"/>
+      <c r="G194" s="13" t="n"/>
+      <c r="H194" s="13" t="n"/>
+      <c r="I194" s="13" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="11" t="inlineStr">
         <is>
-          <t>S20 V01</t>
+          <t>S19 V08</t>
         </is>
       </c>
       <c r="B195" s="12" t="inlineStr">
         <is>
-          <t>AOP Madiran — Strateus</t>
+          <t>AOC Coteaux Varois en Provence — Miraia Rouge</t>
         </is>
       </c>
       <c r="C195" s="12" t="inlineStr">
@@ -5321,14 +5409,10 @@
       </c>
       <c r="D195" s="12" t="inlineStr">
         <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="E195" s="12" t="inlineStr">
-        <is>
-          <t>75 cl</t>
-        </is>
-      </c>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="E195" s="12" t="n"/>
       <c r="F195" s="13" t="n"/>
       <c r="G195" s="13" t="n"/>
       <c r="H195" s="13" t="n"/>
@@ -5337,12 +5421,12 @@
     <row r="196">
       <c r="A196" s="11" t="inlineStr">
         <is>
-          <t>S20 V02</t>
+          <t>S19 V09</t>
         </is>
       </c>
       <c r="B196" s="12" t="inlineStr">
         <is>
-          <t>AOP Madiran — Néolitik</t>
+          <t>AOC Coteaux Varois en Provence — Aquino Rouge</t>
         </is>
       </c>
       <c r="C196" s="12" t="inlineStr">
@@ -5352,14 +5436,10 @@
       </c>
       <c r="D196" s="12" t="inlineStr">
         <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="E196" s="12" t="inlineStr">
-        <is>
-          <t>75 cl</t>
-        </is>
-      </c>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E196" s="12" t="n"/>
       <c r="F196" s="13" t="n"/>
       <c r="G196" s="13" t="n"/>
       <c r="H196" s="13" t="n"/>
@@ -5368,194 +5448,194 @@
     <row r="197">
       <c r="A197" s="11" t="inlineStr">
         <is>
-          <t>S20 V03</t>
+          <t>S19 V10</t>
         </is>
       </c>
       <c r="B197" s="12" t="inlineStr">
         <is>
-          <t>AOP Madiran — Koloss</t>
+          <t>AOC Coteaux Varois en Provence — Aquino Blanc</t>
         </is>
       </c>
       <c r="C197" s="12" t="inlineStr">
         <is>
-          <t>Rouge</t>
+          <t>Blanc</t>
         </is>
       </c>
       <c r="D197" s="12" t="inlineStr">
         <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="E197" s="12" t="inlineStr">
-        <is>
-          <t>75 cl</t>
-        </is>
-      </c>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="E197" s="12" t="n"/>
       <c r="F197" s="13" t="n"/>
       <c r="G197" s="13" t="n"/>
       <c r="H197" s="13" t="n"/>
       <c r="I197" s="13" t="n"/>
     </row>
-    <row r="198">
-      <c r="A198" s="11" t="inlineStr">
-        <is>
-          <t>S20 V04</t>
-        </is>
-      </c>
-      <c r="B198" s="12" t="inlineStr">
-        <is>
-          <t>Vin de France — Koloss</t>
-        </is>
-      </c>
-      <c r="C198" s="12" t="inlineStr">
-        <is>
-          <t>Doux</t>
-        </is>
-      </c>
-      <c r="D198" s="12" t="inlineStr">
+    <row r="199" ht="22" customHeight="1">
+      <c r="A199" s="5" t="inlineStr">
+        <is>
+          <t>S20</t>
+        </is>
+      </c>
+      <c r="B199" s="6" t="inlineStr">
+        <is>
+          <t>Stand 20 — Domaine Stratéus (Sud-Ouest)</t>
+        </is>
+      </c>
+      <c r="C199" s="7" t="n"/>
+      <c r="D199" s="7" t="n"/>
+      <c r="E199" s="7" t="n"/>
+      <c r="F199" s="7" t="n"/>
+      <c r="G199" s="7" t="n"/>
+      <c r="H199" s="7" t="n"/>
+      <c r="I199" s="7" t="n"/>
+    </row>
+    <row r="200" ht="26" customHeight="1">
+      <c r="B200" s="8" t="inlineStr">
+        <is>
+          <t>Domaine Stratéus — paliers du tarif</t>
+        </is>
+      </c>
+      <c r="C200" s="9" t="n"/>
+      <c r="D200" s="9" t="n"/>
+      <c r="E200" s="9" t="n"/>
+      <c r="F200" s="8" t="inlineStr">
+        <is>
+          <t>Prix unique</t>
+        </is>
+      </c>
+      <c r="G200" s="10" t="inlineStr">
+        <is>
+          <t>À partir de 36 bts</t>
+        </is>
+      </c>
+      <c r="H200" s="10" t="inlineStr">
+        <is>
+          <t>À partir de 60 bts</t>
+        </is>
+      </c>
+      <c r="I200" s="10" t="inlineStr">
+        <is>
+          <t>À partir de 120 bts</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="11" t="inlineStr">
+        <is>
+          <t>S20 V01</t>
+        </is>
+      </c>
+      <c r="B201" s="12" t="inlineStr">
+        <is>
+          <t>AOC Madiran — Stratéus Rouge</t>
+        </is>
+      </c>
+      <c r="C201" s="12" t="inlineStr">
+        <is>
+          <t>Rouge</t>
+        </is>
+      </c>
+      <c r="D201" s="12" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="E201" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
+      <c r="F201" s="13" t="n"/>
+      <c r="G201" s="13" t="n"/>
+      <c r="H201" s="13" t="n"/>
+      <c r="I201" s="13" t="n"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="11" t="inlineStr">
+        <is>
+          <t>S20 V02</t>
+        </is>
+      </c>
+      <c r="B202" s="12" t="inlineStr">
+        <is>
+          <t>AOC Madiran — Néolitik Rouge</t>
+        </is>
+      </c>
+      <c r="C202" s="12" t="inlineStr">
+        <is>
+          <t>Rouge</t>
+        </is>
+      </c>
+      <c r="D202" s="12" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="E198" s="12" t="n"/>
-      <c r="F198" s="13" t="n"/>
-      <c r="G198" s="13" t="n"/>
-      <c r="H198" s="13" t="n"/>
-      <c r="I198" s="13" t="n"/>
-    </row>
-    <row r="199">
-      <c r="A199" s="11" t="inlineStr">
-        <is>
-          <t>S20 V05</t>
-        </is>
-      </c>
-      <c r="B199" s="12" t="inlineStr">
-        <is>
-          <t>AOP Pacherenc du Vic-Bilh Sec — Strateus</t>
-        </is>
-      </c>
-      <c r="C199" s="12" t="inlineStr">
-        <is>
-          <t>Blanc sec</t>
-        </is>
-      </c>
-      <c r="D199" s="12" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E199" s="12" t="inlineStr">
-        <is>
-          <t>75 cl</t>
-        </is>
-      </c>
-      <c r="F199" s="13" t="n"/>
-      <c r="G199" s="13" t="n"/>
-      <c r="H199" s="13" t="n"/>
-      <c r="I199" s="13" t="n"/>
-    </row>
-    <row r="200">
-      <c r="A200" s="11" t="inlineStr">
-        <is>
-          <t>S20 V06</t>
-        </is>
-      </c>
-      <c r="B200" s="12" t="inlineStr">
-        <is>
-          <t>AOC Pacherenc du Vic-Bilh Sec — Néolitik</t>
-        </is>
-      </c>
-      <c r="C200" s="12" t="inlineStr">
-        <is>
-          <t>Blanc sec</t>
-        </is>
-      </c>
-      <c r="D200" s="12" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E200" s="12" t="n"/>
-      <c r="F200" s="13" t="n"/>
-      <c r="G200" s="13" t="n"/>
-      <c r="H200" s="13" t="n"/>
-      <c r="I200" s="13" t="n"/>
-    </row>
-    <row r="202" ht="22" customHeight="1">
-      <c r="A202" s="5" t="inlineStr">
-        <is>
-          <t>S21</t>
-        </is>
-      </c>
-      <c r="B202" s="6" t="inlineStr">
-        <is>
-          <t>Stand 21 — Famille d’Exea (Languedoc)</t>
-        </is>
-      </c>
-      <c r="C202" s="7" t="n"/>
-      <c r="D202" s="7" t="n"/>
-      <c r="E202" s="7" t="n"/>
-      <c r="F202" s="7" t="n"/>
-      <c r="G202" s="7" t="n"/>
-      <c r="H202" s="7" t="n"/>
-      <c r="I202" s="7" t="n"/>
-    </row>
-    <row r="203" ht="26" customHeight="1">
-      <c r="B203" s="8" t="inlineStr">
-        <is>
-          <t>Famille d’Exea — paliers du tarif</t>
-        </is>
-      </c>
-      <c r="C203" s="9" t="n"/>
-      <c r="D203" s="9" t="n"/>
-      <c r="E203" s="9" t="n"/>
-      <c r="F203" s="8" t="inlineStr">
-        <is>
-          <t>Prix unique</t>
-        </is>
-      </c>
-      <c r="G203" s="10" t="inlineStr">
-        <is>
-          <t>À partir de 144 bts</t>
-        </is>
-      </c>
-      <c r="H203" s="10" t="inlineStr">
-        <is>
-          <t>À partir de 300 bts</t>
-        </is>
-      </c>
-      <c r="I203" s="10" t="inlineStr">
-        <is>
-          <t>À partir de 600 bts</t>
-        </is>
-      </c>
+      <c r="E202" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
+      <c r="F202" s="13" t="n"/>
+      <c r="G202" s="13" t="n"/>
+      <c r="H202" s="13" t="n"/>
+      <c r="I202" s="13" t="n"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="11" t="inlineStr">
+        <is>
+          <t>S20 V03</t>
+        </is>
+      </c>
+      <c r="B203" s="12" t="inlineStr">
+        <is>
+          <t>AOC Madiran — Koloss Rouge</t>
+        </is>
+      </c>
+      <c r="C203" s="12" t="inlineStr">
+        <is>
+          <t>Rouge</t>
+        </is>
+      </c>
+      <c r="D203" s="12" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="E203" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
+      <c r="F203" s="13" t="n"/>
+      <c r="G203" s="13" t="n"/>
+      <c r="H203" s="13" t="n"/>
+      <c r="I203" s="13" t="n"/>
     </row>
     <row r="204">
       <c r="A204" s="11" t="inlineStr">
         <is>
-          <t>S21 V01</t>
+          <t>S20 V04</t>
         </is>
       </c>
       <c r="B204" s="12" t="inlineStr">
         <is>
-          <t>AOP Minervois — CHANT DE LUNE</t>
+          <t>VDF — Koloss Doux</t>
         </is>
       </c>
       <c r="C204" s="12" t="inlineStr">
         <is>
-          <t>Rouge</t>
+          <t>Doux</t>
         </is>
       </c>
       <c r="D204" s="12" t="inlineStr">
         <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="E204" s="12" t="inlineStr">
-        <is>
-          <t>75 cl</t>
-        </is>
-      </c>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="E204" s="12" t="n"/>
       <c r="F204" s="13" t="n"/>
       <c r="G204" s="13" t="n"/>
       <c r="H204" s="13" t="n"/>
@@ -5564,22 +5644,22 @@
     <row r="205">
       <c r="A205" s="11" t="inlineStr">
         <is>
-          <t>S21 V02</t>
+          <t>S20 V05</t>
         </is>
       </c>
       <c r="B205" s="12" t="inlineStr">
         <is>
-          <t>AOP Corbières — ROUGE SÉRAME</t>
+          <t>AOC Pacherenc du Vic-Bilh sec — Stratéus Blanc</t>
         </is>
       </c>
       <c r="C205" s="12" t="inlineStr">
         <is>
-          <t>Rouge</t>
+          <t>Blanc</t>
         </is>
       </c>
       <c r="D205" s="12" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E205" s="12" t="inlineStr">
@@ -5595,12 +5675,12 @@
     <row r="206">
       <c r="A206" s="11" t="inlineStr">
         <is>
-          <t>S21 V03</t>
+          <t>S20 V06</t>
         </is>
       </c>
       <c r="B206" s="12" t="inlineStr">
         <is>
-          <t>AOP Corbières — BLANC SÉRAME</t>
+          <t>AOC Pacherenc du Vic-Bilh sec — Néolitik Blanc</t>
         </is>
       </c>
       <c r="C206" s="12" t="inlineStr">
@@ -5610,185 +5690,197 @@
       </c>
       <c r="D206" s="12" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E206" s="12" t="inlineStr">
-        <is>
-          <t>75 cl</t>
-        </is>
-      </c>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E206" s="12" t="n"/>
       <c r="F206" s="13" t="n"/>
       <c r="G206" s="13" t="n"/>
       <c r="H206" s="13" t="n"/>
       <c r="I206" s="13" t="n"/>
     </row>
-    <row r="207">
-      <c r="A207" s="11" t="inlineStr">
-        <is>
-          <t>S21 V04</t>
-        </is>
-      </c>
-      <c r="B207" s="12" t="inlineStr">
-        <is>
-          <t>AOP Corbières — OENA</t>
-        </is>
-      </c>
-      <c r="C207" s="12" t="inlineStr">
-        <is>
-          <t>Blanc</t>
-        </is>
-      </c>
-      <c r="D207" s="12" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="E207" s="12" t="inlineStr">
-        <is>
-          <t>75 cl</t>
-        </is>
-      </c>
-      <c r="F207" s="13" t="n"/>
-      <c r="G207" s="13" t="n"/>
-      <c r="H207" s="13" t="n"/>
-      <c r="I207" s="13" t="n"/>
-    </row>
-    <row r="208">
-      <c r="A208" s="11" t="inlineStr">
-        <is>
-          <t>S21 V05</t>
-        </is>
-      </c>
-      <c r="B208" s="12" t="inlineStr">
-        <is>
-          <t>AOP Corbières — JARDINS DE CORBIÈRES</t>
-        </is>
-      </c>
-      <c r="C208" s="12" t="inlineStr">
-        <is>
-          <t>Rouge</t>
-        </is>
-      </c>
-      <c r="D208" s="12" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E208" s="12" t="inlineStr">
-        <is>
-          <t>75 cl</t>
-        </is>
-      </c>
-      <c r="F208" s="13" t="n"/>
-      <c r="G208" s="13" t="n"/>
-      <c r="H208" s="13" t="n"/>
-      <c r="I208" s="13" t="n"/>
-    </row>
-    <row r="210" ht="22" customHeight="1">
-      <c r="A210" s="5" t="inlineStr">
-        <is>
-          <t>S22</t>
-        </is>
-      </c>
-      <c r="B210" s="6" t="inlineStr">
-        <is>
-          <t>Stand 22 — Domaine de la Barbinière (Loire)</t>
-        </is>
-      </c>
-      <c r="C210" s="7" t="n"/>
-      <c r="D210" s="7" t="n"/>
-      <c r="E210" s="7" t="n"/>
-      <c r="F210" s="7" t="n"/>
-      <c r="G210" s="7" t="n"/>
-      <c r="H210" s="7" t="n"/>
-      <c r="I210" s="7" t="n"/>
-    </row>
-    <row r="211" ht="26" customHeight="1">
-      <c r="B211" s="8" t="inlineStr">
-        <is>
-          <t>Domaine de la Barbinière — paliers du tarif</t>
-        </is>
-      </c>
-      <c r="C211" s="9" t="n"/>
-      <c r="D211" s="9" t="n"/>
-      <c r="E211" s="9" t="n"/>
-      <c r="F211" s="8" t="inlineStr">
+    <row r="208" ht="22" customHeight="1">
+      <c r="A208" s="5" t="inlineStr">
+        <is>
+          <t>S21</t>
+        </is>
+      </c>
+      <c r="B208" s="6" t="inlineStr">
+        <is>
+          <t>Stand 21 — Famille d’Exea (Languedoc)</t>
+        </is>
+      </c>
+      <c r="C208" s="7" t="n"/>
+      <c r="D208" s="7" t="n"/>
+      <c r="E208" s="7" t="n"/>
+      <c r="F208" s="7" t="n"/>
+      <c r="G208" s="7" t="n"/>
+      <c r="H208" s="7" t="n"/>
+      <c r="I208" s="7" t="n"/>
+    </row>
+    <row r="209" ht="26" customHeight="1">
+      <c r="B209" s="8" t="inlineStr">
+        <is>
+          <t>Famille d’Exea — paliers du tarif</t>
+        </is>
+      </c>
+      <c r="C209" s="9" t="n"/>
+      <c r="D209" s="9" t="n"/>
+      <c r="E209" s="9" t="n"/>
+      <c r="F209" s="8" t="inlineStr">
         <is>
           <t>Prix unique</t>
         </is>
       </c>
-      <c r="G211" s="10" t="inlineStr">
-        <is>
-          <t>Tarif</t>
-        </is>
-      </c>
-      <c r="H211" s="10" t="n"/>
-      <c r="I211" s="10" t="n"/>
+      <c r="G209" s="10" t="inlineStr">
+        <is>
+          <t>À partir de 144 bts</t>
+        </is>
+      </c>
+      <c r="H209" s="10" t="inlineStr">
+        <is>
+          <t>À partir de 300 bts</t>
+        </is>
+      </c>
+      <c r="I209" s="10" t="inlineStr">
+        <is>
+          <t>À partir de 600 bts</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="11" t="inlineStr">
+        <is>
+          <t>S21 V01</t>
+        </is>
+      </c>
+      <c r="B210" s="12" t="inlineStr">
+        <is>
+          <t>AOC Minervois — Chant de Lune Rouge</t>
+        </is>
+      </c>
+      <c r="C210" s="12" t="inlineStr">
+        <is>
+          <t>Rouge</t>
+        </is>
+      </c>
+      <c r="D210" s="12" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="E210" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
+      <c r="F210" s="13" t="n"/>
+      <c r="G210" s="13" t="n"/>
+      <c r="H210" s="13" t="n"/>
+      <c r="I210" s="13" t="n"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="11" t="inlineStr">
+        <is>
+          <t>S21 V02</t>
+        </is>
+      </c>
+      <c r="B211" s="12" t="inlineStr">
+        <is>
+          <t>AOC Corbières — Rouge Sérame</t>
+        </is>
+      </c>
+      <c r="C211" s="12" t="inlineStr">
+        <is>
+          <t>Rouge</t>
+        </is>
+      </c>
+      <c r="D211" s="12" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E211" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
+      <c r="F211" s="13" t="n"/>
+      <c r="G211" s="13" t="n"/>
+      <c r="H211" s="13" t="n"/>
+      <c r="I211" s="13" t="n"/>
     </row>
     <row r="212">
       <c r="A212" s="11" t="inlineStr">
         <is>
-          <t>S22 V01</t>
+          <t>S21 V03</t>
         </is>
       </c>
       <c r="B212" s="12" t="inlineStr">
         <is>
-          <t>AOC Fiefs Vendéens Chantonnay — Les Silex</t>
+          <t>AOC Corbières — Blanc Sérame</t>
         </is>
       </c>
       <c r="C212" s="12" t="inlineStr">
         <is>
-          <t>Rouge</t>
+          <t>Blanc</t>
         </is>
       </c>
       <c r="D212" s="12" t="inlineStr">
         <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E212" s="12" t="n"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E212" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
       <c r="F212" s="13" t="n"/>
       <c r="G212" s="13" t="n"/>
-      <c r="H212" s="14" t="n"/>
-      <c r="I212" s="14" t="n"/>
+      <c r="H212" s="13" t="n"/>
+      <c r="I212" s="13" t="n"/>
     </row>
     <row r="213">
       <c r="A213" s="11" t="inlineStr">
         <is>
-          <t>S22 V02</t>
+          <t>S21 V04</t>
         </is>
       </c>
       <c r="B213" s="12" t="inlineStr">
         <is>
-          <t>AOC Fiefs Vendéens Chantonnay — Les Gorinières</t>
+          <t>AOC Corbières — Oena Rouge</t>
         </is>
       </c>
       <c r="C213" s="12" t="inlineStr">
         <is>
-          <t>Blanc</t>
+          <t>Rouge</t>
         </is>
       </c>
       <c r="D213" s="12" t="inlineStr">
         <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="E213" s="12" t="n"/>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="E213" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
       <c r="F213" s="13" t="n"/>
       <c r="G213" s="13" t="n"/>
-      <c r="H213" s="14" t="n"/>
-      <c r="I213" s="14" t="n"/>
+      <c r="H213" s="13" t="n"/>
+      <c r="I213" s="13" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="11" t="inlineStr">
         <is>
-          <t>S22 V03</t>
+          <t>S21 V05</t>
         </is>
       </c>
       <c r="B214" s="12" t="inlineStr">
         <is>
-          <t>AOC Fiefs Vendéens Chantonnay — Les Courbes</t>
+          <t>AOC Corbières — Jardins de Corbières Rouge</t>
         </is>
       </c>
       <c r="C214" s="12" t="inlineStr">
@@ -5798,51 +5890,54 @@
       </c>
       <c r="D214" s="12" t="inlineStr">
         <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="E214" s="12" t="n"/>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E214" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
       <c r="F214" s="13" t="n"/>
       <c r="G214" s="13" t="n"/>
-      <c r="H214" s="14" t="n"/>
-      <c r="I214" s="14" t="n"/>
-    </row>
-    <row r="215">
-      <c r="A215" s="11" t="inlineStr">
-        <is>
-          <t>S22 V04</t>
-        </is>
-      </c>
-      <c r="B215" s="12" t="inlineStr">
-        <is>
-          <t>AOC Fiefs Vendéens Chantonnay — Les Amphibol</t>
-        </is>
-      </c>
-      <c r="C215" s="12" t="inlineStr">
-        <is>
-          <t>Blanc</t>
-        </is>
-      </c>
-      <c r="D215" s="12" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E215" s="12" t="n"/>
-      <c r="F215" s="13" t="n"/>
-      <c r="G215" s="13" t="n"/>
-      <c r="H215" s="14" t="n"/>
-      <c r="I215" s="14" t="n"/>
+      <c r="H214" s="13" t="n"/>
+      <c r="I214" s="13" t="n"/>
+    </row>
+    <row r="215" ht="26" customHeight="1">
+      <c r="B215" s="8" t="inlineStr">
+        <is>
+          <t>Famille d’Exea — Jus de Cépages — paliers du tarif</t>
+        </is>
+      </c>
+      <c r="C215" s="9" t="n"/>
+      <c r="D215" s="9" t="n"/>
+      <c r="E215" s="9" t="n"/>
+      <c r="F215" s="8" t="inlineStr">
+        <is>
+          <t>Prix unique</t>
+        </is>
+      </c>
+      <c r="G215" s="10" t="inlineStr">
+        <is>
+          <t>À partir de 144 bts</t>
+        </is>
+      </c>
+      <c r="H215" s="10" t="inlineStr">
+        <is>
+          <t>À partir de 300 bts</t>
+        </is>
+      </c>
+      <c r="I215" s="10" t="n"/>
     </row>
     <row r="216">
       <c r="A216" s="11" t="inlineStr">
         <is>
-          <t>S22 V05</t>
+          <t>S21 V06</t>
         </is>
       </c>
       <c r="B216" s="12" t="inlineStr">
         <is>
-          <t>AOC Fiefs Vendéens Chantonnay — Les Gneiss</t>
+          <t>Jus de cépages – Syrah</t>
         </is>
       </c>
       <c r="C216" s="12" t="inlineStr">
@@ -5852,78 +5947,90 @@
       </c>
       <c r="D216" s="12" t="inlineStr">
         <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E216" s="12" t="n"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E216" s="12" t="inlineStr">
+        <is>
+          <t>50 cl</t>
+        </is>
+      </c>
       <c r="F216" s="13" t="n"/>
       <c r="G216" s="13" t="n"/>
-      <c r="H216" s="14" t="n"/>
+      <c r="H216" s="13" t="n"/>
       <c r="I216" s="14" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="11" t="inlineStr">
         <is>
-          <t>S22 V06</t>
+          <t>S21 V07</t>
         </is>
       </c>
       <c r="B217" s="12" t="inlineStr">
         <is>
-          <t>IGP Val de Loire Pinot Noir — Le Bois Bouquet</t>
+          <t>Jus de cépages – Chardonnay</t>
         </is>
       </c>
       <c r="C217" s="12" t="inlineStr">
         <is>
-          <t>Rouge</t>
+          <t>Blanc</t>
         </is>
       </c>
       <c r="D217" s="12" t="inlineStr">
         <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E217" s="12" t="n"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E217" s="12" t="inlineStr">
+        <is>
+          <t>50 cl</t>
+        </is>
+      </c>
       <c r="F217" s="13" t="n"/>
       <c r="G217" s="13" t="n"/>
-      <c r="H217" s="14" t="n"/>
+      <c r="H217" s="13" t="n"/>
       <c r="I217" s="14" t="n"/>
     </row>
     <row r="218">
       <c r="A218" s="11" t="inlineStr">
         <is>
-          <t>S22 V07</t>
+          <t>S21 V08</t>
         </is>
       </c>
       <c r="B218" s="12" t="inlineStr">
         <is>
-          <t>Méthode Traditionnelle (Extra) — L’O*** Brut</t>
+          <t>Jus de cépages – Grenache</t>
         </is>
       </c>
       <c r="C218" s="12" t="inlineStr">
         <is>
-          <t>Blanc</t>
+          <t>Rosé</t>
         </is>
       </c>
       <c r="D218" s="12" t="inlineStr">
         <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E218" s="12" t="n"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E218" s="12" t="inlineStr">
+        <is>
+          <t>50 cl</t>
+        </is>
+      </c>
       <c r="F218" s="13" t="n"/>
       <c r="G218" s="13" t="n"/>
-      <c r="H218" s="14" t="n"/>
+      <c r="H218" s="13" t="n"/>
       <c r="I218" s="14" t="n"/>
     </row>
     <row r="220" ht="22" customHeight="1">
       <c r="A220" s="5" t="inlineStr">
         <is>
-          <t>S23</t>
+          <t>S22</t>
         </is>
       </c>
       <c r="B220" s="6" t="inlineStr">
         <is>
-          <t>Stand 23 — Champagne Solemme (Champagne)</t>
+          <t>Stand 22 — Domaine de la Barbinière (Loire)</t>
         </is>
       </c>
       <c r="C220" s="7" t="n"/>
@@ -5937,7 +6044,7 @@
     <row r="221" ht="26" customHeight="1">
       <c r="B221" s="8" t="inlineStr">
         <is>
-          <t>Champagne Solemme — paliers du tarif</t>
+          <t>Domaine de la Barbinière — paliers du tarif</t>
         </is>
       </c>
       <c r="C221" s="9" t="n"/>
@@ -5950,293 +6057,269 @@
       </c>
       <c r="G221" s="10" t="inlineStr">
         <is>
-          <t>À partir de 60 bts</t>
-        </is>
-      </c>
-      <c r="H221" s="10" t="inlineStr">
-        <is>
-          <t>À partir de 120 bts</t>
-        </is>
-      </c>
-      <c r="I221" s="10" t="inlineStr">
-        <is>
-          <t>À partir de 240 bts</t>
-        </is>
-      </c>
+          <t>Tarif</t>
+        </is>
+      </c>
+      <c r="H221" s="10" t="n"/>
+      <c r="I221" s="10" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="11" t="inlineStr">
         <is>
-          <t>S23 V01</t>
+          <t>S22 V01</t>
         </is>
       </c>
       <c r="B222" s="12" t="inlineStr">
         <is>
-          <t>AOP Champagne Premier Cru — Terre de Solemme</t>
+          <t>AOC Fiefs Vendéens Chantonnay — Les Silex Rouge</t>
         </is>
       </c>
       <c r="C222" s="12" t="inlineStr">
         <is>
-          <t>Blanc brut</t>
+          <t>Rouge</t>
         </is>
       </c>
       <c r="D222" s="12" t="inlineStr">
         <is>
-          <t>BSA</t>
-        </is>
-      </c>
-      <c r="E222" s="12" t="inlineStr">
-        <is>
-          <t>75 cl</t>
-        </is>
-      </c>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E222" s="12" t="n"/>
       <c r="F222" s="13" t="n"/>
       <c r="G222" s="13" t="n"/>
-      <c r="H222" s="13" t="n"/>
-      <c r="I222" s="13" t="n"/>
+      <c r="H222" s="14" t="n"/>
+      <c r="I222" s="14" t="n"/>
     </row>
     <row r="223">
       <c r="A223" s="11" t="inlineStr">
         <is>
-          <t>S23 V02</t>
+          <t>S22 V02</t>
         </is>
       </c>
       <c r="B223" s="12" t="inlineStr">
         <is>
-          <t>AOP Champagne Premier Cru — Plénitude de Solemme</t>
+          <t>AOC Fiefs Vendéens Chantonnay — Les Gorinières Blanc</t>
         </is>
       </c>
       <c r="C223" s="12" t="inlineStr">
         <is>
-          <t>Blanc extra brut</t>
+          <t>Blanc</t>
         </is>
       </c>
       <c r="D223" s="12" t="inlineStr">
         <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="E223" s="12" t="inlineStr">
-        <is>
-          <t>75 cl</t>
-        </is>
-      </c>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="E223" s="12" t="n"/>
       <c r="F223" s="13" t="n"/>
       <c r="G223" s="13" t="n"/>
-      <c r="H223" s="13" t="n"/>
-      <c r="I223" s="13" t="n"/>
+      <c r="H223" s="14" t="n"/>
+      <c r="I223" s="14" t="n"/>
     </row>
     <row r="224">
       <c r="A224" s="11" t="inlineStr">
         <is>
-          <t>S23 V03</t>
+          <t>S22 V03</t>
         </is>
       </c>
       <c r="B224" s="12" t="inlineStr">
         <is>
-          <t>AOP Champagne Premier Cru — Esprit de Solemme</t>
+          <t>AOC Fiefs Vendéens Chantonnay — Les Courbes Blanc</t>
         </is>
       </c>
       <c r="C224" s="12" t="inlineStr">
         <is>
-          <t>Blanc brut nature</t>
+          <t>Blanc</t>
         </is>
       </c>
       <c r="D224" s="12" t="inlineStr">
         <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="E224" s="12" t="inlineStr">
-        <is>
-          <t>75 cl</t>
-        </is>
-      </c>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="E224" s="12" t="n"/>
       <c r="F224" s="13" t="n"/>
       <c r="G224" s="13" t="n"/>
-      <c r="H224" s="13" t="n"/>
-      <c r="I224" s="13" t="n"/>
+      <c r="H224" s="14" t="n"/>
+      <c r="I224" s="14" t="n"/>
     </row>
     <row r="225">
       <c r="A225" s="11" t="inlineStr">
         <is>
-          <t>S23 V04</t>
+          <t>S22 V04</t>
         </is>
       </c>
       <c r="B225" s="12" t="inlineStr">
         <is>
-          <t>AOP Champagne Premier Cru — Nature de Solemme</t>
+          <t>AOC Fiefs Vendéens Chantonnay — Les Amphibol Blanc</t>
         </is>
       </c>
       <c r="C225" s="12" t="inlineStr">
         <is>
-          <t>Blanc brut nature</t>
+          <t>Blanc</t>
         </is>
       </c>
       <c r="D225" s="12" t="inlineStr">
         <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="E225" s="12" t="inlineStr">
-        <is>
-          <t>75 cl</t>
-        </is>
-      </c>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E225" s="12" t="n"/>
       <c r="F225" s="13" t="n"/>
       <c r="G225" s="13" t="n"/>
-      <c r="H225" s="13" t="n"/>
-      <c r="I225" s="13" t="n"/>
+      <c r="H225" s="14" t="n"/>
+      <c r="I225" s="14" t="n"/>
     </row>
     <row r="226">
       <c r="A226" s="11" t="inlineStr">
         <is>
-          <t>S23 V05</t>
+          <t>S22 V05</t>
         </is>
       </c>
       <c r="B226" s="12" t="inlineStr">
         <is>
-          <t>AOP Champagne Premier Cru — Ambre de Solemme</t>
+          <t>AOC Fiefs Vendéens Chantonnay — Les Gneiss Rouge</t>
         </is>
       </c>
       <c r="C226" s="12" t="inlineStr">
         <is>
-          <t>Blanc brut nature</t>
+          <t>Rouge</t>
         </is>
       </c>
       <c r="D226" s="12" t="inlineStr">
         <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="E226" s="12" t="inlineStr">
-        <is>
-          <t>75 cl</t>
-        </is>
-      </c>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E226" s="12" t="n"/>
       <c r="F226" s="13" t="n"/>
       <c r="G226" s="13" t="n"/>
-      <c r="H226" s="13" t="n"/>
-      <c r="I226" s="13" t="n"/>
+      <c r="H226" s="14" t="n"/>
+      <c r="I226" s="14" t="n"/>
     </row>
     <row r="227">
       <c r="A227" s="11" t="inlineStr">
         <is>
-          <t>S23 V06</t>
+          <t>S22 V06</t>
         </is>
       </c>
       <c r="B227" s="12" t="inlineStr">
         <is>
-          <t>AOP Champagne Premier Cru — Rose de Solemme</t>
+          <t>IGP Val de Loire Pinot Noir — Le Bois Bouquet</t>
         </is>
       </c>
       <c r="C227" s="12" t="inlineStr">
         <is>
-          <t>Rosé brut nature</t>
+          <t>Rouge</t>
         </is>
       </c>
       <c r="D227" s="12" t="inlineStr">
         <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="E227" s="12" t="inlineStr">
-        <is>
-          <t>75 cl</t>
-        </is>
-      </c>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E227" s="12" t="n"/>
       <c r="F227" s="13" t="n"/>
       <c r="G227" s="13" t="n"/>
-      <c r="H227" s="13" t="n"/>
-      <c r="I227" s="13" t="n"/>
-    </row>
-    <row r="229" ht="22" customHeight="1">
-      <c r="A229" s="5" t="inlineStr">
-        <is>
-          <t>S24</t>
-        </is>
-      </c>
-      <c r="B229" s="6" t="inlineStr">
-        <is>
-          <t>Stand 24 — Château Escarderie (Bordeaux)</t>
-        </is>
-      </c>
-      <c r="C229" s="7" t="n"/>
-      <c r="D229" s="7" t="n"/>
-      <c r="E229" s="7" t="n"/>
-      <c r="F229" s="7" t="n"/>
-      <c r="G229" s="7" t="n"/>
-      <c r="H229" s="7" t="n"/>
-      <c r="I229" s="7" t="n"/>
-    </row>
-    <row r="230" ht="26" customHeight="1">
-      <c r="B230" s="8" t="inlineStr">
-        <is>
-          <t>Château l’Escarderie — paliers du tarif</t>
-        </is>
-      </c>
-      <c r="C230" s="9" t="n"/>
-      <c r="D230" s="9" t="n"/>
-      <c r="E230" s="9" t="n"/>
-      <c r="F230" s="8" t="inlineStr">
+      <c r="H227" s="14" t="n"/>
+      <c r="I227" s="14" t="n"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="11" t="inlineStr">
+        <is>
+          <t>S22 V07</t>
+        </is>
+      </c>
+      <c r="B228" s="12" t="inlineStr">
+        <is>
+          <t>Méthode traditionnelle — L’O Brut</t>
+        </is>
+      </c>
+      <c r="C228" s="12" t="inlineStr">
+        <is>
+          <t>Blanc</t>
+        </is>
+      </c>
+      <c r="D228" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E228" s="12" t="n"/>
+      <c r="F228" s="13" t="n"/>
+      <c r="G228" s="13" t="n"/>
+      <c r="H228" s="14" t="n"/>
+      <c r="I228" s="14" t="n"/>
+    </row>
+    <row r="230" ht="22" customHeight="1">
+      <c r="A230" s="5" t="inlineStr">
+        <is>
+          <t>S23</t>
+        </is>
+      </c>
+      <c r="B230" s="6" t="inlineStr">
+        <is>
+          <t>Stand 23 — Champagne Solemme (Champagne)</t>
+        </is>
+      </c>
+      <c r="C230" s="7" t="n"/>
+      <c r="D230" s="7" t="n"/>
+      <c r="E230" s="7" t="n"/>
+      <c r="F230" s="7" t="n"/>
+      <c r="G230" s="7" t="n"/>
+      <c r="H230" s="7" t="n"/>
+      <c r="I230" s="7" t="n"/>
+    </row>
+    <row r="231" ht="26" customHeight="1">
+      <c r="B231" s="8" t="inlineStr">
+        <is>
+          <t>Champagne Solemme — paliers du tarif</t>
+        </is>
+      </c>
+      <c r="C231" s="9" t="n"/>
+      <c r="D231" s="9" t="n"/>
+      <c r="E231" s="9" t="n"/>
+      <c r="F231" s="8" t="inlineStr">
         <is>
           <t>Prix unique</t>
         </is>
       </c>
-      <c r="G230" s="10" t="inlineStr">
-        <is>
-          <t>Tarif</t>
-        </is>
-      </c>
-      <c r="H230" s="10" t="n"/>
-      <c r="I230" s="10" t="n"/>
-    </row>
-    <row r="231">
-      <c r="A231" s="11" t="inlineStr">
-        <is>
-          <t>S24 V01</t>
-        </is>
-      </c>
-      <c r="B231" s="12" t="inlineStr">
-        <is>
-          <t>AOC Fronsac — Château Lafargue</t>
-        </is>
-      </c>
-      <c r="C231" s="12" t="inlineStr">
-        <is>
-          <t>Rouge</t>
-        </is>
-      </c>
-      <c r="D231" s="12" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="E231" s="12" t="n"/>
-      <c r="F231" s="13" t="n"/>
-      <c r="G231" s="13" t="n"/>
-      <c r="H231" s="14" t="n"/>
-      <c r="I231" s="14" t="n"/>
+      <c r="G231" s="10" t="inlineStr">
+        <is>
+          <t>À partir de 60 bts</t>
+        </is>
+      </c>
+      <c r="H231" s="10" t="inlineStr">
+        <is>
+          <t>À partir de 120 bts</t>
+        </is>
+      </c>
+      <c r="I231" s="10" t="inlineStr">
+        <is>
+          <t>À partir de 240 bts</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="11" t="inlineStr">
         <is>
-          <t>S24 V02</t>
+          <t>S23 V01</t>
         </is>
       </c>
       <c r="B232" s="12" t="inlineStr">
         <is>
-          <t>AOP Fronsac — Amphora de Château l'Escarderie</t>
+          <t>Premier Cru Champagne — Terre de Solemme Brut</t>
         </is>
       </c>
       <c r="C232" s="12" t="inlineStr">
         <is>
-          <t>Rouge</t>
+          <t>Blanc brut</t>
         </is>
       </c>
       <c r="D232" s="12" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E232" s="12" t="inlineStr">
@@ -6246,28 +6329,28 @@
       </c>
       <c r="F232" s="13" t="n"/>
       <c r="G232" s="13" t="n"/>
-      <c r="H232" s="14" t="n"/>
-      <c r="I232" s="14" t="n"/>
+      <c r="H232" s="13" t="n"/>
+      <c r="I232" s="13" t="n"/>
     </row>
     <row r="233">
       <c r="A233" s="11" t="inlineStr">
         <is>
-          <t>S24 V03</t>
+          <t>S23 V02</t>
         </is>
       </c>
       <c r="B233" s="12" t="inlineStr">
         <is>
-          <t>Vin de France — La Confiance de l'Escarderie</t>
+          <t>Premier Cru Champagne — Plénitude de Solemme Extra-Brut</t>
         </is>
       </c>
       <c r="C233" s="12" t="inlineStr">
         <is>
-          <t>Rouge</t>
+          <t>Blanc extra brut</t>
         </is>
       </c>
       <c r="D233" s="12" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E233" s="12" t="inlineStr">
@@ -6277,77 +6360,121 @@
       </c>
       <c r="F233" s="13" t="n"/>
       <c r="G233" s="13" t="n"/>
-      <c r="H233" s="14" t="n"/>
-      <c r="I233" s="14" t="n"/>
-    </row>
-    <row r="235" ht="22" customHeight="1">
-      <c r="A235" s="5" t="inlineStr">
-        <is>
-          <t>S25</t>
-        </is>
-      </c>
-      <c r="B235" s="6" t="inlineStr">
-        <is>
-          <t>Stand 25 — Chai Berteaud Manceau (Loire)</t>
-        </is>
-      </c>
-      <c r="C235" s="7" t="n"/>
-      <c r="D235" s="7" t="n"/>
-      <c r="E235" s="7" t="n"/>
-      <c r="F235" s="7" t="n"/>
-      <c r="G235" s="7" t="n"/>
-      <c r="H235" s="7" t="n"/>
-      <c r="I235" s="7" t="n"/>
-    </row>
-    <row r="236" ht="26" customHeight="1">
-      <c r="B236" s="8" t="inlineStr">
-        <is>
-          <t>Chai Berteaud Manceau — paliers du tarif</t>
-        </is>
-      </c>
-      <c r="C236" s="9" t="n"/>
-      <c r="D236" s="9" t="n"/>
-      <c r="E236" s="9" t="n"/>
-      <c r="F236" s="8" t="inlineStr">
-        <is>
-          <t>Prix unique</t>
-        </is>
-      </c>
-      <c r="G236" s="10" t="inlineStr">
-        <is>
-          <t>À partir de 60 bts</t>
-        </is>
-      </c>
-      <c r="H236" s="10" t="inlineStr">
-        <is>
-          <t>À partir de 120 bts</t>
-        </is>
-      </c>
-      <c r="I236" s="10" t="inlineStr">
-        <is>
-          <t>À partir de 240 bts</t>
-        </is>
-      </c>
+      <c r="H233" s="13" t="n"/>
+      <c r="I233" s="13" t="n"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="11" t="inlineStr">
+        <is>
+          <t>S23 V03</t>
+        </is>
+      </c>
+      <c r="B234" s="12" t="inlineStr">
+        <is>
+          <t>Premier Cru Champagne — Esprit de Solemme Brut Nature</t>
+        </is>
+      </c>
+      <c r="C234" s="12" t="inlineStr">
+        <is>
+          <t>Blanc brut nature</t>
+        </is>
+      </c>
+      <c r="D234" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E234" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
+      <c r="F234" s="13" t="n"/>
+      <c r="G234" s="13" t="n"/>
+      <c r="H234" s="13" t="n"/>
+      <c r="I234" s="13" t="n"/>
+    </row>
+    <row r="235">
+      <c r="A235" s="11" t="inlineStr">
+        <is>
+          <t>S23 V04</t>
+        </is>
+      </c>
+      <c r="B235" s="12" t="inlineStr">
+        <is>
+          <t>Premier Cru Champagne — Nature de Solemme Blanc de Blancs Brut Nature</t>
+        </is>
+      </c>
+      <c r="C235" s="12" t="inlineStr">
+        <is>
+          <t>Blanc brut nature</t>
+        </is>
+      </c>
+      <c r="D235" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E235" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
+      <c r="F235" s="13" t="n"/>
+      <c r="G235" s="13" t="n"/>
+      <c r="H235" s="13" t="n"/>
+      <c r="I235" s="13" t="n"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="11" t="inlineStr">
+        <is>
+          <t>S23 V05</t>
+        </is>
+      </c>
+      <c r="B236" s="12" t="inlineStr">
+        <is>
+          <t>Premier Cru Champagne — Ambre de Solemme Blanc de Noirs Brut Nature</t>
+        </is>
+      </c>
+      <c r="C236" s="12" t="inlineStr">
+        <is>
+          <t>Blanc brut nature</t>
+        </is>
+      </c>
+      <c r="D236" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E236" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
+      <c r="F236" s="13" t="n"/>
+      <c r="G236" s="13" t="n"/>
+      <c r="H236" s="13" t="n"/>
+      <c r="I236" s="13" t="n"/>
     </row>
     <row r="237">
       <c r="A237" s="11" t="inlineStr">
         <is>
-          <t>S25 V01</t>
+          <t>S23 V06</t>
         </is>
       </c>
       <c r="B237" s="12" t="inlineStr">
         <is>
-          <t>IGP Val de Loire — Courant – Chenin</t>
+          <t>Premier Cru Champagne — Rose de Solemme Brut Nature</t>
         </is>
       </c>
       <c r="C237" s="12" t="inlineStr">
         <is>
-          <t>Blanc sec</t>
+          <t>Rosé brut nature</t>
         </is>
       </c>
       <c r="D237" s="12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E237" s="12" t="inlineStr">
@@ -6360,284 +6487,256 @@
       <c r="H237" s="13" t="n"/>
       <c r="I237" s="13" t="n"/>
     </row>
-    <row r="238">
-      <c r="A238" s="11" t="inlineStr">
-        <is>
-          <t>S25 V02</t>
-        </is>
-      </c>
-      <c r="B238" s="12" t="inlineStr">
-        <is>
-          <t>IGP Val de Loire — Source – Melon B.</t>
-        </is>
-      </c>
-      <c r="C238" s="12" t="inlineStr">
-        <is>
-          <t>Blanc sec</t>
-        </is>
-      </c>
-      <c r="D238" s="12" t="inlineStr">
+    <row r="239" ht="22" customHeight="1">
+      <c r="A239" s="5" t="inlineStr">
+        <is>
+          <t>S24</t>
+        </is>
+      </c>
+      <c r="B239" s="6" t="inlineStr">
+        <is>
+          <t>Stand 24 — Château Escarderie (Bordeaux)</t>
+        </is>
+      </c>
+      <c r="C239" s="7" t="n"/>
+      <c r="D239" s="7" t="n"/>
+      <c r="E239" s="7" t="n"/>
+      <c r="F239" s="7" t="n"/>
+      <c r="G239" s="7" t="n"/>
+      <c r="H239" s="7" t="n"/>
+      <c r="I239" s="7" t="n"/>
+    </row>
+    <row r="240" ht="26" customHeight="1">
+      <c r="B240" s="8" t="inlineStr">
+        <is>
+          <t>Château l’Escarderie — paliers du tarif</t>
+        </is>
+      </c>
+      <c r="C240" s="9" t="n"/>
+      <c r="D240" s="9" t="n"/>
+      <c r="E240" s="9" t="n"/>
+      <c r="F240" s="8" t="inlineStr">
+        <is>
+          <t>Prix unique</t>
+        </is>
+      </c>
+      <c r="G240" s="10" t="inlineStr">
+        <is>
+          <t>Tarif</t>
+        </is>
+      </c>
+      <c r="H240" s="10" t="n"/>
+      <c r="I240" s="10" t="n"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="11" t="inlineStr">
+        <is>
+          <t>S24 V01</t>
+        </is>
+      </c>
+      <c r="B241" s="12" t="inlineStr">
+        <is>
+          <t>AOC Fronsac — Château Lafargue Rouge</t>
+        </is>
+      </c>
+      <c r="C241" s="12" t="inlineStr">
+        <is>
+          <t>Rouge</t>
+        </is>
+      </c>
+      <c r="D241" s="12" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="E241" s="12" t="n"/>
+      <c r="F241" s="13" t="n"/>
+      <c r="G241" s="13" t="n"/>
+      <c r="H241" s="14" t="n"/>
+      <c r="I241" s="14" t="n"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="11" t="inlineStr">
+        <is>
+          <t>S24 V02</t>
+        </is>
+      </c>
+      <c r="B242" s="12" t="inlineStr">
+        <is>
+          <t>AOC Fronsac — Amphora Rouge</t>
+        </is>
+      </c>
+      <c r="C242" s="12" t="inlineStr">
+        <is>
+          <t>Rouge</t>
+        </is>
+      </c>
+      <c r="D242" s="12" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="E242" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
+      <c r="F242" s="13" t="n"/>
+      <c r="G242" s="13" t="n"/>
+      <c r="H242" s="14" t="n"/>
+      <c r="I242" s="14" t="n"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="11" t="inlineStr">
+        <is>
+          <t>S24 V03</t>
+        </is>
+      </c>
+      <c r="B243" s="12" t="inlineStr">
+        <is>
+          <t>VDF — La Confiance Rouge</t>
+        </is>
+      </c>
+      <c r="C243" s="12" t="inlineStr">
+        <is>
+          <t>Rouge</t>
+        </is>
+      </c>
+      <c r="D243" s="12" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="E238" s="12" t="inlineStr">
-        <is>
-          <t>75 cl</t>
-        </is>
-      </c>
-      <c r="F238" s="13" t="n"/>
-      <c r="G238" s="13" t="n"/>
-      <c r="H238" s="13" t="n"/>
-      <c r="I238" s="13" t="n"/>
-    </row>
-    <row r="239">
-      <c r="A239" s="11" t="inlineStr">
-        <is>
-          <t>S25 V03</t>
-        </is>
-      </c>
-      <c r="B239" s="12" t="inlineStr">
-        <is>
-          <t>IGP Val de Loire — Reflet – Gamay</t>
-        </is>
-      </c>
-      <c r="C239" s="12" t="inlineStr">
-        <is>
-          <t>Rouge</t>
-        </is>
-      </c>
-      <c r="D239" s="12" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="E239" s="12" t="inlineStr">
-        <is>
-          <t>75 cl</t>
-        </is>
-      </c>
-      <c r="F239" s="13" t="n"/>
-      <c r="G239" s="13" t="n"/>
-      <c r="H239" s="13" t="n"/>
-      <c r="I239" s="13" t="n"/>
-    </row>
-    <row r="240">
-      <c r="A240" s="11" t="inlineStr">
-        <is>
-          <t>S25 V04</t>
-        </is>
-      </c>
-      <c r="B240" s="12" t="inlineStr">
-        <is>
-          <t>IGP Val de Loire — L'Eberluant – Chardonnay</t>
-        </is>
-      </c>
-      <c r="C240" s="12" t="inlineStr">
-        <is>
-          <t>Blanc pétillant</t>
-        </is>
-      </c>
-      <c r="D240" s="12" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E240" s="12" t="n"/>
-      <c r="F240" s="13" t="n"/>
-      <c r="G240" s="13" t="n"/>
-      <c r="H240" s="13" t="n"/>
-      <c r="I240" s="13" t="n"/>
-    </row>
-    <row r="242" ht="22" customHeight="1">
-      <c r="A242" s="5" t="inlineStr">
-        <is>
-          <t>S26</t>
-        </is>
-      </c>
-      <c r="B242" s="6" t="inlineStr">
-        <is>
-          <t>Stand 26 — Maison André Goichot (Bourgogne)</t>
-        </is>
-      </c>
-      <c r="C242" s="7" t="n"/>
-      <c r="D242" s="7" t="n"/>
-      <c r="E242" s="7" t="n"/>
-      <c r="F242" s="7" t="n"/>
-      <c r="G242" s="7" t="n"/>
-      <c r="H242" s="7" t="n"/>
-      <c r="I242" s="7" t="n"/>
-    </row>
-    <row r="243" ht="26" customHeight="1">
-      <c r="B243" s="8" t="inlineStr">
-        <is>
-          <t>Château du Cray — paliers du tarif</t>
-        </is>
-      </c>
-      <c r="C243" s="9" t="n"/>
-      <c r="D243" s="9" t="n"/>
-      <c r="E243" s="9" t="n"/>
-      <c r="F243" s="8" t="inlineStr">
+      <c r="E243" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
+      <c r="F243" s="13" t="n"/>
+      <c r="G243" s="13" t="n"/>
+      <c r="H243" s="14" t="n"/>
+      <c r="I243" s="14" t="n"/>
+    </row>
+    <row r="245" ht="22" customHeight="1">
+      <c r="A245" s="5" t="inlineStr">
+        <is>
+          <t>S25</t>
+        </is>
+      </c>
+      <c r="B245" s="6" t="inlineStr">
+        <is>
+          <t>Stand 25 — Chai Berteaud Manceau (Loire)</t>
+        </is>
+      </c>
+      <c r="C245" s="7" t="n"/>
+      <c r="D245" s="7" t="n"/>
+      <c r="E245" s="7" t="n"/>
+      <c r="F245" s="7" t="n"/>
+      <c r="G245" s="7" t="n"/>
+      <c r="H245" s="7" t="n"/>
+      <c r="I245" s="7" t="n"/>
+    </row>
+    <row r="246" ht="26" customHeight="1">
+      <c r="B246" s="8" t="inlineStr">
+        <is>
+          <t>Chai Berteaud Manceau — paliers du tarif</t>
+        </is>
+      </c>
+      <c r="C246" s="9" t="n"/>
+      <c r="D246" s="9" t="n"/>
+      <c r="E246" s="9" t="n"/>
+      <c r="F246" s="8" t="inlineStr">
         <is>
           <t>Prix unique</t>
         </is>
       </c>
-      <c r="G243" s="10" t="inlineStr">
-        <is>
-          <t>À partir de 78 bts</t>
-        </is>
-      </c>
-      <c r="H243" s="10" t="inlineStr">
-        <is>
-          <t>À partir de 126 bts</t>
-        </is>
-      </c>
-      <c r="I243" s="10" t="n"/>
-    </row>
-    <row r="244">
-      <c r="A244" s="11" t="inlineStr">
-        <is>
-          <t>S26 V01</t>
-        </is>
-      </c>
-      <c r="B244" s="12" t="inlineStr">
-        <is>
-          <t>Bourgogne Chardonnay</t>
-        </is>
-      </c>
-      <c r="C244" s="12" t="inlineStr">
-        <is>
-          <t>Blanc</t>
-        </is>
-      </c>
-      <c r="D244" s="12" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E244" s="12" t="inlineStr">
-        <is>
-          <t>75 cl</t>
-        </is>
-      </c>
-      <c r="F244" s="13" t="n"/>
-      <c r="G244" s="13" t="n"/>
-      <c r="H244" s="13" t="n"/>
-      <c r="I244" s="14" t="n"/>
-    </row>
-    <row r="245">
-      <c r="A245" s="11" t="inlineStr">
-        <is>
-          <t>S26 V02</t>
-        </is>
-      </c>
-      <c r="B245" s="12" t="inlineStr">
-        <is>
-          <t>AOC Pouilly-Vinzelles</t>
-        </is>
-      </c>
-      <c r="C245" s="12" t="inlineStr">
-        <is>
-          <t>Blanc</t>
-        </is>
-      </c>
-      <c r="D245" s="12" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E245" s="12" t="n"/>
-      <c r="F245" s="13" t="n"/>
-      <c r="G245" s="13" t="n"/>
-      <c r="H245" s="13" t="n"/>
-      <c r="I245" s="14" t="n"/>
-    </row>
-    <row r="246">
-      <c r="A246" s="11" t="inlineStr">
-        <is>
-          <t>S26 V03</t>
-        </is>
-      </c>
-      <c r="B246" s="12" t="inlineStr">
-        <is>
-          <t>AOP Auxey-Duresses</t>
-        </is>
-      </c>
-      <c r="C246" s="12" t="inlineStr">
-        <is>
-          <t>Rouge</t>
-        </is>
-      </c>
-      <c r="D246" s="12" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E246" s="12" t="inlineStr">
-        <is>
-          <t>75 cl</t>
-        </is>
-      </c>
-      <c r="F246" s="13" t="n"/>
-      <c r="G246" s="13" t="n"/>
-      <c r="H246" s="13" t="n"/>
-      <c r="I246" s="14" t="n"/>
+      <c r="G246" s="10" t="inlineStr">
+        <is>
+          <t>À partir de 60 bts</t>
+        </is>
+      </c>
+      <c r="H246" s="10" t="inlineStr">
+        <is>
+          <t>À partir de 120 bts</t>
+        </is>
+      </c>
+      <c r="I246" s="10" t="inlineStr">
+        <is>
+          <t>À partir de 240 bts</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="11" t="inlineStr">
         <is>
-          <t>S26 V04</t>
+          <t>S25 V01</t>
         </is>
       </c>
       <c r="B247" s="12" t="inlineStr">
         <is>
-          <t>AOC Crémant de Bourgogne — Baron Auguste Blanc</t>
+          <t>IGP Val de Loire — Courant Chenin</t>
         </is>
       </c>
       <c r="C247" s="12" t="inlineStr">
         <is>
-          <t>Blanc</t>
-        </is>
-      </c>
-      <c r="D247" s="12" t="n"/>
-      <c r="E247" s="12" t="n"/>
+          <t>Blanc sec</t>
+        </is>
+      </c>
+      <c r="D247" s="12" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E247" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
       <c r="F247" s="13" t="n"/>
       <c r="G247" s="13" t="n"/>
       <c r="H247" s="13" t="n"/>
-      <c r="I247" s="14" t="n"/>
+      <c r="I247" s="13" t="n"/>
     </row>
     <row r="248">
       <c r="A248" s="11" t="inlineStr">
         <is>
-          <t>S26 V05</t>
+          <t>S25 V02</t>
         </is>
       </c>
       <c r="B248" s="12" t="inlineStr">
         <is>
-          <t>AOC Crémant de Bourgogne — Baron Auguste Rosé</t>
+          <t>IGP Val de Loire — Source Melon B.</t>
         </is>
       </c>
       <c r="C248" s="12" t="inlineStr">
         <is>
-          <t>Rosé</t>
-        </is>
-      </c>
-      <c r="D248" s="12" t="n"/>
-      <c r="E248" s="12" t="n"/>
+          <t>Blanc sec</t>
+        </is>
+      </c>
+      <c r="D248" s="12" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E248" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
       <c r="F248" s="13" t="n"/>
       <c r="G248" s="13" t="n"/>
       <c r="H248" s="13" t="n"/>
-      <c r="I248" s="14" t="n"/>
+      <c r="I248" s="13" t="n"/>
     </row>
     <row r="249">
       <c r="A249" s="11" t="inlineStr">
         <is>
-          <t>S26 V06</t>
+          <t>S25 V03</t>
         </is>
       </c>
       <c r="B249" s="12" t="inlineStr">
         <is>
-          <t>Bourgogne Pinot Noir</t>
+          <t>IGP Val de Loire — Reflet Gamay</t>
         </is>
       </c>
       <c r="C249" s="12" t="inlineStr">
@@ -6647,7 +6746,7 @@
       </c>
       <c r="D249" s="12" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E249" s="12" t="inlineStr">
@@ -6658,138 +6757,94 @@
       <c r="F249" s="13" t="n"/>
       <c r="G249" s="13" t="n"/>
       <c r="H249" s="13" t="n"/>
-      <c r="I249" s="14" t="n"/>
+      <c r="I249" s="13" t="n"/>
     </row>
     <row r="250">
       <c r="A250" s="11" t="inlineStr">
         <is>
-          <t>S26 V07</t>
+          <t>S25 V04</t>
         </is>
       </c>
       <c r="B250" s="12" t="inlineStr">
         <is>
-          <t>AOP Chassagne-Montrachet</t>
+          <t>VDF — L’Eberluant Chardonnay Méthode ancestrale</t>
         </is>
       </c>
       <c r="C250" s="12" t="inlineStr">
         <is>
-          <t>Rouge</t>
+          <t>Blanc pétillant</t>
         </is>
       </c>
       <c r="D250" s="12" t="inlineStr">
         <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E250" s="12" t="inlineStr">
-        <is>
-          <t>75 cl</t>
-        </is>
-      </c>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E250" s="12" t="n"/>
       <c r="F250" s="13" t="n"/>
       <c r="G250" s="13" t="n"/>
       <c r="H250" s="13" t="n"/>
-      <c r="I250" s="14" t="n"/>
-    </row>
-    <row r="251">
-      <c r="A251" s="11" t="inlineStr">
-        <is>
-          <t>S26 V08</t>
-        </is>
-      </c>
-      <c r="B251" s="12" t="inlineStr">
-        <is>
-          <t>AOC Nuits-Saint-Georges — Aux Allots</t>
-        </is>
-      </c>
-      <c r="C251" s="12" t="inlineStr">
-        <is>
-          <t>Rouge</t>
-        </is>
-      </c>
-      <c r="D251" s="12" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E251" s="12" t="n"/>
-      <c r="F251" s="13" t="n"/>
-      <c r="G251" s="13" t="n"/>
-      <c r="H251" s="13" t="n"/>
-      <c r="I251" s="14" t="n"/>
-    </row>
-    <row r="252">
-      <c r="A252" s="11" t="inlineStr">
-        <is>
-          <t>S26 V09</t>
-        </is>
-      </c>
-      <c r="B252" s="12" t="inlineStr">
-        <is>
-          <t>AOC Mercurey</t>
-        </is>
-      </c>
-      <c r="C252" s="12" t="inlineStr">
-        <is>
-          <t>Blanc</t>
-        </is>
-      </c>
-      <c r="D252" s="12" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E252" s="12" t="n"/>
-      <c r="F252" s="13" t="n"/>
-      <c r="G252" s="13" t="n"/>
-      <c r="H252" s="13" t="n"/>
-      <c r="I252" s="14" t="n"/>
-    </row>
-    <row r="253">
-      <c r="A253" s="11" t="inlineStr">
-        <is>
-          <t>S26 V10</t>
-        </is>
-      </c>
-      <c r="B253" s="12" t="inlineStr">
-        <is>
-          <t>AOP Mercurey</t>
-        </is>
-      </c>
-      <c r="C253" s="12" t="inlineStr">
-        <is>
-          <t>Rouge</t>
-        </is>
-      </c>
-      <c r="D253" s="12" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="E253" s="12" t="inlineStr">
-        <is>
-          <t>75 cl</t>
-        </is>
-      </c>
-      <c r="F253" s="13" t="n"/>
-      <c r="G253" s="13" t="n"/>
-      <c r="H253" s="13" t="n"/>
-      <c r="I253" s="14" t="n"/>
+      <c r="I250" s="13" t="n"/>
+    </row>
+    <row r="252" ht="22" customHeight="1">
+      <c r="A252" s="5" t="inlineStr">
+        <is>
+          <t>S26</t>
+        </is>
+      </c>
+      <c r="B252" s="6" t="inlineStr">
+        <is>
+          <t>Stand 26 — Maison André Goichot (Bourgogne)</t>
+        </is>
+      </c>
+      <c r="C252" s="7" t="n"/>
+      <c r="D252" s="7" t="n"/>
+      <c r="E252" s="7" t="n"/>
+      <c r="F252" s="7" t="n"/>
+      <c r="G252" s="7" t="n"/>
+      <c r="H252" s="7" t="n"/>
+      <c r="I252" s="7" t="n"/>
+    </row>
+    <row r="253" ht="26" customHeight="1">
+      <c r="B253" s="8" t="inlineStr">
+        <is>
+          <t>Château du Cray — paliers du tarif</t>
+        </is>
+      </c>
+      <c r="C253" s="9" t="n"/>
+      <c r="D253" s="9" t="n"/>
+      <c r="E253" s="9" t="n"/>
+      <c r="F253" s="8" t="inlineStr">
+        <is>
+          <t>Prix unique</t>
+        </is>
+      </c>
+      <c r="G253" s="10" t="inlineStr">
+        <is>
+          <t>À partir de 78 bts</t>
+        </is>
+      </c>
+      <c r="H253" s="10" t="inlineStr">
+        <is>
+          <t>À partir de 126 bts</t>
+        </is>
+      </c>
+      <c r="I253" s="10" t="n"/>
     </row>
     <row r="254">
       <c r="A254" s="11" t="inlineStr">
         <is>
-          <t>S26 V11</t>
+          <t>S26 V01</t>
         </is>
       </c>
       <c r="B254" s="12" t="inlineStr">
         <is>
-          <t>AOC Givry</t>
+          <t>AOC Bourgogne Chardonnay — Château du Cray Blanc</t>
         </is>
       </c>
       <c r="C254" s="12" t="inlineStr">
         <is>
-          <t>Rouge</t>
+          <t>Blanc</t>
         </is>
       </c>
       <c r="D254" s="12" t="inlineStr">
@@ -6797,7 +6852,11 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="E254" s="12" t="n"/>
+      <c r="E254" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
       <c r="F254" s="13" t="n"/>
       <c r="G254" s="13" t="n"/>
       <c r="H254" s="13" t="n"/>
@@ -6806,34 +6865,320 @@
     <row r="255">
       <c r="A255" s="11" t="inlineStr">
         <is>
-          <t>S26 V12</t>
+          <t>S26 V02</t>
         </is>
       </c>
       <c r="B255" s="12" t="inlineStr">
         <is>
-          <t>AOP Gevrey-Chambertin</t>
+          <t>AOC Pouilly-Vinzelles Blanc</t>
         </is>
       </c>
       <c r="C255" s="12" t="inlineStr">
         <is>
-          <t>Rouge</t>
+          <t>Blanc</t>
         </is>
       </c>
       <c r="D255" s="12" t="inlineStr">
         <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="E255" s="12" t="inlineStr">
-        <is>
-          <t>75 cl</t>
-        </is>
-      </c>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E255" s="12" t="n"/>
       <c r="F255" s="13" t="n"/>
       <c r="G255" s="13" t="n"/>
       <c r="H255" s="13" t="n"/>
       <c r="I255" s="14" t="n"/>
     </row>
+    <row r="256">
+      <c r="A256" s="11" t="inlineStr">
+        <is>
+          <t>S26 V03</t>
+        </is>
+      </c>
+      <c r="B256" s="12" t="inlineStr">
+        <is>
+          <t>AOC Auxey-Duresses</t>
+        </is>
+      </c>
+      <c r="C256" s="12" t="inlineStr">
+        <is>
+          <t>Rouge</t>
+        </is>
+      </c>
+      <c r="D256" s="12" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E256" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
+      <c r="F256" s="13" t="n"/>
+      <c r="G256" s="13" t="n"/>
+      <c r="H256" s="13" t="n"/>
+      <c r="I256" s="14" t="n"/>
+    </row>
+    <row r="257">
+      <c r="A257" s="11" t="inlineStr">
+        <is>
+          <t>S26 V04</t>
+        </is>
+      </c>
+      <c r="B257" s="12" t="inlineStr">
+        <is>
+          <t>AOC Crémant de Bourgogne — Baron Auguste Blanc</t>
+        </is>
+      </c>
+      <c r="C257" s="12" t="inlineStr">
+        <is>
+          <t>Blanc effervescent</t>
+        </is>
+      </c>
+      <c r="D257" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E257" s="12" t="n"/>
+      <c r="F257" s="13" t="n"/>
+      <c r="G257" s="13" t="n"/>
+      <c r="H257" s="13" t="n"/>
+      <c r="I257" s="14" t="n"/>
+    </row>
+    <row r="258">
+      <c r="A258" s="11" t="inlineStr">
+        <is>
+          <t>S26 V05</t>
+        </is>
+      </c>
+      <c r="B258" s="12" t="inlineStr">
+        <is>
+          <t>AOC Crémant de Bourgogne — Baron Auguste Rosé</t>
+        </is>
+      </c>
+      <c r="C258" s="12" t="inlineStr">
+        <is>
+          <t>Rosé effervescent</t>
+        </is>
+      </c>
+      <c r="D258" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E258" s="12" t="n"/>
+      <c r="F258" s="13" t="n"/>
+      <c r="G258" s="13" t="n"/>
+      <c r="H258" s="13" t="n"/>
+      <c r="I258" s="14" t="n"/>
+    </row>
+    <row r="259">
+      <c r="A259" s="11" t="inlineStr">
+        <is>
+          <t>S26 V06</t>
+        </is>
+      </c>
+      <c r="B259" s="12" t="inlineStr">
+        <is>
+          <t>AOC Bourgogne Pinot Noir — Domaine les Guignottes Rouge</t>
+        </is>
+      </c>
+      <c r="C259" s="12" t="inlineStr">
+        <is>
+          <t>Rouge</t>
+        </is>
+      </c>
+      <c r="D259" s="12" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E259" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
+      <c r="F259" s="13" t="n"/>
+      <c r="G259" s="13" t="n"/>
+      <c r="H259" s="13" t="n"/>
+      <c r="I259" s="14" t="n"/>
+    </row>
+    <row r="260">
+      <c r="A260" s="11" t="inlineStr">
+        <is>
+          <t>S26 V07</t>
+        </is>
+      </c>
+      <c r="B260" s="12" t="inlineStr">
+        <is>
+          <t>AOC Chassagne-Montrachet Rouge</t>
+        </is>
+      </c>
+      <c r="C260" s="12" t="inlineStr">
+        <is>
+          <t>Rouge</t>
+        </is>
+      </c>
+      <c r="D260" s="12" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E260" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
+      <c r="F260" s="13" t="n"/>
+      <c r="G260" s="13" t="n"/>
+      <c r="H260" s="13" t="n"/>
+      <c r="I260" s="14" t="n"/>
+    </row>
+    <row r="261">
+      <c r="A261" s="11" t="inlineStr">
+        <is>
+          <t>S26 V08</t>
+        </is>
+      </c>
+      <c r="B261" s="12" t="inlineStr">
+        <is>
+          <t>AOC Nuits-Saint-Georges — Aux Allots Rouge</t>
+        </is>
+      </c>
+      <c r="C261" s="12" t="inlineStr">
+        <is>
+          <t>Rouge</t>
+        </is>
+      </c>
+      <c r="D261" s="12" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E261" s="12" t="n"/>
+      <c r="F261" s="13" t="n"/>
+      <c r="G261" s="13" t="n"/>
+      <c r="H261" s="13" t="n"/>
+      <c r="I261" s="14" t="n"/>
+    </row>
+    <row r="262">
+      <c r="A262" s="11" t="inlineStr">
+        <is>
+          <t>S26 V09</t>
+        </is>
+      </c>
+      <c r="B262" s="12" t="inlineStr">
+        <is>
+          <t>AOC Mercurey Blanc</t>
+        </is>
+      </c>
+      <c r="C262" s="12" t="inlineStr">
+        <is>
+          <t>Blanc</t>
+        </is>
+      </c>
+      <c r="D262" s="12" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E262" s="12" t="n"/>
+      <c r="F262" s="13" t="n"/>
+      <c r="G262" s="13" t="n"/>
+      <c r="H262" s="13" t="n"/>
+      <c r="I262" s="14" t="n"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="11" t="inlineStr">
+        <is>
+          <t>S26 V10</t>
+        </is>
+      </c>
+      <c r="B263" s="12" t="inlineStr">
+        <is>
+          <t>AOC Mercurey Rouge</t>
+        </is>
+      </c>
+      <c r="C263" s="12" t="inlineStr">
+        <is>
+          <t>Rouge</t>
+        </is>
+      </c>
+      <c r="D263" s="12" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="E263" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
+      <c r="F263" s="13" t="n"/>
+      <c r="G263" s="13" t="n"/>
+      <c r="H263" s="13" t="n"/>
+      <c r="I263" s="14" t="n"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="11" t="inlineStr">
+        <is>
+          <t>S26 V11</t>
+        </is>
+      </c>
+      <c r="B264" s="12" t="inlineStr">
+        <is>
+          <t>AOC Givry Rouge</t>
+        </is>
+      </c>
+      <c r="C264" s="12" t="inlineStr">
+        <is>
+          <t>Rouge</t>
+        </is>
+      </c>
+      <c r="D264" s="12" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E264" s="12" t="n"/>
+      <c r="F264" s="13" t="n"/>
+      <c r="G264" s="13" t="n"/>
+      <c r="H264" s="13" t="n"/>
+      <c r="I264" s="14" t="n"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="11" t="inlineStr">
+        <is>
+          <t>S26 V12</t>
+        </is>
+      </c>
+      <c r="B265" s="12" t="inlineStr">
+        <is>
+          <t>AOC Gevrey-Chambertin</t>
+        </is>
+      </c>
+      <c r="C265" s="12" t="inlineStr">
+        <is>
+          <t>Rouge</t>
+        </is>
+      </c>
+      <c r="D265" s="12" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="E265" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
+      <c r="F265" s="13" t="n"/>
+      <c r="G265" s="13" t="n"/>
+      <c r="H265" s="13" t="n"/>
+      <c r="I265" s="14" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tableur/prix-salon-prive-2026.xlsx
+++ b/tableur/prix-salon-prive-2026.xlsx
@@ -511,7 +511,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J271"/>
+  <dimension ref="A1:J280"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,11 @@
           <t>2022</t>
         </is>
       </c>
-      <c r="E8" s="12" t="n"/>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
       <c r="F8" s="13" t="n"/>
       <c r="G8" s="13" t="n">
         <v>7.71</v>
@@ -699,7 +703,11 @@
           <t>2018</t>
         </is>
       </c>
-      <c r="E9" s="12" t="n"/>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
       <c r="F9" s="13" t="n"/>
       <c r="G9" s="13" t="n">
         <v>7.25</v>
@@ -1012,7 +1020,11 @@
           <t>2018</t>
         </is>
       </c>
-      <c r="E19" s="12" t="n"/>
+      <c r="E19" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
       <c r="F19" s="13" t="n"/>
       <c r="G19" s="13" t="n">
         <v>19.14</v>
@@ -1121,7 +1133,7 @@
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
-          <t>Magnum 1,5 L</t>
+          <t>1,5 L</t>
         </is>
       </c>
       <c r="F24" s="13" t="n">
@@ -1189,7 +1201,7 @@
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
-          <t>Magnum 1,5 L</t>
+          <t>1,5 L</t>
         </is>
       </c>
       <c r="F26" s="13" t="n">
@@ -1291,7 +1303,7 @@
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Magnum 1,5 L</t>
+          <t>1,5 L</t>
         </is>
       </c>
       <c r="F29" s="13" t="n">
@@ -1430,7 +1442,11 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="E35" s="12" t="n"/>
+      <c r="E35" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
       <c r="F35" s="13" t="n">
         <v>3.65</v>
       </c>
@@ -1691,10 +1707,10 @@
         <v>6.1</v>
       </c>
       <c r="H44" s="13" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="I44" s="13" t="n">
         <v>5.45</v>
-      </c>
-      <c r="I44" s="13" t="n">
-        <v>5.75</v>
       </c>
       <c r="J44" s="14" t="n"/>
     </row>
@@ -1795,7 +1811,11 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="E47" s="12" t="n"/>
+      <c r="E47" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
       <c r="F47" s="13" t="n"/>
       <c r="G47" s="13" t="n">
         <v>5.75</v>
@@ -1829,16 +1849,20 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E48" s="12" t="n"/>
+      <c r="E48" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
       <c r="F48" s="13" t="n"/>
       <c r="G48" s="13" t="n">
         <v>6.4</v>
       </c>
       <c r="H48" s="13" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="I48" s="13" t="n">
         <v>5.45</v>
-      </c>
-      <c r="I48" s="13" t="n">
-        <v>5.75</v>
       </c>
       <c r="J48" s="14" t="n"/>
     </row>
@@ -2142,7 +2166,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E58" s="12" t="n"/>
+      <c r="E58" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
       <c r="F58" s="13" t="n"/>
       <c r="G58" s="13" t="n">
         <v>4</v>
@@ -2328,7 +2356,7 @@
       </c>
       <c r="B65" s="12" t="inlineStr">
         <is>
-          <t>AOC Côtes du Rhône — Le Prieuré Rouge</t>
+          <t>AOC Luberon — Terroir d’Ansouis Rouge</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
@@ -2338,7 +2366,7 @@
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="E65" s="12" t="inlineStr">
@@ -2348,13 +2376,13 @@
       </c>
       <c r="F65" s="13" t="n"/>
       <c r="G65" s="13" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="H65" s="13" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="I65" s="13" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="J65" s="14" t="n"/>
     </row>
@@ -2366,7 +2394,7 @@
       </c>
       <c r="B66" s="12" t="inlineStr">
         <is>
-          <t>AOC Châteauneuf-du-Pape — Vieilles Vignes Rouge</t>
+          <t>AOC Côtes du Rhône — Le Prieuré Rouge</t>
         </is>
       </c>
       <c r="C66" s="12" t="inlineStr">
@@ -2376,7 +2404,7 @@
       </c>
       <c r="D66" s="12" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E66" s="12" t="inlineStr">
@@ -2386,13 +2414,13 @@
       </c>
       <c r="F66" s="13" t="n"/>
       <c r="G66" s="13" t="n">
-        <v>18</v>
+        <v>5.7</v>
       </c>
       <c r="H66" s="13" t="n">
-        <v>17.5</v>
+        <v>5.4</v>
       </c>
       <c r="I66" s="13" t="n">
-        <v>17</v>
+        <v>5.2</v>
       </c>
       <c r="J66" s="14" t="n"/>
     </row>
@@ -2414,7 +2442,7 @@
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="E67" s="12" t="inlineStr">
@@ -2442,7 +2470,7 @@
       </c>
       <c r="B68" s="12" t="inlineStr">
         <is>
-          <t>AOC Châteauneuf-du-Pape — Le Couchant Rouge</t>
+          <t>AOC Châteauneuf-du-Pape — Vieilles Vignes Rouge</t>
         </is>
       </c>
       <c r="C68" s="12" t="inlineStr">
@@ -2452,7 +2480,7 @@
       </c>
       <c r="D68" s="12" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="E68" s="12" t="inlineStr">
@@ -2462,13 +2490,13 @@
       </c>
       <c r="F68" s="13" t="n"/>
       <c r="G68" s="13" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="H68" s="13" t="n">
-        <v>26.5</v>
+        <v>17.5</v>
       </c>
       <c r="I68" s="13" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="J68" s="14" t="n"/>
     </row>
@@ -2480,17 +2508,17 @@
       </c>
       <c r="B69" s="12" t="inlineStr">
         <is>
-          <t>IGP Méditerranée — Premières Fleurs Blanc</t>
+          <t>AOC Châteauneuf-du-Pape — Le Couchant Rouge</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>Blanc</t>
+          <t>Rouge</t>
         </is>
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="E69" s="12" t="inlineStr">
@@ -2500,13 +2528,13 @@
       </c>
       <c r="F69" s="13" t="n"/>
       <c r="G69" s="13" t="n">
-        <v>5.5</v>
+        <v>27</v>
       </c>
       <c r="H69" s="13" t="n">
-        <v>5.2</v>
+        <v>26.5</v>
       </c>
       <c r="I69" s="13" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="J69" s="14" t="n"/>
     </row>
@@ -2518,17 +2546,17 @@
       </c>
       <c r="B70" s="12" t="inlineStr">
         <is>
-          <t>IGP Méditerranée — Premières Fleurs Rouge</t>
+          <t>IGP Méditerranée — Premières Fleurs Blanc</t>
         </is>
       </c>
       <c r="C70" s="12" t="inlineStr">
         <is>
-          <t>Rouge</t>
+          <t>Blanc</t>
         </is>
       </c>
       <c r="D70" s="12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E70" s="12" t="inlineStr">
@@ -2556,17 +2584,17 @@
       </c>
       <c r="B71" s="12" t="inlineStr">
         <is>
-          <t>AOC Muscat BDV — Or des Dentelles Blanc Moelleux</t>
+          <t>IGP Méditerranée — Premières Fleurs Rouge</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
         <is>
-          <t>Blanc moelleux</t>
+          <t>Rouge</t>
         </is>
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E71" s="12" t="inlineStr">
@@ -2576,13 +2604,13 @@
       </c>
       <c r="F71" s="13" t="n"/>
       <c r="G71" s="13" t="n">
-        <v>7.9</v>
+        <v>5.5</v>
       </c>
       <c r="H71" s="13" t="n">
-        <v>7.4</v>
+        <v>5.2</v>
       </c>
       <c r="I71" s="13" t="n">
-        <v>6.9</v>
+        <v>5</v>
       </c>
       <c r="J71" s="14" t="n"/>
     </row>
@@ -2604,23 +2632,23 @@
       </c>
       <c r="D72" s="12" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="E72" s="12" t="inlineStr">
         <is>
-          <t>37,5 cl</t>
+          <t>75 cl</t>
         </is>
       </c>
       <c r="F72" s="13" t="n"/>
       <c r="G72" s="13" t="n">
-        <v>4.7</v>
+        <v>7.9</v>
       </c>
       <c r="H72" s="13" t="n">
-        <v>4.4</v>
+        <v>7.4</v>
       </c>
       <c r="I72" s="13" t="n">
-        <v>4.1</v>
+        <v>6.9</v>
       </c>
       <c r="J72" s="14" t="n"/>
     </row>
@@ -2632,33 +2660,33 @@
       </c>
       <c r="B73" s="12" t="inlineStr">
         <is>
-          <t>Beaumes de Venise — Les Jumelles Rouge</t>
+          <t>AOC Muscat BDV — Or des Dentelles Blanc Moelleux</t>
         </is>
       </c>
       <c r="C73" s="12" t="inlineStr">
         <is>
-          <t>Rouge</t>
+          <t>Blanc moelleux</t>
         </is>
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="E73" s="12" t="inlineStr">
         <is>
-          <t>75 cl</t>
+          <t>37,5 cl</t>
         </is>
       </c>
       <c r="F73" s="13" t="n"/>
       <c r="G73" s="13" t="n">
-        <v>6.5</v>
+        <v>4.7</v>
       </c>
       <c r="H73" s="13" t="n">
-        <v>6</v>
+        <v>4.4</v>
       </c>
       <c r="I73" s="13" t="n">
-        <v>5.5</v>
+        <v>4.1</v>
       </c>
       <c r="J73" s="14" t="n"/>
     </row>
@@ -2670,7 +2698,7 @@
       </c>
       <c r="B74" s="12" t="inlineStr">
         <is>
-          <t>AOC Côtes du Rhône — Côtes du Rhône Rouge</t>
+          <t>Beaumes de Venise — Les Jumelles Rouge</t>
         </is>
       </c>
       <c r="C74" s="12" t="inlineStr">
@@ -2680,7 +2708,7 @@
       </c>
       <c r="D74" s="12" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E74" s="12" t="inlineStr">
@@ -2690,98 +2718,102 @@
       </c>
       <c r="F74" s="13" t="n"/>
       <c r="G74" s="13" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H74" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="I74" s="13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J74" s="14" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="11" t="inlineStr">
+        <is>
+          <t>S07 V14</t>
+        </is>
+      </c>
+      <c r="B75" s="12" t="inlineStr">
+        <is>
+          <t>AOC Côtes du Rhône — Côtes du Rhône Rouge</t>
+        </is>
+      </c>
+      <c r="C75" s="12" t="inlineStr">
+        <is>
+          <t>Rouge</t>
+        </is>
+      </c>
+      <c r="D75" s="12" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E75" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
+      <c r="F75" s="13" t="n"/>
+      <c r="G75" s="13" t="n">
         <v>5.7</v>
       </c>
-      <c r="H74" s="13" t="n">
+      <c r="H75" s="13" t="n">
         <v>5.4</v>
       </c>
-      <c r="I74" s="13" t="n">
+      <c r="I75" s="13" t="n">
         <v>5.2</v>
       </c>
-      <c r="J74" s="14" t="n"/>
-    </row>
-    <row r="76" ht="22" customHeight="1">
-      <c r="A76" s="5" t="inlineStr">
+      <c r="J75" s="14" t="n"/>
+    </row>
+    <row r="77" ht="22" customHeight="1">
+      <c r="A77" s="5" t="inlineStr">
         <is>
           <t>S08</t>
         </is>
       </c>
-      <c r="B76" s="6" t="inlineStr">
+      <c r="B77" s="6" t="inlineStr">
         <is>
           <t>Stand 8 — Château Falfas (Bordeaux)</t>
         </is>
       </c>
-      <c r="C76" s="7" t="n"/>
-      <c r="D76" s="7" t="n"/>
-      <c r="E76" s="7" t="n"/>
-      <c r="F76" s="7" t="n"/>
-      <c r="G76" s="7" t="n"/>
-      <c r="H76" s="7" t="n"/>
-      <c r="I76" s="7" t="n"/>
-      <c r="J76" s="7" t="n"/>
-    </row>
-    <row r="77" ht="26" customHeight="1">
-      <c r="B77" s="8" t="inlineStr">
+      <c r="C77" s="7" t="n"/>
+      <c r="D77" s="7" t="n"/>
+      <c r="E77" s="7" t="n"/>
+      <c r="F77" s="7" t="n"/>
+      <c r="G77" s="7" t="n"/>
+      <c r="H77" s="7" t="n"/>
+      <c r="I77" s="7" t="n"/>
+      <c r="J77" s="7" t="n"/>
+    </row>
+    <row r="78" ht="26" customHeight="1">
+      <c r="B78" s="8" t="inlineStr">
         <is>
           <t>Château Falfas — paliers du salon</t>
         </is>
       </c>
-      <c r="C77" s="9" t="n"/>
-      <c r="D77" s="9" t="n"/>
-      <c r="E77" s="9" t="n"/>
-      <c r="F77" s="8" t="inlineStr">
+      <c r="C78" s="9" t="n"/>
+      <c r="D78" s="9" t="n"/>
+      <c r="E78" s="9" t="n"/>
+      <c r="F78" s="8" t="inlineStr">
         <is>
           <t>Prix unique</t>
         </is>
       </c>
-      <c r="G77" s="10" t="n"/>
-      <c r="H77" s="10" t="n"/>
-      <c r="I77" s="10" t="n"/>
-      <c r="J77" s="10" t="n"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="11" t="inlineStr">
-        <is>
-          <t>S08 V01</t>
-        </is>
-      </c>
-      <c r="B78" s="12" t="inlineStr">
-        <is>
-          <t>AOC Côtes de Bourg — Les Demoiselles de Falfas</t>
-        </is>
-      </c>
-      <c r="C78" s="12" t="inlineStr">
-        <is>
-          <t>Rouge</t>
-        </is>
-      </c>
-      <c r="D78" s="12" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E78" s="12" t="inlineStr">
-        <is>
-          <t>75 cl</t>
-        </is>
-      </c>
-      <c r="F78" s="13" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="G78" s="14" t="n"/>
-      <c r="H78" s="14" t="n"/>
-      <c r="I78" s="14" t="n"/>
-      <c r="J78" s="14" t="n"/>
+      <c r="G78" s="10" t="n"/>
+      <c r="H78" s="10" t="n"/>
+      <c r="I78" s="10" t="n"/>
+      <c r="J78" s="10" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="11" t="inlineStr">
         <is>
-          <t>S08 V02</t>
+          <t>S08 V01</t>
         </is>
       </c>
       <c r="B79" s="12" t="inlineStr">
         <is>
-          <t>AOC Côtes de Bourg — Château Falfas</t>
+          <t>AOC Côtes de Bourg — Les Demoiselles de Falfas</t>
         </is>
       </c>
       <c r="C79" s="12" t="inlineStr">
@@ -2791,7 +2823,7 @@
       </c>
       <c r="D79" s="12" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E79" s="12" t="inlineStr">
@@ -2800,7 +2832,7 @@
         </is>
       </c>
       <c r="F79" s="13" t="n">
-        <v>12.3</v>
+        <v>9.5</v>
       </c>
       <c r="G79" s="14" t="n"/>
       <c r="H79" s="14" t="n"/>
@@ -2810,7 +2842,7 @@
     <row r="80">
       <c r="A80" s="11" t="inlineStr">
         <is>
-          <t>S08 V03</t>
+          <t>S08 V02</t>
         </is>
       </c>
       <c r="B80" s="12" t="inlineStr">
@@ -2825,7 +2857,7 @@
       </c>
       <c r="D80" s="12" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="E80" s="12" t="inlineStr">
@@ -2844,7 +2876,7 @@
     <row r="81">
       <c r="A81" s="11" t="inlineStr">
         <is>
-          <t>S08 V04</t>
+          <t>S08 V03</t>
         </is>
       </c>
       <c r="B81" s="12" t="inlineStr">
@@ -2859,7 +2891,7 @@
       </c>
       <c r="D81" s="12" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="E81" s="12" t="inlineStr">
@@ -2868,7 +2900,7 @@
         </is>
       </c>
       <c r="F81" s="13" t="n">
-        <v>12.4</v>
+        <v>12.3</v>
       </c>
       <c r="G81" s="14" t="n"/>
       <c r="H81" s="14" t="n"/>
@@ -2878,12 +2910,12 @@
     <row r="82">
       <c r="A82" s="11" t="inlineStr">
         <is>
-          <t>S08 V05</t>
+          <t>S08 V04</t>
         </is>
       </c>
       <c r="B82" s="12" t="inlineStr">
         <is>
-          <t>AOC Côtes de Bourg — Château Falfas Chevalier</t>
+          <t>AOC Côtes de Bourg — Château Falfas</t>
         </is>
       </c>
       <c r="C82" s="12" t="inlineStr">
@@ -2893,7 +2925,7 @@
       </c>
       <c r="D82" s="12" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="E82" s="12" t="inlineStr">
@@ -2902,7 +2934,7 @@
         </is>
       </c>
       <c r="F82" s="13" t="n">
-        <v>24.2</v>
+        <v>12.4</v>
       </c>
       <c r="G82" s="14" t="n"/>
       <c r="H82" s="14" t="n"/>
@@ -2912,7 +2944,7 @@
     <row r="83">
       <c r="A83" s="11" t="inlineStr">
         <is>
-          <t>S08 V06</t>
+          <t>S08 V05</t>
         </is>
       </c>
       <c r="B83" s="12" t="inlineStr">
@@ -2927,7 +2959,7 @@
       </c>
       <c r="D83" s="12" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="E83" s="12" t="inlineStr">
@@ -2936,7 +2968,7 @@
         </is>
       </c>
       <c r="F83" s="13" t="n">
-        <v>23.9</v>
+        <v>24.2</v>
       </c>
       <c r="G83" s="14" t="n"/>
       <c r="H83" s="14" t="n"/>
@@ -2946,12 +2978,12 @@
     <row r="84">
       <c r="A84" s="11" t="inlineStr">
         <is>
-          <t>S08 V07</t>
+          <t>S08 V06</t>
         </is>
       </c>
       <c r="B84" s="12" t="inlineStr">
         <is>
-          <t>AOC Côtes de Bourg — Château Falfas</t>
+          <t>AOC Côtes de Bourg — Château Falfas Chevalier</t>
         </is>
       </c>
       <c r="C84" s="12" t="inlineStr">
@@ -2961,7 +2993,7 @@
       </c>
       <c r="D84" s="12" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="E84" s="12" t="inlineStr">
@@ -2970,116 +3002,112 @@
         </is>
       </c>
       <c r="F84" s="13" t="n">
-        <v>20.1</v>
+        <v>23.9</v>
       </c>
       <c r="G84" s="14" t="n"/>
       <c r="H84" s="14" t="n"/>
       <c r="I84" s="14" t="n"/>
       <c r="J84" s="14" t="n"/>
     </row>
-    <row r="86" ht="22" customHeight="1">
-      <c r="A86" s="5" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="11" t="inlineStr">
+        <is>
+          <t>S08 V07</t>
+        </is>
+      </c>
+      <c r="B85" s="12" t="inlineStr">
+        <is>
+          <t>AOC Côtes de Bourg — Château Falfas</t>
+        </is>
+      </c>
+      <c r="C85" s="12" t="inlineStr">
+        <is>
+          <t>Rouge</t>
+        </is>
+      </c>
+      <c r="D85" s="12" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E85" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
+      <c r="F85" s="13" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="G85" s="14" t="n"/>
+      <c r="H85" s="14" t="n"/>
+      <c r="I85" s="14" t="n"/>
+      <c r="J85" s="14" t="n"/>
+    </row>
+    <row r="87" ht="22" customHeight="1">
+      <c r="A87" s="5" t="inlineStr">
         <is>
           <t>S09</t>
         </is>
       </c>
-      <c r="B86" s="6" t="inlineStr">
+      <c r="B87" s="6" t="inlineStr">
         <is>
           <t>Stand 9 — Domaine Boehler (Alsace)</t>
         </is>
       </c>
-      <c r="C86" s="7" t="n"/>
-      <c r="D86" s="7" t="n"/>
-      <c r="E86" s="7" t="n"/>
-      <c r="F86" s="7" t="n"/>
-      <c r="G86" s="7" t="n"/>
-      <c r="H86" s="7" t="n"/>
-      <c r="I86" s="7" t="n"/>
-      <c r="J86" s="7" t="n"/>
-    </row>
-    <row r="87" ht="26" customHeight="1">
-      <c r="B87" s="8" t="inlineStr">
+      <c r="C87" s="7" t="n"/>
+      <c r="D87" s="7" t="n"/>
+      <c r="E87" s="7" t="n"/>
+      <c r="F87" s="7" t="n"/>
+      <c r="G87" s="7" t="n"/>
+      <c r="H87" s="7" t="n"/>
+      <c r="I87" s="7" t="n"/>
+      <c r="J87" s="7" t="n"/>
+    </row>
+    <row r="88" ht="26" customHeight="1">
+      <c r="B88" s="8" t="inlineStr">
         <is>
           <t>Domaine Boehler — paliers du salon</t>
         </is>
       </c>
-      <c r="C87" s="9" t="n"/>
-      <c r="D87" s="9" t="n"/>
-      <c r="E87" s="9" t="n"/>
-      <c r="F87" s="8" t="inlineStr">
+      <c r="C88" s="9" t="n"/>
+      <c r="D88" s="9" t="n"/>
+      <c r="E88" s="9" t="n"/>
+      <c r="F88" s="8" t="inlineStr">
         <is>
           <t>Prix unique</t>
         </is>
       </c>
-      <c r="G87" s="10" t="inlineStr">
+      <c r="G88" s="10" t="inlineStr">
         <is>
           <t>À partir de 60 bts</t>
         </is>
       </c>
-      <c r="H87" s="10" t="inlineStr">
+      <c r="H88" s="10" t="inlineStr">
         <is>
           <t>À partir de 120 bts</t>
         </is>
       </c>
-      <c r="I87" s="10" t="inlineStr">
+      <c r="I88" s="10" t="inlineStr">
         <is>
           <t>À partir de 300 bts</t>
         </is>
       </c>
-      <c r="J87" s="10" t="n"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="11" t="inlineStr">
-        <is>
-          <t>S09 V01</t>
-        </is>
-      </c>
-      <c r="B88" s="12" t="inlineStr">
-        <is>
-          <t>AOC Crémant d’Alsace</t>
-        </is>
-      </c>
-      <c r="C88" s="12" t="inlineStr">
-        <is>
-          <t>Blanc brut nature</t>
-        </is>
-      </c>
-      <c r="D88" s="12" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="E88" s="12" t="inlineStr">
-        <is>
-          <t>75 cl</t>
-        </is>
-      </c>
-      <c r="F88" s="13" t="n"/>
-      <c r="G88" s="13" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="H88" s="13" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="I88" s="13" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="J88" s="14" t="n"/>
+      <c r="J88" s="10" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="11" t="inlineStr">
         <is>
-          <t>S09 V02</t>
+          <t>S09 V01</t>
         </is>
       </c>
       <c r="B89" s="12" t="inlineStr">
         <is>
-          <t>AOC Alsace — Molse Blanc</t>
+          <t>AOC Crémant d’Alsace</t>
         </is>
       </c>
       <c r="C89" s="12" t="inlineStr">
         <is>
-          <t>Blanc</t>
+          <t>Blanc brut nature</t>
         </is>
       </c>
       <c r="D89" s="12" t="inlineStr">
@@ -3094,30 +3122,30 @@
       </c>
       <c r="F89" s="13" t="n"/>
       <c r="G89" s="13" t="n">
-        <v>6.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H89" s="13" t="n">
-        <v>6.4</v>
+        <v>8.1</v>
       </c>
       <c r="I89" s="13" t="n">
-        <v>5.9</v>
+        <v>7.6</v>
       </c>
       <c r="J89" s="14" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="11" t="inlineStr">
         <is>
-          <t>S09 V03</t>
+          <t>S09 V02</t>
         </is>
       </c>
       <c r="B90" s="12" t="inlineStr">
         <is>
-          <t>AOC Alsace — Molse Rouge</t>
+          <t>AOC Alsace — Molse Blanc</t>
         </is>
       </c>
       <c r="C90" s="12" t="inlineStr">
         <is>
-          <t>Rouge</t>
+          <t>Blanc</t>
         </is>
       </c>
       <c r="D90" s="12" t="inlineStr">
@@ -3132,30 +3160,30 @@
       </c>
       <c r="F90" s="13" t="n"/>
       <c r="G90" s="13" t="n">
-        <v>8.4</v>
+        <v>6.8</v>
       </c>
       <c r="H90" s="13" t="n">
-        <v>7.8</v>
+        <v>6.4</v>
       </c>
       <c r="I90" s="13" t="n">
-        <v>7.3</v>
+        <v>5.9</v>
       </c>
       <c r="J90" s="14" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="11" t="inlineStr">
         <is>
-          <t>S09 V04</t>
+          <t>S09 V03</t>
         </is>
       </c>
       <c r="B91" s="12" t="inlineStr">
         <is>
-          <t>AOC Alsace — Leimen Sylvaner</t>
+          <t>AOC Alsace — Molse Rouge</t>
         </is>
       </c>
       <c r="C91" s="12" t="inlineStr">
         <is>
-          <t>Blanc sec</t>
+          <t>Rouge</t>
         </is>
       </c>
       <c r="D91" s="12" t="inlineStr">
@@ -3170,25 +3198,25 @@
       </c>
       <c r="F91" s="13" t="n"/>
       <c r="G91" s="13" t="n">
-        <v>8.699999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="H91" s="13" t="n">
-        <v>8.1</v>
+        <v>7.8</v>
       </c>
       <c r="I91" s="13" t="n">
-        <v>7.6</v>
+        <v>7.3</v>
       </c>
       <c r="J91" s="14" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="11" t="inlineStr">
         <is>
-          <t>S09 V05</t>
+          <t>S09 V04</t>
         </is>
       </c>
       <c r="B92" s="12" t="inlineStr">
         <is>
-          <t>AOC Alsace — Riesling Holderhurst</t>
+          <t>AOC Alsace — Leimen Sylvaner</t>
         </is>
       </c>
       <c r="C92" s="12" t="inlineStr">
@@ -3198,7 +3226,7 @@
       </c>
       <c r="D92" s="12" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E92" s="12" t="inlineStr">
@@ -3221,12 +3249,12 @@
     <row r="93">
       <c r="A93" s="11" t="inlineStr">
         <is>
-          <t>S09 V06</t>
+          <t>S09 V05</t>
         </is>
       </c>
       <c r="B93" s="12" t="inlineStr">
         <is>
-          <t>AOC Alsace — Riesling Hahnenberg</t>
+          <t>AOC Alsace — Riesling Holderhurst</t>
         </is>
       </c>
       <c r="C93" s="12" t="inlineStr">
@@ -3236,7 +3264,7 @@
       </c>
       <c r="D93" s="12" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="E93" s="12" t="inlineStr">
@@ -3246,25 +3274,25 @@
       </c>
       <c r="F93" s="13" t="n"/>
       <c r="G93" s="13" t="n">
-        <v>11.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H93" s="13" t="n">
-        <v>11</v>
+        <v>8.1</v>
       </c>
       <c r="I93" s="13" t="n">
-        <v>10.5</v>
+        <v>7.6</v>
       </c>
       <c r="J93" s="14" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="11" t="inlineStr">
         <is>
-          <t>S09 V07</t>
+          <t>S09 V06</t>
         </is>
       </c>
       <c r="B94" s="12" t="inlineStr">
         <is>
-          <t>Gewurztraminer Grand Cru Bruderthal</t>
+          <t>AOC Alsace — Riesling Hahnenberg</t>
         </is>
       </c>
       <c r="C94" s="12" t="inlineStr">
@@ -3274,7 +3302,7 @@
       </c>
       <c r="D94" s="12" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E94" s="12" t="inlineStr">
@@ -3284,25 +3312,25 @@
       </c>
       <c r="F94" s="13" t="n"/>
       <c r="G94" s="13" t="n">
-        <v>15.4</v>
+        <v>11.4</v>
       </c>
       <c r="H94" s="13" t="n">
-        <v>14.9</v>
+        <v>11</v>
       </c>
       <c r="I94" s="13" t="n">
-        <v>14.2</v>
+        <v>10.5</v>
       </c>
       <c r="J94" s="14" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="11" t="inlineStr">
         <is>
-          <t>S09 V08</t>
+          <t>S09 V07</t>
         </is>
       </c>
       <c r="B95" s="12" t="inlineStr">
         <is>
-          <t>Riesling Grand Cru Bruderthal</t>
+          <t>Gewurztraminer Grand Cru Bruderthal</t>
         </is>
       </c>
       <c r="C95" s="12" t="inlineStr">
@@ -3322,35 +3350,35 @@
       </c>
       <c r="F95" s="13" t="n"/>
       <c r="G95" s="13" t="n">
-        <v>18.8</v>
+        <v>15.4</v>
       </c>
       <c r="H95" s="13" t="n">
-        <v>18.2</v>
+        <v>14.9</v>
       </c>
       <c r="I95" s="13" t="n">
-        <v>17.3</v>
+        <v>14.2</v>
       </c>
       <c r="J95" s="14" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="11" t="inlineStr">
         <is>
-          <t>S09 V09</t>
+          <t>S09 V08</t>
         </is>
       </c>
       <c r="B96" s="12" t="inlineStr">
         <is>
-          <t>AOC Alsace — Seiler Rouge</t>
+          <t>Riesling Grand Cru Bruderthal</t>
         </is>
       </c>
       <c r="C96" s="12" t="inlineStr">
         <is>
-          <t>Rouge</t>
+          <t>Blanc sec</t>
         </is>
       </c>
       <c r="D96" s="12" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="E96" s="12" t="inlineStr">
@@ -3360,114 +3388,114 @@
       </c>
       <c r="F96" s="13" t="n"/>
       <c r="G96" s="13" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="H96" s="13" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="I96" s="13" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="J96" s="14" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="11" t="inlineStr">
+        <is>
+          <t>S09 V09</t>
+        </is>
+      </c>
+      <c r="B97" s="12" t="inlineStr">
+        <is>
+          <t>AOC Alsace — Seiler Rouge</t>
+        </is>
+      </c>
+      <c r="C97" s="12" t="inlineStr">
+        <is>
+          <t>Rouge</t>
+        </is>
+      </c>
+      <c r="D97" s="12" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="E97" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
+      <c r="F97" s="13" t="n"/>
+      <c r="G97" s="13" t="n">
         <v>10.3</v>
       </c>
-      <c r="H96" s="13" t="n">
+      <c r="H97" s="13" t="n">
         <v>9.9</v>
       </c>
-      <c r="I96" s="13" t="n">
+      <c r="I97" s="13" t="n">
         <v>9.5</v>
       </c>
-      <c r="J96" s="14" t="n"/>
-    </row>
-    <row r="98" ht="22" customHeight="1">
-      <c r="A98" s="5" t="inlineStr">
+      <c r="J97" s="14" t="n"/>
+    </row>
+    <row r="99" ht="22" customHeight="1">
+      <c r="A99" s="5" t="inlineStr">
         <is>
           <t>S10</t>
         </is>
       </c>
-      <c r="B98" s="6" t="inlineStr">
+      <c r="B99" s="6" t="inlineStr">
         <is>
           <t>Stand 10 — François Reverdy (Loire)</t>
         </is>
       </c>
-      <c r="C98" s="7" t="n"/>
-      <c r="D98" s="7" t="n"/>
-      <c r="E98" s="7" t="n"/>
-      <c r="F98" s="7" t="n"/>
-      <c r="G98" s="7" t="n"/>
-      <c r="H98" s="7" t="n"/>
-      <c r="I98" s="7" t="n"/>
-      <c r="J98" s="7" t="n"/>
-    </row>
-    <row r="99" ht="26" customHeight="1">
-      <c r="B99" s="8" t="inlineStr">
+      <c r="C99" s="7" t="n"/>
+      <c r="D99" s="7" t="n"/>
+      <c r="E99" s="7" t="n"/>
+      <c r="F99" s="7" t="n"/>
+      <c r="G99" s="7" t="n"/>
+      <c r="H99" s="7" t="n"/>
+      <c r="I99" s="7" t="n"/>
+      <c r="J99" s="7" t="n"/>
+    </row>
+    <row r="100" ht="26" customHeight="1">
+      <c r="B100" s="8" t="inlineStr">
         <is>
           <t>François Reverdy — paliers du salon</t>
         </is>
       </c>
-      <c r="C99" s="9" t="n"/>
-      <c r="D99" s="9" t="n"/>
-      <c r="E99" s="9" t="n"/>
-      <c r="F99" s="8" t="inlineStr">
+      <c r="C100" s="9" t="n"/>
+      <c r="D100" s="9" t="n"/>
+      <c r="E100" s="9" t="n"/>
+      <c r="F100" s="8" t="inlineStr">
         <is>
           <t>Prix unique</t>
         </is>
       </c>
-      <c r="G99" s="10" t="inlineStr">
+      <c r="G100" s="10" t="inlineStr">
         <is>
           <t>À partir de 42 bts</t>
         </is>
       </c>
-      <c r="H99" s="10" t="inlineStr">
+      <c r="H100" s="10" t="inlineStr">
         <is>
           <t>À partir de 120 bts</t>
         </is>
       </c>
-      <c r="I99" s="10" t="inlineStr">
+      <c r="I100" s="10" t="inlineStr">
         <is>
           <t>À partir de 300 bts</t>
         </is>
       </c>
-      <c r="J99" s="10" t="n"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="11" t="inlineStr">
-        <is>
-          <t>S10 V01</t>
-        </is>
-      </c>
-      <c r="B100" s="12" t="inlineStr">
-        <is>
-          <t>AOC Anjou Blanc</t>
-        </is>
-      </c>
-      <c r="C100" s="12" t="inlineStr">
-        <is>
-          <t>Blanc</t>
-        </is>
-      </c>
-      <c r="D100" s="12" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E100" s="12" t="inlineStr">
-        <is>
-          <t>75 cl</t>
-        </is>
-      </c>
-      <c r="F100" s="13" t="n"/>
-      <c r="G100" s="13" t="n">
-        <v>13.25</v>
-      </c>
-      <c r="H100" s="13" t="n">
-        <v>12.25</v>
-      </c>
-      <c r="I100" s="13" t="n">
-        <v>11.75</v>
-      </c>
-      <c r="J100" s="14" t="n"/>
+      <c r="J100" s="10" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="11" t="inlineStr">
         <is>
-          <t>S10 V02</t>
+          <t>S10 V01</t>
         </is>
       </c>
       <c r="B101" s="12" t="inlineStr">
         <is>
-          <t>IGP Val de Loire — La Grange Jaumain Blanc</t>
+          <t>AOC Anjou Blanc</t>
         </is>
       </c>
       <c r="C101" s="12" t="inlineStr">
@@ -3477,7 +3505,7 @@
       </c>
       <c r="D101" s="12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="E101" s="12" t="inlineStr">
@@ -3487,25 +3515,25 @@
       </c>
       <c r="F101" s="13" t="n"/>
       <c r="G101" s="13" t="n">
-        <v>9.5</v>
+        <v>13.25</v>
       </c>
       <c r="H101" s="13" t="n">
-        <v>9.25</v>
+        <v>12.25</v>
       </c>
       <c r="I101" s="13" t="n">
-        <v>9</v>
+        <v>11.75</v>
       </c>
       <c r="J101" s="14" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="11" t="inlineStr">
         <is>
-          <t>S10 V03</t>
+          <t>S10 V02</t>
         </is>
       </c>
       <c r="B102" s="12" t="inlineStr">
         <is>
-          <t>AOC Saumur Blanc</t>
+          <t>IGP Val de Loire — La Grange Jaumain Blanc</t>
         </is>
       </c>
       <c r="C102" s="12" t="inlineStr">
@@ -3515,7 +3543,7 @@
       </c>
       <c r="D102" s="12" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E102" s="12" t="inlineStr">
@@ -3525,25 +3553,25 @@
       </c>
       <c r="F102" s="13" t="n"/>
       <c r="G102" s="13" t="n">
-        <v>14.5</v>
+        <v>9.5</v>
       </c>
       <c r="H102" s="13" t="n">
-        <v>13.5</v>
+        <v>9.25</v>
       </c>
       <c r="I102" s="13" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J102" s="14" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="11" t="inlineStr">
         <is>
-          <t>S10 V04</t>
+          <t>S10 V03</t>
         </is>
       </c>
       <c r="B103" s="12" t="inlineStr">
         <is>
-          <t>AOC Quincy</t>
+          <t>AOC Saumur Blanc</t>
         </is>
       </c>
       <c r="C103" s="12" t="inlineStr">
@@ -3553,7 +3581,7 @@
       </c>
       <c r="D103" s="12" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E103" s="12" t="inlineStr">
@@ -3563,25 +3591,25 @@
       </c>
       <c r="F103" s="13" t="n"/>
       <c r="G103" s="13" t="n">
-        <v>17.85</v>
+        <v>14.5</v>
       </c>
       <c r="H103" s="13" t="n">
-        <v>16.5</v>
+        <v>13.5</v>
       </c>
       <c r="I103" s="13" t="n">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="J103" s="14" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="11" t="inlineStr">
         <is>
-          <t>S10 V05</t>
+          <t>S10 V04</t>
         </is>
       </c>
       <c r="B104" s="12" t="inlineStr">
         <is>
-          <t>AOC Sancerre Blanc — Les Villaudes</t>
+          <t>AOC Quincy</t>
         </is>
       </c>
       <c r="C104" s="12" t="inlineStr">
@@ -3591,7 +3619,7 @@
       </c>
       <c r="D104" s="12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="E104" s="12" t="inlineStr">
@@ -3601,7 +3629,7 @@
       </c>
       <c r="F104" s="13" t="n"/>
       <c r="G104" s="13" t="n">
-        <v>18</v>
+        <v>17.85</v>
       </c>
       <c r="H104" s="13" t="n">
         <v>16.5</v>
@@ -3614,22 +3642,22 @@
     <row r="105">
       <c r="A105" s="11" t="inlineStr">
         <is>
-          <t>S10 V06</t>
+          <t>S10 V05</t>
         </is>
       </c>
       <c r="B105" s="12" t="inlineStr">
         <is>
-          <t>La Grange Jaumain Rouge – Grolleau Noir</t>
+          <t>AOC Sancerre Blanc — Les Villaudes</t>
         </is>
       </c>
       <c r="C105" s="12" t="inlineStr">
         <is>
-          <t>Rouge</t>
+          <t>Blanc</t>
         </is>
       </c>
       <c r="D105" s="12" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E105" s="12" t="inlineStr">
@@ -3639,25 +3667,25 @@
       </c>
       <c r="F105" s="13" t="n"/>
       <c r="G105" s="13" t="n">
-        <v>10.6</v>
+        <v>18</v>
       </c>
       <c r="H105" s="13" t="n">
-        <v>10.6</v>
+        <v>16.5</v>
       </c>
       <c r="I105" s="13" t="n">
-        <v>10.6</v>
+        <v>15.5</v>
       </c>
       <c r="J105" s="14" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="11" t="inlineStr">
         <is>
-          <t>S10 V07</t>
+          <t>S10 V06</t>
         </is>
       </c>
       <c r="B106" s="12" t="inlineStr">
         <is>
-          <t>AOC Chinon — Franc Rouge</t>
+          <t>La Grange Jaumain Rouge – Grolleau Noir</t>
         </is>
       </c>
       <c r="C106" s="12" t="inlineStr">
@@ -3667,7 +3695,7 @@
       </c>
       <c r="D106" s="12" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E106" s="12" t="inlineStr">
@@ -3677,25 +3705,25 @@
       </c>
       <c r="F106" s="13" t="n"/>
       <c r="G106" s="13" t="n">
-        <v>13.75</v>
+        <v>10.6</v>
       </c>
       <c r="H106" s="13" t="n">
-        <v>12.85</v>
+        <v>10.6</v>
       </c>
       <c r="I106" s="13" t="n">
-        <v>12.25</v>
+        <v>10.6</v>
       </c>
       <c r="J106" s="14" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="11" t="inlineStr">
         <is>
-          <t>S10 V08</t>
+          <t>S10 V07</t>
         </is>
       </c>
       <c r="B107" s="12" t="inlineStr">
         <is>
-          <t>AOC Chinon — Cravant Rouge</t>
+          <t>AOC Chinon — Franc Rouge</t>
         </is>
       </c>
       <c r="C107" s="12" t="inlineStr">
@@ -3705,7 +3733,7 @@
       </c>
       <c r="D107" s="12" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="E107" s="12" t="inlineStr">
@@ -3715,25 +3743,25 @@
       </c>
       <c r="F107" s="13" t="n"/>
       <c r="G107" s="13" t="n">
-        <v>17</v>
+        <v>13.75</v>
       </c>
       <c r="H107" s="13" t="n">
-        <v>15.75</v>
+        <v>12.85</v>
       </c>
       <c r="I107" s="13" t="n">
-        <v>14.75</v>
+        <v>12.25</v>
       </c>
       <c r="J107" s="14" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="11" t="inlineStr">
         <is>
-          <t>S10 V09</t>
+          <t>S10 V08</t>
         </is>
       </c>
       <c r="B108" s="12" t="inlineStr">
         <is>
-          <t>IGP Val de Loire — La Grange Jaumain Les Soudannes Rouge</t>
+          <t>AOC Chinon — Cravant Rouge</t>
         </is>
       </c>
       <c r="C108" s="12" t="inlineStr">
@@ -3743,7 +3771,7 @@
       </c>
       <c r="D108" s="12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E108" s="12" t="inlineStr">
@@ -3753,98 +3781,102 @@
       </c>
       <c r="F108" s="13" t="n"/>
       <c r="G108" s="13" t="n">
+        <v>17</v>
+      </c>
+      <c r="H108" s="13" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="I108" s="13" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="J108" s="14" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="11" t="inlineStr">
+        <is>
+          <t>S10 V09</t>
+        </is>
+      </c>
+      <c r="B109" s="12" t="inlineStr">
+        <is>
+          <t>IGP Val de Loire — La Grange Jaumain Les Soudannes Rouge</t>
+        </is>
+      </c>
+      <c r="C109" s="12" t="inlineStr">
+        <is>
+          <t>Rouge</t>
+        </is>
+      </c>
+      <c r="D109" s="12" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E109" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
+      <c r="F109" s="13" t="n"/>
+      <c r="G109" s="13" t="n">
         <v>9.5</v>
       </c>
-      <c r="H108" s="13" t="n">
+      <c r="H109" s="13" t="n">
         <v>9.25</v>
       </c>
-      <c r="I108" s="13" t="n">
+      <c r="I109" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="J108" s="14" t="n"/>
-    </row>
-    <row r="110" ht="22" customHeight="1">
-      <c r="A110" s="5" t="inlineStr">
+      <c r="J109" s="14" t="n"/>
+    </row>
+    <row r="111" ht="22" customHeight="1">
+      <c r="A111" s="5" t="inlineStr">
         <is>
           <t>S11</t>
         </is>
       </c>
-      <c r="B110" s="6" t="inlineStr">
+      <c r="B111" s="6" t="inlineStr">
         <is>
           <t>Stand 11 — Champagne Dekeyne (Champagne)</t>
         </is>
       </c>
-      <c r="C110" s="7" t="n"/>
-      <c r="D110" s="7" t="n"/>
-      <c r="E110" s="7" t="n"/>
-      <c r="F110" s="7" t="n"/>
-      <c r="G110" s="7" t="n"/>
-      <c r="H110" s="7" t="n"/>
-      <c r="I110" s="7" t="n"/>
-      <c r="J110" s="7" t="n"/>
-    </row>
-    <row r="111" ht="26" customHeight="1">
-      <c r="B111" s="8" t="inlineStr">
+      <c r="C111" s="7" t="n"/>
+      <c r="D111" s="7" t="n"/>
+      <c r="E111" s="7" t="n"/>
+      <c r="F111" s="7" t="n"/>
+      <c r="G111" s="7" t="n"/>
+      <c r="H111" s="7" t="n"/>
+      <c r="I111" s="7" t="n"/>
+      <c r="J111" s="7" t="n"/>
+    </row>
+    <row r="112" ht="26" customHeight="1">
+      <c r="B112" s="8" t="inlineStr">
         <is>
           <t>Champagne Dekeyne — paliers du salon</t>
         </is>
       </c>
-      <c r="C111" s="9" t="n"/>
-      <c r="D111" s="9" t="n"/>
-      <c r="E111" s="9" t="n"/>
-      <c r="F111" s="8" t="inlineStr">
+      <c r="C112" s="9" t="n"/>
+      <c r="D112" s="9" t="n"/>
+      <c r="E112" s="9" t="n"/>
+      <c r="F112" s="8" t="inlineStr">
         <is>
           <t>Prix unique</t>
         </is>
       </c>
-      <c r="G111" s="10" t="n"/>
-      <c r="H111" s="10" t="n"/>
-      <c r="I111" s="10" t="n"/>
-      <c r="J111" s="10" t="n"/>
-    </row>
-    <row r="112">
-      <c r="A112" s="11" t="inlineStr">
-        <is>
-          <t>S11 V01</t>
-        </is>
-      </c>
-      <c r="B112" s="12" t="inlineStr">
-        <is>
-          <t>AOC Champagne — Voglonniers Brut</t>
-        </is>
-      </c>
-      <c r="C112" s="12" t="inlineStr">
-        <is>
-          <t>Blanc extra brut</t>
-        </is>
-      </c>
-      <c r="D112" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E112" s="12" t="inlineStr">
-        <is>
-          <t>75 cl</t>
-        </is>
-      </c>
-      <c r="F112" s="13" t="n">
-        <v>19.96</v>
-      </c>
-      <c r="G112" s="14" t="n"/>
-      <c r="H112" s="14" t="n"/>
-      <c r="I112" s="14" t="n"/>
-      <c r="J112" s="14" t="n"/>
+      <c r="G112" s="10" t="n"/>
+      <c r="H112" s="10" t="n"/>
+      <c r="I112" s="10" t="n"/>
+      <c r="J112" s="10" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="11" t="inlineStr">
         <is>
-          <t>S11 V02</t>
+          <t>S11 V01</t>
         </is>
       </c>
       <c r="B113" s="12" t="inlineStr">
         <is>
-          <t>AOC Champagne — Nature Brut</t>
+          <t>AOC Champagne — Voglonniers Brut</t>
         </is>
       </c>
       <c r="C113" s="12" t="inlineStr">
@@ -3863,7 +3895,7 @@
         </is>
       </c>
       <c r="F113" s="13" t="n">
-        <v>25.41</v>
+        <v>19.96</v>
       </c>
       <c r="G113" s="14" t="n"/>
       <c r="H113" s="14" t="n"/>
@@ -3873,12 +3905,12 @@
     <row r="114">
       <c r="A114" s="11" t="inlineStr">
         <is>
-          <t>S11 V03</t>
+          <t>S11 V02</t>
         </is>
       </c>
       <c r="B114" s="12" t="inlineStr">
         <is>
-          <t>AOC Champagne — Chardonnay Extra-Brut</t>
+          <t>AOC Champagne — Nature Brut</t>
         </is>
       </c>
       <c r="C114" s="12" t="inlineStr">
@@ -3897,7 +3929,7 @@
         </is>
       </c>
       <c r="F114" s="13" t="n">
-        <v>26.48</v>
+        <v>25.41</v>
       </c>
       <c r="G114" s="14" t="n"/>
       <c r="H114" s="14" t="n"/>
@@ -3907,127 +3939,127 @@
     <row r="115">
       <c r="A115" s="11" t="inlineStr">
         <is>
-          <t>S11 V04</t>
+          <t>S11 V03</t>
         </is>
       </c>
       <c r="B115" s="12" t="inlineStr">
         <is>
-          <t>AOC Champagne — Supernova Extra-Brut Zéro Dosage</t>
-        </is>
-      </c>
-      <c r="C115" s="12" t="n"/>
+          <t>AOC Champagne — Chardonnay Extra-Brut</t>
+        </is>
+      </c>
+      <c r="C115" s="12" t="inlineStr">
+        <is>
+          <t>Blanc extra brut</t>
+        </is>
+      </c>
       <c r="D115" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E115" s="12" t="n"/>
+      <c r="E115" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
       <c r="F115" s="13" t="n">
-        <v>36.83</v>
+        <v>26.48</v>
       </c>
       <c r="G115" s="14" t="n"/>
       <c r="H115" s="14" t="n"/>
       <c r="I115" s="14" t="n"/>
       <c r="J115" s="14" t="n"/>
     </row>
-    <row r="117" ht="22" customHeight="1">
-      <c r="A117" s="5" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="11" t="inlineStr">
+        <is>
+          <t>S11 V04</t>
+        </is>
+      </c>
+      <c r="B116" s="12" t="inlineStr">
+        <is>
+          <t>AOC Champagne — Supernova Extra-Brut Zéro Dosage</t>
+        </is>
+      </c>
+      <c r="C116" s="12" t="n"/>
+      <c r="D116" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E116" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
+      <c r="F116" s="13" t="n">
+        <v>36.83</v>
+      </c>
+      <c r="G116" s="14" t="n"/>
+      <c r="H116" s="14" t="n"/>
+      <c r="I116" s="14" t="n"/>
+      <c r="J116" s="14" t="n"/>
+    </row>
+    <row r="118" ht="22" customHeight="1">
+      <c r="A118" s="5" t="inlineStr">
         <is>
           <t>S12</t>
         </is>
       </c>
-      <c r="B117" s="6" t="inlineStr">
+      <c r="B118" s="6" t="inlineStr">
         <is>
           <t>Stand 12 — Domaine Trichon (Rhône)</t>
         </is>
       </c>
-      <c r="C117" s="7" t="n"/>
-      <c r="D117" s="7" t="n"/>
-      <c r="E117" s="7" t="n"/>
-      <c r="F117" s="7" t="n"/>
-      <c r="G117" s="7" t="n"/>
-      <c r="H117" s="7" t="n"/>
-      <c r="I117" s="7" t="n"/>
-      <c r="J117" s="7" t="n"/>
-    </row>
-    <row r="118" ht="26" customHeight="1">
-      <c r="B118" s="8" t="inlineStr">
+      <c r="C118" s="7" t="n"/>
+      <c r="D118" s="7" t="n"/>
+      <c r="E118" s="7" t="n"/>
+      <c r="F118" s="7" t="n"/>
+      <c r="G118" s="7" t="n"/>
+      <c r="H118" s="7" t="n"/>
+      <c r="I118" s="7" t="n"/>
+      <c r="J118" s="7" t="n"/>
+    </row>
+    <row r="119" ht="26" customHeight="1">
+      <c r="B119" s="8" t="inlineStr">
         <is>
           <t>Domaine Trichon — paliers du salon</t>
         </is>
       </c>
-      <c r="C118" s="9" t="n"/>
-      <c r="D118" s="9" t="n"/>
-      <c r="E118" s="9" t="n"/>
-      <c r="F118" s="8" t="inlineStr">
+      <c r="C119" s="9" t="n"/>
+      <c r="D119" s="9" t="n"/>
+      <c r="E119" s="9" t="n"/>
+      <c r="F119" s="8" t="inlineStr">
         <is>
           <t>Prix unique</t>
         </is>
       </c>
-      <c r="G118" s="10" t="inlineStr">
+      <c r="G119" s="10" t="inlineStr">
         <is>
           <t>À partir de 120 cols</t>
         </is>
       </c>
-      <c r="H118" s="10" t="inlineStr">
+      <c r="H119" s="10" t="inlineStr">
         <is>
           <t>À partir de 300 cols</t>
         </is>
       </c>
-      <c r="I118" s="10" t="inlineStr">
+      <c r="I119" s="10" t="inlineStr">
         <is>
           <t>À partir de 600 cols</t>
         </is>
       </c>
-      <c r="J118" s="10" t="n"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="11" t="inlineStr">
-        <is>
-          <t>S12 V01</t>
-        </is>
-      </c>
-      <c r="B119" s="12" t="inlineStr">
-        <is>
-          <t>AOC Bugey — Mas de Lusanne Brut Blanc</t>
-        </is>
-      </c>
-      <c r="C119" s="12" t="inlineStr">
-        <is>
-          <t>Blanc effervescent</t>
-        </is>
-      </c>
-      <c r="D119" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E119" s="12" t="inlineStr">
-        <is>
-          <t>75 cl</t>
-        </is>
-      </c>
-      <c r="F119" s="13" t="n"/>
-      <c r="G119" s="13" t="n">
-        <v>7.43</v>
-      </c>
-      <c r="H119" s="13" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="I119" s="13" t="n">
-        <v>6.73</v>
-      </c>
-      <c r="J119" s="14" t="n"/>
+      <c r="J119" s="10" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="11" t="inlineStr">
         <is>
-          <t>S12 V02</t>
+          <t>S12 V01</t>
         </is>
       </c>
       <c r="B120" s="12" t="inlineStr">
         <is>
-          <t>AOC Bugey — Mas de Lusanne Extra-Brut Blanc</t>
+          <t>AOC Bugey — Mas de Lusanne Brut Blanc</t>
         </is>
       </c>
       <c r="C120" s="12" t="inlineStr">
@@ -4060,22 +4092,22 @@
     <row r="121">
       <c r="A121" s="11" t="inlineStr">
         <is>
-          <t>S12 V03</t>
+          <t>S12 V02</t>
         </is>
       </c>
       <c r="B121" s="12" t="inlineStr">
         <is>
-          <t>AOC Bugey — Mas de Lusanne Mondeuse Rouge</t>
+          <t>AOC Bugey — Mas de Lusanne Extra-Brut Blanc</t>
         </is>
       </c>
       <c r="C121" s="12" t="inlineStr">
         <is>
-          <t>Rouge</t>
+          <t>Blanc effervescent</t>
         </is>
       </c>
       <c r="D121" s="12" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E121" s="12" t="inlineStr">
@@ -4085,25 +4117,25 @@
       </c>
       <c r="F121" s="13" t="n"/>
       <c r="G121" s="13" t="n">
-        <v>7.38</v>
+        <v>7.43</v>
       </c>
       <c r="H121" s="13" t="n">
-        <v>6.98</v>
+        <v>6.9</v>
       </c>
       <c r="I121" s="13" t="n">
-        <v>6.58</v>
+        <v>6.73</v>
       </c>
       <c r="J121" s="14" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="11" t="inlineStr">
         <is>
-          <t>S12 V04</t>
+          <t>S12 V03</t>
         </is>
       </c>
       <c r="B122" s="12" t="inlineStr">
         <is>
-          <t>AOC Bugey — Mas de Lusanne Pinot Noir Rouge</t>
+          <t>AOC Bugey — Mas de Lusanne Mondeuse Rouge</t>
         </is>
       </c>
       <c r="C122" s="12" t="inlineStr">
@@ -4123,25 +4155,25 @@
       </c>
       <c r="F122" s="13" t="n"/>
       <c r="G122" s="13" t="n">
-        <v>6.99</v>
+        <v>7.38</v>
       </c>
       <c r="H122" s="13" t="n">
-        <v>6.67</v>
+        <v>6.98</v>
       </c>
       <c r="I122" s="13" t="n">
-        <v>6.35</v>
+        <v>6.58</v>
       </c>
       <c r="J122" s="14" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="11" t="inlineStr">
         <is>
-          <t>S12 V05</t>
+          <t>S12 V04</t>
         </is>
       </c>
       <c r="B123" s="12" t="inlineStr">
         <is>
-          <t>AOC Côtes du Rhône — Mas de Lusanne Rouge</t>
+          <t>AOC Bugey — Mas de Lusanne Pinot Noir Rouge</t>
         </is>
       </c>
       <c r="C123" s="12" t="inlineStr">
@@ -4151,7 +4183,7 @@
       </c>
       <c r="D123" s="12" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="E123" s="12" t="inlineStr">
@@ -4161,25 +4193,25 @@
       </c>
       <c r="F123" s="13" t="n"/>
       <c r="G123" s="13" t="n">
-        <v>4.8</v>
+        <v>6.99</v>
       </c>
       <c r="H123" s="13" t="n">
-        <v>4.67</v>
+        <v>6.67</v>
       </c>
       <c r="I123" s="13" t="n">
-        <v>4.54</v>
+        <v>6.35</v>
       </c>
       <c r="J123" s="14" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="11" t="inlineStr">
         <is>
-          <t>S12 V06</t>
+          <t>S12 V05</t>
         </is>
       </c>
       <c r="B124" s="12" t="inlineStr">
         <is>
-          <t>AOC Bugey — Mas de Lusanne Gamay Rouge</t>
+          <t>AOC Côtes du Rhône — Mas de Lusanne Rouge</t>
         </is>
       </c>
       <c r="C124" s="12" t="inlineStr">
@@ -4189,7 +4221,7 @@
       </c>
       <c r="D124" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E124" s="12" t="inlineStr">
@@ -4199,35 +4231,35 @@
       </c>
       <c r="F124" s="13" t="n"/>
       <c r="G124" s="13" t="n">
-        <v>5.85</v>
+        <v>4.8</v>
       </c>
       <c r="H124" s="13" t="n">
-        <v>5.59</v>
+        <v>4.67</v>
       </c>
       <c r="I124" s="13" t="n">
-        <v>5.32</v>
+        <v>4.54</v>
       </c>
       <c r="J124" s="14" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="11" t="inlineStr">
         <is>
-          <t>S12 V07</t>
+          <t>S12 V06</t>
         </is>
       </c>
       <c r="B125" s="12" t="inlineStr">
         <is>
-          <t>AOC Bugey — Mas de Lusanne Chardonnay Blanc</t>
+          <t>AOC Bugey — Mas de Lusanne Gamay Rouge</t>
         </is>
       </c>
       <c r="C125" s="12" t="inlineStr">
         <is>
-          <t>Blanc</t>
+          <t>Rouge</t>
         </is>
       </c>
       <c r="D125" s="12" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E125" s="12" t="inlineStr">
@@ -4237,25 +4269,25 @@
       </c>
       <c r="F125" s="13" t="n"/>
       <c r="G125" s="13" t="n">
-        <v>7.25</v>
+        <v>5.85</v>
       </c>
       <c r="H125" s="13" t="n">
-        <v>6.8</v>
+        <v>5.59</v>
       </c>
       <c r="I125" s="13" t="n">
-        <v>6.35</v>
+        <v>5.32</v>
       </c>
       <c r="J125" s="14" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="11" t="inlineStr">
         <is>
-          <t>S12 V08</t>
+          <t>S12 V07</t>
         </is>
       </c>
       <c r="B126" s="12" t="inlineStr">
         <is>
-          <t>AOC Vacqueyras — Mas de Lusanne Vacqueyras Blanc</t>
+          <t>AOC Bugey — Mas de Lusanne Chardonnay Blanc</t>
         </is>
       </c>
       <c r="C126" s="12" t="inlineStr">
@@ -4265,7 +4297,7 @@
       </c>
       <c r="D126" s="12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="E126" s="12" t="inlineStr">
@@ -4275,35 +4307,35 @@
       </c>
       <c r="F126" s="13" t="n"/>
       <c r="G126" s="13" t="n">
-        <v>9.550000000000001</v>
+        <v>7.25</v>
       </c>
       <c r="H126" s="13" t="n">
-        <v>9.119999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="I126" s="13" t="n">
-        <v>8.68</v>
+        <v>6.35</v>
       </c>
       <c r="J126" s="14" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="11" t="inlineStr">
         <is>
-          <t>S12 V09</t>
+          <t>S12 V08</t>
         </is>
       </c>
       <c r="B127" s="12" t="inlineStr">
         <is>
-          <t>AOC Vacqueyras — Mas de Lusanne Vacqueyras Rouge</t>
+          <t>AOC Vacqueyras — Mas de Lusanne Vacqueyras Blanc</t>
         </is>
       </c>
       <c r="C127" s="12" t="inlineStr">
         <is>
-          <t>Rouge</t>
+          <t>Blanc</t>
         </is>
       </c>
       <c r="D127" s="12" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E127" s="12" t="inlineStr">
@@ -4313,31 +4345,35 @@
       </c>
       <c r="F127" s="13" t="n"/>
       <c r="G127" s="13" t="n">
-        <v>9.35</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="H127" s="13" t="n">
-        <v>8.93</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="I127" s="13" t="n">
-        <v>8.5</v>
+        <v>8.68</v>
       </c>
       <c r="J127" s="14" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="11" t="inlineStr">
         <is>
-          <t>S12 V10</t>
+          <t>S12 V09</t>
         </is>
       </c>
       <c r="B128" s="12" t="inlineStr">
         <is>
-          <t>Mas de Lusanne Pétillant de Jus de Raisin 0 %</t>
-        </is>
-      </c>
-      <c r="C128" s="12" t="n"/>
+          <t>AOC Vacqueyras — Mas de Lusanne Vacqueyras Rouge</t>
+        </is>
+      </c>
+      <c r="C128" s="12" t="inlineStr">
+        <is>
+          <t>Rouge</t>
+        </is>
+      </c>
       <c r="D128" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="E128" s="12" t="inlineStr">
@@ -4347,98 +4383,98 @@
       </c>
       <c r="F128" s="13" t="n"/>
       <c r="G128" s="13" t="n">
+        <v>9.35</v>
+      </c>
+      <c r="H128" s="13" t="n">
+        <v>8.93</v>
+      </c>
+      <c r="I128" s="13" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="J128" s="14" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="11" t="inlineStr">
+        <is>
+          <t>S12 V10</t>
+        </is>
+      </c>
+      <c r="B129" s="12" t="inlineStr">
+        <is>
+          <t>Mas de Lusanne Pétillant de Jus de Raisin 0 %</t>
+        </is>
+      </c>
+      <c r="C129" s="12" t="n"/>
+      <c r="D129" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E129" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
+      <c r="F129" s="13" t="n"/>
+      <c r="G129" s="13" t="n">
         <v>5.08</v>
       </c>
-      <c r="H128" s="13" t="n">
+      <c r="H129" s="13" t="n">
         <v>5.08</v>
       </c>
-      <c r="I128" s="13" t="n">
+      <c r="I129" s="13" t="n">
         <v>5.08</v>
       </c>
-      <c r="J128" s="14" t="n"/>
-    </row>
-    <row r="130" ht="22" customHeight="1">
-      <c r="A130" s="5" t="inlineStr">
+      <c r="J129" s="14" t="n"/>
+    </row>
+    <row r="131" ht="22" customHeight="1">
+      <c r="A131" s="5" t="inlineStr">
         <is>
           <t>S13</t>
         </is>
       </c>
-      <c r="B130" s="6" t="inlineStr">
+      <c r="B131" s="6" t="inlineStr">
         <is>
           <t>Stand 13 — Château de Gragnos (Languedoc)</t>
         </is>
       </c>
-      <c r="C130" s="7" t="n"/>
-      <c r="D130" s="7" t="n"/>
-      <c r="E130" s="7" t="n"/>
-      <c r="F130" s="7" t="n"/>
-      <c r="G130" s="7" t="n"/>
-      <c r="H130" s="7" t="n"/>
-      <c r="I130" s="7" t="n"/>
-      <c r="J130" s="7" t="n"/>
-    </row>
-    <row r="131" ht="26" customHeight="1">
-      <c r="B131" s="8" t="inlineStr">
+      <c r="C131" s="7" t="n"/>
+      <c r="D131" s="7" t="n"/>
+      <c r="E131" s="7" t="n"/>
+      <c r="F131" s="7" t="n"/>
+      <c r="G131" s="7" t="n"/>
+      <c r="H131" s="7" t="n"/>
+      <c r="I131" s="7" t="n"/>
+      <c r="J131" s="7" t="n"/>
+    </row>
+    <row r="132" ht="26" customHeight="1">
+      <c r="B132" s="8" t="inlineStr">
         <is>
           <t>Château de Gragnos — paliers du salon</t>
         </is>
       </c>
-      <c r="C131" s="9" t="n"/>
-      <c r="D131" s="9" t="n"/>
-      <c r="E131" s="9" t="n"/>
-      <c r="F131" s="8" t="inlineStr">
+      <c r="C132" s="9" t="n"/>
+      <c r="D132" s="9" t="n"/>
+      <c r="E132" s="9" t="n"/>
+      <c r="F132" s="8" t="inlineStr">
         <is>
           <t>Prix unique</t>
         </is>
       </c>
-      <c r="G131" s="10" t="n"/>
-      <c r="H131" s="10" t="n"/>
-      <c r="I131" s="10" t="n"/>
-      <c r="J131" s="10" t="n"/>
-    </row>
-    <row r="132">
-      <c r="A132" s="11" t="inlineStr">
-        <is>
-          <t>S13 V01</t>
-        </is>
-      </c>
-      <c r="B132" s="12" t="inlineStr">
-        <is>
-          <t>VDF — Léon Rouge</t>
-        </is>
-      </c>
-      <c r="C132" s="12" t="inlineStr">
-        <is>
-          <t>Rouge</t>
-        </is>
-      </c>
-      <c r="D132" s="12" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="E132" s="12" t="inlineStr">
-        <is>
-          <t>75 cl</t>
-        </is>
-      </c>
-      <c r="F132" s="13" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="G132" s="14" t="n"/>
-      <c r="H132" s="14" t="n"/>
-      <c r="I132" s="14" t="n"/>
-      <c r="J132" s="14" t="n"/>
+      <c r="G132" s="10" t="n"/>
+      <c r="H132" s="10" t="n"/>
+      <c r="I132" s="10" t="n"/>
+      <c r="J132" s="10" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="11" t="inlineStr">
         <is>
-          <t>S13 V02</t>
+          <t>S13 V01</t>
         </is>
       </c>
       <c r="B133" s="12" t="inlineStr">
         <is>
-          <t>AOC Saint-Chinian — Lou Daro Rouge</t>
+          <t>VDF — Léon Rouge</t>
         </is>
       </c>
       <c r="C133" s="12" t="inlineStr">
@@ -4448,7 +4484,7 @@
       </c>
       <c r="D133" s="12" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E133" s="12" t="inlineStr">
@@ -4457,7 +4493,7 @@
         </is>
       </c>
       <c r="F133" s="13" t="n">
-        <v>6.7</v>
+        <v>4.85</v>
       </c>
       <c r="G133" s="14" t="n"/>
       <c r="H133" s="14" t="n"/>
@@ -4467,12 +4503,12 @@
     <row r="134">
       <c r="A134" s="11" t="inlineStr">
         <is>
-          <t>S13 V03</t>
+          <t>S13 V02</t>
         </is>
       </c>
       <c r="B134" s="12" t="inlineStr">
         <is>
-          <t>AOC Saint-Chinian — Henri Rouge</t>
+          <t>AOC Saint-Chinian — Lou Daro Rouge</t>
         </is>
       </c>
       <c r="C134" s="12" t="inlineStr">
@@ -4482,7 +4518,7 @@
       </c>
       <c r="D134" s="12" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="E134" s="12" t="inlineStr">
@@ -4491,7 +4527,7 @@
         </is>
       </c>
       <c r="F134" s="13" t="n">
-        <v>4.85</v>
+        <v>6.7</v>
       </c>
       <c r="G134" s="14" t="n"/>
       <c r="H134" s="14" t="n"/>
@@ -4501,25 +4537,29 @@
     <row r="135">
       <c r="A135" s="11" t="inlineStr">
         <is>
-          <t>S13 V04</t>
+          <t>S13 V03</t>
         </is>
       </c>
       <c r="B135" s="12" t="inlineStr">
         <is>
-          <t>AOC Saint-Chinian — Juliette Blanc</t>
+          <t>AOC Saint-Chinian — Henri Rouge</t>
         </is>
       </c>
       <c r="C135" s="12" t="inlineStr">
         <is>
-          <t>Blanc</t>
+          <t>Rouge</t>
         </is>
       </c>
       <c r="D135" s="12" t="inlineStr">
         <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E135" s="12" t="n"/>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="E135" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
       <c r="F135" s="13" t="n">
         <v>4.85</v>
       </c>
@@ -4531,12 +4571,12 @@
     <row r="136">
       <c r="A136" s="11" t="inlineStr">
         <is>
-          <t>S13 V05</t>
+          <t>S13 V04</t>
         </is>
       </c>
       <c r="B136" s="12" t="inlineStr">
         <is>
-          <t>IGP Pays d’Hérault Monts de la Grage — Grain de Blanc</t>
+          <t>AOC Saint-Chinian — Juliette Blanc</t>
         </is>
       </c>
       <c r="C136" s="12" t="inlineStr">
@@ -4555,101 +4595,103 @@
         </is>
       </c>
       <c r="F136" s="13" t="n">
-        <v>6.7</v>
+        <v>4.85</v>
       </c>
       <c r="G136" s="14" t="n"/>
       <c r="H136" s="14" t="n"/>
       <c r="I136" s="14" t="n"/>
       <c r="J136" s="14" t="n"/>
     </row>
-    <row r="138" ht="22" customHeight="1">
-      <c r="A138" s="5" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="11" t="inlineStr">
+        <is>
+          <t>S13 V05</t>
+        </is>
+      </c>
+      <c r="B137" s="12" t="inlineStr">
+        <is>
+          <t>IGP Pays d’Hérault Monts de la Grage — Grain de Blanc</t>
+        </is>
+      </c>
+      <c r="C137" s="12" t="inlineStr">
+        <is>
+          <t>Blanc</t>
+        </is>
+      </c>
+      <c r="D137" s="12" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E137" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
+      <c r="F137" s="13" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G137" s="14" t="n"/>
+      <c r="H137" s="14" t="n"/>
+      <c r="I137" s="14" t="n"/>
+      <c r="J137" s="14" t="n"/>
+    </row>
+    <row r="139" ht="22" customHeight="1">
+      <c r="A139" s="5" t="inlineStr">
         <is>
           <t>S14</t>
         </is>
       </c>
-      <c r="B138" s="6" t="inlineStr">
+      <c r="B139" s="6" t="inlineStr">
         <is>
           <t>Stand 14 — Domaine des Noëls (Loire)</t>
         </is>
       </c>
-      <c r="C138" s="7" t="n"/>
-      <c r="D138" s="7" t="n"/>
-      <c r="E138" s="7" t="n"/>
-      <c r="F138" s="7" t="n"/>
-      <c r="G138" s="7" t="n"/>
-      <c r="H138" s="7" t="n"/>
-      <c r="I138" s="7" t="n"/>
-      <c r="J138" s="7" t="n"/>
-    </row>
-    <row r="139" ht="26" customHeight="1">
-      <c r="B139" s="8" t="inlineStr">
+      <c r="C139" s="7" t="n"/>
+      <c r="D139" s="7" t="n"/>
+      <c r="E139" s="7" t="n"/>
+      <c r="F139" s="7" t="n"/>
+      <c r="G139" s="7" t="n"/>
+      <c r="H139" s="7" t="n"/>
+      <c r="I139" s="7" t="n"/>
+      <c r="J139" s="7" t="n"/>
+    </row>
+    <row r="140" ht="26" customHeight="1">
+      <c r="B140" s="8" t="inlineStr">
         <is>
           <t>Domaine des Noëls — paliers du salon</t>
         </is>
       </c>
-      <c r="C139" s="9" t="n"/>
-      <c r="D139" s="9" t="n"/>
-      <c r="E139" s="9" t="n"/>
-      <c r="F139" s="8" t="inlineStr">
+      <c r="C140" s="9" t="n"/>
+      <c r="D140" s="9" t="n"/>
+      <c r="E140" s="9" t="n"/>
+      <c r="F140" s="8" t="inlineStr">
         <is>
           <t>Prix unique</t>
         </is>
       </c>
-      <c r="G139" s="10" t="inlineStr">
+      <c r="G140" s="10" t="inlineStr">
         <is>
           <t>À partir de 120 bts</t>
         </is>
       </c>
-      <c r="H139" s="10" t="inlineStr">
+      <c r="H140" s="10" t="inlineStr">
         <is>
           <t>À partir de 240 bts</t>
         </is>
       </c>
-      <c r="I139" s="10" t="n"/>
-      <c r="J139" s="10" t="n"/>
-    </row>
-    <row r="140">
-      <c r="A140" s="11" t="inlineStr">
-        <is>
-          <t>S14 V01</t>
-        </is>
-      </c>
-      <c r="B140" s="12" t="inlineStr">
-        <is>
-          <t>AOC Anjou Blanc</t>
-        </is>
-      </c>
-      <c r="C140" s="12" t="inlineStr">
-        <is>
-          <t>Blanc</t>
-        </is>
-      </c>
-      <c r="D140" s="12" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="E140" s="12" t="n"/>
-      <c r="F140" s="13" t="n"/>
-      <c r="G140" s="13" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="H140" s="13" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="I140" s="14" t="n"/>
-      <c r="J140" s="14" t="n"/>
+      <c r="I140" s="10" t="n"/>
+      <c r="J140" s="10" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="11" t="inlineStr">
         <is>
-          <t>S14 V02</t>
+          <t>S14 V01</t>
         </is>
       </c>
       <c r="B141" s="12" t="inlineStr">
         <is>
-          <t>AOC Anjou Blanc — Promenade de Noëls</t>
+          <t>AOC Anjou Blanc</t>
         </is>
       </c>
       <c r="C141" s="12" t="inlineStr">
@@ -4669,10 +4711,10 @@
       </c>
       <c r="F141" s="13" t="n"/>
       <c r="G141" s="13" t="n">
-        <v>5.7</v>
+        <v>3.6</v>
       </c>
       <c r="H141" s="13" t="n">
-        <v>5.6</v>
+        <v>3.4</v>
       </c>
       <c r="I141" s="14" t="n"/>
       <c r="J141" s="14" t="n"/>
@@ -4680,22 +4722,22 @@
     <row r="142">
       <c r="A142" s="11" t="inlineStr">
         <is>
-          <t>S14 V03</t>
+          <t>S14 V02</t>
         </is>
       </c>
       <c r="B142" s="12" t="inlineStr">
         <is>
-          <t>AOC Sauvignon</t>
+          <t>AOC Anjou Blanc — Promenade de Noëls</t>
         </is>
       </c>
       <c r="C142" s="12" t="inlineStr">
         <is>
-          <t>Blanc sec</t>
+          <t>Blanc</t>
         </is>
       </c>
       <c r="D142" s="12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E142" s="12" t="inlineStr">
@@ -4705,10 +4747,10 @@
       </c>
       <c r="F142" s="13" t="n"/>
       <c r="G142" s="13" t="n">
-        <v>3.6</v>
+        <v>5.7</v>
       </c>
       <c r="H142" s="13" t="n">
-        <v>3.4</v>
+        <v>5.6</v>
       </c>
       <c r="I142" s="14" t="n"/>
       <c r="J142" s="14" t="n"/>
@@ -4716,17 +4758,17 @@
     <row r="143">
       <c r="A143" s="11" t="inlineStr">
         <is>
-          <t>S14 V04</t>
+          <t>S14 V03</t>
         </is>
       </c>
       <c r="B143" s="12" t="inlineStr">
         <is>
-          <t>AOC Coteaux du Layon</t>
+          <t>AOC Sauvignon</t>
         </is>
       </c>
       <c r="C143" s="12" t="inlineStr">
         <is>
-          <t>Blanc moelleux</t>
+          <t>Blanc sec</t>
         </is>
       </c>
       <c r="D143" s="12" t="inlineStr">
@@ -4741,10 +4783,10 @@
       </c>
       <c r="F143" s="13" t="n"/>
       <c r="G143" s="13" t="n">
-        <v>5.7</v>
+        <v>3.6</v>
       </c>
       <c r="H143" s="13" t="n">
-        <v>5.6</v>
+        <v>3.4</v>
       </c>
       <c r="I143" s="14" t="n"/>
       <c r="J143" s="14" t="n"/>
@@ -4752,12 +4794,12 @@
     <row r="144">
       <c r="A144" s="11" t="inlineStr">
         <is>
-          <t>S14 V05</t>
+          <t>S14 V04</t>
         </is>
       </c>
       <c r="B144" s="12" t="inlineStr">
         <is>
-          <t>AOC Coteaux du Layon Faye</t>
+          <t>AOC Coteaux du Layon</t>
         </is>
       </c>
       <c r="C144" s="12" t="inlineStr">
@@ -4777,10 +4819,10 @@
       </c>
       <c r="F144" s="13" t="n"/>
       <c r="G144" s="13" t="n">
-        <v>9.699999999999999</v>
+        <v>5.7</v>
       </c>
       <c r="H144" s="13" t="n">
-        <v>9.6</v>
+        <v>5.6</v>
       </c>
       <c r="I144" s="14" t="n"/>
       <c r="J144" s="14" t="n"/>
@@ -4788,22 +4830,22 @@
     <row r="145">
       <c r="A145" s="11" t="inlineStr">
         <is>
-          <t>S14 V06</t>
+          <t>S14 V05</t>
         </is>
       </c>
       <c r="B145" s="12" t="inlineStr">
         <is>
-          <t>AOC Crémant de Loire</t>
+          <t>AOC Coteaux du Layon Faye</t>
         </is>
       </c>
       <c r="C145" s="12" t="inlineStr">
         <is>
-          <t>Blanc brut</t>
+          <t>Blanc moelleux</t>
         </is>
       </c>
       <c r="D145" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E145" s="12" t="inlineStr">
@@ -4813,10 +4855,10 @@
       </c>
       <c r="F145" s="13" t="n"/>
       <c r="G145" s="13" t="n">
-        <v>5.8</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H145" s="13" t="n">
-        <v>5.6</v>
+        <v>9.6</v>
       </c>
       <c r="I145" s="14" t="n"/>
       <c r="J145" s="14" t="n"/>
@@ -4824,22 +4866,22 @@
     <row r="146">
       <c r="A146" s="11" t="inlineStr">
         <is>
-          <t>S14 V07</t>
+          <t>S14 V06</t>
         </is>
       </c>
       <c r="B146" s="12" t="inlineStr">
         <is>
-          <t>AOC Rosé de Loire</t>
+          <t>AOC Crémant de Loire</t>
         </is>
       </c>
       <c r="C146" s="12" t="inlineStr">
         <is>
-          <t>Rosé sec léger</t>
+          <t>Blanc brut</t>
         </is>
       </c>
       <c r="D146" s="12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E146" s="12" t="inlineStr">
@@ -4849,117 +4891,115 @@
       </c>
       <c r="F146" s="13" t="n"/>
       <c r="G146" s="13" t="n">
-        <v>3.5</v>
+        <v>5.8</v>
       </c>
       <c r="H146" s="13" t="n">
-        <v>3.3</v>
+        <v>5.6</v>
       </c>
       <c r="I146" s="14" t="n"/>
       <c r="J146" s="14" t="n"/>
     </row>
-    <row r="148" ht="22" customHeight="1">
-      <c r="A148" s="5" t="inlineStr">
+    <row r="147">
+      <c r="A147" s="11" t="inlineStr">
+        <is>
+          <t>S14 V07</t>
+        </is>
+      </c>
+      <c r="B147" s="12" t="inlineStr">
+        <is>
+          <t>AOC Rosé de Loire</t>
+        </is>
+      </c>
+      <c r="C147" s="12" t="inlineStr">
+        <is>
+          <t>Rosé sec léger</t>
+        </is>
+      </c>
+      <c r="D147" s="12" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E147" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
+      <c r="F147" s="13" t="n"/>
+      <c r="G147" s="13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H147" s="13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I147" s="14" t="n"/>
+      <c r="J147" s="14" t="n"/>
+    </row>
+    <row r="149" ht="22" customHeight="1">
+      <c r="A149" s="5" t="inlineStr">
         <is>
           <t>S15</t>
         </is>
       </c>
-      <c r="B148" s="6" t="inlineStr">
+      <c r="B149" s="6" t="inlineStr">
         <is>
           <t>Stand 15 — Champagne Vazart-Coquart (Champagne)</t>
         </is>
       </c>
-      <c r="C148" s="7" t="n"/>
-      <c r="D148" s="7" t="n"/>
-      <c r="E148" s="7" t="n"/>
-      <c r="F148" s="7" t="n"/>
-      <c r="G148" s="7" t="n"/>
-      <c r="H148" s="7" t="n"/>
-      <c r="I148" s="7" t="n"/>
-      <c r="J148" s="7" t="n"/>
-    </row>
-    <row r="149" ht="26" customHeight="1">
-      <c r="B149" s="8" t="inlineStr">
+      <c r="C149" s="7" t="n"/>
+      <c r="D149" s="7" t="n"/>
+      <c r="E149" s="7" t="n"/>
+      <c r="F149" s="7" t="n"/>
+      <c r="G149" s="7" t="n"/>
+      <c r="H149" s="7" t="n"/>
+      <c r="I149" s="7" t="n"/>
+      <c r="J149" s="7" t="n"/>
+    </row>
+    <row r="150" ht="26" customHeight="1">
+      <c r="B150" s="8" t="inlineStr">
         <is>
           <t>Vazart-Coquart &amp; Fils — paliers du salon</t>
         </is>
       </c>
-      <c r="C149" s="9" t="n"/>
-      <c r="D149" s="9" t="n"/>
-      <c r="E149" s="9" t="n"/>
-      <c r="F149" s="8" t="inlineStr">
+      <c r="C150" s="9" t="n"/>
+      <c r="D150" s="9" t="n"/>
+      <c r="E150" s="9" t="n"/>
+      <c r="F150" s="8" t="inlineStr">
         <is>
           <t>Prix unique</t>
         </is>
       </c>
-      <c r="G149" s="10" t="inlineStr">
+      <c r="G150" s="10" t="inlineStr">
         <is>
           <t>À partir de 48 bts</t>
         </is>
       </c>
-      <c r="H149" s="10" t="inlineStr">
+      <c r="H150" s="10" t="inlineStr">
         <is>
           <t>À partir de 78 bts</t>
         </is>
       </c>
-      <c r="I149" s="10" t="inlineStr">
+      <c r="I150" s="10" t="inlineStr">
         <is>
           <t>À partir de 96 bts</t>
         </is>
       </c>
-      <c r="J149" s="10" t="n"/>
-    </row>
-    <row r="150">
-      <c r="A150" s="11" t="inlineStr">
-        <is>
-          <t>S15 V01</t>
-        </is>
-      </c>
-      <c r="B150" s="12" t="inlineStr">
-        <is>
-          <t>Grand Cru Chouilly — Cuvée Camille Extra-Brut Blanc de Blancs</t>
-        </is>
-      </c>
-      <c r="C150" s="12" t="inlineStr">
-        <is>
-          <t>Blanc brut</t>
-        </is>
-      </c>
-      <c r="D150" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E150" s="12" t="inlineStr">
-        <is>
-          <t>75 cl</t>
-        </is>
-      </c>
-      <c r="F150" s="13" t="n"/>
-      <c r="G150" s="13" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="H150" s="13" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="I150" s="13" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="J150" s="14" t="n"/>
+      <c r="J150" s="10" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="11" t="inlineStr">
         <is>
-          <t>S15 V02</t>
+          <t>S15 V01</t>
         </is>
       </c>
       <c r="B151" s="12" t="inlineStr">
         <is>
-          <t>Grand Cru Chouilly — Brut Réserve Blanc de Blancs</t>
+          <t>Grand Cru Chouilly — Cuvée Camille Extra-Brut Blanc de Blancs</t>
         </is>
       </c>
       <c r="C151" s="12" t="inlineStr">
         <is>
-          <t>Blanc de Blancs</t>
+          <t>Blanc brut</t>
         </is>
       </c>
       <c r="D151" s="12" t="inlineStr">
@@ -4974,20 +5014,20 @@
       </c>
       <c r="F151" s="13" t="n"/>
       <c r="G151" s="13" t="n">
-        <v>20.8</v>
+        <v>20.1</v>
       </c>
       <c r="H151" s="13" t="n">
-        <v>20.6</v>
+        <v>19.9</v>
       </c>
       <c r="I151" s="13" t="n">
-        <v>20.3</v>
+        <v>19.6</v>
       </c>
       <c r="J151" s="14" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="11" t="inlineStr">
         <is>
-          <t>S15 V03</t>
+          <t>S15 V02</t>
         </is>
       </c>
       <c r="B152" s="12" t="inlineStr">
@@ -5007,35 +5047,35 @@
       </c>
       <c r="E152" s="12" t="inlineStr">
         <is>
-          <t>Magnum 1,5 L</t>
+          <t>75 cl</t>
         </is>
       </c>
       <c r="F152" s="13" t="n"/>
       <c r="G152" s="13" t="n">
-        <v>47.9</v>
+        <v>20.8</v>
       </c>
       <c r="H152" s="13" t="n">
-        <v>47.5</v>
+        <v>20.6</v>
       </c>
       <c r="I152" s="13" t="n">
-        <v>46.9</v>
+        <v>20.3</v>
       </c>
       <c r="J152" s="14" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="11" t="inlineStr">
         <is>
-          <t>S15 V04</t>
+          <t>S15 V03</t>
         </is>
       </c>
       <c r="B153" s="12" t="inlineStr">
         <is>
-          <t>Grand Cru Chouilly — Rosé Brut</t>
+          <t>Grand Cru Chouilly — Brut Réserve Blanc de Blancs</t>
         </is>
       </c>
       <c r="C153" s="12" t="inlineStr">
         <is>
-          <t>Rosé effervescent</t>
+          <t>Blanc de Blancs</t>
         </is>
       </c>
       <c r="D153" s="12" t="inlineStr">
@@ -5045,40 +5085,40 @@
       </c>
       <c r="E153" s="12" t="inlineStr">
         <is>
-          <t>75 cl</t>
+          <t>1,5 L</t>
         </is>
       </c>
       <c r="F153" s="13" t="n"/>
       <c r="G153" s="13" t="n">
-        <v>22.9</v>
+        <v>47.9</v>
       </c>
       <c r="H153" s="13" t="n">
-        <v>22.7</v>
+        <v>47.5</v>
       </c>
       <c r="I153" s="13" t="n">
-        <v>22.4</v>
+        <v>46.9</v>
       </c>
       <c r="J153" s="14" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="11" t="inlineStr">
         <is>
-          <t>S15 V05</t>
+          <t>S15 V04</t>
         </is>
       </c>
       <c r="B154" s="12" t="inlineStr">
         <is>
-          <t>Grand Cru Chouilly — Spécial Club Blanc de Blancs Extra-Brut</t>
+          <t>Grand Cru Chouilly — Rosé Brut</t>
         </is>
       </c>
       <c r="C154" s="12" t="inlineStr">
         <is>
-          <t>Blanc de Blancs</t>
+          <t>Rosé effervescent</t>
         </is>
       </c>
       <c r="D154" s="12" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E154" s="12" t="inlineStr">
@@ -5088,25 +5128,25 @@
       </c>
       <c r="F154" s="13" t="n"/>
       <c r="G154" s="13" t="n">
-        <v>41.1</v>
+        <v>22.9</v>
       </c>
       <c r="H154" s="13" t="n">
-        <v>40.9</v>
+        <v>22.7</v>
       </c>
       <c r="I154" s="13" t="n">
-        <v>40.6</v>
+        <v>22.4</v>
       </c>
       <c r="J154" s="14" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="11" t="inlineStr">
         <is>
-          <t>S15 V06</t>
+          <t>S15 V05</t>
         </is>
       </c>
       <c r="B155" s="12" t="inlineStr">
         <is>
-          <t>Grand Cru Chouilly — Extra Brut</t>
+          <t>Grand Cru Chouilly — Spécial Club Blanc de Blancs Extra-Brut</t>
         </is>
       </c>
       <c r="C155" s="12" t="inlineStr">
@@ -5116,7 +5156,7 @@
       </c>
       <c r="D155" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="E155" s="12" t="inlineStr">
@@ -5126,28 +5166,32 @@
       </c>
       <c r="F155" s="13" t="n"/>
       <c r="G155" s="13" t="n">
-        <v>25</v>
+        <v>41.1</v>
       </c>
       <c r="H155" s="13" t="n">
-        <v>24.8</v>
+        <v>40.9</v>
       </c>
       <c r="I155" s="13" t="n">
-        <v>24.5</v>
+        <v>40.6</v>
       </c>
       <c r="J155" s="14" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="11" t="inlineStr">
         <is>
-          <t>S15 V07</t>
+          <t>S15 V06</t>
         </is>
       </c>
       <c r="B156" s="12" t="inlineStr">
         <is>
-          <t>Grand Cru Chouilly — 82/18 Blanc de Blancs Zéro Dosage</t>
-        </is>
-      </c>
-      <c r="C156" s="12" t="n"/>
+          <t>Grand Cru Chouilly — Extra Brut</t>
+        </is>
+      </c>
+      <c r="C156" s="12" t="inlineStr">
+        <is>
+          <t>Blanc de Blancs</t>
+        </is>
+      </c>
       <c r="D156" s="12" t="inlineStr">
         <is>
           <t>—</t>
@@ -5160,98 +5204,98 @@
       </c>
       <c r="F156" s="13" t="n"/>
       <c r="G156" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="H156" s="13" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="I156" s="13" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="J156" s="14" t="n"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="11" t="inlineStr">
+        <is>
+          <t>S15 V07</t>
+        </is>
+      </c>
+      <c r="B157" s="12" t="inlineStr">
+        <is>
+          <t>Grand Cru Chouilly — 82/18 Blanc de Blancs Zéro Dosage</t>
+        </is>
+      </c>
+      <c r="C157" s="12" t="n"/>
+      <c r="D157" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E157" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
+      <c r="F157" s="13" t="n"/>
+      <c r="G157" s="13" t="n">
         <v>51.8</v>
       </c>
-      <c r="H156" s="13" t="n">
+      <c r="H157" s="13" t="n">
         <v>51.6</v>
       </c>
-      <c r="I156" s="13" t="n">
+      <c r="I157" s="13" t="n">
         <v>51.3</v>
       </c>
-      <c r="J156" s="14" t="n"/>
-    </row>
-    <row r="158" ht="22" customHeight="1">
-      <c r="A158" s="5" t="inlineStr">
+      <c r="J157" s="14" t="n"/>
+    </row>
+    <row r="159" ht="22" customHeight="1">
+      <c r="A159" s="5" t="inlineStr">
         <is>
           <t>S16</t>
         </is>
       </c>
-      <c r="B158" s="6" t="inlineStr">
+      <c r="B159" s="6" t="inlineStr">
         <is>
           <t>Stand 16 — Château Pré La Lande (Bordeaux)</t>
         </is>
       </c>
-      <c r="C158" s="7" t="n"/>
-      <c r="D158" s="7" t="n"/>
-      <c r="E158" s="7" t="n"/>
-      <c r="F158" s="7" t="n"/>
-      <c r="G158" s="7" t="n"/>
-      <c r="H158" s="7" t="n"/>
-      <c r="I158" s="7" t="n"/>
-      <c r="J158" s="7" t="n"/>
-    </row>
-    <row r="159" ht="26" customHeight="1">
-      <c r="B159" s="8" t="inlineStr">
+      <c r="C159" s="7" t="n"/>
+      <c r="D159" s="7" t="n"/>
+      <c r="E159" s="7" t="n"/>
+      <c r="F159" s="7" t="n"/>
+      <c r="G159" s="7" t="n"/>
+      <c r="H159" s="7" t="n"/>
+      <c r="I159" s="7" t="n"/>
+      <c r="J159" s="7" t="n"/>
+    </row>
+    <row r="160" ht="26" customHeight="1">
+      <c r="B160" s="8" t="inlineStr">
         <is>
           <t>Château Pré la Lande — paliers du salon</t>
         </is>
       </c>
-      <c r="C159" s="9" t="n"/>
-      <c r="D159" s="9" t="n"/>
-      <c r="E159" s="9" t="n"/>
-      <c r="F159" s="8" t="inlineStr">
+      <c r="C160" s="9" t="n"/>
+      <c r="D160" s="9" t="n"/>
+      <c r="E160" s="9" t="n"/>
+      <c r="F160" s="8" t="inlineStr">
         <is>
           <t>Prix unique</t>
         </is>
       </c>
-      <c r="G159" s="10" t="n"/>
-      <c r="H159" s="10" t="n"/>
-      <c r="I159" s="10" t="n"/>
-      <c r="J159" s="10" t="n"/>
-    </row>
-    <row r="160">
-      <c r="A160" s="11" t="inlineStr">
-        <is>
-          <t>S16 V01</t>
-        </is>
-      </c>
-      <c r="B160" s="12" t="inlineStr">
-        <is>
-          <t>AOC Sainte-Foy Côtes de Bordeaux — Cuvée Diane Rouge</t>
-        </is>
-      </c>
-      <c r="C160" s="12" t="inlineStr">
-        <is>
-          <t>Rouge</t>
-        </is>
-      </c>
-      <c r="D160" s="12" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="E160" s="12" t="inlineStr">
-        <is>
-          <t>75 cl</t>
-        </is>
-      </c>
-      <c r="F160" s="13" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="G160" s="14" t="n"/>
-      <c r="H160" s="14" t="n"/>
-      <c r="I160" s="14" t="n"/>
-      <c r="J160" s="14" t="n"/>
+      <c r="G160" s="10" t="n"/>
+      <c r="H160" s="10" t="n"/>
+      <c r="I160" s="10" t="n"/>
+      <c r="J160" s="10" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="11" t="inlineStr">
         <is>
-          <t>S16 V02</t>
+          <t>S16 V01</t>
         </is>
       </c>
       <c r="B161" s="12" t="inlineStr">
         <is>
-          <t>AOC Sainte-Foy Côtes de Bordeaux — Cuvée TerraCotta</t>
+          <t>AOC Sainte-Foy Côtes de Bordeaux — Cuvée Diane Rouge</t>
         </is>
       </c>
       <c r="C161" s="12" t="inlineStr">
@@ -5261,7 +5305,7 @@
       </c>
       <c r="D161" s="12" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="E161" s="12" t="inlineStr">
@@ -5270,7 +5314,7 @@
         </is>
       </c>
       <c r="F161" s="13" t="n">
-        <v>8.9</v>
+        <v>9.9</v>
       </c>
       <c r="G161" s="14" t="n"/>
       <c r="H161" s="14" t="n"/>
@@ -5280,12 +5324,12 @@
     <row r="162">
       <c r="A162" s="11" t="inlineStr">
         <is>
-          <t>S16 V03</t>
+          <t>S16 V02</t>
         </is>
       </c>
       <c r="B162" s="12" t="inlineStr">
         <is>
-          <t>AOC Sainte-Foy Côtes de Bordeaux — Cuvée des Fontenelles</t>
+          <t>AOC Sainte-Foy Côtes de Bordeaux — Cuvée TerraCotta</t>
         </is>
       </c>
       <c r="C162" s="12" t="inlineStr">
@@ -5295,7 +5339,7 @@
       </c>
       <c r="D162" s="12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="E162" s="12" t="inlineStr">
@@ -5304,100 +5348,100 @@
         </is>
       </c>
       <c r="F162" s="13" t="n">
-        <v>7.5</v>
+        <v>8.9</v>
       </c>
       <c r="G162" s="14" t="n"/>
       <c r="H162" s="14" t="n"/>
       <c r="I162" s="14" t="n"/>
       <c r="J162" s="14" t="n"/>
     </row>
-    <row r="164" ht="22" customHeight="1">
-      <c r="A164" s="5" t="inlineStr">
+    <row r="163">
+      <c r="A163" s="11" t="inlineStr">
+        <is>
+          <t>S16 V03</t>
+        </is>
+      </c>
+      <c r="B163" s="12" t="inlineStr">
+        <is>
+          <t>AOC Sainte-Foy Côtes de Bordeaux — Cuvée des Fontenelles</t>
+        </is>
+      </c>
+      <c r="C163" s="12" t="inlineStr">
+        <is>
+          <t>Rouge</t>
+        </is>
+      </c>
+      <c r="D163" s="12" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E163" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
+      <c r="F163" s="13" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="G163" s="14" t="n"/>
+      <c r="H163" s="14" t="n"/>
+      <c r="I163" s="14" t="n"/>
+      <c r="J163" s="14" t="n"/>
+    </row>
+    <row r="165" ht="22" customHeight="1">
+      <c r="A165" s="5" t="inlineStr">
         <is>
           <t>S17</t>
         </is>
       </c>
-      <c r="B164" s="6" t="inlineStr">
+      <c r="B165" s="6" t="inlineStr">
         <is>
           <t>Stand 17 — Vignobles Jean de Villebois (Loire)</t>
         </is>
       </c>
-      <c r="C164" s="7" t="n"/>
-      <c r="D164" s="7" t="n"/>
-      <c r="E164" s="7" t="n"/>
-      <c r="F164" s="7" t="n"/>
-      <c r="G164" s="7" t="n"/>
-      <c r="H164" s="7" t="n"/>
-      <c r="I164" s="7" t="n"/>
-      <c r="J164" s="7" t="n"/>
-    </row>
-    <row r="165" ht="26" customHeight="1">
-      <c r="B165" s="8" t="inlineStr">
+      <c r="C165" s="7" t="n"/>
+      <c r="D165" s="7" t="n"/>
+      <c r="E165" s="7" t="n"/>
+      <c r="F165" s="7" t="n"/>
+      <c r="G165" s="7" t="n"/>
+      <c r="H165" s="7" t="n"/>
+      <c r="I165" s="7" t="n"/>
+      <c r="J165" s="7" t="n"/>
+    </row>
+    <row r="166" ht="26" customHeight="1">
+      <c r="B166" s="8" t="inlineStr">
         <is>
           <t>Domaine Jean de Villebois — paliers du salon</t>
         </is>
       </c>
-      <c r="C165" s="9" t="n"/>
-      <c r="D165" s="9" t="n"/>
-      <c r="E165" s="9" t="n"/>
-      <c r="F165" s="8" t="inlineStr">
+      <c r="C166" s="9" t="n"/>
+      <c r="D166" s="9" t="n"/>
+      <c r="E166" s="9" t="n"/>
+      <c r="F166" s="8" t="inlineStr">
         <is>
           <t>Prix unique</t>
         </is>
       </c>
-      <c r="G165" s="10" t="n"/>
-      <c r="H165" s="10" t="n"/>
-      <c r="I165" s="10" t="n"/>
-      <c r="J165" s="10" t="n"/>
-    </row>
-    <row r="166">
-      <c r="A166" s="11" t="inlineStr">
-        <is>
-          <t>S17 V01</t>
-        </is>
-      </c>
-      <c r="B166" s="12" t="inlineStr">
-        <is>
-          <t>AOC Menetou-Salon Rouge</t>
-        </is>
-      </c>
-      <c r="C166" s="12" t="inlineStr">
-        <is>
-          <t>Rouge</t>
-        </is>
-      </c>
-      <c r="D166" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E166" s="12" t="inlineStr">
-        <is>
-          <t>75 cl</t>
-        </is>
-      </c>
-      <c r="F166" s="13" t="n">
-        <v>9.25</v>
-      </c>
-      <c r="G166" s="14" t="n"/>
-      <c r="H166" s="14" t="n"/>
-      <c r="I166" s="14" t="n"/>
-      <c r="J166" s="14" t="n"/>
+      <c r="G166" s="10" t="n"/>
+      <c r="H166" s="10" t="n"/>
+      <c r="I166" s="10" t="n"/>
+      <c r="J166" s="10" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="11" t="inlineStr">
         <is>
-          <t>S17 V02</t>
+          <t>S17 V01</t>
         </is>
       </c>
       <c r="B167" s="12" t="inlineStr">
         <is>
-          <t>AOC Menetou-Salon Blanc</t>
+          <t>AOC Menetou-Salon Rouge</t>
         </is>
       </c>
       <c r="C167" s="12" t="inlineStr">
         <is>
-          <t>Blanc</t>
+          <t>Rouge</t>
         </is>
       </c>
       <c r="D167" s="12" t="inlineStr">
@@ -5421,12 +5465,12 @@
     <row r="168">
       <c r="A168" s="11" t="inlineStr">
         <is>
-          <t>S17 V03</t>
+          <t>S17 V02</t>
         </is>
       </c>
       <c r="B168" s="12" t="inlineStr">
         <is>
-          <t>AOC Quincy</t>
+          <t>AOC Menetou-Salon Blanc</t>
         </is>
       </c>
       <c r="C168" s="12" t="inlineStr">
@@ -5445,7 +5489,7 @@
         </is>
       </c>
       <c r="F168" s="13" t="n">
-        <v>9.199999999999999</v>
+        <v>9.25</v>
       </c>
       <c r="G168" s="14" t="n"/>
       <c r="H168" s="14" t="n"/>
@@ -5455,12 +5499,12 @@
     <row r="169">
       <c r="A169" s="11" t="inlineStr">
         <is>
-          <t>S17 V04</t>
+          <t>S17 V03</t>
         </is>
       </c>
       <c r="B169" s="12" t="inlineStr">
         <is>
-          <t>AOC Sancerre — Les Beltins Blanc</t>
+          <t>AOC Quincy</t>
         </is>
       </c>
       <c r="C169" s="12" t="inlineStr">
@@ -5470,7 +5514,7 @@
       </c>
       <c r="D169" s="12" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E169" s="12" t="inlineStr">
@@ -5479,7 +5523,7 @@
         </is>
       </c>
       <c r="F169" s="13" t="n">
-        <v>25.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G169" s="14" t="n"/>
       <c r="H169" s="14" t="n"/>
@@ -5489,12 +5533,12 @@
     <row r="170">
       <c r="A170" s="11" t="inlineStr">
         <is>
-          <t>S17 V05</t>
+          <t>S17 V04</t>
         </is>
       </c>
       <c r="B170" s="12" t="inlineStr">
         <is>
-          <t>AOC Sancerre — Chêne à la Rouline Blanc</t>
+          <t>AOC Sancerre — Les Beltins Blanc</t>
         </is>
       </c>
       <c r="C170" s="12" t="inlineStr">
@@ -5523,12 +5567,12 @@
     <row r="171">
       <c r="A171" s="11" t="inlineStr">
         <is>
-          <t>S17 V06</t>
+          <t>S17 V05</t>
         </is>
       </c>
       <c r="B171" s="12" t="inlineStr">
         <is>
-          <t>AOC Pouilly-Fumé — Vignes de Tréleau Blanc</t>
+          <t>AOC Sancerre — Chêne à la Rouline Blanc</t>
         </is>
       </c>
       <c r="C171" s="12" t="inlineStr">
@@ -5538,7 +5582,7 @@
       </c>
       <c r="D171" s="12" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="E171" s="12" t="inlineStr">
@@ -5557,17 +5601,17 @@
     <row r="172">
       <c r="A172" s="11" t="inlineStr">
         <is>
-          <t>S17 V07</t>
+          <t>S17 V06</t>
         </is>
       </c>
       <c r="B172" s="12" t="inlineStr">
         <is>
-          <t>AOC Sancerre — La Louisonne Rouge</t>
+          <t>AOC Pouilly-Fumé — Vignes de Tréleau Blanc</t>
         </is>
       </c>
       <c r="C172" s="12" t="inlineStr">
         <is>
-          <t>Rouge</t>
+          <t>Blanc</t>
         </is>
       </c>
       <c r="D172" s="12" t="inlineStr">
@@ -5591,22 +5635,22 @@
     <row r="173">
       <c r="A173" s="11" t="inlineStr">
         <is>
-          <t>S17 V08</t>
+          <t>S17 V07</t>
         </is>
       </c>
       <c r="B173" s="12" t="inlineStr">
         <is>
-          <t>AOC Pouilly-Fumé</t>
+          <t>AOC Sancerre — La Louisonne Rouge</t>
         </is>
       </c>
       <c r="C173" s="12" t="inlineStr">
         <is>
-          <t>Blanc</t>
+          <t>Rouge</t>
         </is>
       </c>
       <c r="D173" s="12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="E173" s="12" t="inlineStr">
@@ -5615,7 +5659,7 @@
         </is>
       </c>
       <c r="F173" s="13" t="n">
-        <v>11.5</v>
+        <v>25.4</v>
       </c>
       <c r="G173" s="14" t="n"/>
       <c r="H173" s="14" t="n"/>
@@ -5625,12 +5669,12 @@
     <row r="174">
       <c r="A174" s="11" t="inlineStr">
         <is>
-          <t>S17 V09</t>
+          <t>S17 V08</t>
         </is>
       </c>
       <c r="B174" s="12" t="inlineStr">
         <is>
-          <t>AOC Touraine Chenonceaux</t>
+          <t>AOC Pouilly-Fumé</t>
         </is>
       </c>
       <c r="C174" s="12" t="inlineStr">
@@ -5640,7 +5684,7 @@
       </c>
       <c r="D174" s="12" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E174" s="12" t="inlineStr">
@@ -5649,7 +5693,7 @@
         </is>
       </c>
       <c r="F174" s="13" t="n">
-        <v>6.15</v>
+        <v>11.5</v>
       </c>
       <c r="G174" s="14" t="n"/>
       <c r="H174" s="14" t="n"/>
@@ -5659,12 +5703,12 @@
     <row r="175">
       <c r="A175" s="11" t="inlineStr">
         <is>
-          <t>S17 V10</t>
+          <t>S17 V09</t>
         </is>
       </c>
       <c r="B175" s="12" t="inlineStr">
         <is>
-          <t>AOC Sauvignon Blanc</t>
+          <t>AOC Touraine Chenonceaux</t>
         </is>
       </c>
       <c r="C175" s="12" t="inlineStr">
@@ -5674,7 +5718,7 @@
       </c>
       <c r="D175" s="12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E175" s="12" t="inlineStr">
@@ -5683,7 +5727,7 @@
         </is>
       </c>
       <c r="F175" s="13" t="n">
-        <v>4.7</v>
+        <v>6.15</v>
       </c>
       <c r="G175" s="14" t="n"/>
       <c r="H175" s="14" t="n"/>
@@ -5693,22 +5737,22 @@
     <row r="176">
       <c r="A176" s="11" t="inlineStr">
         <is>
-          <t>S17 V11</t>
+          <t>S17 V10</t>
         </is>
       </c>
       <c r="B176" s="12" t="inlineStr">
         <is>
-          <t>AOC Pinot Noir Rosé</t>
+          <t>AOC Sauvignon Blanc</t>
         </is>
       </c>
       <c r="C176" s="12" t="inlineStr">
         <is>
-          <t>Rosé</t>
+          <t>Blanc</t>
         </is>
       </c>
       <c r="D176" s="12" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E176" s="12" t="inlineStr">
@@ -5717,7 +5761,7 @@
         </is>
       </c>
       <c r="F176" s="13" t="n">
-        <v>4.45</v>
+        <v>4.7</v>
       </c>
       <c r="G176" s="14" t="n"/>
       <c r="H176" s="14" t="n"/>
@@ -5727,17 +5771,17 @@
     <row r="177">
       <c r="A177" s="11" t="inlineStr">
         <is>
-          <t>S17 V12</t>
+          <t>S17 V11</t>
         </is>
       </c>
       <c r="B177" s="12" t="inlineStr">
         <is>
-          <t>AOC Pinot Noir</t>
+          <t>AOC Pinot Noir Rosé</t>
         </is>
       </c>
       <c r="C177" s="12" t="inlineStr">
         <is>
-          <t>Rouge</t>
+          <t>Rosé</t>
         </is>
       </c>
       <c r="D177" s="12" t="inlineStr">
@@ -5751,95 +5795,95 @@
         </is>
       </c>
       <c r="F177" s="13" t="n">
-        <v>4.5</v>
+        <v>4.45</v>
       </c>
       <c r="G177" s="14" t="n"/>
       <c r="H177" s="14" t="n"/>
       <c r="I177" s="14" t="n"/>
       <c r="J177" s="14" t="n"/>
     </row>
-    <row r="179" ht="22" customHeight="1">
-      <c r="A179" s="5" t="inlineStr">
+    <row r="178">
+      <c r="A178" s="11" t="inlineStr">
+        <is>
+          <t>S17 V12</t>
+        </is>
+      </c>
+      <c r="B178" s="12" t="inlineStr">
+        <is>
+          <t>AOC Pinot Noir</t>
+        </is>
+      </c>
+      <c r="C178" s="12" t="inlineStr">
+        <is>
+          <t>Rouge</t>
+        </is>
+      </c>
+      <c r="D178" s="12" t="inlineStr">
+        <is>
+          <t>2024/25</t>
+        </is>
+      </c>
+      <c r="E178" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
+      <c r="F178" s="13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G178" s="14" t="n"/>
+      <c r="H178" s="14" t="n"/>
+      <c r="I178" s="14" t="n"/>
+      <c r="J178" s="14" t="n"/>
+    </row>
+    <row r="180" ht="22" customHeight="1">
+      <c r="A180" s="5" t="inlineStr">
         <is>
           <t>S18</t>
         </is>
       </c>
-      <c r="B179" s="6" t="inlineStr">
+      <c r="B180" s="6" t="inlineStr">
         <is>
           <t>Stand 18 — Domaine Sébastien Magnien (Bourgogne)</t>
         </is>
       </c>
-      <c r="C179" s="7" t="n"/>
-      <c r="D179" s="7" t="n"/>
-      <c r="E179" s="7" t="n"/>
-      <c r="F179" s="7" t="n"/>
-      <c r="G179" s="7" t="n"/>
-      <c r="H179" s="7" t="n"/>
-      <c r="I179" s="7" t="n"/>
-      <c r="J179" s="7" t="n"/>
-    </row>
-    <row r="180" ht="26" customHeight="1">
-      <c r="B180" s="8" t="inlineStr">
+      <c r="C180" s="7" t="n"/>
+      <c r="D180" s="7" t="n"/>
+      <c r="E180" s="7" t="n"/>
+      <c r="F180" s="7" t="n"/>
+      <c r="G180" s="7" t="n"/>
+      <c r="H180" s="7" t="n"/>
+      <c r="I180" s="7" t="n"/>
+      <c r="J180" s="7" t="n"/>
+    </row>
+    <row r="181" ht="26" customHeight="1">
+      <c r="B181" s="8" t="inlineStr">
         <is>
           <t>Domaine Sébastien Magnien — paliers du salon</t>
         </is>
       </c>
-      <c r="C180" s="9" t="n"/>
-      <c r="D180" s="9" t="n"/>
-      <c r="E180" s="9" t="n"/>
-      <c r="F180" s="8" t="inlineStr">
+      <c r="C181" s="9" t="n"/>
+      <c r="D181" s="9" t="n"/>
+      <c r="E181" s="9" t="n"/>
+      <c r="F181" s="8" t="inlineStr">
         <is>
           <t>Prix unique</t>
         </is>
       </c>
-      <c r="G180" s="10" t="n"/>
-      <c r="H180" s="10" t="n"/>
-      <c r="I180" s="10" t="n"/>
-      <c r="J180" s="10" t="n"/>
-    </row>
-    <row r="181">
-      <c r="A181" s="11" t="inlineStr">
-        <is>
-          <t>S18 V01</t>
-        </is>
-      </c>
-      <c r="B181" s="12" t="inlineStr">
-        <is>
-          <t>AOC Hautes-Côtes de Beaune</t>
-        </is>
-      </c>
-      <c r="C181" s="12" t="inlineStr">
-        <is>
-          <t>Blanc</t>
-        </is>
-      </c>
-      <c r="D181" s="12" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="E181" s="12" t="inlineStr">
-        <is>
-          <t>75 cl</t>
-        </is>
-      </c>
-      <c r="F181" s="13" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="G181" s="14" t="n"/>
-      <c r="H181" s="14" t="n"/>
-      <c r="I181" s="14" t="n"/>
-      <c r="J181" s="14" t="n"/>
+      <c r="G181" s="10" t="n"/>
+      <c r="H181" s="10" t="n"/>
+      <c r="I181" s="10" t="n"/>
+      <c r="J181" s="10" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="11" t="inlineStr">
         <is>
-          <t>S18 V02</t>
+          <t>S18 V01</t>
         </is>
       </c>
       <c r="B182" s="12" t="inlineStr">
         <is>
-          <t>AOC Meursault</t>
+          <t>AOC Hautes-Côtes de Beaune</t>
         </is>
       </c>
       <c r="C182" s="12" t="inlineStr">
@@ -5852,9 +5896,13 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="E182" s="12" t="n"/>
+      <c r="E182" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
       <c r="F182" s="13" t="n">
-        <v>35</v>
+        <v>13.5</v>
       </c>
       <c r="G182" s="14" t="n"/>
       <c r="H182" s="14" t="n"/>
@@ -5864,12 +5912,12 @@
     <row r="183">
       <c r="A183" s="11" t="inlineStr">
         <is>
-          <t>S18 V03</t>
+          <t>S18 V02</t>
         </is>
       </c>
       <c r="B183" s="12" t="inlineStr">
         <is>
-          <t>Beaune 1er Cru — Les Aigrots</t>
+          <t>AOC Meursault</t>
         </is>
       </c>
       <c r="C183" s="12" t="inlineStr">
@@ -5879,12 +5927,16 @@
       </c>
       <c r="D183" s="12" t="inlineStr">
         <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E183" s="12" t="n"/>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="E183" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
       <c r="F183" s="13" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="G183" s="14" t="n"/>
       <c r="H183" s="14" t="n"/>
@@ -5894,22 +5946,22 @@
     <row r="184">
       <c r="A184" s="11" t="inlineStr">
         <is>
-          <t>S18 V04</t>
+          <t>S18 V03</t>
         </is>
       </c>
       <c r="B184" s="12" t="inlineStr">
         <is>
-          <t>AOC Hautes-Côtes de Beaune — Clos de la Perrière</t>
+          <t>Beaune 1er Cru — Les Aigrots</t>
         </is>
       </c>
       <c r="C184" s="12" t="inlineStr">
         <is>
-          <t>Rouge</t>
+          <t>Blanc</t>
         </is>
       </c>
       <c r="D184" s="12" t="inlineStr">
         <is>
-          <t>2023/24</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="E184" s="12" t="inlineStr">
@@ -5918,7 +5970,7 @@
         </is>
       </c>
       <c r="F184" s="13" t="n">
-        <v>14.5</v>
+        <v>24</v>
       </c>
       <c r="G184" s="14" t="n"/>
       <c r="H184" s="14" t="n"/>
@@ -5928,12 +5980,12 @@
     <row r="185">
       <c r="A185" s="11" t="inlineStr">
         <is>
-          <t>S18 V05</t>
+          <t>S18 V04</t>
         </is>
       </c>
       <c r="B185" s="12" t="inlineStr">
         <is>
-          <t>AOC Beaune — Les Bons Feuvres</t>
+          <t>AOC Hautes-Côtes de Beaune — Clos de la Perrière</t>
         </is>
       </c>
       <c r="C185" s="12" t="inlineStr">
@@ -5952,7 +6004,7 @@
         </is>
       </c>
       <c r="F185" s="13" t="n">
-        <v>18</v>
+        <v>14.5</v>
       </c>
       <c r="G185" s="14" t="n"/>
       <c r="H185" s="14" t="n"/>
@@ -5962,12 +6014,12 @@
     <row r="186">
       <c r="A186" s="11" t="inlineStr">
         <is>
-          <t>S18 V06</t>
+          <t>S18 V05</t>
         </is>
       </c>
       <c r="B186" s="12" t="inlineStr">
         <is>
-          <t>Beaune 1er Cru — Les Aigrots</t>
+          <t>AOC Beaune — Les Bons Feuvres</t>
         </is>
       </c>
       <c r="C186" s="12" t="inlineStr">
@@ -5977,7 +6029,7 @@
       </c>
       <c r="D186" s="12" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023/24</t>
         </is>
       </c>
       <c r="E186" s="12" t="inlineStr">
@@ -5986,7 +6038,7 @@
         </is>
       </c>
       <c r="F186" s="13" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G186" s="14" t="n"/>
       <c r="H186" s="14" t="n"/>
@@ -5996,12 +6048,12 @@
     <row r="187">
       <c r="A187" s="11" t="inlineStr">
         <is>
-          <t>S18 V07</t>
+          <t>S18 V06</t>
         </is>
       </c>
       <c r="B187" s="12" t="inlineStr">
         <is>
-          <t>AOC Pommard — Les Perrières</t>
+          <t>Beaune 1er Cru — Les Aigrots</t>
         </is>
       </c>
       <c r="C187" s="12" t="inlineStr">
@@ -6020,116 +6072,112 @@
         </is>
       </c>
       <c r="F187" s="13" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G187" s="14" t="n"/>
       <c r="H187" s="14" t="n"/>
       <c r="I187" s="14" t="n"/>
       <c r="J187" s="14" t="n"/>
     </row>
-    <row r="189" ht="22" customHeight="1">
-      <c r="A189" s="5" t="inlineStr">
+    <row r="188">
+      <c r="A188" s="11" t="inlineStr">
+        <is>
+          <t>S18 V07</t>
+        </is>
+      </c>
+      <c r="B188" s="12" t="inlineStr">
+        <is>
+          <t>AOC Pommard — Les Perrières</t>
+        </is>
+      </c>
+      <c r="C188" s="12" t="inlineStr">
+        <is>
+          <t>Rouge</t>
+        </is>
+      </c>
+      <c r="D188" s="12" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="E188" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
+      <c r="F188" s="13" t="n">
+        <v>24</v>
+      </c>
+      <c r="G188" s="14" t="n"/>
+      <c r="H188" s="14" t="n"/>
+      <c r="I188" s="14" t="n"/>
+      <c r="J188" s="14" t="n"/>
+    </row>
+    <row r="190" ht="22" customHeight="1">
+      <c r="A190" s="5" t="inlineStr">
         <is>
           <t>S19</t>
         </is>
       </c>
-      <c r="B189" s="6" t="inlineStr">
+      <c r="B190" s="6" t="inlineStr">
         <is>
           <t>Stand 19 — Bastide de Blacailloux (Provence)</t>
         </is>
       </c>
-      <c r="C189" s="7" t="n"/>
-      <c r="D189" s="7" t="n"/>
-      <c r="E189" s="7" t="n"/>
-      <c r="F189" s="7" t="n"/>
-      <c r="G189" s="7" t="n"/>
-      <c r="H189" s="7" t="n"/>
-      <c r="I189" s="7" t="n"/>
-      <c r="J189" s="7" t="n"/>
-    </row>
-    <row r="190" ht="26" customHeight="1">
-      <c r="B190" s="8" t="inlineStr">
+      <c r="C190" s="7" t="n"/>
+      <c r="D190" s="7" t="n"/>
+      <c r="E190" s="7" t="n"/>
+      <c r="F190" s="7" t="n"/>
+      <c r="G190" s="7" t="n"/>
+      <c r="H190" s="7" t="n"/>
+      <c r="I190" s="7" t="n"/>
+      <c r="J190" s="7" t="n"/>
+    </row>
+    <row r="191" ht="26" customHeight="1">
+      <c r="B191" s="8" t="inlineStr">
         <is>
           <t>Bastide de Blacailloux — paliers du salon</t>
         </is>
       </c>
-      <c r="C190" s="9" t="n"/>
-      <c r="D190" s="9" t="n"/>
-      <c r="E190" s="9" t="n"/>
-      <c r="F190" s="8" t="inlineStr">
+      <c r="C191" s="9" t="n"/>
+      <c r="D191" s="9" t="n"/>
+      <c r="E191" s="9" t="n"/>
+      <c r="F191" s="8" t="inlineStr">
         <is>
           <t>Prix unique</t>
         </is>
       </c>
-      <c r="G190" s="10" t="inlineStr">
+      <c r="G191" s="10" t="inlineStr">
         <is>
           <t>À partir de 120 bts</t>
         </is>
       </c>
-      <c r="H190" s="10" t="inlineStr">
+      <c r="H191" s="10" t="inlineStr">
         <is>
           <t>À partir de 180 bts</t>
         </is>
       </c>
-      <c r="I190" s="10" t="inlineStr">
+      <c r="I191" s="10" t="inlineStr">
         <is>
           <t>À partir de 600 bts</t>
         </is>
       </c>
-      <c r="J190" s="10" t="n"/>
-    </row>
-    <row r="191">
-      <c r="A191" s="11" t="inlineStr">
-        <is>
-          <t>S19 V01</t>
-        </is>
-      </c>
-      <c r="B191" s="12" t="inlineStr">
-        <is>
-          <t>IGP Var Sainte Baume — Sainte-Probace Rosé</t>
-        </is>
-      </c>
-      <c r="C191" s="12" t="inlineStr">
-        <is>
-          <t>Rosé</t>
-        </is>
-      </c>
-      <c r="D191" s="12" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E191" s="12" t="inlineStr">
-        <is>
-          <t>75 cl</t>
-        </is>
-      </c>
-      <c r="F191" s="13" t="n"/>
-      <c r="G191" s="13" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="H191" s="13" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="I191" s="13" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="J191" s="14" t="n"/>
+      <c r="J191" s="10" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="11" t="inlineStr">
         <is>
-          <t>S19 V02</t>
+          <t>S19 V01</t>
         </is>
       </c>
       <c r="B192" s="12" t="inlineStr">
         <is>
-          <t>IGP Var Sainte Baume — Sainte-Probace Blanc</t>
+          <t>IGP Var Sainte Baume — Sainte-Probace Rosé</t>
         </is>
       </c>
       <c r="C192" s="12" t="inlineStr">
         <is>
-          <t>Blanc</t>
+          <t>Rosé</t>
         </is>
       </c>
       <c r="D192" s="12" t="inlineStr">
@@ -6144,10 +6192,10 @@
       </c>
       <c r="F192" s="13" t="n"/>
       <c r="G192" s="13" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="H192" s="13" t="n">
-        <v>5.35</v>
+        <v>5.15</v>
       </c>
       <c r="I192" s="13" t="n">
         <v>4.85</v>
@@ -6157,17 +6205,17 @@
     <row r="193">
       <c r="A193" s="11" t="inlineStr">
         <is>
-          <t>S19 V03</t>
+          <t>S19 V02</t>
         </is>
       </c>
       <c r="B193" s="12" t="inlineStr">
         <is>
-          <t>IGP Var Sainte Baume — Sainte-Probace Rouge</t>
+          <t>IGP Var Sainte Baume — Sainte-Probace Blanc</t>
         </is>
       </c>
       <c r="C193" s="12" t="inlineStr">
         <is>
-          <t>Rouge</t>
+          <t>Blanc</t>
         </is>
       </c>
       <c r="D193" s="12" t="inlineStr">
@@ -6195,17 +6243,17 @@
     <row r="194">
       <c r="A194" s="11" t="inlineStr">
         <is>
-          <t>S19 V04</t>
+          <t>S19 V03</t>
         </is>
       </c>
       <c r="B194" s="12" t="inlineStr">
         <is>
-          <t>AOC Coteaux Varois en Provence — Joio Rosé</t>
+          <t>IGP Var Sainte Baume — Sainte-Probace Rouge</t>
         </is>
       </c>
       <c r="C194" s="12" t="inlineStr">
         <is>
-          <t>Rosé</t>
+          <t>Rouge</t>
         </is>
       </c>
       <c r="D194" s="12" t="inlineStr">
@@ -6220,30 +6268,30 @@
       </c>
       <c r="F194" s="13" t="n"/>
       <c r="G194" s="13" t="n">
-        <v>6.3</v>
+        <v>5.5</v>
       </c>
       <c r="H194" s="13" t="n">
-        <v>6.15</v>
+        <v>5.35</v>
       </c>
       <c r="I194" s="13" t="n">
-        <v>5.9</v>
+        <v>4.85</v>
       </c>
       <c r="J194" s="14" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="11" t="inlineStr">
         <is>
-          <t>S19 V05</t>
+          <t>S19 V04</t>
         </is>
       </c>
       <c r="B195" s="12" t="inlineStr">
         <is>
-          <t>AOC Coteaux Varois en Provence — Joio Blanc</t>
+          <t>AOC Coteaux Varois en Provence — Joio Rosé</t>
         </is>
       </c>
       <c r="C195" s="12" t="inlineStr">
         <is>
-          <t>Blanc</t>
+          <t>Rosé</t>
         </is>
       </c>
       <c r="D195" s="12" t="inlineStr">
@@ -6264,29 +6312,29 @@
         <v>6.15</v>
       </c>
       <c r="I195" s="13" t="n">
-        <v>5.95</v>
+        <v>5.9</v>
       </c>
       <c r="J195" s="14" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="11" t="inlineStr">
         <is>
-          <t>S19 V06</t>
+          <t>S19 V05</t>
         </is>
       </c>
       <c r="B196" s="12" t="inlineStr">
         <is>
-          <t>AOC Coteaux Varois en Provence — Joio Rouge</t>
+          <t>AOC Coteaux Varois en Provence — Joio Blanc</t>
         </is>
       </c>
       <c r="C196" s="12" t="inlineStr">
         <is>
-          <t>Rouge</t>
+          <t>Blanc</t>
         </is>
       </c>
       <c r="D196" s="12" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E196" s="12" t="inlineStr">
@@ -6296,30 +6344,30 @@
       </c>
       <c r="F196" s="13" t="n"/>
       <c r="G196" s="13" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="H196" s="13" t="n">
-        <v>6.25</v>
+        <v>6.15</v>
       </c>
       <c r="I196" s="13" t="n">
-        <v>6.1</v>
+        <v>5.95</v>
       </c>
       <c r="J196" s="14" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="11" t="inlineStr">
         <is>
-          <t>S19 V07</t>
+          <t>S19 V06</t>
         </is>
       </c>
       <c r="B197" s="12" t="inlineStr">
         <is>
-          <t>AOC Coteaux Varois en Provence — Miraia Blanc</t>
+          <t>AOC Coteaux Varois en Provence — Joio Rouge</t>
         </is>
       </c>
       <c r="C197" s="12" t="inlineStr">
         <is>
-          <t>Blanc</t>
+          <t>Rouge</t>
         </is>
       </c>
       <c r="D197" s="12" t="inlineStr">
@@ -6334,35 +6382,35 @@
       </c>
       <c r="F197" s="13" t="n"/>
       <c r="G197" s="13" t="n">
-        <v>9.300000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="H197" s="13" t="n">
-        <v>9.050000000000001</v>
+        <v>6.25</v>
       </c>
       <c r="I197" s="13" t="n">
-        <v>8.800000000000001</v>
+        <v>6.1</v>
       </c>
       <c r="J197" s="14" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="11" t="inlineStr">
         <is>
-          <t>S19 V08</t>
+          <t>S19 V07</t>
         </is>
       </c>
       <c r="B198" s="12" t="inlineStr">
         <is>
-          <t>AOC Coteaux Varois en Provence — Miraia Rouge</t>
+          <t>AOC Coteaux Varois en Provence — Miraia Blanc</t>
         </is>
       </c>
       <c r="C198" s="12" t="inlineStr">
         <is>
-          <t>Rouge</t>
+          <t>Blanc</t>
         </is>
       </c>
       <c r="D198" s="12" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E198" s="12" t="inlineStr">
@@ -6372,25 +6420,25 @@
       </c>
       <c r="F198" s="13" t="n"/>
       <c r="G198" s="13" t="n">
-        <v>8.699999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H198" s="13" t="n">
-        <v>8.550000000000001</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="I198" s="13" t="n">
-        <v>8.300000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J198" s="14" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="11" t="inlineStr">
         <is>
-          <t>S19 V09</t>
+          <t>S19 V08</t>
         </is>
       </c>
       <c r="B199" s="12" t="inlineStr">
         <is>
-          <t>AOC Coteaux Varois en Provence — Aquino Rouge</t>
+          <t>AOC Coteaux Varois en Provence — Miraia Rouge</t>
         </is>
       </c>
       <c r="C199" s="12" t="inlineStr">
@@ -6400,7 +6448,7 @@
       </c>
       <c r="D199" s="12" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="E199" s="12" t="inlineStr">
@@ -6410,35 +6458,35 @@
       </c>
       <c r="F199" s="13" t="n"/>
       <c r="G199" s="13" t="n">
-        <v>16.3</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H199" s="13" t="n">
-        <v>16</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="I199" s="13" t="n">
-        <v>15.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J199" s="14" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="11" t="inlineStr">
         <is>
-          <t>S19 V10</t>
+          <t>S19 V09</t>
         </is>
       </c>
       <c r="B200" s="12" t="inlineStr">
         <is>
-          <t>AOC Coteaux Varois en Provence — Aquino Blanc</t>
+          <t>AOC Coteaux Varois en Provence — Aquino Rouge</t>
         </is>
       </c>
       <c r="C200" s="12" t="inlineStr">
         <is>
-          <t>Blanc</t>
+          <t>Rouge</t>
         </is>
       </c>
       <c r="D200" s="12" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="E200" s="12" t="inlineStr">
@@ -6458,104 +6506,104 @@
       </c>
       <c r="J200" s="14" t="n"/>
     </row>
-    <row r="202" ht="22" customHeight="1">
-      <c r="A202" s="5" t="inlineStr">
+    <row r="201">
+      <c r="A201" s="11" t="inlineStr">
+        <is>
+          <t>S19 V10</t>
+        </is>
+      </c>
+      <c r="B201" s="12" t="inlineStr">
+        <is>
+          <t>AOC Coteaux Varois en Provence — Aquino Blanc</t>
+        </is>
+      </c>
+      <c r="C201" s="12" t="inlineStr">
+        <is>
+          <t>Blanc</t>
+        </is>
+      </c>
+      <c r="D201" s="12" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="E201" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
+      <c r="F201" s="13" t="n"/>
+      <c r="G201" s="13" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="H201" s="13" t="n">
+        <v>16</v>
+      </c>
+      <c r="I201" s="13" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="J201" s="14" t="n"/>
+    </row>
+    <row r="203" ht="22" customHeight="1">
+      <c r="A203" s="5" t="inlineStr">
         <is>
           <t>S20</t>
         </is>
       </c>
-      <c r="B202" s="6" t="inlineStr">
+      <c r="B203" s="6" t="inlineStr">
         <is>
           <t>Stand 20 — Domaine Stratéus (Sud-Ouest)</t>
         </is>
       </c>
-      <c r="C202" s="7" t="n"/>
-      <c r="D202" s="7" t="n"/>
-      <c r="E202" s="7" t="n"/>
-      <c r="F202" s="7" t="n"/>
-      <c r="G202" s="7" t="n"/>
-      <c r="H202" s="7" t="n"/>
-      <c r="I202" s="7" t="n"/>
-      <c r="J202" s="7" t="n"/>
-    </row>
-    <row r="203" ht="26" customHeight="1">
-      <c r="B203" s="8" t="inlineStr">
+      <c r="C203" s="7" t="n"/>
+      <c r="D203" s="7" t="n"/>
+      <c r="E203" s="7" t="n"/>
+      <c r="F203" s="7" t="n"/>
+      <c r="G203" s="7" t="n"/>
+      <c r="H203" s="7" t="n"/>
+      <c r="I203" s="7" t="n"/>
+      <c r="J203" s="7" t="n"/>
+    </row>
+    <row r="204" ht="26" customHeight="1">
+      <c r="B204" s="8" t="inlineStr">
         <is>
           <t>Domaine Stratéus — paliers du salon</t>
         </is>
       </c>
-      <c r="C203" s="9" t="n"/>
-      <c r="D203" s="9" t="n"/>
-      <c r="E203" s="9" t="n"/>
-      <c r="F203" s="8" t="inlineStr">
+      <c r="C204" s="9" t="n"/>
+      <c r="D204" s="9" t="n"/>
+      <c r="E204" s="9" t="n"/>
+      <c r="F204" s="8" t="inlineStr">
         <is>
           <t>Prix unique</t>
         </is>
       </c>
-      <c r="G203" s="10" t="inlineStr">
+      <c r="G204" s="10" t="inlineStr">
         <is>
           <t>À partir de 60 bts</t>
         </is>
       </c>
-      <c r="H203" s="10" t="inlineStr">
+      <c r="H204" s="10" t="inlineStr">
         <is>
           <t>À partir de 120 bts</t>
         </is>
       </c>
-      <c r="I203" s="10" t="inlineStr">
+      <c r="I204" s="10" t="inlineStr">
         <is>
           <t>À partir de 300 bts</t>
         </is>
       </c>
-      <c r="J203" s="10" t="n"/>
-    </row>
-    <row r="204">
-      <c r="A204" s="11" t="inlineStr">
-        <is>
-          <t>S20 V01</t>
-        </is>
-      </c>
-      <c r="B204" s="12" t="inlineStr">
-        <is>
-          <t>AOC Madiran — Stratéus Rouge</t>
-        </is>
-      </c>
-      <c r="C204" s="12" t="inlineStr">
-        <is>
-          <t>Rouge</t>
-        </is>
-      </c>
-      <c r="D204" s="12" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="E204" s="12" t="inlineStr">
-        <is>
-          <t>75 cl</t>
-        </is>
-      </c>
-      <c r="F204" s="13" t="n"/>
-      <c r="G204" s="13" t="n">
-        <v>11.45</v>
-      </c>
-      <c r="H204" s="13" t="n">
-        <v>11</v>
-      </c>
-      <c r="I204" s="13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="J204" s="14" t="n"/>
+      <c r="J204" s="10" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="11" t="inlineStr">
         <is>
-          <t>S20 V02</t>
+          <t>S20 V01</t>
         </is>
       </c>
       <c r="B205" s="12" t="inlineStr">
         <is>
-          <t>AOC Madiran — Néolitik Rouge</t>
+          <t>AOC Madiran — Stratéus Rouge</t>
         </is>
       </c>
       <c r="C205" s="12" t="inlineStr">
@@ -6565,7 +6613,7 @@
       </c>
       <c r="D205" s="12" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="E205" s="12" t="inlineStr">
@@ -6575,25 +6623,25 @@
       </c>
       <c r="F205" s="13" t="n"/>
       <c r="G205" s="13" t="n">
-        <v>14</v>
+        <v>11.45</v>
       </c>
       <c r="H205" s="13" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="I205" s="13" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="J205" s="14" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="11" t="inlineStr">
         <is>
-          <t>S20 V03</t>
+          <t>S20 V02</t>
         </is>
       </c>
       <c r="B206" s="12" t="inlineStr">
         <is>
-          <t>AOC Madiran — Koloss Rouge</t>
+          <t>AOC Madiran — Néolitik Rouge</t>
         </is>
       </c>
       <c r="C206" s="12" t="inlineStr">
@@ -6613,30 +6661,30 @@
       </c>
       <c r="F206" s="13" t="n"/>
       <c r="G206" s="13" t="n">
-        <v>6.5</v>
+        <v>14</v>
       </c>
       <c r="H206" s="13" t="n">
-        <v>6</v>
+        <v>12.5</v>
       </c>
       <c r="I206" s="13" t="n">
-        <v>5.5</v>
+        <v>12</v>
       </c>
       <c r="J206" s="14" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="11" t="inlineStr">
         <is>
-          <t>S20 V04</t>
+          <t>S20 V03</t>
         </is>
       </c>
       <c r="B207" s="12" t="inlineStr">
         <is>
-          <t>VDF — Koloss Doux</t>
+          <t>AOC Madiran — Koloss Rouge</t>
         </is>
       </c>
       <c r="C207" s="12" t="inlineStr">
         <is>
-          <t>Doux</t>
+          <t>Rouge</t>
         </is>
       </c>
       <c r="D207" s="12" t="inlineStr">
@@ -6644,7 +6692,11 @@
           <t>2022</t>
         </is>
       </c>
-      <c r="E207" s="12" t="n"/>
+      <c r="E207" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
       <c r="F207" s="13" t="n"/>
       <c r="G207" s="13" t="n">
         <v>6.5</v>
@@ -6660,22 +6712,22 @@
     <row r="208">
       <c r="A208" s="11" t="inlineStr">
         <is>
-          <t>S20 V05</t>
+          <t>S20 V04</t>
         </is>
       </c>
       <c r="B208" s="12" t="inlineStr">
         <is>
-          <t>AOC Pacherenc du Vic-Bilh sec — Stratéus Blanc</t>
+          <t>VDF — Koloss Doux</t>
         </is>
       </c>
       <c r="C208" s="12" t="inlineStr">
         <is>
-          <t>Blanc</t>
+          <t>Doux</t>
         </is>
       </c>
       <c r="D208" s="12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="E208" s="12" t="inlineStr">
@@ -6685,25 +6737,25 @@
       </c>
       <c r="F208" s="13" t="n"/>
       <c r="G208" s="13" t="n">
-        <v>11.45</v>
+        <v>6.5</v>
       </c>
       <c r="H208" s="13" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I208" s="13" t="n">
-        <v>10.5</v>
+        <v>5.5</v>
       </c>
       <c r="J208" s="14" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="11" t="inlineStr">
         <is>
-          <t>S20 V06</t>
+          <t>S20 V05</t>
         </is>
       </c>
       <c r="B209" s="12" t="inlineStr">
         <is>
-          <t>AOC Pacherenc du Vic-Bilh sec — Néolitik Blanc</t>
+          <t>AOC Pacherenc du Vic-Bilh sec — Stratéus Blanc</t>
         </is>
       </c>
       <c r="C209" s="12" t="inlineStr">
@@ -6716,117 +6768,121 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="E209" s="12" t="n"/>
+      <c r="E209" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
       <c r="F209" s="13" t="n"/>
       <c r="G209" s="13" t="n">
+        <v>11.45</v>
+      </c>
+      <c r="H209" s="13" t="n">
+        <v>11</v>
+      </c>
+      <c r="I209" s="13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="J209" s="14" t="n"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="11" t="inlineStr">
+        <is>
+          <t>S20 V06</t>
+        </is>
+      </c>
+      <c r="B210" s="12" t="inlineStr">
+        <is>
+          <t>AOC Pacherenc du Vic-Bilh sec — Néolitik Blanc</t>
+        </is>
+      </c>
+      <c r="C210" s="12" t="inlineStr">
+        <is>
+          <t>Blanc</t>
+        </is>
+      </c>
+      <c r="D210" s="12" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E210" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
+      <c r="F210" s="13" t="n"/>
+      <c r="G210" s="13" t="n">
         <v>14</v>
       </c>
-      <c r="H209" s="13" t="n">
+      <c r="H210" s="13" t="n">
         <v>12.5</v>
       </c>
-      <c r="I209" s="13" t="n">
+      <c r="I210" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="J209" s="14" t="n"/>
-    </row>
-    <row r="211" ht="22" customHeight="1">
-      <c r="A211" s="5" t="inlineStr">
+      <c r="J210" s="14" t="n"/>
+    </row>
+    <row r="212" ht="22" customHeight="1">
+      <c r="A212" s="5" t="inlineStr">
         <is>
           <t>S21</t>
         </is>
       </c>
-      <c r="B211" s="6" t="inlineStr">
+      <c r="B212" s="6" t="inlineStr">
         <is>
           <t>Stand 21 — Famille d’Exea (Languedoc)</t>
         </is>
       </c>
-      <c r="C211" s="7" t="n"/>
-      <c r="D211" s="7" t="n"/>
-      <c r="E211" s="7" t="n"/>
-      <c r="F211" s="7" t="n"/>
-      <c r="G211" s="7" t="n"/>
-      <c r="H211" s="7" t="n"/>
-      <c r="I211" s="7" t="n"/>
-      <c r="J211" s="7" t="n"/>
-    </row>
-    <row r="212" ht="26" customHeight="1">
-      <c r="B212" s="8" t="inlineStr">
+      <c r="C212" s="7" t="n"/>
+      <c r="D212" s="7" t="n"/>
+      <c r="E212" s="7" t="n"/>
+      <c r="F212" s="7" t="n"/>
+      <c r="G212" s="7" t="n"/>
+      <c r="H212" s="7" t="n"/>
+      <c r="I212" s="7" t="n"/>
+      <c r="J212" s="7" t="n"/>
+    </row>
+    <row r="213" ht="26" customHeight="1">
+      <c r="B213" s="8" t="inlineStr">
         <is>
           <t>Famille d’Exea — paliers du salon</t>
         </is>
       </c>
-      <c r="C212" s="9" t="n"/>
-      <c r="D212" s="9" t="n"/>
-      <c r="E212" s="9" t="n"/>
-      <c r="F212" s="8" t="inlineStr">
+      <c r="C213" s="9" t="n"/>
+      <c r="D213" s="9" t="n"/>
+      <c r="E213" s="9" t="n"/>
+      <c r="F213" s="8" t="inlineStr">
         <is>
           <t>Prix unique</t>
         </is>
       </c>
-      <c r="G212" s="10" t="inlineStr">
+      <c r="G213" s="10" t="inlineStr">
         <is>
           <t>À partir de 144 cols</t>
         </is>
       </c>
-      <c r="H212" s="10" t="inlineStr">
+      <c r="H213" s="10" t="inlineStr">
         <is>
           <t>À partir de 300 cols</t>
         </is>
       </c>
-      <c r="I212" s="10" t="inlineStr">
+      <c r="I213" s="10" t="inlineStr">
         <is>
           <t>1 palette</t>
         </is>
       </c>
-      <c r="J212" s="10" t="n"/>
-    </row>
-    <row r="213">
-      <c r="A213" s="11" t="inlineStr">
-        <is>
-          <t>S21 V01</t>
-        </is>
-      </c>
-      <c r="B213" s="12" t="inlineStr">
-        <is>
-          <t>AOC Minervois — Chant de Lune Rouge</t>
-        </is>
-      </c>
-      <c r="C213" s="12" t="inlineStr">
-        <is>
-          <t>Rouge</t>
-        </is>
-      </c>
-      <c r="D213" s="12" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="E213" s="12" t="inlineStr">
-        <is>
-          <t>75 cl</t>
-        </is>
-      </c>
-      <c r="F213" s="13" t="n"/>
-      <c r="G213" s="13" t="n">
-        <v>7.78</v>
-      </c>
-      <c r="H213" s="13" t="n">
-        <v>7.16</v>
-      </c>
-      <c r="I213" s="13" t="n">
-        <v>6.13</v>
-      </c>
-      <c r="J213" s="14" t="n"/>
+      <c r="J213" s="10" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="11" t="inlineStr">
         <is>
-          <t>S21 V02</t>
+          <t>S21 V01</t>
         </is>
       </c>
       <c r="B214" s="12" t="inlineStr">
         <is>
-          <t>AOC Minervois — Chant de Lune Rouge, disponible en décembre 2026</t>
+          <t>AOC Minervois — Chant de Lune Rouge</t>
         </is>
       </c>
       <c r="C214" s="12" t="inlineStr">
@@ -6836,35 +6892,35 @@
       </c>
       <c r="D214" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E214" s="12" t="inlineStr">
         <is>
-          <t>Magnum 1,5 L</t>
+          <t>75 cl</t>
         </is>
       </c>
       <c r="F214" s="13" t="n"/>
       <c r="G214" s="13" t="n">
-        <v>16</v>
+        <v>7.78</v>
       </c>
       <c r="H214" s="13" t="n">
-        <v>14.72</v>
+        <v>7.16</v>
       </c>
       <c r="I214" s="13" t="n">
-        <v>12.6</v>
+        <v>6.13</v>
       </c>
       <c r="J214" s="14" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="11" t="inlineStr">
         <is>
-          <t>S21 V03</t>
+          <t>S21 V02</t>
         </is>
       </c>
       <c r="B215" s="12" t="inlineStr">
         <is>
-          <t>AOC Corbières — Rouge Sérame</t>
+          <t>AOC Minervois — Chant de Lune Rouge, disponible en décembre 2026</t>
         </is>
       </c>
       <c r="C215" s="12" t="inlineStr">
@@ -6874,45 +6930,45 @@
       </c>
       <c r="D215" s="12" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E215" s="12" t="inlineStr">
         <is>
-          <t>75 cl</t>
+          <t>1,5 L</t>
         </is>
       </c>
       <c r="F215" s="13" t="n"/>
       <c r="G215" s="13" t="n">
-        <v>7.78</v>
+        <v>16</v>
       </c>
       <c r="H215" s="13" t="n">
-        <v>7.16</v>
+        <v>14.72</v>
       </c>
       <c r="I215" s="13" t="n">
-        <v>6.13</v>
+        <v>12.6</v>
       </c>
       <c r="J215" s="14" t="n"/>
     </row>
     <row r="216">
       <c r="A216" s="11" t="inlineStr">
         <is>
-          <t>S21 V04</t>
+          <t>S21 V03</t>
         </is>
       </c>
       <c r="B216" s="12" t="inlineStr">
         <is>
-          <t>AOC Corbières — Blanc Sérame</t>
+          <t>AOC Corbières — Rouge Sérame</t>
         </is>
       </c>
       <c r="C216" s="12" t="inlineStr">
         <is>
-          <t>Blanc</t>
+          <t>Rouge</t>
         </is>
       </c>
       <c r="D216" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="E216" s="12" t="inlineStr">
@@ -6935,22 +6991,22 @@
     <row r="217">
       <c r="A217" s="11" t="inlineStr">
         <is>
-          <t>S21 V05</t>
+          <t>S21 V04</t>
         </is>
       </c>
       <c r="B217" s="12" t="inlineStr">
         <is>
-          <t>AOC Corbières — Oena Rouge</t>
+          <t>AOC Corbières — Blanc Sérame</t>
         </is>
       </c>
       <c r="C217" s="12" t="inlineStr">
         <is>
-          <t>Rouge</t>
+          <t>Blanc</t>
         </is>
       </c>
       <c r="D217" s="12" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E217" s="12" t="inlineStr">
@@ -6960,25 +7016,25 @@
       </c>
       <c r="F217" s="13" t="n"/>
       <c r="G217" s="13" t="n">
-        <v>14</v>
+        <v>7.78</v>
       </c>
       <c r="H217" s="13" t="n">
-        <v>14</v>
+        <v>7.16</v>
       </c>
       <c r="I217" s="13" t="n">
-        <v>14</v>
+        <v>6.13</v>
       </c>
       <c r="J217" s="14" t="n"/>
     </row>
     <row r="218">
       <c r="A218" s="11" t="inlineStr">
         <is>
-          <t>S21 V06</t>
+          <t>S21 V05</t>
         </is>
       </c>
       <c r="B218" s="12" t="inlineStr">
         <is>
-          <t>AOC Corbières — Jardins de Corbières Rouge</t>
+          <t>AOC Corbières — Oena Rouge</t>
         </is>
       </c>
       <c r="C218" s="12" t="inlineStr">
@@ -6988,7 +7044,7 @@
       </c>
       <c r="D218" s="12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="E218" s="12" t="inlineStr">
@@ -6998,25 +7054,25 @@
       </c>
       <c r="F218" s="13" t="n"/>
       <c r="G218" s="13" t="n">
-        <v>4.74</v>
+        <v>14</v>
       </c>
       <c r="H218" s="13" t="n">
-        <v>4.36</v>
+        <v>14</v>
       </c>
       <c r="I218" s="13" t="n">
-        <v>4.08</v>
+        <v>14</v>
       </c>
       <c r="J218" s="14" t="n"/>
     </row>
     <row r="219">
       <c r="A219" s="11" t="inlineStr">
         <is>
-          <t>S21 V07</t>
+          <t>S21 V06</t>
         </is>
       </c>
       <c r="B219" s="12" t="inlineStr">
         <is>
-          <t>AOC Corbières — Jardins de Corbières Rouge, disponible en décembre 2026</t>
+          <t>AOC Corbières — Jardins de Corbières Rouge</t>
         </is>
       </c>
       <c r="C219" s="12" t="inlineStr">
@@ -7026,99 +7082,105 @@
       </c>
       <c r="D219" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E219" s="12" t="inlineStr">
         <is>
-          <t>Magnum 1,5 L</t>
+          <t>75 cl</t>
         </is>
       </c>
       <c r="F219" s="13" t="n"/>
       <c r="G219" s="13" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="H219" s="13" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="I219" s="13" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="J219" s="14" t="n"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="11" t="inlineStr">
+        <is>
+          <t>S21 V07</t>
+        </is>
+      </c>
+      <c r="B220" s="12" t="inlineStr">
+        <is>
+          <t>AOC Corbières — Jardins de Corbières Rouge, disponible en décembre 2026</t>
+        </is>
+      </c>
+      <c r="C220" s="12" t="inlineStr">
+        <is>
+          <t>Rouge</t>
+        </is>
+      </c>
+      <c r="D220" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E220" s="12" t="inlineStr">
+        <is>
+          <t>1,5 L</t>
+        </is>
+      </c>
+      <c r="F220" s="13" t="n"/>
+      <c r="G220" s="13" t="n">
         <v>9.91</v>
       </c>
-      <c r="H219" s="13" t="n">
+      <c r="H220" s="13" t="n">
         <v>9.119999999999999</v>
       </c>
-      <c r="I219" s="13" t="n">
+      <c r="I220" s="13" t="n">
         <v>7.81</v>
       </c>
-      <c r="J219" s="14" t="n"/>
-    </row>
-    <row r="220" ht="26" customHeight="1">
-      <c r="B220" s="8" t="inlineStr">
+      <c r="J220" s="14" t="n"/>
+    </row>
+    <row r="221" ht="26" customHeight="1">
+      <c r="B221" s="8" t="inlineStr">
         <is>
           <t>Famille d’Exea — Jus de Cépages — paliers du salon</t>
         </is>
       </c>
-      <c r="C220" s="9" t="n"/>
-      <c r="D220" s="9" t="n"/>
-      <c r="E220" s="9" t="n"/>
-      <c r="F220" s="8" t="inlineStr">
+      <c r="C221" s="9" t="n"/>
+      <c r="D221" s="9" t="n"/>
+      <c r="E221" s="9" t="n"/>
+      <c r="F221" s="8" t="inlineStr">
         <is>
           <t>Prix unique</t>
         </is>
       </c>
-      <c r="G220" s="10" t="inlineStr">
+      <c r="G221" s="10" t="inlineStr">
+        <is>
+          <t>À partir de 72 bts</t>
+        </is>
+      </c>
+      <c r="H221" s="10" t="inlineStr">
         <is>
           <t>À partir de 144 bts</t>
         </is>
       </c>
-      <c r="H220" s="10" t="inlineStr">
-        <is>
-          <t>À partir de 300 bts</t>
-        </is>
-      </c>
-      <c r="I220" s="10" t="n"/>
-      <c r="J220" s="10" t="n"/>
-    </row>
-    <row r="221">
-      <c r="A221" s="11" t="inlineStr">
-        <is>
-          <t>S21 V08</t>
-        </is>
-      </c>
-      <c r="B221" s="12" t="inlineStr">
-        <is>
-          <t>Jus de cépages – Syrah</t>
-        </is>
-      </c>
-      <c r="C221" s="12" t="inlineStr">
-        <is>
-          <t>Rouge</t>
-        </is>
-      </c>
-      <c r="D221" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E221" s="12" t="inlineStr">
-        <is>
-          <t>50 cl</t>
-        </is>
-      </c>
-      <c r="F221" s="13" t="n"/>
-      <c r="G221" s="13" t="n"/>
-      <c r="H221" s="13" t="n"/>
-      <c r="I221" s="14" t="n"/>
-      <c r="J221" s="14" t="n"/>
+      <c r="I221" s="10" t="n"/>
+      <c r="J221" s="10" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="11" t="inlineStr">
         <is>
-          <t>S21 V09</t>
+          <t>S21 V08</t>
         </is>
       </c>
       <c r="B222" s="12" t="inlineStr">
         <is>
-          <t>Jus de cépages – Chardonnay</t>
+          <t>Jus de cépages – Syrah</t>
         </is>
       </c>
       <c r="C222" s="12" t="inlineStr">
         <is>
-          <t>Blanc</t>
+          <t>Rouge</t>
         </is>
       </c>
       <c r="D222" s="12" t="inlineStr">
@@ -7132,121 +7194,177 @@
         </is>
       </c>
       <c r="F222" s="13" t="n"/>
-      <c r="G222" s="13" t="n"/>
-      <c r="H222" s="13" t="n"/>
+      <c r="G222" s="13" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="H222" s="13" t="n">
+        <v>2.39</v>
+      </c>
       <c r="I222" s="14" t="n"/>
       <c r="J222" s="14" t="n"/>
     </row>
-    <row r="223">
-      <c r="A223" s="11" t="inlineStr">
+    <row r="223" ht="26" customHeight="1">
+      <c r="B223" s="8" t="inlineStr">
+        <is>
+          <t>Famille d’Exea — Jus de Cépages — paliers du salon</t>
+        </is>
+      </c>
+      <c r="C223" s="9" t="n"/>
+      <c r="D223" s="9" t="n"/>
+      <c r="E223" s="9" t="n"/>
+      <c r="F223" s="8" t="inlineStr">
+        <is>
+          <t>Prix unique</t>
+        </is>
+      </c>
+      <c r="G223" s="10" t="inlineStr">
+        <is>
+          <t>À partir de 144 bts</t>
+        </is>
+      </c>
+      <c r="H223" s="10" t="inlineStr">
+        <is>
+          <t>À partir de 300 bts</t>
+        </is>
+      </c>
+      <c r="I223" s="10" t="n"/>
+      <c r="J223" s="10" t="n"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="11" t="inlineStr">
+        <is>
+          <t>S21 V09</t>
+        </is>
+      </c>
+      <c r="B224" s="12" t="inlineStr">
+        <is>
+          <t>Jus de cépages – Syrah</t>
+        </is>
+      </c>
+      <c r="C224" s="12" t="inlineStr">
+        <is>
+          <t>Rouge</t>
+        </is>
+      </c>
+      <c r="D224" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E224" s="12" t="inlineStr">
+        <is>
+          <t>25 cl</t>
+        </is>
+      </c>
+      <c r="F224" s="13" t="n"/>
+      <c r="G224" s="13" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="H224" s="13" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="I224" s="14" t="n"/>
+      <c r="J224" s="14" t="n"/>
+    </row>
+    <row r="225" ht="26" customHeight="1">
+      <c r="B225" s="8" t="inlineStr">
+        <is>
+          <t>Famille d’Exea — Jus de Cépages — paliers du salon</t>
+        </is>
+      </c>
+      <c r="C225" s="9" t="n"/>
+      <c r="D225" s="9" t="n"/>
+      <c r="E225" s="9" t="n"/>
+      <c r="F225" s="8" t="inlineStr">
+        <is>
+          <t>Prix unique</t>
+        </is>
+      </c>
+      <c r="G225" s="10" t="inlineStr">
+        <is>
+          <t>À partir de 72 bts</t>
+        </is>
+      </c>
+      <c r="H225" s="10" t="inlineStr">
+        <is>
+          <t>À partir de 144 bts</t>
+        </is>
+      </c>
+      <c r="I225" s="10" t="n"/>
+      <c r="J225" s="10" t="n"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="11" t="inlineStr">
         <is>
           <t>S21 V10</t>
         </is>
       </c>
-      <c r="B223" s="12" t="inlineStr">
-        <is>
-          <t>Jus de cépages – Grenache</t>
-        </is>
-      </c>
-      <c r="C223" s="12" t="inlineStr">
-        <is>
-          <t>Rosé</t>
-        </is>
-      </c>
-      <c r="D223" s="12" t="inlineStr">
+      <c r="B226" s="12" t="inlineStr">
+        <is>
+          <t>Jus de cépages – Chardonnay</t>
+        </is>
+      </c>
+      <c r="C226" s="12" t="inlineStr">
+        <is>
+          <t>Blanc</t>
+        </is>
+      </c>
+      <c r="D226" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E223" s="12" t="inlineStr">
+      <c r="E226" s="12" t="inlineStr">
         <is>
           <t>50 cl</t>
         </is>
       </c>
-      <c r="F223" s="13" t="n"/>
-      <c r="G223" s="13" t="n"/>
-      <c r="H223" s="13" t="n"/>
-      <c r="I223" s="14" t="n"/>
-      <c r="J223" s="14" t="n"/>
-    </row>
-    <row r="225" ht="22" customHeight="1">
-      <c r="A225" s="5" t="inlineStr">
-        <is>
-          <t>S22</t>
-        </is>
-      </c>
-      <c r="B225" s="6" t="inlineStr">
-        <is>
-          <t>Stand 22 — Domaine de la Barbinière (Loire)</t>
-        </is>
-      </c>
-      <c r="C225" s="7" t="n"/>
-      <c r="D225" s="7" t="n"/>
-      <c r="E225" s="7" t="n"/>
-      <c r="F225" s="7" t="n"/>
-      <c r="G225" s="7" t="n"/>
-      <c r="H225" s="7" t="n"/>
-      <c r="I225" s="7" t="n"/>
-      <c r="J225" s="7" t="n"/>
-    </row>
-    <row r="226" ht="26" customHeight="1">
-      <c r="B226" s="8" t="inlineStr">
-        <is>
-          <t>Domaine de la Barbinière — paliers du salon</t>
-        </is>
-      </c>
-      <c r="C226" s="9" t="n"/>
-      <c r="D226" s="9" t="n"/>
-      <c r="E226" s="9" t="n"/>
-      <c r="F226" s="8" t="inlineStr">
+      <c r="F226" s="13" t="n"/>
+      <c r="G226" s="13" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="H226" s="13" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="I226" s="14" t="n"/>
+      <c r="J226" s="14" t="n"/>
+    </row>
+    <row r="227" ht="26" customHeight="1">
+      <c r="B227" s="8" t="inlineStr">
+        <is>
+          <t>Famille d’Exea — Jus de Cépages — paliers du salon</t>
+        </is>
+      </c>
+      <c r="C227" s="9" t="n"/>
+      <c r="D227" s="9" t="n"/>
+      <c r="E227" s="9" t="n"/>
+      <c r="F227" s="8" t="inlineStr">
         <is>
           <t>Prix unique</t>
         </is>
       </c>
-      <c r="G226" s="10" t="n"/>
-      <c r="H226" s="10" t="n"/>
-      <c r="I226" s="10" t="n"/>
-      <c r="J226" s="10" t="n"/>
-    </row>
-    <row r="227">
-      <c r="A227" s="11" t="inlineStr">
-        <is>
-          <t>S22 V01</t>
-        </is>
-      </c>
-      <c r="B227" s="12" t="inlineStr">
-        <is>
-          <t>AOC Fiefs Vendéens Chantonnay — Les Silex Rouge</t>
-        </is>
-      </c>
-      <c r="C227" s="12" t="inlineStr">
-        <is>
-          <t>Rouge</t>
-        </is>
-      </c>
-      <c r="D227" s="12" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E227" s="12" t="n"/>
-      <c r="F227" s="13" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="G227" s="14" t="n"/>
-      <c r="H227" s="14" t="n"/>
-      <c r="I227" s="14" t="n"/>
-      <c r="J227" s="14" t="n"/>
+      <c r="G227" s="10" t="inlineStr">
+        <is>
+          <t>À partir de 144 bts</t>
+        </is>
+      </c>
+      <c r="H227" s="10" t="inlineStr">
+        <is>
+          <t>À partir de 300 bts</t>
+        </is>
+      </c>
+      <c r="I227" s="10" t="n"/>
+      <c r="J227" s="10" t="n"/>
     </row>
     <row r="228">
       <c r="A228" s="11" t="inlineStr">
         <is>
-          <t>S22 V02</t>
+          <t>S21 V11</t>
         </is>
       </c>
       <c r="B228" s="12" t="inlineStr">
         <is>
-          <t>AOC Fiefs Vendéens Chantonnay — Les Gorinières Blanc</t>
+          <t>Jus de cépages – Chardonnay</t>
         </is>
       </c>
       <c r="C228" s="12" t="inlineStr">
@@ -7256,238 +7374,242 @@
       </c>
       <c r="D228" s="12" t="inlineStr">
         <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="E228" s="12" t="n"/>
-      <c r="F228" s="13" t="n">
-        <v>7.84</v>
-      </c>
-      <c r="G228" s="14" t="n"/>
-      <c r="H228" s="14" t="n"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E228" s="12" t="inlineStr">
+        <is>
+          <t>25 cl</t>
+        </is>
+      </c>
+      <c r="F228" s="13" t="n"/>
+      <c r="G228" s="13" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="H228" s="13" t="n">
+        <v>1.74</v>
+      </c>
       <c r="I228" s="14" t="n"/>
       <c r="J228" s="14" t="n"/>
     </row>
-    <row r="229">
-      <c r="A229" s="11" t="inlineStr">
-        <is>
-          <t>S22 V03</t>
-        </is>
-      </c>
-      <c r="B229" s="12" t="inlineStr">
-        <is>
-          <t>AOC Fiefs Vendéens Chantonnay — Les Courbes Blanc</t>
-        </is>
-      </c>
-      <c r="C229" s="12" t="inlineStr">
-        <is>
-          <t>Blanc</t>
-        </is>
-      </c>
-      <c r="D229" s="12" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="E229" s="12" t="n"/>
-      <c r="F229" s="13" t="n">
-        <v>7.23</v>
-      </c>
-      <c r="G229" s="14" t="n"/>
-      <c r="H229" s="14" t="n"/>
-      <c r="I229" s="14" t="n"/>
-      <c r="J229" s="14" t="n"/>
+    <row r="229" ht="26" customHeight="1">
+      <c r="B229" s="8" t="inlineStr">
+        <is>
+          <t>Famille d’Exea — Jus de Cépages — paliers du salon</t>
+        </is>
+      </c>
+      <c r="C229" s="9" t="n"/>
+      <c r="D229" s="9" t="n"/>
+      <c r="E229" s="9" t="n"/>
+      <c r="F229" s="8" t="inlineStr">
+        <is>
+          <t>Prix unique</t>
+        </is>
+      </c>
+      <c r="G229" s="10" t="inlineStr">
+        <is>
+          <t>À partir de 72 bts</t>
+        </is>
+      </c>
+      <c r="H229" s="10" t="inlineStr">
+        <is>
+          <t>À partir de 144 bts</t>
+        </is>
+      </c>
+      <c r="I229" s="10" t="n"/>
+      <c r="J229" s="10" t="n"/>
     </row>
     <row r="230">
       <c r="A230" s="11" t="inlineStr">
         <is>
-          <t>S22 V04</t>
+          <t>S21 V12</t>
         </is>
       </c>
       <c r="B230" s="12" t="inlineStr">
         <is>
-          <t>AOC Fiefs Vendéens Chantonnay — Les Amphibol Blanc</t>
+          <t>Jus de cépages – Grenache</t>
         </is>
       </c>
       <c r="C230" s="12" t="inlineStr">
         <is>
-          <t>Blanc</t>
+          <t>Rosé</t>
         </is>
       </c>
       <c r="D230" s="12" t="inlineStr">
         <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E230" s="12" t="n"/>
-      <c r="F230" s="13" t="n">
-        <v>5.66</v>
-      </c>
-      <c r="G230" s="14" t="n"/>
-      <c r="H230" s="14" t="n"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E230" s="12" t="inlineStr">
+        <is>
+          <t>50 cl</t>
+        </is>
+      </c>
+      <c r="F230" s="13" t="n"/>
+      <c r="G230" s="13" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="H230" s="13" t="n">
+        <v>2.39</v>
+      </c>
       <c r="I230" s="14" t="n"/>
       <c r="J230" s="14" t="n"/>
     </row>
-    <row r="231">
-      <c r="A231" s="11" t="inlineStr">
-        <is>
-          <t>S22 V05</t>
-        </is>
-      </c>
-      <c r="B231" s="12" t="inlineStr">
-        <is>
-          <t>AOC Fiefs Vendéens Chantonnay — Les Gneiss Rouge</t>
-        </is>
-      </c>
-      <c r="C231" s="12" t="inlineStr">
-        <is>
-          <t>Rouge</t>
-        </is>
-      </c>
-      <c r="D231" s="12" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E231" s="12" t="n"/>
-      <c r="F231" s="13" t="n">
-        <v>5.13</v>
-      </c>
-      <c r="G231" s="14" t="n"/>
-      <c r="H231" s="14" t="n"/>
-      <c r="I231" s="14" t="n"/>
-      <c r="J231" s="14" t="n"/>
+    <row r="231" ht="26" customHeight="1">
+      <c r="B231" s="8" t="inlineStr">
+        <is>
+          <t>Famille d’Exea — Jus de Cépages — paliers du salon</t>
+        </is>
+      </c>
+      <c r="C231" s="9" t="n"/>
+      <c r="D231" s="9" t="n"/>
+      <c r="E231" s="9" t="n"/>
+      <c r="F231" s="8" t="inlineStr">
+        <is>
+          <t>Prix unique</t>
+        </is>
+      </c>
+      <c r="G231" s="10" t="inlineStr">
+        <is>
+          <t>À partir de 144 bts</t>
+        </is>
+      </c>
+      <c r="H231" s="10" t="inlineStr">
+        <is>
+          <t>À partir de 300 bts</t>
+        </is>
+      </c>
+      <c r="I231" s="10" t="n"/>
+      <c r="J231" s="10" t="n"/>
     </row>
     <row r="232">
       <c r="A232" s="11" t="inlineStr">
         <is>
-          <t>S22 V06</t>
+          <t>S21 V13</t>
         </is>
       </c>
       <c r="B232" s="12" t="inlineStr">
         <is>
-          <t>IGP Val de Loire Pinot Noir — Le Bois Bouquet</t>
+          <t>Jus de cépages – Grenache</t>
         </is>
       </c>
       <c r="C232" s="12" t="inlineStr">
         <is>
-          <t>Rouge</t>
+          <t>Rosé</t>
         </is>
       </c>
       <c r="D232" s="12" t="inlineStr">
         <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E232" s="12" t="n"/>
-      <c r="F232" s="13" t="n">
-        <v>6.72</v>
-      </c>
-      <c r="G232" s="14" t="n"/>
-      <c r="H232" s="14" t="n"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E232" s="12" t="inlineStr">
+        <is>
+          <t>25 cl</t>
+        </is>
+      </c>
+      <c r="F232" s="13" t="n"/>
+      <c r="G232" s="13" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="H232" s="13" t="n">
+        <v>1.74</v>
+      </c>
       <c r="I232" s="14" t="n"/>
       <c r="J232" s="14" t="n"/>
     </row>
-    <row r="233">
-      <c r="A233" s="11" t="inlineStr">
-        <is>
-          <t>S22 V07</t>
-        </is>
-      </c>
-      <c r="B233" s="12" t="inlineStr">
-        <is>
-          <t>Méthode traditionnelle — L’O Brut</t>
-        </is>
-      </c>
-      <c r="C233" s="12" t="inlineStr">
-        <is>
-          <t>Blanc</t>
-        </is>
-      </c>
-      <c r="D233" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E233" s="12" t="n"/>
-      <c r="F233" s="13" t="n">
-        <v>6.28</v>
-      </c>
-      <c r="G233" s="14" t="n"/>
-      <c r="H233" s="14" t="n"/>
-      <c r="I233" s="14" t="n"/>
-      <c r="J233" s="14" t="n"/>
-    </row>
-    <row r="235" ht="22" customHeight="1">
-      <c r="A235" s="5" t="inlineStr">
-        <is>
-          <t>S23</t>
-        </is>
-      </c>
-      <c r="B235" s="6" t="inlineStr">
-        <is>
-          <t>Stand 23 — Champagne Solemme (Champagne)</t>
-        </is>
-      </c>
-      <c r="C235" s="7" t="n"/>
-      <c r="D235" s="7" t="n"/>
-      <c r="E235" s="7" t="n"/>
-      <c r="F235" s="7" t="n"/>
-      <c r="G235" s="7" t="n"/>
-      <c r="H235" s="7" t="n"/>
-      <c r="I235" s="7" t="n"/>
-      <c r="J235" s="7" t="n"/>
-    </row>
-    <row r="236" ht="26" customHeight="1">
-      <c r="B236" s="8" t="inlineStr">
-        <is>
-          <t>Champagne Solemme — paliers du salon</t>
-        </is>
-      </c>
-      <c r="C236" s="9" t="n"/>
-      <c r="D236" s="9" t="n"/>
-      <c r="E236" s="9" t="n"/>
-      <c r="F236" s="8" t="inlineStr">
+    <row r="234" ht="22" customHeight="1">
+      <c r="A234" s="5" t="inlineStr">
+        <is>
+          <t>S22</t>
+        </is>
+      </c>
+      <c r="B234" s="6" t="inlineStr">
+        <is>
+          <t>Stand 22 — Domaine de la Barbinière (Loire)</t>
+        </is>
+      </c>
+      <c r="C234" s="7" t="n"/>
+      <c r="D234" s="7" t="n"/>
+      <c r="E234" s="7" t="n"/>
+      <c r="F234" s="7" t="n"/>
+      <c r="G234" s="7" t="n"/>
+      <c r="H234" s="7" t="n"/>
+      <c r="I234" s="7" t="n"/>
+      <c r="J234" s="7" t="n"/>
+    </row>
+    <row r="235" ht="26" customHeight="1">
+      <c r="B235" s="8" t="inlineStr">
+        <is>
+          <t>Domaine de la Barbinière — paliers du salon</t>
+        </is>
+      </c>
+      <c r="C235" s="9" t="n"/>
+      <c r="D235" s="9" t="n"/>
+      <c r="E235" s="9" t="n"/>
+      <c r="F235" s="8" t="inlineStr">
         <is>
           <t>Prix unique</t>
         </is>
       </c>
-      <c r="G236" s="10" t="inlineStr">
-        <is>
-          <t>À partir de 60 bts</t>
-        </is>
-      </c>
-      <c r="H236" s="10" t="inlineStr">
-        <is>
-          <t>À partir de 120 bts</t>
-        </is>
-      </c>
-      <c r="I236" s="10" t="inlineStr">
-        <is>
-          <t>À partir de 240 bts</t>
-        </is>
-      </c>
-      <c r="J236" s="10" t="n"/>
+      <c r="G235" s="10" t="n"/>
+      <c r="H235" s="10" t="n"/>
+      <c r="I235" s="10" t="n"/>
+      <c r="J235" s="10" t="n"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="11" t="inlineStr">
+        <is>
+          <t>S22 V01</t>
+        </is>
+      </c>
+      <c r="B236" s="12" t="inlineStr">
+        <is>
+          <t>AOC Fiefs Vendéens Chantonnay — Les Silex Rouge</t>
+        </is>
+      </c>
+      <c r="C236" s="12" t="inlineStr">
+        <is>
+          <t>Rouge</t>
+        </is>
+      </c>
+      <c r="D236" s="12" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E236" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
+      <c r="F236" s="13" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="G236" s="14" t="n"/>
+      <c r="H236" s="14" t="n"/>
+      <c r="I236" s="14" t="n"/>
+      <c r="J236" s="14" t="n"/>
     </row>
     <row r="237">
       <c r="A237" s="11" t="inlineStr">
         <is>
-          <t>S23 V01</t>
+          <t>S22 V02</t>
         </is>
       </c>
       <c r="B237" s="12" t="inlineStr">
         <is>
-          <t>Premier Cru Champagne — Terre de Solemme Brut</t>
+          <t>AOC Fiefs Vendéens Chantonnay — Les Gorinières Blanc</t>
         </is>
       </c>
       <c r="C237" s="12" t="inlineStr">
         <is>
-          <t>Blanc brut</t>
+          <t>Blanc</t>
         </is>
       </c>
       <c r="D237" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E237" s="12" t="inlineStr">
@@ -7495,37 +7617,33 @@
           <t>75 cl</t>
         </is>
       </c>
-      <c r="F237" s="13" t="n"/>
-      <c r="G237" s="13" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="H237" s="13" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="I237" s="13" t="n">
-        <v>20</v>
-      </c>
+      <c r="F237" s="13" t="n">
+        <v>7.84</v>
+      </c>
+      <c r="G237" s="14" t="n"/>
+      <c r="H237" s="14" t="n"/>
+      <c r="I237" s="14" t="n"/>
       <c r="J237" s="14" t="n"/>
     </row>
     <row r="238">
       <c r="A238" s="11" t="inlineStr">
         <is>
-          <t>S23 V02</t>
+          <t>S22 V03</t>
         </is>
       </c>
       <c r="B238" s="12" t="inlineStr">
         <is>
-          <t>Premier Cru Champagne — Plénitude de Solemme Extra-Brut</t>
+          <t>AOC Fiefs Vendéens Chantonnay — Les Courbes Blanc</t>
         </is>
       </c>
       <c r="C238" s="12" t="inlineStr">
         <is>
-          <t>Blanc extra brut</t>
+          <t>Blanc</t>
         </is>
       </c>
       <c r="D238" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="E238" s="12" t="inlineStr">
@@ -7533,71 +7651,67 @@
           <t>75 cl</t>
         </is>
       </c>
-      <c r="F238" s="13" t="n"/>
-      <c r="G238" s="13" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="H238" s="13" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="I238" s="13" t="n">
-        <v>21.1</v>
-      </c>
+      <c r="F238" s="13" t="n">
+        <v>7.23</v>
+      </c>
+      <c r="G238" s="14" t="n"/>
+      <c r="H238" s="14" t="n"/>
+      <c r="I238" s="14" t="n"/>
       <c r="J238" s="14" t="n"/>
     </row>
     <row r="239">
       <c r="A239" s="11" t="inlineStr">
         <is>
-          <t>S23 V03</t>
+          <t>S22 V04</t>
         </is>
       </c>
       <c r="B239" s="12" t="inlineStr">
         <is>
-          <t>Premier Cru Champagne — Plénitude de Solemme Extra-Brut</t>
+          <t>AOC Fiefs Vendéens Chantonnay — Les Amphibol Blanc</t>
         </is>
       </c>
       <c r="C239" s="12" t="inlineStr">
         <is>
-          <t>Blanc extra brut</t>
+          <t>Blanc</t>
         </is>
       </c>
       <c r="D239" s="12" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E239" s="12" t="inlineStr">
         <is>
-          <t>Magnum 1,5 L</t>
+          <t>75 cl</t>
         </is>
       </c>
       <c r="F239" s="13" t="n">
-        <v>58</v>
-      </c>
-      <c r="G239" s="13" t="n"/>
-      <c r="H239" s="13" t="n"/>
-      <c r="I239" s="13" t="n"/>
+        <v>5.66</v>
+      </c>
+      <c r="G239" s="14" t="n"/>
+      <c r="H239" s="14" t="n"/>
+      <c r="I239" s="14" t="n"/>
       <c r="J239" s="14" t="n"/>
     </row>
     <row r="240">
       <c r="A240" s="11" t="inlineStr">
         <is>
-          <t>S23 V04</t>
+          <t>S22 V05</t>
         </is>
       </c>
       <c r="B240" s="12" t="inlineStr">
         <is>
-          <t>Premier Cru Champagne — Esprit de Solemme Brut Nature</t>
+          <t>AOC Fiefs Vendéens Chantonnay — Les Gneiss Rouge</t>
         </is>
       </c>
       <c r="C240" s="12" t="inlineStr">
         <is>
-          <t>Blanc brut nature</t>
+          <t>Rouge</t>
         </is>
       </c>
       <c r="D240" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="E240" s="12" t="inlineStr">
@@ -7605,37 +7719,33 @@
           <t>75 cl</t>
         </is>
       </c>
-      <c r="F240" s="13" t="n"/>
-      <c r="G240" s="13" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="H240" s="13" t="n">
-        <v>25.1</v>
-      </c>
-      <c r="I240" s="13" t="n">
-        <v>24.5</v>
-      </c>
+      <c r="F240" s="13" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="G240" s="14" t="n"/>
+      <c r="H240" s="14" t="n"/>
+      <c r="I240" s="14" t="n"/>
       <c r="J240" s="14" t="n"/>
     </row>
     <row r="241">
       <c r="A241" s="11" t="inlineStr">
         <is>
-          <t>S23 V05</t>
+          <t>S22 V06</t>
         </is>
       </c>
       <c r="B241" s="12" t="inlineStr">
         <is>
-          <t>Premier Cru Champagne — Nature de Solemme Blanc de Blancs Brut Nature</t>
+          <t>IGP Val de Loire Pinot Noir — Le Bois Bouquet</t>
         </is>
       </c>
       <c r="C241" s="12" t="inlineStr">
         <is>
-          <t>Blanc brut nature</t>
+          <t>Rouge</t>
         </is>
       </c>
       <c r="D241" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="E241" s="12" t="inlineStr">
@@ -7643,32 +7753,28 @@
           <t>75 cl</t>
         </is>
       </c>
-      <c r="F241" s="13" t="n"/>
-      <c r="G241" s="13" t="n">
-        <v>32</v>
-      </c>
-      <c r="H241" s="13" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="I241" s="13" t="n">
-        <v>30.5</v>
-      </c>
+      <c r="F241" s="13" t="n">
+        <v>6.72</v>
+      </c>
+      <c r="G241" s="14" t="n"/>
+      <c r="H241" s="14" t="n"/>
+      <c r="I241" s="14" t="n"/>
       <c r="J241" s="14" t="n"/>
     </row>
     <row r="242">
       <c r="A242" s="11" t="inlineStr">
         <is>
-          <t>S23 V06</t>
+          <t>S22 V07</t>
         </is>
       </c>
       <c r="B242" s="12" t="inlineStr">
         <is>
-          <t>Premier Cru Champagne — Ambre de Solemme Blanc de Noirs Brut Nature</t>
+          <t>Méthode traditionnelle — L’O Brut</t>
         </is>
       </c>
       <c r="C242" s="12" t="inlineStr">
         <is>
-          <t>Blanc brut nature</t>
+          <t>Blanc</t>
         </is>
       </c>
       <c r="D242" s="12" t="inlineStr">
@@ -7681,178 +7787,194 @@
           <t>75 cl</t>
         </is>
       </c>
-      <c r="F242" s="13" t="n"/>
-      <c r="G242" s="13" t="n">
-        <v>33.5</v>
-      </c>
-      <c r="H242" s="13" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="I242" s="13" t="n">
-        <v>31.85</v>
-      </c>
+      <c r="F242" s="13" t="n">
+        <v>6.28</v>
+      </c>
+      <c r="G242" s="14" t="n"/>
+      <c r="H242" s="14" t="n"/>
+      <c r="I242" s="14" t="n"/>
       <c r="J242" s="14" t="n"/>
     </row>
-    <row r="243">
-      <c r="A243" s="11" t="inlineStr">
-        <is>
-          <t>S23 V07</t>
-        </is>
-      </c>
-      <c r="B243" s="12" t="inlineStr">
-        <is>
-          <t>Premier Cru Champagne — Rose de Solemme Brut Nature</t>
-        </is>
-      </c>
-      <c r="C243" s="12" t="inlineStr">
-        <is>
-          <t>Rosé brut nature</t>
-        </is>
-      </c>
-      <c r="D243" s="12" t="inlineStr">
+    <row r="244" ht="22" customHeight="1">
+      <c r="A244" s="5" t="inlineStr">
+        <is>
+          <t>S23</t>
+        </is>
+      </c>
+      <c r="B244" s="6" t="inlineStr">
+        <is>
+          <t>Stand 23 — Champagne Solemme (Champagne)</t>
+        </is>
+      </c>
+      <c r="C244" s="7" t="n"/>
+      <c r="D244" s="7" t="n"/>
+      <c r="E244" s="7" t="n"/>
+      <c r="F244" s="7" t="n"/>
+      <c r="G244" s="7" t="n"/>
+      <c r="H244" s="7" t="n"/>
+      <c r="I244" s="7" t="n"/>
+      <c r="J244" s="7" t="n"/>
+    </row>
+    <row r="245" ht="26" customHeight="1">
+      <c r="B245" s="8" t="inlineStr">
+        <is>
+          <t>Champagne Solemme — paliers du salon</t>
+        </is>
+      </c>
+      <c r="C245" s="9" t="n"/>
+      <c r="D245" s="9" t="n"/>
+      <c r="E245" s="9" t="n"/>
+      <c r="F245" s="8" t="inlineStr">
+        <is>
+          <t>Prix unique</t>
+        </is>
+      </c>
+      <c r="G245" s="10" t="inlineStr">
+        <is>
+          <t>À partir de 60 bts</t>
+        </is>
+      </c>
+      <c r="H245" s="10" t="inlineStr">
+        <is>
+          <t>À partir de 120 bts</t>
+        </is>
+      </c>
+      <c r="I245" s="10" t="inlineStr">
+        <is>
+          <t>À partir de 240 bts</t>
+        </is>
+      </c>
+      <c r="J245" s="10" t="n"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="11" t="inlineStr">
+        <is>
+          <t>S23 V01</t>
+        </is>
+      </c>
+      <c r="B246" s="12" t="inlineStr">
+        <is>
+          <t>Premier Cru Champagne — Terre de Solemme Brut</t>
+        </is>
+      </c>
+      <c r="C246" s="12" t="inlineStr">
+        <is>
+          <t>Blanc brut</t>
+        </is>
+      </c>
+      <c r="D246" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E243" s="12" t="inlineStr">
-        <is>
-          <t>75 cl</t>
-        </is>
-      </c>
-      <c r="F243" s="13" t="n"/>
-      <c r="G243" s="13" t="n">
-        <v>36</v>
-      </c>
-      <c r="H243" s="13" t="n">
-        <v>35.1</v>
-      </c>
-      <c r="I243" s="13" t="n">
-        <v>34.2</v>
-      </c>
-      <c r="J243" s="14" t="n"/>
-    </row>
-    <row r="245" ht="22" customHeight="1">
-      <c r="A245" s="5" t="inlineStr">
-        <is>
-          <t>S24</t>
-        </is>
-      </c>
-      <c r="B245" s="6" t="inlineStr">
-        <is>
-          <t>Stand 24 — Château Escarderie (Bordeaux)</t>
-        </is>
-      </c>
-      <c r="C245" s="7" t="n"/>
-      <c r="D245" s="7" t="n"/>
-      <c r="E245" s="7" t="n"/>
-      <c r="F245" s="7" t="n"/>
-      <c r="G245" s="7" t="n"/>
-      <c r="H245" s="7" t="n"/>
-      <c r="I245" s="7" t="n"/>
-      <c r="J245" s="7" t="n"/>
-    </row>
-    <row r="246" ht="26" customHeight="1">
-      <c r="B246" s="8" t="inlineStr">
-        <is>
-          <t>Château l’Escarderie — paliers du salon</t>
-        </is>
-      </c>
-      <c r="C246" s="9" t="n"/>
-      <c r="D246" s="9" t="n"/>
-      <c r="E246" s="9" t="n"/>
-      <c r="F246" s="8" t="inlineStr">
-        <is>
-          <t>Prix unique</t>
-        </is>
-      </c>
-      <c r="G246" s="10" t="n"/>
-      <c r="H246" s="10" t="n"/>
-      <c r="I246" s="10" t="n"/>
-      <c r="J246" s="10" t="n"/>
+      <c r="E246" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
+      <c r="F246" s="13" t="n"/>
+      <c r="G246" s="13" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="H246" s="13" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="I246" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="J246" s="14" t="n"/>
     </row>
     <row r="247">
       <c r="A247" s="11" t="inlineStr">
         <is>
-          <t>S24 V01</t>
+          <t>S23 V02</t>
         </is>
       </c>
       <c r="B247" s="12" t="inlineStr">
         <is>
-          <t>AOC Fronsac — Château Lafargue Rouge</t>
+          <t>Premier Cru Champagne — Plénitude de Solemme Extra-Brut</t>
         </is>
       </c>
       <c r="C247" s="12" t="inlineStr">
         <is>
-          <t>Rouge</t>
+          <t>Blanc extra brut</t>
         </is>
       </c>
       <c r="D247" s="12" t="inlineStr">
         <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="E247" s="12" t="n"/>
-      <c r="F247" s="13" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="G247" s="14" t="n"/>
-      <c r="H247" s="14" t="n"/>
-      <c r="I247" s="14" t="n"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E247" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
+      <c r="F247" s="13" t="n"/>
+      <c r="G247" s="13" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="H247" s="13" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="I247" s="13" t="n">
+        <v>21.1</v>
+      </c>
       <c r="J247" s="14" t="n"/>
     </row>
     <row r="248">
       <c r="A248" s="11" t="inlineStr">
         <is>
-          <t>S24 V02</t>
+          <t>S23 V03</t>
         </is>
       </c>
       <c r="B248" s="12" t="inlineStr">
         <is>
-          <t>AOC Fronsac — Amphora Rouge</t>
+          <t>Premier Cru Champagne — Plénitude de Solemme Extra-Brut</t>
         </is>
       </c>
       <c r="C248" s="12" t="inlineStr">
         <is>
-          <t>Rouge</t>
+          <t>Blanc extra brut</t>
         </is>
       </c>
       <c r="D248" s="12" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="E248" s="12" t="inlineStr">
         <is>
-          <t>75 cl</t>
+          <t>1,5 L</t>
         </is>
       </c>
       <c r="F248" s="13" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="G248" s="14" t="n"/>
-      <c r="H248" s="14" t="n"/>
-      <c r="I248" s="14" t="n"/>
+        <v>58</v>
+      </c>
+      <c r="G248" s="13" t="n"/>
+      <c r="H248" s="13" t="n"/>
+      <c r="I248" s="13" t="n"/>
       <c r="J248" s="14" t="n"/>
     </row>
     <row r="249">
       <c r="A249" s="11" t="inlineStr">
         <is>
-          <t>S24 V03</t>
+          <t>S23 V04</t>
         </is>
       </c>
       <c r="B249" s="12" t="inlineStr">
         <is>
-          <t>VDF — La Confiance Rouge</t>
+          <t>Premier Cru Champagne — Esprit de Solemme Brut Nature</t>
         </is>
       </c>
       <c r="C249" s="12" t="inlineStr">
         <is>
-          <t>Rouge</t>
+          <t>Blanc brut nature</t>
         </is>
       </c>
       <c r="D249" s="12" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E249" s="12" t="inlineStr">
@@ -7860,469 +7982,467 @@
           <t>75 cl</t>
         </is>
       </c>
-      <c r="F249" s="13" t="n">
-        <v>8.449999999999999</v>
-      </c>
-      <c r="G249" s="14" t="n"/>
-      <c r="H249" s="14" t="n"/>
-      <c r="I249" s="14" t="n"/>
+      <c r="F249" s="13" t="n"/>
+      <c r="G249" s="13" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="H249" s="13" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="I249" s="13" t="n">
+        <v>24.5</v>
+      </c>
       <c r="J249" s="14" t="n"/>
     </row>
-    <row r="251" ht="22" customHeight="1">
-      <c r="A251" s="5" t="inlineStr">
-        <is>
-          <t>S25</t>
-        </is>
-      </c>
-      <c r="B251" s="6" t="inlineStr">
-        <is>
-          <t>Stand 25 — Chai Berteaud Manceau (Loire)</t>
-        </is>
-      </c>
-      <c r="C251" s="7" t="n"/>
-      <c r="D251" s="7" t="n"/>
-      <c r="E251" s="7" t="n"/>
-      <c r="F251" s="7" t="n"/>
-      <c r="G251" s="7" t="n"/>
-      <c r="H251" s="7" t="n"/>
-      <c r="I251" s="7" t="n"/>
-      <c r="J251" s="7" t="n"/>
-    </row>
-    <row r="252" ht="26" customHeight="1">
-      <c r="B252" s="8" t="inlineStr">
-        <is>
-          <t>Chai Berteaud Manceau — paliers du salon</t>
-        </is>
-      </c>
-      <c r="C252" s="9" t="n"/>
-      <c r="D252" s="9" t="n"/>
-      <c r="E252" s="9" t="n"/>
-      <c r="F252" s="8" t="inlineStr">
+    <row r="250">
+      <c r="A250" s="11" t="inlineStr">
+        <is>
+          <t>S23 V05</t>
+        </is>
+      </c>
+      <c r="B250" s="12" t="inlineStr">
+        <is>
+          <t>Premier Cru Champagne — Nature de Solemme Blanc de Blancs Brut Nature</t>
+        </is>
+      </c>
+      <c r="C250" s="12" t="inlineStr">
+        <is>
+          <t>Blanc brut nature</t>
+        </is>
+      </c>
+      <c r="D250" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E250" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
+      <c r="F250" s="13" t="n"/>
+      <c r="G250" s="13" t="n">
+        <v>32</v>
+      </c>
+      <c r="H250" s="13" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="I250" s="13" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="J250" s="14" t="n"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="11" t="inlineStr">
+        <is>
+          <t>S23 V06</t>
+        </is>
+      </c>
+      <c r="B251" s="12" t="inlineStr">
+        <is>
+          <t>Premier Cru Champagne — Ambre de Solemme Blanc de Noirs Brut Nature</t>
+        </is>
+      </c>
+      <c r="C251" s="12" t="inlineStr">
+        <is>
+          <t>Blanc brut nature</t>
+        </is>
+      </c>
+      <c r="D251" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E251" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
+      <c r="F251" s="13" t="n"/>
+      <c r="G251" s="13" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="H251" s="13" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="I251" s="13" t="n">
+        <v>31.85</v>
+      </c>
+      <c r="J251" s="14" t="n"/>
+    </row>
+    <row r="252">
+      <c r="A252" s="11" t="inlineStr">
+        <is>
+          <t>S23 V07</t>
+        </is>
+      </c>
+      <c r="B252" s="12" t="inlineStr">
+        <is>
+          <t>Premier Cru Champagne — Rose de Solemme Brut Nature</t>
+        </is>
+      </c>
+      <c r="C252" s="12" t="inlineStr">
+        <is>
+          <t>Rosé brut nature</t>
+        </is>
+      </c>
+      <c r="D252" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E252" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
+      <c r="F252" s="13" t="n"/>
+      <c r="G252" s="13" t="n">
+        <v>36</v>
+      </c>
+      <c r="H252" s="13" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="I252" s="13" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="J252" s="14" t="n"/>
+    </row>
+    <row r="254" ht="22" customHeight="1">
+      <c r="A254" s="5" t="inlineStr">
+        <is>
+          <t>S24</t>
+        </is>
+      </c>
+      <c r="B254" s="6" t="inlineStr">
+        <is>
+          <t>Stand 24 — Château Escarderie (Bordeaux)</t>
+        </is>
+      </c>
+      <c r="C254" s="7" t="n"/>
+      <c r="D254" s="7" t="n"/>
+      <c r="E254" s="7" t="n"/>
+      <c r="F254" s="7" t="n"/>
+      <c r="G254" s="7" t="n"/>
+      <c r="H254" s="7" t="n"/>
+      <c r="I254" s="7" t="n"/>
+      <c r="J254" s="7" t="n"/>
+    </row>
+    <row r="255" ht="26" customHeight="1">
+      <c r="B255" s="8" t="inlineStr">
+        <is>
+          <t>Château l’Escarderie — paliers du salon</t>
+        </is>
+      </c>
+      <c r="C255" s="9" t="n"/>
+      <c r="D255" s="9" t="n"/>
+      <c r="E255" s="9" t="n"/>
+      <c r="F255" s="8" t="inlineStr">
         <is>
           <t>Prix unique</t>
         </is>
       </c>
-      <c r="G252" s="10" t="inlineStr">
-        <is>
-          <t>À partir de 36 cols</t>
-        </is>
-      </c>
-      <c r="H252" s="10" t="inlineStr">
-        <is>
-          <t>À partir de 60 cols</t>
-        </is>
-      </c>
-      <c r="I252" s="10" t="inlineStr">
-        <is>
-          <t>À partir de 120 cols</t>
-        </is>
-      </c>
-      <c r="J252" s="10" t="inlineStr">
-        <is>
-          <t>À partir de 240 cols</t>
-        </is>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" s="11" t="inlineStr">
-        <is>
-          <t>S25 V01</t>
-        </is>
-      </c>
-      <c r="B253" s="12" t="inlineStr">
-        <is>
-          <t>IGP Val de Loire — Courant Chenin</t>
-        </is>
-      </c>
-      <c r="C253" s="12" t="inlineStr">
-        <is>
-          <t>Blanc sec</t>
-        </is>
-      </c>
-      <c r="D253" s="12" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E253" s="12" t="inlineStr">
-        <is>
-          <t>75 cl</t>
-        </is>
-      </c>
-      <c r="F253" s="13" t="n"/>
-      <c r="G253" s="13" t="n">
-        <v>6.95</v>
-      </c>
-      <c r="H253" s="13" t="n">
-        <v>6.45</v>
-      </c>
-      <c r="I253" s="13" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="J253" s="13" t="n">
-        <v>5.75</v>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" s="11" t="inlineStr">
-        <is>
-          <t>S25 V02</t>
-        </is>
-      </c>
-      <c r="B254" s="12" t="inlineStr">
-        <is>
-          <t>IGP Val de Loire — Source Melon B.</t>
-        </is>
-      </c>
-      <c r="C254" s="12" t="inlineStr">
-        <is>
-          <t>Blanc sec</t>
-        </is>
-      </c>
-      <c r="D254" s="12" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E254" s="12" t="inlineStr">
-        <is>
-          <t>75 cl</t>
-        </is>
-      </c>
-      <c r="F254" s="13" t="n"/>
-      <c r="G254" s="13" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="H254" s="13" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="I254" s="13" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="J254" s="13" t="n">
-        <v>4.75</v>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" s="11" t="inlineStr">
-        <is>
-          <t>S25 V03</t>
-        </is>
-      </c>
-      <c r="B255" s="12" t="inlineStr">
-        <is>
-          <t>IGP Val de Loire — Reflet Gamay</t>
-        </is>
-      </c>
-      <c r="C255" s="12" t="inlineStr">
-        <is>
-          <t>Rouge</t>
-        </is>
-      </c>
-      <c r="D255" s="12" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="E255" s="12" t="inlineStr">
-        <is>
-          <t>75 cl</t>
-        </is>
-      </c>
-      <c r="F255" s="13" t="n"/>
-      <c r="G255" s="13" t="n">
-        <v>6.95</v>
-      </c>
-      <c r="H255" s="13" t="n">
-        <v>6.45</v>
-      </c>
-      <c r="I255" s="13" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="J255" s="13" t="n">
-        <v>5.75</v>
-      </c>
+      <c r="G255" s="10" t="n"/>
+      <c r="H255" s="10" t="n"/>
+      <c r="I255" s="10" t="n"/>
+      <c r="J255" s="10" t="n"/>
     </row>
     <row r="256">
       <c r="A256" s="11" t="inlineStr">
         <is>
-          <t>S25 V04</t>
+          <t>S24 V01</t>
         </is>
       </c>
       <c r="B256" s="12" t="inlineStr">
         <is>
-          <t>VDF — L’Eberluant Chardonnay Méthode ancestrale</t>
+          <t>AOC Fronsac — Château Lafargue Rouge</t>
         </is>
       </c>
       <c r="C256" s="12" t="inlineStr">
         <is>
-          <t>Blanc pétillant</t>
+          <t>Rouge</t>
         </is>
       </c>
       <c r="D256" s="12" t="inlineStr">
         <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E256" s="12" t="n"/>
-      <c r="F256" s="13" t="n"/>
-      <c r="G256" s="13" t="n">
-        <v>6.95</v>
-      </c>
-      <c r="H256" s="13" t="n">
-        <v>6.45</v>
-      </c>
-      <c r="I256" s="13" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="J256" s="13" t="n">
-        <v>5.75</v>
-      </c>
-    </row>
-    <row r="258" ht="22" customHeight="1">
-      <c r="A258" s="5" t="inlineStr">
-        <is>
-          <t>S26</t>
-        </is>
-      </c>
-      <c r="B258" s="6" t="inlineStr">
-        <is>
-          <t>Stand 26 — Maison André Goichot (Bourgogne)</t>
-        </is>
-      </c>
-      <c r="C258" s="7" t="n"/>
-      <c r="D258" s="7" t="n"/>
-      <c r="E258" s="7" t="n"/>
-      <c r="F258" s="7" t="n"/>
-      <c r="G258" s="7" t="n"/>
-      <c r="H258" s="7" t="n"/>
-      <c r="I258" s="7" t="n"/>
-      <c r="J258" s="7" t="n"/>
-    </row>
-    <row r="259" ht="26" customHeight="1">
-      <c r="B259" s="8" t="inlineStr">
-        <is>
-          <t>Domaine Les Guignottes — paliers du salon</t>
-        </is>
-      </c>
-      <c r="C259" s="9" t="n"/>
-      <c r="D259" s="9" t="n"/>
-      <c r="E259" s="9" t="n"/>
-      <c r="F259" s="8" t="inlineStr">
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="E256" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
+      <c r="F256" s="13" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="G256" s="14" t="n"/>
+      <c r="H256" s="14" t="n"/>
+      <c r="I256" s="14" t="n"/>
+      <c r="J256" s="14" t="n"/>
+    </row>
+    <row r="257">
+      <c r="A257" s="11" t="inlineStr">
+        <is>
+          <t>S24 V02</t>
+        </is>
+      </c>
+      <c r="B257" s="12" t="inlineStr">
+        <is>
+          <t>AOC Fronsac — Amphora Rouge</t>
+        </is>
+      </c>
+      <c r="C257" s="12" t="inlineStr">
+        <is>
+          <t>Rouge</t>
+        </is>
+      </c>
+      <c r="D257" s="12" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="E257" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
+      <c r="F257" s="13" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="G257" s="14" t="n"/>
+      <c r="H257" s="14" t="n"/>
+      <c r="I257" s="14" t="n"/>
+      <c r="J257" s="14" t="n"/>
+    </row>
+    <row r="258">
+      <c r="A258" s="11" t="inlineStr">
+        <is>
+          <t>S24 V03</t>
+        </is>
+      </c>
+      <c r="B258" s="12" t="inlineStr">
+        <is>
+          <t>VDF — La Confiance Rouge</t>
+        </is>
+      </c>
+      <c r="C258" s="12" t="inlineStr">
+        <is>
+          <t>Rouge</t>
+        </is>
+      </c>
+      <c r="D258" s="12" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E258" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
+      <c r="F258" s="13" t="n">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="G258" s="14" t="n"/>
+      <c r="H258" s="14" t="n"/>
+      <c r="I258" s="14" t="n"/>
+      <c r="J258" s="14" t="n"/>
+    </row>
+    <row r="260" ht="22" customHeight="1">
+      <c r="A260" s="5" t="inlineStr">
+        <is>
+          <t>S25</t>
+        </is>
+      </c>
+      <c r="B260" s="6" t="inlineStr">
+        <is>
+          <t>Stand 25 — Chai Berteaud Manceau (Loire)</t>
+        </is>
+      </c>
+      <c r="C260" s="7" t="n"/>
+      <c r="D260" s="7" t="n"/>
+      <c r="E260" s="7" t="n"/>
+      <c r="F260" s="7" t="n"/>
+      <c r="G260" s="7" t="n"/>
+      <c r="H260" s="7" t="n"/>
+      <c r="I260" s="7" t="n"/>
+      <c r="J260" s="7" t="n"/>
+    </row>
+    <row r="261" ht="26" customHeight="1">
+      <c r="B261" s="8" t="inlineStr">
+        <is>
+          <t>Chai Berteaud Manceau — paliers du salon</t>
+        </is>
+      </c>
+      <c r="C261" s="9" t="n"/>
+      <c r="D261" s="9" t="n"/>
+      <c r="E261" s="9" t="n"/>
+      <c r="F261" s="8" t="inlineStr">
         <is>
           <t>Prix unique</t>
         </is>
       </c>
-      <c r="G259" s="10" t="inlineStr">
-        <is>
-          <t>À partir de 60 bts</t>
-        </is>
-      </c>
-      <c r="H259" s="10" t="inlineStr">
-        <is>
-          <t>À partir de 120 bts</t>
-        </is>
-      </c>
-      <c r="I259" s="10" t="inlineStr">
-        <is>
-          <t>À partir de 300 bts</t>
-        </is>
-      </c>
-      <c r="J259" s="10" t="n"/>
-    </row>
-    <row r="260">
-      <c r="A260" s="11" t="inlineStr">
-        <is>
-          <t>S26 V01</t>
-        </is>
-      </c>
-      <c r="B260" s="12" t="inlineStr">
-        <is>
-          <t>AOP Bourgogne Chardonnay</t>
-        </is>
-      </c>
-      <c r="C260" s="12" t="inlineStr">
-        <is>
-          <t>Blanc</t>
-        </is>
-      </c>
-      <c r="D260" s="12" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E260" s="12" t="inlineStr">
-        <is>
-          <t>75 cl</t>
-        </is>
-      </c>
-      <c r="F260" s="13" t="n"/>
-      <c r="G260" s="13" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="H260" s="13" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="I260" s="13" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="J260" s="14" t="n"/>
-    </row>
-    <row r="261">
-      <c r="A261" s="11" t="inlineStr">
-        <is>
-          <t>S26 V02</t>
-        </is>
-      </c>
-      <c r="B261" s="12" t="inlineStr">
-        <is>
-          <t>AOC Pouilly-Vinzelles Blanc</t>
-        </is>
-      </c>
-      <c r="C261" s="12" t="inlineStr">
-        <is>
-          <t>Blanc</t>
-        </is>
-      </c>
-      <c r="D261" s="12" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E261" s="12" t="n"/>
-      <c r="F261" s="13" t="n"/>
-      <c r="G261" s="13" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="H261" s="13" t="n">
-        <v>15</v>
-      </c>
-      <c r="I261" s="13" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="J261" s="14" t="n"/>
+      <c r="G261" s="10" t="inlineStr">
+        <is>
+          <t>À partir de 36 cols</t>
+        </is>
+      </c>
+      <c r="H261" s="10" t="inlineStr">
+        <is>
+          <t>À partir de 60 cols</t>
+        </is>
+      </c>
+      <c r="I261" s="10" t="inlineStr">
+        <is>
+          <t>À partir de 120 cols</t>
+        </is>
+      </c>
+      <c r="J261" s="10" t="inlineStr">
+        <is>
+          <t>À partir de 240 cols</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="11" t="inlineStr">
         <is>
-          <t>S26 V03</t>
+          <t>S25 V01</t>
         </is>
       </c>
       <c r="B262" s="12" t="inlineStr">
         <is>
-          <t>AOC Auxey-Duresses</t>
+          <t>IGP Val de Loire — Courant Chenin</t>
         </is>
       </c>
       <c r="C262" s="12" t="inlineStr">
         <is>
-          <t>Blanc</t>
+          <t>Blanc sec</t>
         </is>
       </c>
       <c r="D262" s="12" t="inlineStr">
         <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E262" s="12" t="n"/>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E262" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
       <c r="F262" s="13" t="n"/>
       <c r="G262" s="13" t="n">
-        <v>22.5</v>
+        <v>6.95</v>
       </c>
       <c r="H262" s="13" t="n">
-        <v>22.2</v>
+        <v>6.45</v>
       </c>
       <c r="I262" s="13" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="J262" s="14" t="n"/>
+        <v>5.95</v>
+      </c>
+      <c r="J262" s="13" t="n">
+        <v>5.75</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="11" t="inlineStr">
         <is>
-          <t>S26 V04</t>
+          <t>S25 V02</t>
         </is>
       </c>
       <c r="B263" s="12" t="inlineStr">
         <is>
-          <t>AOC Crémant de Bourgogne — Baron Auguste Blanc</t>
+          <t>IGP Val de Loire — Source Melon B.</t>
         </is>
       </c>
       <c r="C263" s="12" t="inlineStr">
         <is>
-          <t>Blanc effervescent</t>
+          <t>Blanc sec</t>
         </is>
       </c>
       <c r="D263" s="12" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E263" s="12" t="n"/>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E263" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
       <c r="F263" s="13" t="n"/>
       <c r="G263" s="13" t="n">
-        <v>9.300000000000001</v>
+        <v>5.95</v>
       </c>
       <c r="H263" s="13" t="n">
-        <v>9</v>
+        <v>5.45</v>
       </c>
       <c r="I263" s="13" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="J263" s="14" t="n"/>
+        <v>4.95</v>
+      </c>
+      <c r="J263" s="13" t="n">
+        <v>4.75</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" s="11" t="inlineStr">
         <is>
-          <t>S26 V05</t>
+          <t>S25 V03</t>
         </is>
       </c>
       <c r="B264" s="12" t="inlineStr">
         <is>
-          <t>AOC Crémant de Bourgogne — Baron Auguste Rosé</t>
+          <t>IGP Val de Loire — Reflet Gamay</t>
         </is>
       </c>
       <c r="C264" s="12" t="inlineStr">
         <is>
-          <t>Rosé effervescent</t>
+          <t>Rouge</t>
         </is>
       </c>
       <c r="D264" s="12" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E264" s="12" t="n"/>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="E264" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
       <c r="F264" s="13" t="n"/>
       <c r="G264" s="13" t="n">
-        <v>9.300000000000001</v>
+        <v>6.95</v>
       </c>
       <c r="H264" s="13" t="n">
-        <v>9</v>
+        <v>6.45</v>
       </c>
       <c r="I264" s="13" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="J264" s="14" t="n"/>
+        <v>5.95</v>
+      </c>
+      <c r="J264" s="13" t="n">
+        <v>5.75</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" s="11" t="inlineStr">
         <is>
-          <t>S26 V06</t>
+          <t>S25 V04</t>
         </is>
       </c>
       <c r="B265" s="12" t="inlineStr">
         <is>
-          <t>AOC Bourgogne Pinot Noir — Domaine les Guignottes Rouge</t>
+          <t>VDF — L’Eberluant Chardonnay Méthode ancestrale</t>
         </is>
       </c>
       <c r="C265" s="12" t="inlineStr">
         <is>
-          <t>Rouge</t>
+          <t>Blanc pétillant</t>
         </is>
       </c>
       <c r="D265" s="12" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E265" s="12" t="inlineStr">
@@ -8332,141 +8452,88 @@
       </c>
       <c r="F265" s="13" t="n"/>
       <c r="G265" s="13" t="n">
-        <v>8.9</v>
+        <v>6.95</v>
       </c>
       <c r="H265" s="13" t="n">
-        <v>8.6</v>
+        <v>6.45</v>
       </c>
       <c r="I265" s="13" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="J265" s="14" t="n"/>
-    </row>
-    <row r="266">
-      <c r="A266" s="11" t="inlineStr">
-        <is>
-          <t>S26 V07</t>
-        </is>
-      </c>
-      <c r="B266" s="12" t="inlineStr">
-        <is>
-          <t>AOC Chassagne-Montrachet Rouge</t>
-        </is>
-      </c>
-      <c r="C266" s="12" t="inlineStr">
-        <is>
-          <t>Rouge</t>
-        </is>
-      </c>
-      <c r="D266" s="12" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E266" s="12" t="inlineStr">
-        <is>
-          <t>75 cl</t>
-        </is>
-      </c>
-      <c r="F266" s="13" t="n"/>
-      <c r="G266" s="13" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="H266" s="13" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="I266" s="13" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="J266" s="14" t="n"/>
-    </row>
-    <row r="267">
-      <c r="A267" s="11" t="inlineStr">
-        <is>
-          <t>S26 V08</t>
-        </is>
-      </c>
-      <c r="B267" s="12" t="inlineStr">
-        <is>
-          <t>AOC Nuits-Saint-Georges — Aux Allots Rouge</t>
-        </is>
-      </c>
-      <c r="C267" s="12" t="inlineStr">
-        <is>
-          <t>Rouge</t>
-        </is>
-      </c>
-      <c r="D267" s="12" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E267" s="12" t="n"/>
-      <c r="F267" s="13" t="n"/>
-      <c r="G267" s="13" t="n">
-        <v>33.9</v>
-      </c>
-      <c r="H267" s="13" t="n">
-        <v>33.6</v>
-      </c>
-      <c r="I267" s="13" t="n">
-        <v>32.3</v>
-      </c>
-      <c r="J267" s="14" t="n"/>
-    </row>
-    <row r="268">
-      <c r="A268" s="11" t="inlineStr">
-        <is>
-          <t>S26 V09</t>
-        </is>
-      </c>
-      <c r="B268" s="12" t="inlineStr">
-        <is>
-          <t>AOC Mercurey Blanc</t>
-        </is>
-      </c>
-      <c r="C268" s="12" t="inlineStr">
-        <is>
-          <t>Blanc</t>
-        </is>
-      </c>
-      <c r="D268" s="12" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E268" s="12" t="n"/>
-      <c r="F268" s="13" t="n"/>
-      <c r="G268" s="13" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="H268" s="13" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="I268" s="13" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="J268" s="14" t="n"/>
+        <v>5.95</v>
+      </c>
+      <c r="J265" s="13" t="n">
+        <v>5.75</v>
+      </c>
+    </row>
+    <row r="267" ht="22" customHeight="1">
+      <c r="A267" s="5" t="inlineStr">
+        <is>
+          <t>S26</t>
+        </is>
+      </c>
+      <c r="B267" s="6" t="inlineStr">
+        <is>
+          <t>Stand 26 — Maison André Goichot (Bourgogne)</t>
+        </is>
+      </c>
+      <c r="C267" s="7" t="n"/>
+      <c r="D267" s="7" t="n"/>
+      <c r="E267" s="7" t="n"/>
+      <c r="F267" s="7" t="n"/>
+      <c r="G267" s="7" t="n"/>
+      <c r="H267" s="7" t="n"/>
+      <c r="I267" s="7" t="n"/>
+      <c r="J267" s="7" t="n"/>
+    </row>
+    <row r="268" ht="26" customHeight="1">
+      <c r="B268" s="8" t="inlineStr">
+        <is>
+          <t>Domaine Les Guignottes — paliers du salon</t>
+        </is>
+      </c>
+      <c r="C268" s="9" t="n"/>
+      <c r="D268" s="9" t="n"/>
+      <c r="E268" s="9" t="n"/>
+      <c r="F268" s="8" t="inlineStr">
+        <is>
+          <t>Prix unique</t>
+        </is>
+      </c>
+      <c r="G268" s="10" t="inlineStr">
+        <is>
+          <t>À partir de 60 bts</t>
+        </is>
+      </c>
+      <c r="H268" s="10" t="inlineStr">
+        <is>
+          <t>À partir de 120 bts</t>
+        </is>
+      </c>
+      <c r="I268" s="10" t="inlineStr">
+        <is>
+          <t>À partir de 300 bts</t>
+        </is>
+      </c>
+      <c r="J268" s="10" t="n"/>
     </row>
     <row r="269">
       <c r="A269" s="11" t="inlineStr">
         <is>
-          <t>S26 V10</t>
+          <t>S26 V01</t>
         </is>
       </c>
       <c r="B269" s="12" t="inlineStr">
         <is>
-          <t>AOC Mercurey Rouge</t>
+          <t>AOP Bourgogne Chardonnay</t>
         </is>
       </c>
       <c r="C269" s="12" t="inlineStr">
         <is>
-          <t>Rouge</t>
+          <t>Blanc</t>
         </is>
       </c>
       <c r="D269" s="12" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="E269" s="12" t="inlineStr">
@@ -8476,30 +8543,30 @@
       </c>
       <c r="F269" s="13" t="n"/>
       <c r="G269" s="13" t="n">
-        <v>16.5</v>
+        <v>8.9</v>
       </c>
       <c r="H269" s="13" t="n">
-        <v>16.2</v>
+        <v>8.6</v>
       </c>
       <c r="I269" s="13" t="n">
-        <v>15.4</v>
+        <v>8.1</v>
       </c>
       <c r="J269" s="14" t="n"/>
     </row>
     <row r="270">
       <c r="A270" s="11" t="inlineStr">
         <is>
-          <t>S26 V11</t>
+          <t>S26 V02</t>
         </is>
       </c>
       <c r="B270" s="12" t="inlineStr">
         <is>
-          <t>AOC Givry Rouge</t>
+          <t>AOC Pouilly-Vinzelles Blanc</t>
         </is>
       </c>
       <c r="C270" s="12" t="inlineStr">
         <is>
-          <t>Rouge</t>
+          <t>Blanc</t>
         </is>
       </c>
       <c r="D270" s="12" t="inlineStr">
@@ -8507,38 +8574,42 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="E270" s="12" t="n"/>
+      <c r="E270" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
       <c r="F270" s="13" t="n"/>
       <c r="G270" s="13" t="n">
-        <v>16.5</v>
+        <v>15.3</v>
       </c>
       <c r="H270" s="13" t="n">
-        <v>16.2</v>
+        <v>15</v>
       </c>
       <c r="I270" s="13" t="n">
-        <v>15.4</v>
+        <v>14.3</v>
       </c>
       <c r="J270" s="14" t="n"/>
     </row>
     <row r="271">
       <c r="A271" s="11" t="inlineStr">
         <is>
-          <t>S26 V12</t>
+          <t>S26 V03</t>
         </is>
       </c>
       <c r="B271" s="12" t="inlineStr">
         <is>
-          <t>AOC Gevrey-Chambertin</t>
+          <t>AOC Auxey-Duresses</t>
         </is>
       </c>
       <c r="C271" s="12" t="inlineStr">
         <is>
-          <t>Rouge</t>
+          <t>Blanc</t>
         </is>
       </c>
       <c r="D271" s="12" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="E271" s="12" t="inlineStr">
@@ -8548,15 +8619,357 @@
       </c>
       <c r="F271" s="13" t="n"/>
       <c r="G271" s="13" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="H271" s="13" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="I271" s="13" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="J271" s="14" t="n"/>
+    </row>
+    <row r="272">
+      <c r="A272" s="11" t="inlineStr">
+        <is>
+          <t>S26 V04</t>
+        </is>
+      </c>
+      <c r="B272" s="12" t="inlineStr">
+        <is>
+          <t>AOC Crémant de Bourgogne — Baron Auguste Blanc</t>
+        </is>
+      </c>
+      <c r="C272" s="12" t="inlineStr">
+        <is>
+          <t>Blanc effervescent</t>
+        </is>
+      </c>
+      <c r="D272" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E272" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
+      <c r="F272" s="13" t="n"/>
+      <c r="G272" s="13" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="H272" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="I272" s="13" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="J272" s="14" t="n"/>
+    </row>
+    <row r="273">
+      <c r="A273" s="11" t="inlineStr">
+        <is>
+          <t>S26 V05</t>
+        </is>
+      </c>
+      <c r="B273" s="12" t="inlineStr">
+        <is>
+          <t>AOC Crémant de Bourgogne — Baron Auguste Rosé</t>
+        </is>
+      </c>
+      <c r="C273" s="12" t="inlineStr">
+        <is>
+          <t>Rosé effervescent</t>
+        </is>
+      </c>
+      <c r="D273" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E273" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
+      <c r="F273" s="13" t="n"/>
+      <c r="G273" s="13" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="H273" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="I273" s="13" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="J273" s="14" t="n"/>
+    </row>
+    <row r="274">
+      <c r="A274" s="11" t="inlineStr">
+        <is>
+          <t>S26 V06</t>
+        </is>
+      </c>
+      <c r="B274" s="12" t="inlineStr">
+        <is>
+          <t>AOC Bourgogne Pinot Noir — Domaine les Guignottes Rouge</t>
+        </is>
+      </c>
+      <c r="C274" s="12" t="inlineStr">
+        <is>
+          <t>Rouge</t>
+        </is>
+      </c>
+      <c r="D274" s="12" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E274" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
+      <c r="F274" s="13" t="n"/>
+      <c r="G274" s="13" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="H274" s="13" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="I274" s="13" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="J274" s="14" t="n"/>
+    </row>
+    <row r="275">
+      <c r="A275" s="11" t="inlineStr">
+        <is>
+          <t>S26 V07</t>
+        </is>
+      </c>
+      <c r="B275" s="12" t="inlineStr">
+        <is>
+          <t>AOC Chassagne-Montrachet Rouge</t>
+        </is>
+      </c>
+      <c r="C275" s="12" t="inlineStr">
+        <is>
+          <t>Rouge</t>
+        </is>
+      </c>
+      <c r="D275" s="12" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E275" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
+      <c r="F275" s="13" t="n"/>
+      <c r="G275" s="13" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="H275" s="13" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="I275" s="13" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="J275" s="14" t="n"/>
+    </row>
+    <row r="276">
+      <c r="A276" s="11" t="inlineStr">
+        <is>
+          <t>S26 V08</t>
+        </is>
+      </c>
+      <c r="B276" s="12" t="inlineStr">
+        <is>
+          <t>AOC Nuits-Saint-Georges — Aux Allots Rouge</t>
+        </is>
+      </c>
+      <c r="C276" s="12" t="inlineStr">
+        <is>
+          <t>Rouge</t>
+        </is>
+      </c>
+      <c r="D276" s="12" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E276" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
+      <c r="F276" s="13" t="n"/>
+      <c r="G276" s="13" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="H276" s="13" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="I276" s="13" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="J276" s="14" t="n"/>
+    </row>
+    <row r="277">
+      <c r="A277" s="11" t="inlineStr">
+        <is>
+          <t>S26 V09</t>
+        </is>
+      </c>
+      <c r="B277" s="12" t="inlineStr">
+        <is>
+          <t>AOC Mercurey Blanc</t>
+        </is>
+      </c>
+      <c r="C277" s="12" t="inlineStr">
+        <is>
+          <t>Blanc</t>
+        </is>
+      </c>
+      <c r="D277" s="12" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E277" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
+      <c r="F277" s="13" t="n"/>
+      <c r="G277" s="13" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="H277" s="13" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="I277" s="13" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="J277" s="14" t="n"/>
+    </row>
+    <row r="278">
+      <c r="A278" s="11" t="inlineStr">
+        <is>
+          <t>S26 V10</t>
+        </is>
+      </c>
+      <c r="B278" s="12" t="inlineStr">
+        <is>
+          <t>AOC Mercurey Rouge</t>
+        </is>
+      </c>
+      <c r="C278" s="12" t="inlineStr">
+        <is>
+          <t>Rouge</t>
+        </is>
+      </c>
+      <c r="D278" s="12" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="E278" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
+      <c r="F278" s="13" t="n"/>
+      <c r="G278" s="13" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="H278" s="13" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="I278" s="13" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="J278" s="14" t="n"/>
+    </row>
+    <row r="279">
+      <c r="A279" s="11" t="inlineStr">
+        <is>
+          <t>S26 V11</t>
+        </is>
+      </c>
+      <c r="B279" s="12" t="inlineStr">
+        <is>
+          <t>AOC Givry Rouge</t>
+        </is>
+      </c>
+      <c r="C279" s="12" t="inlineStr">
+        <is>
+          <t>Rouge</t>
+        </is>
+      </c>
+      <c r="D279" s="12" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E279" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
+      <c r="F279" s="13" t="n"/>
+      <c r="G279" s="13" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="H279" s="13" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="I279" s="13" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="J279" s="14" t="n"/>
+    </row>
+    <row r="280">
+      <c r="A280" s="11" t="inlineStr">
+        <is>
+          <t>S26 V12</t>
+        </is>
+      </c>
+      <c r="B280" s="12" t="inlineStr">
+        <is>
+          <t>AOC Gevrey-Chambertin</t>
+        </is>
+      </c>
+      <c r="C280" s="12" t="inlineStr">
+        <is>
+          <t>Rouge</t>
+        </is>
+      </c>
+      <c r="D280" s="12" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="E280" s="12" t="inlineStr">
+        <is>
+          <t>75 cl</t>
+        </is>
+      </c>
+      <c r="F280" s="13" t="n"/>
+      <c r="G280" s="13" t="n">
         <v>43.5</v>
       </c>
-      <c r="H271" s="13" t="n">
+      <c r="H280" s="13" t="n">
         <v>43.2</v>
       </c>
-      <c r="I271" s="13" t="n">
+      <c r="I280" s="13" t="n">
         <v>41.6</v>
       </c>
-      <c r="J271" s="14" t="n"/>
+      <c r="J280" s="14" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
